--- a/作業/面接練習/G3面接準備中岫.xlsx
+++ b/作業/面接練習/G3面接準備中岫.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aaa115298\Desktop\G3\G3\G3試験中岫作業\G3\作業\面接練習\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60B97E2E-4C74-47F3-B2F8-3A0EE81907BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5070B29-F0F8-459C-85AF-01876E15E38A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="1013" sheetId="2" r:id="rId2"/>
-    <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
+    <sheet name="1014" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="237" uniqueCount="234">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="259" uniqueCount="256">
   <si>
     <t>No</t>
   </si>
@@ -1935,16 +1935,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t xml:space="preserve">私は、デジタルビジネスプラットフォーム開発本部、ソフトウェア33開発室の中岫茉希と申します。
-デジタルプリンティング事業本部と連携し、商業印刷機Mogamiの高画質化に向けた技術開発を担当しています。
-商業印刷機では、インクの定着性を高めるため、印刷前にプライマと呼ばれる液体を付与しています。このプライマの量によって画質が変化するため、適切な量を設定することが重要です。
-そこで私は、プライマの量が画質に与える影響を分析し、その関係を明らかにしました。また、その結果を踏まえ、適切なプライマ量を効率的に決定できるよう、評価方法や判断手順を整理し、評価フローを再構築しました。
-これらの取り組みを通じて、商業印刷機の安定した高画質化と、開発の効率化に貢献しています。
-本日はよろしくお願いいたします。
-</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>私は、デジタルビジネスプラットフォーム開発本部、ソフトウェア33開発室の中岫茉希と申します。
 私は、デジタルプリンティング事業本部と連携し、商業印刷向けインクジェットプリンターMogamiの高画質化に向けた技術開発を担当しています。
 商業印刷の分野では、従来のオフセット印刷で使用されてきたさまざまな用紙を、デジタル印刷でも使用したいというニーズがあります。そのため、商業印刷機には、多様な用紙に対応しながら、安定した高画質を実現することが求められています。Mogamiにおいても、高画質化と用紙対応力の向上が重要な開発課題の一つとなっています。社内資料では、Mogamiの顧客価値として、高画質・高品位に加え、幅広い用紙への対応が挙げられています。
@@ -2110,6 +2100,8 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
       </rPr>
       <t xml:space="preserve">
 課は15名程度で、3つのチームに分かれています。イメソル向けセンサ技術、イメソル向け3次元技術、イメコミ向け現像技術の3つです。現像技術チームは、4人でAI現像を開発しています。
@@ -2257,6 +2249,8 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
       </rPr>
       <t xml:space="preserve">
 ・イメージング製品の付加価値を高める画像処理技術の開発です。課には３つのチームがあり、イメコミ、イメソルなど事業部と協業し、製品に搭載する画像処理技術の開発に従事しております。</t>
@@ -4173,12 +4167,209 @@
 Mogamiのメディア対応では複数領域の知見が必要となるため、専門の異なる関係者が集まると、同じ用語でも定義が異なったり、現象の捉え方がずれたりすることがあります。そのような場面で、議論の前提や用語の定義をそろえ、各担当者の知見をつなぎながら、判断すべき論点を明確にする姿勢を見習いたいと考えています。</t>
     <phoneticPr fontId="1"/>
   </si>
+  <si>
+    <t>Q1. あなたの検討しているチームの編成と状況を教えてください</t>
+  </si>
+  <si>
+    <t>Q2. そのチームでどういう役割を担っていますか</t>
+  </si>
+  <si>
+    <t>Q3. もう一方のチームと競合やトラブルはありますか</t>
+  </si>
+  <si>
+    <t>Q4. 事業部との間で意見の違いはありましたか</t>
+  </si>
+  <si>
+    <t>Q5. その問題はどう落ち着きましたか</t>
+  </si>
+  <si>
+    <t>Q6. 用紙対応力向上チームは何名ですか</t>
+  </si>
+  <si>
+    <t>Q7. G3になったらどんなことをしたいですか</t>
+  </si>
+  <si>
+    <t>Q8. それはG3になってからでないと難しいのですか</t>
+  </si>
+  <si>
+    <t>Q9. 巻き込むとは誰を巻き込むのですか</t>
+  </si>
+  <si>
+    <t>Q10. 入社後一番苦労したことは</t>
+  </si>
+  <si>
+    <t>Q11. それはうまくできたと思いますか</t>
+  </si>
+  <si>
+    <t>プライマー量評価用チャートを解析し、データから課題を抽出しています。そのうえで、どのような対策を打つべきか、たたき台を作る役割を担っています。</t>
+  </si>
+  <si>
+    <t>チーム間での競合やトラブルは特にありません。</t>
+  </si>
+  <si>
+    <t>将来、紙種が増えた場合に、新しい評価フローの導入によって評価時間をどれだけ短縮できるかを定量的に示しました。その結果、新手法の導入について合意を得ることができました。</t>
+  </si>
+  <si>
+    <t>所属している用紙対応力向上チームは2名です。筋ムラのメカニズム解析チームも2名で、全体では4名体制です。</t>
+  </si>
+  <si>
+    <t>現状は画像処理の観点を中心に検討していますが、画質改善にはメカやインクなど、ほかの技術領域も関係します。G3になったら、自分の専門以外の観点も考慮し、より効率的な改善方法を考えられる人材になりたいです。</t>
+  </si>
+  <si>
+    <t>技術的に、今の立場では不可能というわけではありません。ただし、課題に応じて誰を巻き込めばよいかを見極めることは、まだ難しいと感じています。今後の業務経験を通じて各分野の専門家とその強みを理解し、適切に巻き込めるようになりたいです。</t>
+  </si>
+  <si>
+    <t>画像処理以外の分野の専門家です。今回の検討でも、インク分野は自分たちだけでは知識が不足していたため、インクの専門家に相談し、助言を受けながら進めました。</t>
+  </si>
+  <si>
+    <t>プライマーと画質の関係を明らかにすることです。化学の知識が必要な領域でしたが、部内に詳しい人がいなかったため、論文や特許を読みながら知識を習得し、メカニズムを整理しました。</t>
+  </si>
+  <si>
+    <t>できたと考えています。特に、自分が何を理解できていないのかを明確にしたうえで、事業部と議論できたことが良かった点です。</t>
+  </si>
+  <si>
+    <t>チームは次の2つに分かれています。
+・筋ムラのメカニズム解析チーム
+・用紙対応力向上とプライマー量設計効率化チーム
+私は後者に所属しています。</t>
+  </si>
+  <si>
+    <t>評価フローの再構築で新手法を提案した際、受け入れに対する抵抗がありました。
+事業部は「現行フローで評価できており、慣れているため現行手法を使いたい」という考えでした。一方、私たちは「将来的に紙種が増えることを考えると、新手法の方が効率的」と考えており、その点で意見の違いがありました。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">私は、デジタルビジネスプラットフォーム開発本部、ソフトウェア33開発室の中岫茉希と申します。
+デジタルプリンティング事業本部と連携し、商業印刷機Mogamiの画質を向上させるための技術開発を担当しています。
+私たちのチームでは、大きく２つのテーマについて取り組んでいます。１つは印刷時に発生する筋状の色むらの原因解明、もう一つは印刷できる用紙の種類を増やすことです。私は後者の用紙対応力の向上を担当しています。
+具体的には、印刷前に塗る液体の量が画質に与える影響を分析し、明らかにしました。また適切な量を効率よく決められるよう、評価方法を見直した。
+これらの取り組みを通じて、商業印刷機の安定した高画質化と、開発の効率化に貢献しています。
+本日はよろしくお願いいたします。
+</t>
+    <rPh sb="80" eb="82">
+      <t>ガシツ</t>
+    </rPh>
+    <rPh sb="83" eb="85">
+      <t>コウジョウ</t>
+    </rPh>
+    <rPh sb="106" eb="107">
+      <t>ワタシ</t>
+    </rPh>
+    <rPh sb="116" eb="117">
+      <t>オオ</t>
+    </rPh>
+    <rPh sb="129" eb="130">
+      <t>ト</t>
+    </rPh>
+    <rPh sb="131" eb="132">
+      <t>ク</t>
+    </rPh>
+    <rPh sb="141" eb="144">
+      <t>インサツジ</t>
+    </rPh>
+    <rPh sb="145" eb="147">
+      <t>ハッセイ</t>
+    </rPh>
+    <rPh sb="149" eb="151">
+      <t>スジジョウ</t>
+    </rPh>
+    <rPh sb="152" eb="153">
+      <t>イロ</t>
+    </rPh>
+    <rPh sb="156" eb="158">
+      <t>ゲンイン</t>
+    </rPh>
+    <rPh sb="158" eb="160">
+      <t>カイメイ</t>
+    </rPh>
+    <rPh sb="163" eb="164">
+      <t>ヒト</t>
+    </rPh>
+    <rPh sb="166" eb="168">
+      <t>インサツ</t>
+    </rPh>
+    <rPh sb="171" eb="173">
+      <t>ヨウシ</t>
+    </rPh>
+    <rPh sb="174" eb="176">
+      <t>シュルイ</t>
+    </rPh>
+    <rPh sb="177" eb="178">
+      <t>フ</t>
+    </rPh>
+    <rPh sb="185" eb="186">
+      <t>ワタシ</t>
+    </rPh>
+    <rPh sb="187" eb="189">
+      <t>コウシャ</t>
+    </rPh>
+    <rPh sb="190" eb="195">
+      <t>ヨウシタイオウリョク</t>
+    </rPh>
+    <rPh sb="196" eb="198">
+      <t>コウジョウ</t>
+    </rPh>
+    <rPh sb="199" eb="201">
+      <t>タントウ</t>
+    </rPh>
+    <rPh sb="209" eb="212">
+      <t>グタイテキ</t>
+    </rPh>
+    <rPh sb="215" eb="218">
+      <t>インサツマエ</t>
+    </rPh>
+    <rPh sb="219" eb="220">
+      <t>ヌ</t>
+    </rPh>
+    <rPh sb="221" eb="223">
+      <t>エキタイ</t>
+    </rPh>
+    <rPh sb="224" eb="225">
+      <t>リョウ</t>
+    </rPh>
+    <rPh sb="226" eb="228">
+      <t>ガシツ</t>
+    </rPh>
+    <rPh sb="229" eb="230">
+      <t>アタ</t>
+    </rPh>
+    <rPh sb="232" eb="234">
+      <t>エイキョウ</t>
+    </rPh>
+    <rPh sb="235" eb="237">
+      <t>ブンセキ</t>
+    </rPh>
+    <rPh sb="239" eb="240">
+      <t>アキ</t>
+    </rPh>
+    <rPh sb="250" eb="252">
+      <t>テキセツ</t>
+    </rPh>
+    <rPh sb="253" eb="254">
+      <t>リョウ</t>
+    </rPh>
+    <rPh sb="255" eb="257">
+      <t>コウリツ</t>
+    </rPh>
+    <rPh sb="259" eb="260">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="267" eb="269">
+      <t>ヒョウカ</t>
+    </rPh>
+    <rPh sb="269" eb="271">
+      <t>ホウホウ</t>
+    </rPh>
+    <rPh sb="272" eb="274">
+      <t>ミナオ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="17">
+  <fonts count="19">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -4298,8 +4489,21 @@
       <family val="3"/>
       <charset val="128"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF404040"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF404040"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -4330,8 +4534,18 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD9EAF7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="4">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -4384,13 +4598,22 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFD9E1F2"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -4482,6 +4705,12 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -4724,16 +4953,16 @@
         <v>0</v>
       </c>
       <c r="B2" s="23" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C2" s="18" t="s">
-        <v>183</v>
+        <v>255</v>
       </c>
       <c r="D2" s="25" t="s">
         <v>175</v>
       </c>
       <c r="E2" s="13" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="F2" s="20" t="s">
         <v>152</v>
@@ -4748,10 +4977,10 @@
     <row r="3" spans="1:9" ht="409.5">
       <c r="A3" s="28"/>
       <c r="B3" s="23" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C3" s="29" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="E3" s="26"/>
       <c r="F3" s="20"/>
@@ -4764,13 +4993,13 @@
         <v>95</v>
       </c>
       <c r="C4" s="18" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="D4" s="25" t="s">
         <v>176</v>
       </c>
       <c r="E4" s="21" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F4" s="20" t="s">
         <v>153</v>
@@ -4788,7 +5017,7 @@
         <v>55</v>
       </c>
       <c r="E5" s="13" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F5" s="20"/>
     </row>
@@ -4803,7 +5032,7 @@
         <v>56</v>
       </c>
       <c r="E6" s="13" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F6" s="13"/>
     </row>
@@ -4818,7 +5047,7 @@
         <v>94</v>
       </c>
       <c r="E7" s="21" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F7" s="14"/>
       <c r="I7" s="6"/>
@@ -4831,10 +5060,10 @@
         <v>98</v>
       </c>
       <c r="C8" s="18" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="E8" s="13" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="F8" s="14"/>
     </row>
@@ -4849,7 +5078,7 @@
         <v>57</v>
       </c>
       <c r="E9" s="13" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="F9" s="20"/>
     </row>
@@ -4861,10 +5090,10 @@
         <v>100</v>
       </c>
       <c r="C10" s="18" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="E10" s="12" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F10" s="20"/>
     </row>
@@ -4879,7 +5108,7 @@
         <v>58</v>
       </c>
       <c r="E11" s="12" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="F11" s="14"/>
     </row>
@@ -4894,7 +5123,7 @@
         <v>178</v>
       </c>
       <c r="E12" s="13" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F12" s="14"/>
     </row>
@@ -4922,7 +5151,7 @@
         <v>179</v>
       </c>
       <c r="E14" s="13" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="F14" s="20"/>
       <c r="G14" s="10"/>
@@ -4938,7 +5167,7 @@
         <v>60</v>
       </c>
       <c r="E15" s="13" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="F15" s="20"/>
     </row>
@@ -4953,7 +5182,7 @@
         <v>61</v>
       </c>
       <c r="E16" s="13" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="F16" s="20"/>
     </row>
@@ -4968,7 +5197,7 @@
         <v>180</v>
       </c>
       <c r="E17" s="13" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="F17" s="20"/>
     </row>
@@ -4983,7 +5212,7 @@
         <v>62</v>
       </c>
       <c r="E18" s="12" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="F18" s="20"/>
     </row>
@@ -5011,7 +5240,7 @@
         <v>64</v>
       </c>
       <c r="E20" s="13" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="F20" s="20"/>
     </row>
@@ -5026,7 +5255,7 @@
         <v>65</v>
       </c>
       <c r="E21" s="13" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="22" spans="1:6" ht="27">
@@ -5040,7 +5269,7 @@
         <v>66</v>
       </c>
       <c r="E22" s="12" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="F22" s="20"/>
     </row>
@@ -5055,7 +5284,7 @@
         <v>67</v>
       </c>
       <c r="E23" s="13" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F23" s="20"/>
     </row>
@@ -5070,7 +5299,7 @@
         <v>68</v>
       </c>
       <c r="E24" s="12" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F24" s="20"/>
     </row>
@@ -5106,7 +5335,7 @@
         <v>116</v>
       </c>
       <c r="C27" s="30" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="E27" s="13"/>
       <c r="F27" s="14"/>
@@ -5122,7 +5351,7 @@
         <v>70</v>
       </c>
       <c r="E28" s="13" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="F28" s="20"/>
     </row>
@@ -5137,7 +5366,7 @@
         <v>71</v>
       </c>
       <c r="E29" s="13" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="F29" s="20"/>
     </row>
@@ -5152,7 +5381,7 @@
         <v>72</v>
       </c>
       <c r="E30" s="12" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="F30" s="20"/>
     </row>
@@ -5178,7 +5407,7 @@
         <v>73</v>
       </c>
       <c r="E32" s="13" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="F32" s="20"/>
     </row>
@@ -5193,7 +5422,7 @@
         <v>74</v>
       </c>
       <c r="E33" s="12" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F33" s="13"/>
       <c r="I33" s="6"/>
@@ -5209,7 +5438,7 @@
         <v>75</v>
       </c>
       <c r="E34" s="12" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="F34" s="20"/>
     </row>
@@ -5237,7 +5466,7 @@
         <v>77</v>
       </c>
       <c r="E36" s="13" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F36" s="20"/>
     </row>
@@ -5252,7 +5481,7 @@
         <v>78</v>
       </c>
       <c r="E37" s="13" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="F37" s="20"/>
     </row>
@@ -5267,7 +5496,7 @@
         <v>79</v>
       </c>
       <c r="E38" s="13" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="F38" s="20"/>
     </row>
@@ -5282,7 +5511,7 @@
         <v>80</v>
       </c>
       <c r="E39" s="13" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="F39" s="14"/>
     </row>
@@ -5347,7 +5576,7 @@
         <v>84</v>
       </c>
       <c r="E44" s="13" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F44" s="13"/>
     </row>
@@ -5362,7 +5591,7 @@
         <v>85</v>
       </c>
       <c r="E45" s="13" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="F45" s="13"/>
     </row>
@@ -5377,7 +5606,7 @@
         <v>86</v>
       </c>
       <c r="E46" s="13" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="F46" s="13"/>
     </row>
@@ -5427,7 +5656,7 @@
         <v>88</v>
       </c>
       <c r="E50" s="13" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="F50" s="13"/>
     </row>
@@ -5442,7 +5671,7 @@
         <v>89</v>
       </c>
       <c r="E51" s="13" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="F51" s="13"/>
     </row>
@@ -5457,7 +5686,7 @@
         <v>90</v>
       </c>
       <c r="E52" s="13" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="F52" s="13"/>
     </row>
@@ -5470,7 +5699,7 @@
         <v>91</v>
       </c>
       <c r="E53" s="12" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="F53" s="13"/>
     </row>
@@ -5490,7 +5719,7 @@
       </c>
       <c r="C55" s="5"/>
       <c r="E55" s="13" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="F55" s="13"/>
     </row>
@@ -5501,7 +5730,7 @@
       </c>
       <c r="C56" s="5"/>
       <c r="E56" s="13" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="F56" s="13"/>
     </row>
@@ -5512,7 +5741,7 @@
       </c>
       <c r="C57" s="5"/>
       <c r="E57" s="13" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F57" s="13"/>
     </row>
@@ -5523,7 +5752,7 @@
       </c>
       <c r="C58" s="5"/>
       <c r="E58" s="12" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="F58" s="13"/>
     </row>
@@ -5547,7 +5776,7 @@
         <v>93</v>
       </c>
       <c r="E60" s="12" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F60" s="13"/>
     </row>
@@ -5560,7 +5789,7 @@
       </c>
       <c r="C61" s="5"/>
       <c r="E61" s="13" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
     </row>
     <row r="62" spans="1:6" ht="40.5">
@@ -5572,7 +5801,7 @@
       </c>
       <c r="C62" s="5"/>
       <c r="E62" s="13" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
   </sheetData>
@@ -5727,9 +5956,102 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:B11"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="69.625" customWidth="1"/>
+    <col min="2" max="2" width="66.375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" ht="60">
+      <c r="A1" s="31" t="s">
+        <v>233</v>
+      </c>
+      <c r="B1" s="32" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" ht="54.95" customHeight="1">
+      <c r="A2" s="31" t="s">
+        <v>234</v>
+      </c>
+      <c r="B2" s="32" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="54.95" customHeight="1">
+      <c r="A3" s="31" t="s">
+        <v>235</v>
+      </c>
+      <c r="B3" s="32" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="90">
+      <c r="A4" s="31" t="s">
+        <v>236</v>
+      </c>
+      <c r="B4" s="32" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" ht="54.95" customHeight="1">
+      <c r="A5" s="31" t="s">
+        <v>237</v>
+      </c>
+      <c r="B5" s="32" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" ht="54.95" customHeight="1">
+      <c r="A6" s="31" t="s">
+        <v>238</v>
+      </c>
+      <c r="B6" s="32" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" ht="60">
+      <c r="A7" s="31" t="s">
+        <v>239</v>
+      </c>
+      <c r="B7" s="32" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" ht="60">
+      <c r="A8" s="31" t="s">
+        <v>240</v>
+      </c>
+      <c r="B8" s="32" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" ht="54.95" customHeight="1">
+      <c r="A9" s="31" t="s">
+        <v>241</v>
+      </c>
+      <c r="B9" s="32" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" ht="54.95" customHeight="1">
+      <c r="A10" s="31" t="s">
+        <v>242</v>
+      </c>
+      <c r="B10" s="32" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" ht="54.95" customHeight="1">
+      <c r="A11" s="31" t="s">
+        <v>243</v>
+      </c>
+      <c r="B11" s="32" t="s">
+        <v>252</v>
+      </c>
+    </row>
+  </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/作業/面接練習/G3面接準備中岫.xlsx
+++ b/作業/面接練習/G3面接準備中岫.xlsx
@@ -8,14 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aaa115298\Desktop\G3\G3\G3試験中岫作業\G3\作業\面接練習\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5070B29-F0F8-459C-85AF-01876E15E38A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{333FA04E-09A4-4151-BA94-35BCDFE120B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="1013" sheetId="2" r:id="rId2"/>
-    <sheet name="1014" sheetId="3" r:id="rId3"/>
+    <sheet name="Sheet3" sheetId="5" r:id="rId2"/>
+    <sheet name="1013" sheetId="2" r:id="rId3"/>
+    <sheet name="1014" sheetId="3" r:id="rId4"/>
+    <sheet name="1015" sheetId="4" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -33,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="259" uniqueCount="256">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="272" uniqueCount="266">
   <si>
     <t>No</t>
   </si>
@@ -228,9 +230,6 @@
   </si>
   <si>
     <t>私の仕事は、Mogamiで使用するメディアの特性を把握し、狙った画質と性能を安定して実現できるかを評価することです。まず対象メディアと使用条件を整理し、必要な評価項目と判定基準を決めます。次に評価結果から課題の発生条件を特定し、関係者と原因仮説を立てます。最後に設定や制御条件の見直し効果を確認し、使用可能な範囲と注意点を明確にします。</t>
-  </si>
-  <si>
-    <t>勝ち目は、幅広いメディアを安定して扱えることと、その対応を迅速に実現できることにあると考えています。単に対応メディア数を増やすだけでなく、顧客用途で求められる画質と生産性を両立し、メディア追加時にも効率よく評価・設定できる仕組みを作ることが競争力になります。</t>
   </si>
   <si>
     <t>既存の評価方法にとらわれず、より早く正確にメディアの適性を判断できる方法へ挑戦することです。</t>
@@ -1958,35 +1957,6 @@
   </si>
   <si>
     <t>自己紹介（３分）</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>課の構成は管理職2名、主任5名、一般職〇名です。私たちのチームには、大きく二つのテーマがあります。一つはスジムラの発生メカニズムの解明、もう一つはMogamiの用紙対応力の向上です。
-私は用紙対応力向上のテーマに所属し、主にプライマに関する検討を行っています。私の役割は、文献調査や評価用チャートの分析を通じて、プライマが画質に与える影響や技術課題を整理し、その後の開発をどのような方針で進めるかを先行して検討することです。また、検討結果を基に、プライマ量を決定する評価フローの再構築にも取り組みました。</t>
-    <rPh sb="0" eb="1">
-      <t>カ</t>
-    </rPh>
-    <rPh sb="2" eb="4">
-      <t>コウセイ</t>
-    </rPh>
-    <rPh sb="5" eb="8">
-      <t>カンリショク</t>
-    </rPh>
-    <rPh sb="9" eb="10">
-      <t>メイ</t>
-    </rPh>
-    <rPh sb="11" eb="13">
-      <t>シュニン</t>
-    </rPh>
-    <rPh sb="14" eb="15">
-      <t>メイ</t>
-    </rPh>
-    <rPh sb="16" eb="19">
-      <t>イッパンショク</t>
-    </rPh>
-    <rPh sb="20" eb="21">
-      <t>メイ</t>
-    </rPh>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -4238,131 +4208,140 @@
 事業部は「現行フローで評価できており、慣れているため現行手法を使いたい」という考えでした。一方、私たちは「将来的に紙種が増えることを考えると、新手法の方が効率的」と考えており、その点で意見の違いがありました。</t>
   </si>
   <si>
-    <t xml:space="preserve">私は、デジタルビジネスプラットフォーム開発本部、ソフトウェア33開発室の中岫茉希と申します。
-デジタルプリンティング事業本部と連携し、商業印刷機Mogamiの画質を向上させるための技術開発を担当しています。
-私たちのチームでは、大きく２つのテーマについて取り組んでいます。１つは印刷時に発生する筋状の色むらの原因解明、もう一つは印刷できる用紙の種類を増やすことです。私は後者の用紙対応力の向上を担当しています。
-具体的には、印刷前に塗る液体の量が画質に与える影響を分析し、明らかにしました。また適切な量を効率よく決められるよう、評価方法を見直した。
-これらの取り組みを通じて、商業印刷機の安定した高画質化と、開発の効率化に貢献しています。
-本日はよろしくお願いいたします。
-</t>
-    <rPh sb="80" eb="82">
-      <t>ガシツ</t>
-    </rPh>
-    <rPh sb="83" eb="85">
-      <t>コウジョウ</t>
-    </rPh>
-    <rPh sb="106" eb="107">
-      <t>ワタシ</t>
-    </rPh>
-    <rPh sb="116" eb="117">
-      <t>オオ</t>
-    </rPh>
-    <rPh sb="129" eb="130">
+    <t>私は、デジタルビジネスプラットフォーム開発本部、ソフトウェア33開発室の中岫茉希と申します。
+デジタルプリンティング事業本部と連携し、商業印刷機Mogamiの画質向上に向けた技術開発を担当しています。
+商業印刷では、カタログやパンフレットなど、用途に応じてさまざまな種類の用紙が使用されます。そのため、幅広い用紙に対して、安定した画質で印刷できることが求められます。
+私はチームの中で、Mogamiが対応できる用紙の種類を増やすための技術開発に取り組んでいます。具体的には、印刷条件が画質に与える影響を分析し、その関係を明らかにするとともに、用紙に応じた条件を効率的に決めるための評価方法を構築しました。
+これらの取り組みを通じて、Mogamiの用紙対応力の向上と、開発の効率化に貢献しています。
+本日はよろしくお願いいたします。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>組織の課題は？それに対してどうしたか</t>
+    <rPh sb="0" eb="2">
+      <t>ソシキ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>カダイ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>タイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>部の年頭方針は</t>
+    <rPh sb="0" eb="1">
+      <t>ブ</t>
+    </rPh>
+    <rPh sb="2" eb="6">
+      <t>ネントウホウシン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>技術者として、仕事したい？マネージャー？</t>
+    <rPh sb="0" eb="3">
+      <t>ギジュツシャ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>シゴト</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>組織の課題はコミュニケーションだけでは、解決できないのでは？それ以外の取り組みは</t>
+    <rPh sb="0" eb="2">
+      <t>ソシキ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>カダイ</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>カイケツ</t>
+    </rPh>
+    <rPh sb="32" eb="34">
+      <t>イガイ</t>
+    </rPh>
+    <rPh sb="35" eb="36">
       <t>ト</t>
     </rPh>
-    <rPh sb="131" eb="132">
+    <rPh sb="37" eb="38">
       <t>ク</t>
     </rPh>
-    <rPh sb="141" eb="144">
-      <t>インサツジ</t>
-    </rPh>
-    <rPh sb="145" eb="147">
-      <t>ハッセイ</t>
-    </rPh>
-    <rPh sb="149" eb="151">
-      <t>スジジョウ</t>
-    </rPh>
-    <rPh sb="152" eb="153">
-      <t>イロ</t>
-    </rPh>
-    <rPh sb="156" eb="158">
-      <t>ゲンイン</t>
-    </rPh>
-    <rPh sb="158" eb="160">
-      <t>カイメイ</t>
-    </rPh>
-    <rPh sb="163" eb="164">
-      <t>ヒト</t>
-    </rPh>
-    <rPh sb="166" eb="168">
-      <t>インサツ</t>
-    </rPh>
-    <rPh sb="171" eb="173">
-      <t>ヨウシ</t>
-    </rPh>
-    <rPh sb="174" eb="176">
-      <t>シュルイ</t>
-    </rPh>
-    <rPh sb="177" eb="178">
-      <t>フ</t>
-    </rPh>
-    <rPh sb="185" eb="186">
-      <t>ワタシ</t>
-    </rPh>
-    <rPh sb="187" eb="189">
-      <t>コウシャ</t>
-    </rPh>
-    <rPh sb="190" eb="195">
-      <t>ヨウシタイオウリョク</t>
-    </rPh>
-    <rPh sb="196" eb="198">
-      <t>コウジョウ</t>
-    </rPh>
-    <rPh sb="199" eb="201">
-      <t>タントウ</t>
-    </rPh>
-    <rPh sb="209" eb="212">
-      <t>グタイテキ</t>
-    </rPh>
-    <rPh sb="215" eb="218">
-      <t>インサツマエ</t>
-    </rPh>
-    <rPh sb="219" eb="220">
-      <t>ヌ</t>
-    </rPh>
-    <rPh sb="221" eb="223">
-      <t>エキタイ</t>
-    </rPh>
-    <rPh sb="224" eb="225">
-      <t>リョウ</t>
-    </rPh>
-    <rPh sb="226" eb="228">
-      <t>ガシツ</t>
-    </rPh>
-    <rPh sb="229" eb="230">
-      <t>アタ</t>
-    </rPh>
-    <rPh sb="232" eb="234">
-      <t>エイキョウ</t>
-    </rPh>
-    <rPh sb="235" eb="237">
-      <t>ブンセキ</t>
-    </rPh>
-    <rPh sb="239" eb="240">
-      <t>アキ</t>
-    </rPh>
-    <rPh sb="250" eb="252">
-      <t>テキセツ</t>
-    </rPh>
-    <rPh sb="253" eb="254">
-      <t>リョウ</t>
-    </rPh>
-    <rPh sb="255" eb="257">
-      <t>コウリツ</t>
-    </rPh>
-    <rPh sb="259" eb="260">
-      <t>キ</t>
-    </rPh>
-    <rPh sb="267" eb="269">
-      <t>ヒョウカ</t>
-    </rPh>
-    <rPh sb="269" eb="271">
-      <t>ホウホウ</t>
-    </rPh>
-    <rPh sb="272" eb="274">
-      <t>ミナオ</t>
-    </rPh>
     <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>課の構成と、あなたの役割</t>
+    <rPh sb="0" eb="1">
+      <t>カ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>コウセイ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>ヤクワリ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>キヤノンは、商業印刷市場では後発で、現時点ではシェアを拡大している段階にあると認識しています。
+ 一方で、オフィス印刷で培ってきた画像形成技術や画質分析の知見があり、高画質は十分に競争力のある領域です。実際にMogamiも、文字品位や光沢均一性などの画質面で競合に対する強みが確認されています。
+ ただし、商業印刷では、お客様が保有している多種多様な用紙をそのまま使えることが重要です。Mogamiは、一部の用紙で画質を安定させるために個別調整が必要で、多数の用紙へ効率的に対応する点にはまだ課題があります。
+ そのため、キヤノンの立ち位置は、高画質という強みを持ちながら、用紙対応力を高めることで、商業印刷市場でさらに競争力とシェアを伸ばそうとしている段階だと考えています。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>課の構成は管理職2名、主任5名、一般職〇名です。私たちのチームには、大きく二つのテーマがあります。一つはスジムラの発生メカニズムの解明、もう一つはMogamiの用紙対応力の向上です。
+ソフトウェア33開発室では、主に商業印刷機を対象に、測定・解析技術やAIを活用して、画質、安定性、用紙対応力を向上させる技術開発を行っています。具体的には、電子写真方式とインクジェット方式の両方について、画質劣化の原因を分析し、製品設計や画質改善につなげるプロジェクトに取り組んでいます。</t>
+    <rPh sb="0" eb="1">
+      <t>カ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>コウセイ</t>
+    </rPh>
+    <rPh sb="5" eb="8">
+      <t>カンリショク</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>メイ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>シュニン</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>メイ</t>
+    </rPh>
+    <rPh sb="16" eb="19">
+      <t>イッパンショク</t>
+    </rPh>
+    <rPh sb="20" eb="21">
+      <t>メイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ソフトウェア開発第三部では、画質定量化技術をコアとして、プリンティング製品の開発を支援しています。目視で判断していた画質を数値で評価するとともに、画質劣化の原因や各部品の影響を分析し、開発の上流段階から設計へ反映することで、製品力と開発生産性の向上を目指しています。
+課の年頭方針は測定解析とAIの両軸に基づいた画質・安定性・メディア対応力向上技術の開発生産性を向上し、プリンティング事業拡大に貢献</t>
+    <rPh sb="192" eb="193">
+      <t>カ</t>
+    </rPh>
+    <rPh sb="194" eb="198">
+      <t>ネントウホウシン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>デジタルビジネスプラットフォーム開発本部ソフトウェア12開発室の森本と申します。</t>
+  </si>
+  <si>
+    <t>2023年に入社し、入社当初はイメージング事業本部に配属され、ボリュメトリックビデオの開発、DBPに異動してからはカメラやCT装置といった画像処理技術に関わる開発を行ってきました。</t>
+  </si>
+  <si>
+    <t>そのように入社して以来、一貫して三次元画像処理やメディカル領域といったキヤノンにとって新しい領域の画像処理に携わっています。</t>
+  </si>
+  <si>
+    <t>直近ではイメージング事業本部と連携し、少数のカメラで人間の3Dモデルを生成する技術の開発を担当しています。</t>
   </si>
 </sst>
 </file>
@@ -4613,7 +4592,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -4712,6 +4691,12 @@
     </xf>
     <xf numFmtId="0" fontId="18" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -4948,24 +4933,24 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="283.5">
+    <row r="2" spans="1:9" ht="262.5">
       <c r="A2" s="4">
         <v>0</v>
       </c>
       <c r="B2" s="23" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C2" s="18" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="D2" s="25" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E2" s="13" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="F2" s="20" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>5</v>
@@ -4977,10 +4962,10 @@
     <row r="3" spans="1:9" ht="409.5">
       <c r="A3" s="28"/>
       <c r="B3" s="23" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C3" s="29" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E3" s="26"/>
       <c r="F3" s="20"/>
@@ -4990,19 +4975,19 @@
         <v>1</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C4" s="18" t="s">
+        <v>260</v>
+      </c>
+      <c r="D4" s="25" t="s">
+        <v>175</v>
+      </c>
+      <c r="E4" s="21" t="s">
         <v>186</v>
       </c>
-      <c r="D4" s="25" t="s">
-        <v>176</v>
-      </c>
-      <c r="E4" s="21" t="s">
-        <v>188</v>
-      </c>
       <c r="F4" s="20" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="G4" s="6"/>
     </row>
@@ -5011,13 +4996,13 @@
         <v>7</v>
       </c>
       <c r="B5" s="23" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C5" s="5" t="s">
         <v>55</v>
       </c>
       <c r="E5" s="13" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="F5" s="20"/>
     </row>
@@ -5026,13 +5011,13 @@
         <v>8</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C6" s="5" t="s">
         <v>56</v>
       </c>
       <c r="E6" s="13" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="F6" s="13"/>
     </row>
@@ -5041,13 +5026,13 @@
         <v>9</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C7" s="18" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E7" s="21" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="F7" s="14"/>
       <c r="I7" s="6"/>
@@ -5057,13 +5042,13 @@
         <v>10</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C8" s="18" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="E8" s="13" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="F8" s="14"/>
     </row>
@@ -5072,13 +5057,13 @@
         <v>2</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C9" s="5" t="s">
         <v>57</v>
       </c>
       <c r="E9" s="13" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="F9" s="20"/>
     </row>
@@ -5087,13 +5072,13 @@
         <v>3</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C10" s="18" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="E10" s="12" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="F10" s="20"/>
     </row>
@@ -5102,13 +5087,13 @@
         <v>11</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C11" s="5" t="s">
         <v>58</v>
       </c>
       <c r="E11" s="12" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="F11" s="14"/>
     </row>
@@ -5117,13 +5102,13 @@
         <v>12</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C12" s="18" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="E12" s="13" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="F12" s="14"/>
     </row>
@@ -5132,7 +5117,7 @@
         <v>13</v>
       </c>
       <c r="B13" s="11" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C13" s="17" t="s">
         <v>59</v>
@@ -5145,13 +5130,13 @@
         <v>4</v>
       </c>
       <c r="B14" s="11" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C14" s="18" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="E14" s="13" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="F14" s="20"/>
       <c r="G14" s="10"/>
@@ -5161,13 +5146,13 @@
         <v>14</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C15" s="17" t="s">
         <v>60</v>
       </c>
       <c r="E15" s="13" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="F15" s="20"/>
     </row>
@@ -5176,13 +5161,13 @@
         <v>15</v>
       </c>
       <c r="B16" s="11" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C16" s="5" t="s">
         <v>61</v>
       </c>
       <c r="E16" s="13" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="F16" s="20"/>
     </row>
@@ -5191,13 +5176,13 @@
         <v>16</v>
       </c>
       <c r="B17" s="11" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C17" s="18" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="E17" s="13" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="F17" s="20"/>
     </row>
@@ -5206,13 +5191,13 @@
         <v>17</v>
       </c>
       <c r="B18" s="11" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C18" s="5" t="s">
         <v>62</v>
       </c>
       <c r="E18" s="12" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="F18" s="20"/>
     </row>
@@ -5221,7 +5206,7 @@
         <v>18</v>
       </c>
       <c r="B19" s="11" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C19" s="17" t="s">
         <v>63</v>
@@ -5234,28 +5219,28 @@
         <v>19</v>
       </c>
       <c r="B20" s="11" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C20" s="5" t="s">
         <v>64</v>
       </c>
       <c r="E20" s="13" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="F20" s="20"/>
     </row>
-    <row r="21" spans="1:6" ht="108">
+    <row r="21" spans="1:6" ht="175.5">
       <c r="A21" s="4" t="s">
         <v>20</v>
       </c>
       <c r="B21" s="23" t="s">
-        <v>181</v>
-      </c>
-      <c r="C21" s="5" t="s">
-        <v>65</v>
+        <v>180</v>
+      </c>
+      <c r="C21" s="18" t="s">
+        <v>259</v>
       </c>
       <c r="E21" s="13" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
     </row>
     <row r="22" spans="1:6" ht="27">
@@ -5263,13 +5248,13 @@
         <v>21</v>
       </c>
       <c r="B22" s="11" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E22" s="12" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="F22" s="20"/>
     </row>
@@ -5278,13 +5263,13 @@
         <v>22</v>
       </c>
       <c r="B23" s="11" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C23" s="17" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E23" s="13" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="F23" s="20"/>
     </row>
@@ -5293,13 +5278,13 @@
         <v>23</v>
       </c>
       <c r="B24" s="11" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E24" s="12" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="F24" s="20"/>
     </row>
@@ -5308,7 +5293,7 @@
         <v>24</v>
       </c>
       <c r="B25" s="19" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C25" s="17"/>
       <c r="E25" s="12"/>
@@ -5319,10 +5304,10 @@
         <v>25</v>
       </c>
       <c r="B26" s="11" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E26" s="13"/>
       <c r="F26" s="20"/>
@@ -5332,10 +5317,10 @@
         <v>26</v>
       </c>
       <c r="B27" s="11" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C27" s="30" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="E27" s="13"/>
       <c r="F27" s="14"/>
@@ -5345,13 +5330,13 @@
         <v>27</v>
       </c>
       <c r="B28" s="11" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E28" s="13" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="F28" s="20"/>
     </row>
@@ -5360,13 +5345,13 @@
         <v>28</v>
       </c>
       <c r="B29" s="11" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E29" s="13" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="F29" s="20"/>
     </row>
@@ -5375,13 +5360,13 @@
         <v>29</v>
       </c>
       <c r="B30" s="11" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E30" s="12" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="F30" s="20"/>
     </row>
@@ -5390,7 +5375,7 @@
         <v>30</v>
       </c>
       <c r="B31" s="11" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C31" s="5"/>
       <c r="E31" s="22"/>
@@ -5401,13 +5386,13 @@
         <v>31</v>
       </c>
       <c r="B32" s="11" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E32" s="13" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="F32" s="20"/>
     </row>
@@ -5416,13 +5401,13 @@
         <v>32</v>
       </c>
       <c r="B33" s="11" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E33" s="12" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="F33" s="13"/>
       <c r="I33" s="6"/>
@@ -5432,13 +5417,13 @@
         <v>33</v>
       </c>
       <c r="B34" s="11" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E34" s="12" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="F34" s="20"/>
     </row>
@@ -5447,10 +5432,10 @@
         <v>34</v>
       </c>
       <c r="B35" s="11" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E35" s="13"/>
       <c r="F35" s="20"/>
@@ -5460,13 +5445,13 @@
         <v>35</v>
       </c>
       <c r="B36" s="11" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E36" s="13" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="F36" s="20"/>
     </row>
@@ -5475,13 +5460,13 @@
         <v>36</v>
       </c>
       <c r="B37" s="11" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E37" s="13" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="F37" s="20"/>
     </row>
@@ -5490,13 +5475,13 @@
         <v>37</v>
       </c>
       <c r="B38" s="11" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E38" s="13" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="F38" s="20"/>
     </row>
@@ -5505,13 +5490,13 @@
         <v>38</v>
       </c>
       <c r="B39" s="11" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E39" s="13" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="F39" s="14"/>
     </row>
@@ -5520,10 +5505,10 @@
         <v>39</v>
       </c>
       <c r="B40" s="11" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E40" s="13"/>
       <c r="F40" s="15"/>
@@ -5533,10 +5518,10 @@
         <v>40</v>
       </c>
       <c r="B41" s="11" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E41" s="13"/>
       <c r="F41" s="13"/>
@@ -5546,10 +5531,10 @@
         <v>41</v>
       </c>
       <c r="B42" s="11" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E42" s="13"/>
       <c r="F42" s="13"/>
@@ -5559,7 +5544,7 @@
         <v>42</v>
       </c>
       <c r="B43" s="11" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C43" s="5"/>
       <c r="E43" s="13"/>
@@ -5570,13 +5555,13 @@
         <v>43</v>
       </c>
       <c r="B44" s="11" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E44" s="13" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="F44" s="13"/>
     </row>
@@ -5585,13 +5570,13 @@
         <v>44</v>
       </c>
       <c r="B45" s="11" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C45" s="17" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E45" s="13" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="F45" s="13"/>
     </row>
@@ -5600,13 +5585,13 @@
         <v>45</v>
       </c>
       <c r="B46" s="11" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C46" s="17" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E46" s="13" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="F46" s="13"/>
     </row>
@@ -5615,7 +5600,7 @@
         <v>46</v>
       </c>
       <c r="B47" s="11" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C47" s="5"/>
       <c r="E47" s="22"/>
@@ -5626,7 +5611,7 @@
         <v>47</v>
       </c>
       <c r="B48" s="11" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C48" s="5"/>
       <c r="E48" s="22"/>
@@ -5637,10 +5622,10 @@
         <v>48</v>
       </c>
       <c r="B49" s="11" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E49" s="13"/>
       <c r="F49" s="13"/>
@@ -5650,13 +5635,13 @@
         <v>49</v>
       </c>
       <c r="B50" s="11" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C50" s="5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E50" s="13" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="F50" s="13"/>
     </row>
@@ -5665,13 +5650,13 @@
         <v>50</v>
       </c>
       <c r="B51" s="11" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C51" s="5" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E51" s="13" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="F51" s="13"/>
     </row>
@@ -5680,33 +5665,33 @@
         <v>51</v>
       </c>
       <c r="B52" s="11" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C52" s="5" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E52" s="13" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="F52" s="13"/>
     </row>
     <row r="53" spans="1:6" ht="94.5">
       <c r="A53" s="4"/>
       <c r="B53" s="11" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C53" s="5" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E53" s="12" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="F53" s="13"/>
     </row>
     <row r="54" spans="1:6">
       <c r="A54" s="4"/>
       <c r="B54" s="11" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C54" s="27"/>
       <c r="E54" s="13"/>
@@ -5715,54 +5700,54 @@
     <row r="55" spans="1:6" ht="27">
       <c r="A55" s="4"/>
       <c r="B55" s="11" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C55" s="5"/>
       <c r="E55" s="13" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="F55" s="13"/>
     </row>
     <row r="56" spans="1:6">
       <c r="A56" s="4"/>
       <c r="B56" s="11" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C56" s="5"/>
       <c r="E56" s="13" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="F56" s="13"/>
     </row>
     <row r="57" spans="1:6" ht="40.5">
       <c r="A57" s="4"/>
       <c r="B57" s="11" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C57" s="5"/>
       <c r="E57" s="13" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="F57" s="13"/>
     </row>
     <row r="58" spans="1:6" ht="40.5">
       <c r="A58" s="4"/>
       <c r="B58" s="11" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C58" s="5"/>
       <c r="E58" s="12" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="F58" s="13"/>
     </row>
     <row r="59" spans="1:6" ht="54">
       <c r="A59" s="4"/>
       <c r="B59" s="11" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C59" s="5" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E59" s="13"/>
       <c r="F59" s="13"/>
@@ -5770,13 +5755,13 @@
     <row r="60" spans="1:6" ht="54">
       <c r="A60" s="4"/>
       <c r="B60" s="11" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C60" s="5" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E60" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="F60" s="13"/>
     </row>
@@ -5785,11 +5770,11 @@
         <v>52</v>
       </c>
       <c r="B61" s="11" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C61" s="5"/>
       <c r="E61" s="13" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="62" spans="1:6" ht="40.5">
@@ -5797,21 +5782,52 @@
         <v>53</v>
       </c>
       <c r="B62" s="11" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C62" s="5"/>
       <c r="E62" s="13" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
-  <pageSetup paperSize="8" scale="50" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="8" scale="50" orientation="landscape" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C945A8A3-E413-4358-BBE4-EF5A44242598}">
+  <dimension ref="A1:A4"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" s="34" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1">
+      <c r="A2" s="34" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" s="34" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1">
+      <c r="A4" s="34" t="s">
+        <v>265</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:B21"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
@@ -5826,125 +5842,125 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="24" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B2" s="24"/>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="24" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B3" s="24"/>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="24" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B4" s="24"/>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="24" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B5" s="24"/>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="24" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B6" s="24"/>
     </row>
     <row r="7" spans="1:2" ht="54">
       <c r="A7" s="24" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B7" s="23" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="24" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B8" s="24"/>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="24" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B9" s="24"/>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="24" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B10" s="24"/>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="24" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B11" s="24"/>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="24" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B12" s="24"/>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="24" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B13" s="24"/>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="24" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B14" s="24"/>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="24" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B15" s="24"/>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="24" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B16" s="24"/>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="24" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B17" s="24"/>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="24" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B18" s="24"/>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="24" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B19" s="24"/>
     </row>
     <row r="20" spans="1:2" ht="67.5">
       <c r="A20" s="24" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B20" s="23" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="24" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B21" s="24"/>
     </row>
@@ -5954,7 +5970,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:B11"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
@@ -5965,91 +5981,208 @@
   <sheetData>
     <row r="1" spans="1:2" ht="60">
       <c r="A1" s="31" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="B1" s="32" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="54.95" customHeight="1">
       <c r="A2" s="31" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="B2" s="32" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="54.95" customHeight="1">
       <c r="A3" s="31" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="B3" s="32" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="90">
       <c r="A4" s="31" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="B4" s="32" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="54.95" customHeight="1">
       <c r="A5" s="31" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="B5" s="32" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="54.95" customHeight="1">
       <c r="A6" s="31" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="B6" s="32" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="60">
       <c r="A7" s="31" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B7" s="32" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="60">
       <c r="A8" s="31" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="B8" s="32" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="54.95" customHeight="1">
       <c r="A9" s="31" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="B9" s="32" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="54.95" customHeight="1">
       <c r="A10" s="31" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="B10" s="32" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="54.95" customHeight="1">
       <c r="A11" s="31" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="B11" s="32" t="s">
-        <v>252</v>
-      </c>
+        <v>250</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{05FA0C31-4B39-4CC9-AFFE-ADB97979182D}">
+  <dimension ref="A1:B21"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
+  <cols>
+    <col min="1" max="1" width="150.375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="103.375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" s="24"/>
+      <c r="B1" s="24"/>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" s="24" t="s">
+        <v>153</v>
+      </c>
+      <c r="B2" s="24"/>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" s="33" t="s">
+        <v>258</v>
+      </c>
+      <c r="B3" s="24"/>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" s="33" t="s">
+        <v>254</v>
+      </c>
+      <c r="B4" s="24"/>
+    </row>
+    <row r="5" spans="1:2" ht="67.5">
+      <c r="A5" s="33" t="s">
+        <v>255</v>
+      </c>
+      <c r="B5" s="23" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" s="33" t="s">
+        <v>256</v>
+      </c>
+      <c r="B6" s="24"/>
+    </row>
+    <row r="7" spans="1:2" ht="54">
+      <c r="A7" s="33" t="s">
+        <v>257</v>
+      </c>
+      <c r="B7" s="23" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" s="24"/>
+      <c r="B8" s="24"/>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" s="24"/>
+      <c r="B9" s="24"/>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10" s="24"/>
+      <c r="B10" s="24"/>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" s="24"/>
+      <c r="B11" s="24"/>
+    </row>
+    <row r="12" spans="1:2">
+      <c r="A12" s="24"/>
+      <c r="B12" s="24"/>
+    </row>
+    <row r="13" spans="1:2">
+      <c r="A13" s="24"/>
+      <c r="B13" s="24"/>
+    </row>
+    <row r="14" spans="1:2">
+      <c r="A14" s="24"/>
+      <c r="B14" s="24"/>
+    </row>
+    <row r="15" spans="1:2">
+      <c r="A15" s="24"/>
+      <c r="B15" s="24"/>
+    </row>
+    <row r="16" spans="1:2">
+      <c r="A16" s="24"/>
+      <c r="B16" s="24"/>
+    </row>
+    <row r="17" spans="1:2">
+      <c r="A17" s="24"/>
+      <c r="B17" s="24"/>
+    </row>
+    <row r="18" spans="1:2">
+      <c r="A18" s="24"/>
+      <c r="B18" s="24"/>
+    </row>
+    <row r="19" spans="1:2">
+      <c r="A19" s="24"/>
+      <c r="B19" s="24"/>
+    </row>
+    <row r="20" spans="1:2" ht="67.5">
+      <c r="A20" s="24"/>
+      <c r="B20" s="23" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2">
+      <c r="A21" s="24"/>
+      <c r="B21" s="24"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>

--- a/作業/面接練習/G3面接準備中岫.xlsx
+++ b/作業/面接練習/G3面接準備中岫.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aaa115298\Desktop\G3\G3\G3試験中岫作業\G3\作業\面接練習\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/df213c2b7ba35e42/デスクトップ/試験/G3/作業/面接練習/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{333FA04E-09A4-4151-BA94-35BCDFE120B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="41" documentId="13_ncr:1_{333FA04E-09A4-4151-BA94-35BCDFE120B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1C8459F0-4D71-4D82-83A7-77FB30CC7EC0}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -18,6 +18,8 @@
     <sheet name="1013" sheetId="2" r:id="rId3"/>
     <sheet name="1014" sheetId="3" r:id="rId4"/>
     <sheet name="1015" sheetId="4" r:id="rId5"/>
+    <sheet name="1016" sheetId="7" r:id="rId6"/>
+    <sheet name="Sheet2" sheetId="6" r:id="rId7"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -35,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="272" uniqueCount="266">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="294" uniqueCount="284">
   <si>
     <t>No</t>
   </si>
@@ -238,9 +240,6 @@
     <t>特定の方法に固執せず、Mogamiのメディア対応力を高めるために有効な技術を取り入れます。新しい測定手法やデータ分析技術が有効であれば、自ら試して効果と適用範囲を確認し、評価・開発プロセスへ展開します。</t>
   </si>
   <si>
-    <t>答えだけを教えるのではなく、メディア課題をどのように分解し、どの事実を確認して判断するかを伝えます。最初は評価計画と結果をこまめにレビューし、理解度に応じて任せる範囲を広げ、自力で次の検証を組み立てられるように育成します。</t>
-  </si>
-  <si>
     <t>相談しやすい時間と場を作り、作業が止まっている兆候があればこちらから声をかけます。すぐに答えを示すのではなく、目的、現状、困っている点、次に確認すべきことを一緒に整理し、本人が次の行動を決められるよう支援します。</t>
   </si>
   <si>
@@ -314,10 +313,6 @@
   </si>
   <si>
     <t>本社部門の目的は、複数事業に共通する技術と開発力を蓄積し、全社最適の観点で事業へ提供することだと考えています。Mogamiのメディア対応で得た評価・分析の知見を体系化し、他製品や次世代開発へ展開することが、その役割への貢献になります。</t>
-  </si>
-  <si>
-    <t>画質評価・解析を通じて製品の高画質化を実現すること。その中で、現在は顧客が求める多種多様な用紙に対して経験的・属人的に評価解析をしているが、紙物性に基づき体系化することで設計の効率化をはかっている</t>
-    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>現在の課の構成と、チームの中でのあなたの役割を教えてください。</t>
@@ -1720,16 +1715,6 @@
       </rPr>
       <t>Mogamiのメディア対応力全体を見て課題を設定し、周囲を動かす立場へ変わります。判断に必要な情報を整理し、関係者間の認識をそろえ、製品価値につながる結論まで責任を持つようになります。</t>
     </r>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>課の課題は、個別製品や担当者ごとに得られた知見が分散し、横展開しにくいことです。Mogamiで得た紙特性、評価結果、対応条件を共通の観点で整理し、他テーマ（IJにかかわらず電子写真）でも検索・再利用できる形にすることで、検討の重複を減らし開発速度を上げたいと考えています。</t>
-    <rPh sb="49" eb="50">
-      <t>カミ</t>
-    </rPh>
-    <rPh sb="86" eb="90">
-      <t>デンシシャシン</t>
-    </rPh>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -4208,15 +4193,6 @@
 事業部は「現行フローで評価できており、慣れているため現行手法を使いたい」という考えでした。一方、私たちは「将来的に紙種が増えることを考えると、新手法の方が効率的」と考えており、その点で意見の違いがありました。</t>
   </si>
   <si>
-    <t>私は、デジタルビジネスプラットフォーム開発本部、ソフトウェア33開発室の中岫茉希と申します。
-デジタルプリンティング事業本部と連携し、商業印刷機Mogamiの画質向上に向けた技術開発を担当しています。
-商業印刷では、カタログやパンフレットなど、用途に応じてさまざまな種類の用紙が使用されます。そのため、幅広い用紙に対して、安定した画質で印刷できることが求められます。
-私はチームの中で、Mogamiが対応できる用紙の種類を増やすための技術開発に取り組んでいます。具体的には、印刷条件が画質に与える影響を分析し、その関係を明らかにするとともに、用紙に応じた条件を効率的に決めるための評価方法を構築しました。
-これらの取り組みを通じて、Mogamiの用紙対応力の向上と、開発の効率化に貢献しています。
-本日はよろしくお願いいたします。</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>組織の課題は？それに対してどうしたか</t>
     <rPh sb="0" eb="2">
       <t>ソシキ</t>
@@ -4292,35 +4268,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>課の構成は管理職2名、主任5名、一般職〇名です。私たちのチームには、大きく二つのテーマがあります。一つはスジムラの発生メカニズムの解明、もう一つはMogamiの用紙対応力の向上です。
-ソフトウェア33開発室では、主に商業印刷機を対象に、測定・解析技術やAIを活用して、画質、安定性、用紙対応力を向上させる技術開発を行っています。具体的には、電子写真方式とインクジェット方式の両方について、画質劣化の原因を分析し、製品設計や画質改善につなげるプロジェクトに取り組んでいます。</t>
-    <rPh sb="0" eb="1">
-      <t>カ</t>
-    </rPh>
-    <rPh sb="2" eb="4">
-      <t>コウセイ</t>
-    </rPh>
-    <rPh sb="5" eb="8">
-      <t>カンリショク</t>
-    </rPh>
-    <rPh sb="9" eb="10">
-      <t>メイ</t>
-    </rPh>
-    <rPh sb="11" eb="13">
-      <t>シュニン</t>
-    </rPh>
-    <rPh sb="14" eb="15">
-      <t>メイ</t>
-    </rPh>
-    <rPh sb="16" eb="19">
-      <t>イッパンショク</t>
-    </rPh>
-    <rPh sb="20" eb="21">
-      <t>メイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>ソフトウェア開発第三部では、画質定量化技術をコアとして、プリンティング製品の開発を支援しています。目視で判断していた画質を数値で評価するとともに、画質劣化の原因や各部品の影響を分析し、開発の上流段階から設計へ反映することで、製品力と開発生産性の向上を目指しています。
 課の年頭方針は測定解析とAIの両軸に基づいた画質・安定性・メディア対応力向上技術の開発生産性を向上し、プリンティング事業拡大に貢献</t>
     <rPh sb="192" eb="193">
@@ -4342,13 +4289,353 @@
   </si>
   <si>
     <t>直近ではイメージング事業本部と連携し、少数のカメラで人間の3Dモデルを生成する技術の開発を担当しています。</t>
+  </si>
+  <si>
+    <t>スジムラチームとの関係？どのように協力しながらやっているのか</t>
+    <rPh sb="9" eb="11">
+      <t>カンケイ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>キョウリョク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>チーム内、チーム外のトラブルはあったか</t>
+    <rPh sb="3" eb="4">
+      <t>ナイ</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>ソト</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>連携先はどこか？</t>
+    <rPh sb="0" eb="2">
+      <t>レンケイ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>サキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>キヤノンにとっての画質とは何か</t>
+    <rPh sb="9" eb="11">
+      <t>ガシツ</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>ナニ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>G3になったら何が変わる？</t>
+    <rPh sb="7" eb="8">
+      <t>ナニ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>カ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>課の構成は管理職2名、主任5名、G3、〇一般職〇名です。私たちのチームには、大きく二つのテーマがあります。一つはスジムラの発生メカニズムの解明、もう一つはMogamiの用紙対応力の向上です。
+ソフトウェア33開発室では、主に商業印刷機を対象に、測定・解析技術やAIを活用して、画質、安定性、用紙対応力を向上させる技術開発を行っています。具体的には、電子写真方式とインクジェット方式の両方について、画質劣化の原因を分析し、製品設計や画質改善につなげるプロジェクトに取り組んでいます。</t>
+    <rPh sb="0" eb="1">
+      <t>カ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>コウセイ</t>
+    </rPh>
+    <rPh sb="5" eb="8">
+      <t>カンリショク</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>メイ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>シュニン</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>メイ</t>
+    </rPh>
+    <rPh sb="20" eb="23">
+      <t>イッパンショク</t>
+    </rPh>
+    <rPh sb="24" eb="25">
+      <t>メイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>協力することで心がけていること</t>
+    <rPh sb="0" eb="2">
+      <t>キョウリョク</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>ココロ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ボリュメトリックの課題（商業印刷での課題）</t>
+    <rPh sb="9" eb="11">
+      <t>カダイ</t>
+    </rPh>
+    <rPh sb="12" eb="16">
+      <t>ショウギョウインサツ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>カダイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>生成AIのリスクについて</t>
+    <rPh sb="0" eb="2">
+      <t>セイセイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>連携先の構成と議論内容は</t>
+    <rPh sb="0" eb="2">
+      <t>レンケイ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>サキ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>コウセイ</t>
+    </rPh>
+    <rPh sb="7" eb="11">
+      <t>ギロンナイヨウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>世の中でどう影響を与えるか</t>
+    <rPh sb="0" eb="1">
+      <t>ヨ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ナカ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>エイキョウ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>アタ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>世の中どう変わっていくか</t>
+    <rPh sb="0" eb="1">
+      <t>ヨ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ナカ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>カ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>今後のキャリア</t>
+    <rPh sb="0" eb="2">
+      <t>コンゴ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>特許
+定例
+スジムラメカニズム展開と、プライマの関係図作成の議論</t>
+    <rPh sb="0" eb="2">
+      <t>トッキョ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>テイレイ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>テンカイ</t>
+    </rPh>
+    <rPh sb="24" eb="27">
+      <t>カンケイズ</t>
+    </rPh>
+    <rPh sb="27" eb="29">
+      <t>サクセイ</t>
+    </rPh>
+    <rPh sb="30" eb="32">
+      <t>ギロン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ビジネス観点を入れた内容にしたい</t>
+    <rPh sb="4" eb="6">
+      <t>カンテン</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>イ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>ナイヨウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>高画質と生産性の両立
+高画質を設計するための印刷条件やメカ的な設計を、紙ごとに調整しなければならない。お客さんは小ロット、短納期を希望しているため、依頼されてから、求められた品質で早く納入することが求められる。</t>
+    <rPh sb="11" eb="14">
+      <t>コウガシツ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>セッケイ</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>インサツ</t>
+    </rPh>
+    <rPh sb="24" eb="26">
+      <t>ジョウケン</t>
+    </rPh>
+    <rPh sb="29" eb="30">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="31" eb="33">
+      <t>セッケイ</t>
+    </rPh>
+    <rPh sb="35" eb="36">
+      <t>カミ</t>
+    </rPh>
+    <rPh sb="39" eb="41">
+      <t>チョウセイ</t>
+    </rPh>
+    <rPh sb="52" eb="53">
+      <t>キャク</t>
+    </rPh>
+    <rPh sb="56" eb="57">
+      <t>ショウ</t>
+    </rPh>
+    <rPh sb="61" eb="64">
+      <t>タンノウキ</t>
+    </rPh>
+    <rPh sb="65" eb="67">
+      <t>キボウ</t>
+    </rPh>
+    <rPh sb="74" eb="76">
+      <t>イライ</t>
+    </rPh>
+    <rPh sb="82" eb="83">
+      <t>モト</t>
+    </rPh>
+    <rPh sb="87" eb="89">
+      <t>ヒンシツ</t>
+    </rPh>
+    <rPh sb="90" eb="91">
+      <t>ハヤ</t>
+    </rPh>
+    <rPh sb="92" eb="94">
+      <t>ノウニュウ</t>
+    </rPh>
+    <rPh sb="99" eb="100">
+      <t>モト</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>私は、デジタルビジネスプラットフォーム開発本部、ソフトウェア33開発室の中岫茉希と申します。</t>
+  </si>
+  <si>
+    <t>画質定量化技術をコアとして、プリンティング製品の開発を支援しています。直近では、デジタルプリンティング事業本部と連携し、商業印刷機Mogamiの画質向上に向けた技術開発を担当しており、画質劣化の原因を解析することで、画質の向上を実現するための設計効率化を目指しています。</t>
+  </si>
+  <si>
+    <t>本日はよろしくお願いいたします。</t>
+  </si>
+  <si>
+    <t>デジタルビジネスプラットフォーム開発本部、ソフトウェア33開発室の中岫茉希と申します。
+私は、画質定量化技術を軸に、プリンティング製品の開発を支援する技術開発に取り組んでいます。画像の画質を定量的に評価・解析することで、画質の変化や劣化の原因を明らかにし、製品の品質向上につなげることを目指しています。
+直近では、デジタルプリンティング事業本部と連携し、商業印刷機Mogamiの画質向上に向けた技術開発を担当しています。画質劣化の原因を解析し、その結果を設計にフィードバックすることで、画質改善に向けた設計の効率化を目指しています。
+本日はよろしくお願いいたします。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>課の年頭方針は測定解析とAIの両軸に基づいた画質・安定性・メディア対応力向上技術の開発生産性を向上し、プリンティング事業拡大に貢献</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>課の課題は、個別製品や担当者ごとに得られた知見が分散し、横展開しにくいことです。Mogamiで得た紙特性、評価結果、対応条件を共通の観点で整理し、他テーマ（IJにかかわらず電子写真）でも検索・再利用できる形にすることで、検討の重複を減らし開発速度を上げたいと考えています。
+IJ、電子写真同じような画質弊害が発生することがある。その場合、メカニズムの解析では両者のメンバーで、議論を行い効率的に得られるようにしている。</t>
+    <rPh sb="49" eb="50">
+      <t>カミ</t>
+    </rPh>
+    <rPh sb="86" eb="90">
+      <t>デンシシャシン</t>
+    </rPh>
+    <rPh sb="141" eb="145">
+      <t>デンシシャシン</t>
+    </rPh>
+    <rPh sb="145" eb="146">
+      <t>オナ</t>
+    </rPh>
+    <rPh sb="150" eb="152">
+      <t>ガシツ</t>
+    </rPh>
+    <rPh sb="152" eb="154">
+      <t>ヘイガイ</t>
+    </rPh>
+    <rPh sb="155" eb="157">
+      <t>ハッセイ</t>
+    </rPh>
+    <rPh sb="167" eb="169">
+      <t>バアイ</t>
+    </rPh>
+    <rPh sb="180" eb="182">
+      <t>リョウシャ</t>
+    </rPh>
+    <rPh sb="189" eb="191">
+      <t>ギロン</t>
+    </rPh>
+    <rPh sb="192" eb="193">
+      <t>オコナ</t>
+    </rPh>
+    <rPh sb="194" eb="196">
+      <t>コウリツ</t>
+    </rPh>
+    <rPh sb="196" eb="197">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="198" eb="199">
+      <t>エ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>答えだけを教えるのではなく、解析の方向性だけ示しタスクを進めるようにする。最初は評価計画と結果をこまめにレビューし、理解度に応じて任せる範囲を広げ、自力で次の検証を組み立てられるように育成します。</t>
+    <rPh sb="14" eb="16">
+      <t>カイセキ</t>
+    </rPh>
+    <rPh sb="17" eb="20">
+      <t>ホウコウセイ</t>
+    </rPh>
+    <rPh sb="22" eb="23">
+      <t>シメ</t>
+    </rPh>
+    <rPh sb="28" eb="29">
+      <t>スス</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="19">
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -4481,6 +4768,14 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
   </fonts>
   <fills count="8">
     <fill>
@@ -4592,7 +4887,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -4697,6 +4992,12 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -4892,21 +5193,21 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:I62"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18.75"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="10.625" style="2" customWidth="1"/>
-    <col min="2" max="2" width="50.375" style="1" customWidth="1"/>
+    <col min="1" max="1" width="10.6328125" style="2" customWidth="1"/>
+    <col min="2" max="2" width="50.36328125" style="1" customWidth="1"/>
     <col min="3" max="3" width="52" customWidth="1"/>
     <col min="4" max="4" width="52" style="25" customWidth="1"/>
-    <col min="5" max="5" width="119.125" style="6" customWidth="1"/>
-    <col min="6" max="6" width="116.875" style="6" customWidth="1"/>
-    <col min="7" max="7" width="35.875" style="3" customWidth="1"/>
-    <col min="8" max="8" width="64.25" style="3" customWidth="1"/>
-    <col min="9" max="9" width="111.625" style="3" customWidth="1"/>
+    <col min="5" max="5" width="119.08984375" style="6" customWidth="1"/>
+    <col min="6" max="6" width="116.90625" style="6" customWidth="1"/>
+    <col min="7" max="7" width="35.90625" style="3" customWidth="1"/>
+    <col min="8" max="8" width="64.26953125" style="3" customWidth="1"/>
+    <col min="9" max="9" width="111.6328125" style="3" customWidth="1"/>
     <col min="10" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="13.5">
+    <row r="1" spans="1:9" ht="13">
       <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
@@ -4933,24 +5234,24 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="262.5">
+    <row r="2" spans="1:9" ht="270">
       <c r="A2" s="4">
         <v>0</v>
       </c>
       <c r="B2" s="23" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="C2" s="18" t="s">
-        <v>253</v>
+        <v>280</v>
       </c>
       <c r="D2" s="25" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="E2" s="13" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="F2" s="20" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>5</v>
@@ -4962,62 +5263,62 @@
     <row r="3" spans="1:9" ht="409.5">
       <c r="A3" s="28"/>
       <c r="B3" s="23" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="C3" s="29" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="E3" s="26"/>
       <c r="F3" s="20"/>
     </row>
-    <row r="4" spans="1:9" ht="262.5">
+    <row r="4" spans="1:9" ht="252">
       <c r="A4" s="4">
         <v>1</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C4" s="18" t="s">
-        <v>260</v>
+        <v>266</v>
       </c>
       <c r="D4" s="25" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="E4" s="21" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="F4" s="20" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="G4" s="6"/>
     </row>
-    <row r="5" spans="1:9" ht="81">
+    <row r="5" spans="1:9" ht="78">
       <c r="A5" s="4" t="s">
         <v>7</v>
       </c>
       <c r="B5" s="23" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="C5" s="5" t="s">
         <v>55</v>
       </c>
       <c r="E5" s="13" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="F5" s="20"/>
     </row>
-    <row r="6" spans="1:9" ht="94.5">
+    <row r="6" spans="1:9" ht="91">
       <c r="A6" s="4" t="s">
         <v>8</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="C6" s="5" t="s">
         <v>56</v>
       </c>
       <c r="E6" s="13" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="F6" s="13"/>
     </row>
@@ -5026,98 +5327,98 @@
         <v>9</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C7" s="18" t="s">
-        <v>93</v>
+        <v>281</v>
       </c>
       <c r="E7" s="21" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="F7" s="14"/>
       <c r="I7" s="6"/>
     </row>
-    <row r="8" spans="1:9" ht="94.5">
+    <row r="8" spans="1:9" ht="91">
       <c r="A8" s="4" t="s">
         <v>10</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C8" s="18" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="E8" s="13" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="F8" s="14"/>
     </row>
-    <row r="9" spans="1:9" ht="108">
+    <row r="9" spans="1:9" ht="104">
       <c r="A9" s="4">
         <v>2</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="C9" s="5" t="s">
         <v>57</v>
       </c>
       <c r="E9" s="13" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="F9" s="20"/>
     </row>
-    <row r="10" spans="1:9" ht="148.5">
+    <row r="10" spans="1:9" ht="169">
       <c r="A10" s="4">
         <v>3</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C10" s="18" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="E10" s="12" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="F10" s="20"/>
     </row>
-    <row r="11" spans="1:9" ht="54">
+    <row r="11" spans="1:9" ht="65">
       <c r="A11" s="4" t="s">
         <v>11</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>100</v>
-      </c>
-      <c r="C11" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="C11" s="17" t="s">
         <v>58</v>
       </c>
       <c r="E11" s="12" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="F11" s="14"/>
     </row>
-    <row r="12" spans="1:9" ht="67.5">
+    <row r="12" spans="1:9" ht="91">
       <c r="A12" s="4" t="s">
         <v>12</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C12" s="18" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="E12" s="13" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="F12" s="14"/>
     </row>
-    <row r="13" spans="1:9" ht="54">
+    <row r="13" spans="1:9" ht="52">
       <c r="A13" s="4" t="s">
         <v>13</v>
       </c>
       <c r="B13" s="11" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C13" s="17" t="s">
         <v>59</v>
@@ -5125,88 +5426,88 @@
       <c r="E13" s="13"/>
       <c r="F13" s="14"/>
     </row>
-    <row r="14" spans="1:9" ht="135">
+    <row r="14" spans="1:9" ht="143">
       <c r="A14" s="4">
         <v>4</v>
       </c>
       <c r="B14" s="11" t="s">
-        <v>103</v>
-      </c>
-      <c r="C14" s="18" t="s">
-        <v>178</v>
+        <v>101</v>
+      </c>
+      <c r="C14" s="36" t="s">
+        <v>282</v>
       </c>
       <c r="E14" s="13" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="F14" s="20"/>
       <c r="G14" s="10"/>
     </row>
-    <row r="15" spans="1:9" ht="54">
+    <row r="15" spans="1:9" ht="65">
       <c r="A15" s="4" t="s">
         <v>14</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C15" s="17" t="s">
         <v>60</v>
       </c>
       <c r="E15" s="13" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="F15" s="20"/>
     </row>
-    <row r="16" spans="1:9" ht="54">
+    <row r="16" spans="1:9" ht="65">
       <c r="A16" s="4" t="s">
         <v>15</v>
       </c>
       <c r="B16" s="11" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="C16" s="5" t="s">
         <v>61</v>
       </c>
       <c r="E16" s="13" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="F16" s="20"/>
     </row>
-    <row r="17" spans="1:6" ht="94.5">
+    <row r="17" spans="1:6" ht="91">
       <c r="A17" s="4" t="s">
         <v>16</v>
       </c>
       <c r="B17" s="11" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="C17" s="18" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="E17" s="13" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="F17" s="20"/>
     </row>
-    <row r="18" spans="1:6" ht="54">
+    <row r="18" spans="1:6" ht="65">
       <c r="A18" s="4" t="s">
         <v>17</v>
       </c>
       <c r="B18" s="11" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C18" s="5" t="s">
         <v>62</v>
       </c>
       <c r="E18" s="12" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="F18" s="20"/>
     </row>
-    <row r="19" spans="1:6" ht="67.5">
+    <row r="19" spans="1:6" ht="65">
       <c r="A19" s="4" t="s">
         <v>18</v>
       </c>
       <c r="B19" s="11" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C19" s="17" t="s">
         <v>63</v>
@@ -5214,77 +5515,77 @@
       <c r="E19" s="13"/>
       <c r="F19" s="20"/>
     </row>
-    <row r="20" spans="1:6" ht="81">
+    <row r="20" spans="1:6" ht="91">
       <c r="A20" s="4" t="s">
         <v>19</v>
       </c>
       <c r="B20" s="11" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C20" s="5" t="s">
         <v>64</v>
       </c>
       <c r="E20" s="13" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="F20" s="20"/>
     </row>
-    <row r="21" spans="1:6" ht="175.5">
+    <row r="21" spans="1:6" ht="169">
       <c r="A21" s="4" t="s">
         <v>20</v>
       </c>
       <c r="B21" s="23" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="C21" s="18" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="E21" s="13" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" ht="27">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" ht="26">
       <c r="A22" s="4" t="s">
         <v>21</v>
       </c>
       <c r="B22" s="11" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C22" s="5" t="s">
         <v>65</v>
       </c>
       <c r="E22" s="12" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="F22" s="20"/>
     </row>
-    <row r="23" spans="1:6" ht="54">
+    <row r="23" spans="1:6" ht="52">
       <c r="A23" s="4" t="s">
         <v>22</v>
       </c>
       <c r="B23" s="11" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C23" s="17" t="s">
         <v>66</v>
       </c>
       <c r="E23" s="13" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="F23" s="20"/>
     </row>
-    <row r="24" spans="1:6" ht="54">
+    <row r="24" spans="1:6" ht="52">
       <c r="A24" s="4" t="s">
         <v>23</v>
       </c>
       <c r="B24" s="11" t="s">
-        <v>112</v>
-      </c>
-      <c r="C24" s="5" t="s">
-        <v>67</v>
+        <v>110</v>
+      </c>
+      <c r="C24" s="18" t="s">
+        <v>283</v>
       </c>
       <c r="E24" s="12" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="F24" s="20"/>
     </row>
@@ -5293,80 +5594,80 @@
         <v>24</v>
       </c>
       <c r="B25" s="19" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C25" s="17"/>
       <c r="E25" s="12"/>
       <c r="F25" s="20"/>
     </row>
-    <row r="26" spans="1:6" ht="54">
+    <row r="26" spans="1:6" ht="52">
       <c r="A26" s="4" t="s">
         <v>25</v>
       </c>
       <c r="B26" s="11" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E26" s="13"/>
       <c r="F26" s="20"/>
     </row>
-    <row r="27" spans="1:6" ht="135">
+    <row r="27" spans="1:6" ht="130">
       <c r="A27" s="4" t="s">
         <v>26</v>
       </c>
       <c r="B27" s="11" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="C27" s="30" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="E27" s="13"/>
       <c r="F27" s="14"/>
     </row>
-    <row r="28" spans="1:6" ht="108">
+    <row r="28" spans="1:6" ht="104">
       <c r="A28" s="4" t="s">
         <v>27</v>
       </c>
       <c r="B28" s="11" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E28" s="13" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="F28" s="20"/>
     </row>
-    <row r="29" spans="1:6" ht="54">
+    <row r="29" spans="1:6" ht="52">
       <c r="A29" s="4" t="s">
         <v>28</v>
       </c>
       <c r="B29" s="11" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E29" s="13" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="F29" s="20"/>
     </row>
-    <row r="30" spans="1:6" ht="54">
+    <row r="30" spans="1:6" ht="52">
       <c r="A30" s="4" t="s">
         <v>29</v>
       </c>
       <c r="B30" s="11" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E30" s="12" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="F30" s="20"/>
     </row>
@@ -5375,418 +5676,418 @@
         <v>30</v>
       </c>
       <c r="B31" s="11" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C31" s="5"/>
       <c r="E31" s="22"/>
       <c r="F31" s="20"/>
     </row>
-    <row r="32" spans="1:6" ht="54">
+    <row r="32" spans="1:6" ht="52">
       <c r="A32" s="4" t="s">
         <v>31</v>
       </c>
       <c r="B32" s="11" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E32" s="13" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="F32" s="20"/>
     </row>
-    <row r="33" spans="1:9" ht="67.5">
+    <row r="33" spans="1:9" ht="65">
       <c r="A33" s="4" t="s">
         <v>32</v>
       </c>
       <c r="B33" s="11" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E33" s="12" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="F33" s="13"/>
       <c r="I33" s="6"/>
     </row>
-    <row r="34" spans="1:9" ht="54">
+    <row r="34" spans="1:9" ht="52">
       <c r="A34" s="4" t="s">
         <v>33</v>
       </c>
       <c r="B34" s="11" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E34" s="12" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="F34" s="20"/>
     </row>
-    <row r="35" spans="1:9" ht="54">
+    <row r="35" spans="1:9" ht="52">
       <c r="A35" s="4" t="s">
         <v>34</v>
       </c>
       <c r="B35" s="11" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E35" s="13"/>
       <c r="F35" s="20"/>
     </row>
-    <row r="36" spans="1:9" ht="54">
+    <row r="36" spans="1:9" ht="52">
       <c r="A36" s="4" t="s">
         <v>35</v>
       </c>
       <c r="B36" s="11" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E36" s="13" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="F36" s="20"/>
     </row>
-    <row r="37" spans="1:9" ht="67.5">
+    <row r="37" spans="1:9" ht="65">
       <c r="A37" s="4" t="s">
         <v>36</v>
       </c>
       <c r="B37" s="11" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E37" s="13" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="F37" s="20"/>
     </row>
-    <row r="38" spans="1:9" ht="54">
+    <row r="38" spans="1:9" ht="65">
       <c r="A38" s="4" t="s">
         <v>37</v>
       </c>
       <c r="B38" s="11" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E38" s="13" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="F38" s="20"/>
     </row>
-    <row r="39" spans="1:9" ht="84">
+    <row r="39" spans="1:9" ht="81">
       <c r="A39" s="4" t="s">
         <v>38</v>
       </c>
       <c r="B39" s="11" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E39" s="13" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="F39" s="14"/>
     </row>
-    <row r="40" spans="1:9" ht="67.5">
+    <row r="40" spans="1:9" ht="78">
       <c r="A40" s="4" t="s">
         <v>39</v>
       </c>
       <c r="B40" s="11" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E40" s="13"/>
       <c r="F40" s="15"/>
     </row>
-    <row r="41" spans="1:9" ht="67.5">
+    <row r="41" spans="1:9" ht="65">
       <c r="A41" s="4" t="s">
         <v>40</v>
       </c>
       <c r="B41" s="11" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E41" s="13"/>
       <c r="F41" s="13"/>
     </row>
-    <row r="42" spans="1:9" ht="54">
+    <row r="42" spans="1:9" ht="65">
       <c r="A42" s="4" t="s">
         <v>41</v>
       </c>
       <c r="B42" s="11" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E42" s="13"/>
       <c r="F42" s="13"/>
     </row>
-    <row r="43" spans="1:9" ht="27">
+    <row r="43" spans="1:9" ht="26">
       <c r="A43" s="4" t="s">
         <v>42</v>
       </c>
       <c r="B43" s="11" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C43" s="5"/>
       <c r="E43" s="13"/>
       <c r="F43" s="13"/>
     </row>
-    <row r="44" spans="1:9" ht="67.5">
+    <row r="44" spans="1:9" ht="65">
       <c r="A44" s="4" t="s">
         <v>43</v>
       </c>
       <c r="B44" s="11" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E44" s="13" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="F44" s="13"/>
     </row>
-    <row r="45" spans="1:9" ht="69">
+    <row r="45" spans="1:9" ht="78">
       <c r="A45" s="4" t="s">
         <v>44</v>
       </c>
       <c r="B45" s="11" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="C45" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E45" s="13" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="F45" s="13"/>
     </row>
-    <row r="46" spans="1:9" ht="67.5">
+    <row r="46" spans="1:9" ht="65">
       <c r="A46" s="4" t="s">
         <v>45</v>
       </c>
       <c r="B46" s="11" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="C46" s="17" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E46" s="13" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="F46" s="13"/>
     </row>
-    <row r="47" spans="1:9" ht="27">
+    <row r="47" spans="1:9" ht="26">
       <c r="A47" s="4" t="s">
         <v>46</v>
       </c>
       <c r="B47" s="11" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="C47" s="5"/>
       <c r="E47" s="22"/>
       <c r="F47" s="13"/>
     </row>
-    <row r="48" spans="1:9" ht="27">
+    <row r="48" spans="1:9" ht="26">
       <c r="A48" s="4" t="s">
         <v>47</v>
       </c>
       <c r="B48" s="11" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="C48" s="5"/>
       <c r="E48" s="22"/>
       <c r="F48" s="13"/>
     </row>
-    <row r="49" spans="1:6" ht="54">
+    <row r="49" spans="1:6" ht="52">
       <c r="A49" s="4" t="s">
         <v>48</v>
       </c>
       <c r="B49" s="11" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E49" s="13"/>
       <c r="F49" s="13"/>
     </row>
-    <row r="50" spans="1:6" ht="54">
+    <row r="50" spans="1:6" ht="52">
       <c r="A50" s="4" t="s">
         <v>49</v>
       </c>
       <c r="B50" s="11" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="C50" s="5" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E50" s="13" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="F50" s="13"/>
     </row>
-    <row r="51" spans="1:6" ht="67.5">
+    <row r="51" spans="1:6" ht="65">
       <c r="A51" s="4" t="s">
         <v>50</v>
       </c>
       <c r="B51" s="11" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="C51" s="5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E51" s="13" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="F51" s="13"/>
     </row>
-    <row r="52" spans="1:6" ht="67.5">
+    <row r="52" spans="1:6" ht="65">
       <c r="A52" s="4" t="s">
         <v>51</v>
       </c>
       <c r="B52" s="11" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="C52" s="5" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E52" s="13" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="F52" s="13"/>
     </row>
-    <row r="53" spans="1:6" ht="94.5">
+    <row r="53" spans="1:6" ht="91">
       <c r="A53" s="4"/>
       <c r="B53" s="11" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="C53" s="5" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E53" s="12" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="F53" s="13"/>
     </row>
     <row r="54" spans="1:6">
       <c r="A54" s="4"/>
       <c r="B54" s="11" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="C54" s="27"/>
       <c r="E54" s="13"/>
       <c r="F54" s="13"/>
     </row>
-    <row r="55" spans="1:6" ht="27">
+    <row r="55" spans="1:6" ht="26">
       <c r="A55" s="4"/>
       <c r="B55" s="11" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="C55" s="5"/>
       <c r="E55" s="13" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="F55" s="13"/>
     </row>
     <row r="56" spans="1:6">
       <c r="A56" s="4"/>
       <c r="B56" s="11" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="C56" s="5"/>
       <c r="E56" s="13" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="F56" s="13"/>
     </row>
-    <row r="57" spans="1:6" ht="40.5">
+    <row r="57" spans="1:6" ht="39">
       <c r="A57" s="4"/>
       <c r="B57" s="11" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="C57" s="5"/>
       <c r="E57" s="13" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="F57" s="13"/>
     </row>
-    <row r="58" spans="1:6" ht="40.5">
+    <row r="58" spans="1:6" ht="39">
       <c r="A58" s="4"/>
       <c r="B58" s="11" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="C58" s="5"/>
       <c r="E58" s="12" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="F58" s="13"/>
     </row>
-    <row r="59" spans="1:6" ht="54">
+    <row r="59" spans="1:6" ht="52">
       <c r="A59" s="4"/>
       <c r="B59" s="11" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C59" s="5" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E59" s="13"/>
       <c r="F59" s="13"/>
     </row>
-    <row r="60" spans="1:6" ht="54">
+    <row r="60" spans="1:6" ht="65">
       <c r="A60" s="4"/>
       <c r="B60" s="11" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="C60" s="5" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E60" s="12" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="F60" s="13"/>
     </row>
-    <row r="61" spans="1:6" ht="27">
+    <row r="61" spans="1:6" ht="39">
       <c r="A61" s="4" t="s">
         <v>52</v>
       </c>
       <c r="B61" s="11" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="C61" s="5"/>
       <c r="E61" s="13" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="62" spans="1:6" ht="40.5">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" ht="39">
       <c r="A62" s="4" t="s">
         <v>53</v>
       </c>
       <c r="B62" s="11" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="C62" s="5"/>
       <c r="E62" s="13" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
     </row>
   </sheetData>
@@ -5798,27 +6099,42 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C945A8A3-E413-4358-BBE4-EF5A44242598}">
-  <dimension ref="A1:A4"/>
-  <sheetFormatPr defaultRowHeight="13.5"/>
+  <dimension ref="A1:A12"/>
+  <sheetFormatPr defaultRowHeight="13"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="34" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
     </row>
     <row r="2" spans="1:1">
       <c r="A2" s="34" t="s">
-        <v>263</v>
+        <v>258</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="34" t="s">
-        <v>264</v>
+        <v>259</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" s="34" t="s">
-        <v>265</v>
+        <v>260</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1">
+      <c r="A6" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1">
+      <c r="A9" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1">
+      <c r="A12" t="s">
+        <v>279</v>
       </c>
     </row>
   </sheetData>
@@ -5830,10 +6146,10 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:B21"/>
-  <sheetFormatPr defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultRowHeight="13"/>
   <cols>
-    <col min="1" max="1" width="150.375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="103.375" customWidth="1"/>
+    <col min="1" max="1" width="150.36328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="103.36328125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
@@ -5842,125 +6158,125 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="24" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="B2" s="24"/>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="24" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="B3" s="24"/>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="24" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="B4" s="24"/>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="24" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="B5" s="24"/>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="24" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="B6" s="24"/>
     </row>
-    <row r="7" spans="1:2" ht="54">
+    <row r="7" spans="1:2" ht="52">
       <c r="A7" s="24" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="B7" s="23" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="24" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="B8" s="24"/>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="24" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="B9" s="24"/>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="24" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="B10" s="24"/>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="24" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="B11" s="24"/>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="24" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="B12" s="24"/>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="24" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="B13" s="24"/>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="24" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="B14" s="24"/>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="24" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="B15" s="24"/>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="24" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="B16" s="24"/>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="24" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="B17" s="24"/>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="24" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="B18" s="24"/>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="24" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="B19" s="24"/>
     </row>
-    <row r="20" spans="1:2" ht="67.5">
+    <row r="20" spans="1:2" ht="65">
       <c r="A20" s="24" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="B20" s="23" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="24" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="B21" s="24"/>
     </row>
@@ -5973,98 +6289,98 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:B11"/>
-  <sheetFormatPr defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultRowHeight="13"/>
   <cols>
-    <col min="1" max="1" width="69.625" customWidth="1"/>
-    <col min="2" max="2" width="66.375" customWidth="1"/>
+    <col min="1" max="1" width="69.6328125" customWidth="1"/>
+    <col min="2" max="2" width="66.36328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="60">
+    <row r="1" spans="1:2" ht="58">
       <c r="A1" s="31" t="s">
+        <v>228</v>
+      </c>
+      <c r="B1" s="32" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" ht="55" customHeight="1">
+      <c r="A2" s="31" t="s">
+        <v>229</v>
+      </c>
+      <c r="B2" s="32" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="55" customHeight="1">
+      <c r="A3" s="31" t="s">
+        <v>230</v>
+      </c>
+      <c r="B3" s="32" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="87">
+      <c r="A4" s="31" t="s">
         <v>231</v>
       </c>
-      <c r="B1" s="32" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" ht="54.95" customHeight="1">
-      <c r="A2" s="31" t="s">
+      <c r="B4" s="32" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" ht="55" customHeight="1">
+      <c r="A5" s="31" t="s">
         <v>232</v>
       </c>
-      <c r="B2" s="32" t="s">
+      <c r="B5" s="32" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" ht="55" customHeight="1">
+      <c r="A6" s="31" t="s">
+        <v>233</v>
+      </c>
+      <c r="B6" s="32" t="s">
         <v>242</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="54.95" customHeight="1">
-      <c r="A3" s="31" t="s">
-        <v>233</v>
-      </c>
-      <c r="B3" s="32" t="s">
+    <row r="7" spans="1:2" ht="58">
+      <c r="A7" s="31" t="s">
+        <v>234</v>
+      </c>
+      <c r="B7" s="32" t="s">
         <v>243</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="90">
-      <c r="A4" s="31" t="s">
-        <v>234</v>
-      </c>
-      <c r="B4" s="32" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" ht="54.95" customHeight="1">
-      <c r="A5" s="31" t="s">
+    <row r="8" spans="1:2" ht="58">
+      <c r="A8" s="31" t="s">
         <v>235</v>
       </c>
-      <c r="B5" s="32" t="s">
+      <c r="B8" s="32" t="s">
         <v>244</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="54.95" customHeight="1">
-      <c r="A6" s="31" t="s">
+    <row r="9" spans="1:2" ht="55" customHeight="1">
+      <c r="A9" s="31" t="s">
         <v>236</v>
       </c>
-      <c r="B6" s="32" t="s">
+      <c r="B9" s="32" t="s">
         <v>245</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="60">
-      <c r="A7" s="31" t="s">
+    <row r="10" spans="1:2" ht="55" customHeight="1">
+      <c r="A10" s="31" t="s">
         <v>237</v>
       </c>
-      <c r="B7" s="32" t="s">
+      <c r="B10" s="32" t="s">
         <v>246</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="60">
-      <c r="A8" s="31" t="s">
+    <row r="11" spans="1:2" ht="55" customHeight="1">
+      <c r="A11" s="31" t="s">
         <v>238</v>
       </c>
-      <c r="B8" s="32" t="s">
+      <c r="B11" s="32" t="s">
         <v>247</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" ht="54.95" customHeight="1">
-      <c r="A9" s="31" t="s">
-        <v>239</v>
-      </c>
-      <c r="B9" s="32" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" ht="54.95" customHeight="1">
-      <c r="A10" s="31" t="s">
-        <v>240</v>
-      </c>
-      <c r="B10" s="32" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" ht="54.95" customHeight="1">
-      <c r="A11" s="31" t="s">
-        <v>241</v>
-      </c>
-      <c r="B11" s="32" t="s">
-        <v>250</v>
       </c>
     </row>
   </sheetData>
@@ -6076,10 +6392,10 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{05FA0C31-4B39-4CC9-AFFE-ADB97979182D}">
   <dimension ref="A1:B21"/>
-  <sheetFormatPr defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultRowHeight="13"/>
   <cols>
-    <col min="1" max="1" width="150.375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="103.375" customWidth="1"/>
+    <col min="1" max="1" width="150.36328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="103.36328125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
@@ -6088,42 +6404,42 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="24" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="B2" s="24"/>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="33" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="B3" s="24"/>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="33" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="B4" s="24"/>
     </row>
-    <row r="5" spans="1:2" ht="67.5">
+    <row r="5" spans="1:2" ht="65">
       <c r="A5" s="33" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="B5" s="23" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="33" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="B6" s="24"/>
     </row>
-    <row r="7" spans="1:2" ht="54">
+    <row r="7" spans="1:2" ht="52">
       <c r="A7" s="33" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="B7" s="23" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -6174,10 +6490,10 @@
       <c r="A19" s="24"/>
       <c r="B19" s="24"/>
     </row>
-    <row r="20" spans="1:2" ht="67.5">
+    <row r="20" spans="1:2" ht="65">
       <c r="A20" s="24"/>
       <c r="B20" s="23" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -6188,4 +6504,152 @@
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E3B1E147-F943-43CF-88AE-86DE70DEEA3B}">
+  <dimension ref="A1:B21"/>
+  <sheetFormatPr defaultRowHeight="13"/>
+  <cols>
+    <col min="1" max="1" width="150.36328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="103.36328125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" s="24"/>
+      <c r="B1" s="24"/>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" s="24" t="s">
+        <v>151</v>
+      </c>
+      <c r="B2" s="24"/>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" s="33" t="s">
+        <v>254</v>
+      </c>
+      <c r="B3" s="24"/>
+    </row>
+    <row r="4" spans="1:2" ht="39">
+      <c r="A4" s="33" t="s">
+        <v>261</v>
+      </c>
+      <c r="B4" s="23" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" ht="65">
+      <c r="A5" s="33" t="s">
+        <v>262</v>
+      </c>
+      <c r="B5" s="23" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" s="33" t="s">
+        <v>263</v>
+      </c>
+      <c r="B6" s="24"/>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" s="33" t="s">
+        <v>264</v>
+      </c>
+      <c r="B7" s="23"/>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" s="35" t="s">
+        <v>265</v>
+      </c>
+      <c r="B8" s="33" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" s="33" t="s">
+        <v>267</v>
+      </c>
+      <c r="B9" s="24"/>
+    </row>
+    <row r="10" spans="1:2" ht="39">
+      <c r="A10" s="33" t="s">
+        <v>268</v>
+      </c>
+      <c r="B10" s="23" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" s="33" t="s">
+        <v>269</v>
+      </c>
+      <c r="B11" s="24"/>
+    </row>
+    <row r="12" spans="1:2">
+      <c r="A12" s="35" t="s">
+        <v>270</v>
+      </c>
+      <c r="B12" s="24"/>
+    </row>
+    <row r="13" spans="1:2">
+      <c r="A13" s="33" t="s">
+        <v>271</v>
+      </c>
+      <c r="B13" s="24"/>
+    </row>
+    <row r="14" spans="1:2">
+      <c r="A14" s="33" t="s">
+        <v>272</v>
+      </c>
+      <c r="B14" s="24"/>
+    </row>
+    <row r="15" spans="1:2">
+      <c r="A15" s="33" t="s">
+        <v>273</v>
+      </c>
+      <c r="B15" s="24"/>
+    </row>
+    <row r="16" spans="1:2">
+      <c r="A16" s="24"/>
+      <c r="B16" s="24"/>
+    </row>
+    <row r="17" spans="1:2">
+      <c r="A17" s="24"/>
+      <c r="B17" s="24"/>
+    </row>
+    <row r="18" spans="1:2">
+      <c r="A18" s="24"/>
+      <c r="B18" s="24"/>
+    </row>
+    <row r="19" spans="1:2">
+      <c r="A19" s="24"/>
+      <c r="B19" s="24"/>
+    </row>
+    <row r="20" spans="1:2" ht="65">
+      <c r="A20" s="24"/>
+      <c r="B20" s="23" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2">
+      <c r="A21" s="24"/>
+      <c r="B21" s="24"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4E6BF410-1D86-4886-AF32-D2372AA65DBD}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="13"/>
+  <sheetData/>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/作業/面接練習/G3面接準備中岫.xlsx
+++ b/作業/面接練習/G3面接準備中岫.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/df213c2b7ba35e42/デスクトップ/試験/G3/作業/面接練習/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aaa115298\Desktop\G3\G3\G3試験中岫作業\G3\作業\面接練習\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="41" documentId="13_ncr:1_{333FA04E-09A4-4151-BA94-35BCDFE120B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1C8459F0-4D71-4D82-83A7-77FB30CC7EC0}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2AEB519A-D76D-4323-8D4C-B1056013937A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -4341,35 +4341,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>課の構成は管理職2名、主任5名、G3、〇一般職〇名です。私たちのチームには、大きく二つのテーマがあります。一つはスジムラの発生メカニズムの解明、もう一つはMogamiの用紙対応力の向上です。
-ソフトウェア33開発室では、主に商業印刷機を対象に、測定・解析技術やAIを活用して、画質、安定性、用紙対応力を向上させる技術開発を行っています。具体的には、電子写真方式とインクジェット方式の両方について、画質劣化の原因を分析し、製品設計や画質改善につなげるプロジェクトに取り組んでいます。</t>
-    <rPh sb="0" eb="1">
-      <t>カ</t>
-    </rPh>
-    <rPh sb="2" eb="4">
-      <t>コウセイ</t>
-    </rPh>
-    <rPh sb="5" eb="8">
-      <t>カンリショク</t>
-    </rPh>
-    <rPh sb="9" eb="10">
-      <t>メイ</t>
-    </rPh>
-    <rPh sb="11" eb="13">
-      <t>シュニン</t>
-    </rPh>
-    <rPh sb="14" eb="15">
-      <t>メイ</t>
-    </rPh>
-    <rPh sb="20" eb="23">
-      <t>イッパンショク</t>
-    </rPh>
-    <rPh sb="24" eb="25">
-      <t>メイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>協力することで心がけていること</t>
     <rPh sb="0" eb="2">
       <t>キョウリョク</t>
@@ -4557,17 +4528,6 @@
     <t>本日はよろしくお願いいたします。</t>
   </si>
   <si>
-    <t>デジタルビジネスプラットフォーム開発本部、ソフトウェア33開発室の中岫茉希と申します。
-私は、画質定量化技術を軸に、プリンティング製品の開発を支援する技術開発に取り組んでいます。画像の画質を定量的に評価・解析することで、画質の変化や劣化の原因を明らかにし、製品の品質向上につなげることを目指しています。
-直近では、デジタルプリンティング事業本部と連携し、商業印刷機Mogamiの画質向上に向けた技術開発を担当しています。画質劣化の原因を解析し、その結果を設計にフィードバックすることで、画質改善に向けた設計の効率化を目指しています。
-本日はよろしくお願いいたします。</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>課の年頭方針は測定解析とAIの両軸に基づいた画質・安定性・メディア対応力向上技術の開発生産性を向上し、プリンティング事業拡大に貢献</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>課の課題は、個別製品や担当者ごとに得られた知見が分散し、横展開しにくいことです。Mogamiで得た紙特性、評価結果、対応条件を共通の観点で整理し、他テーマ（IJにかかわらず電子写真）でも検索・再利用できる形にすることで、検討の重複を減らし開発速度を上げたいと考えています。
 IJ、電子写真同じような画質弊害が発生することがある。その場合、メカニズムの解析では両者のメンバーで、議論を行い効率的に得られるようにしている。</t>
     <rPh sb="49" eb="50">
@@ -4628,6 +4588,89 @@
     <rPh sb="28" eb="29">
       <t>スス</t>
     </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t xml:space="preserve">[本部]技術の質を徹底的に向上することにより、事業の技術開発をリードし、DBPを次のステージに進化させる
+[センター]AI Inside / Powered / Driven実現へ徹底的に貢献する
+「事業の力を引き出す事業支援」で、点の事業支援から線・面の支援に進化する
+本部横断の連携で他本部も巻き込み、「やれる範囲」を広げ、「やるべきこと」を増やして実行する
+[部]画質定量化技術をコアとした技術支援により、製品設計における画質課題の開発下流への流出を抑止することで、製品開発の生産性向上に貢献する。
+[課]測定解析とAIの両軸に基づいた画質・安定性・メディア対応力向上技術の開発生産性を向上し、プリンティング事業拡大に貢献
+</t>
+    <rPh sb="1" eb="3">
+      <t>ホンブ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>課の構成は管理職2名、主任5名、G3、〇一般職〇名です。私たちのチームには、大きく二つのテーマがあります。一つはスジムラの発生メカニズムの解明、もう一つはMogamiの用紙対応力の向上です。
+ソフトウェア33開発室では、主に商業印刷機を対象に、測定・解析技術やAIを活用して、画質、安定性、用紙対応力を向上させる技術開発を行っています。具体的には、電子写真方式とインクジェット方式の両方について、画質劣化の原因を分析し、製品設計や画質改善につなげるプロジェクトに取り組んでいます。
+私は商業IJ印刷機Mogamiの用紙対応力向上のテーマに所属し、主にプライマに関する検討を行っています。プライマは画質を向上させるために打つ透明インクで、打つ量によって画質を低下させたりします。私の役割は、文献調査や評価用チャートの分析を通じて、プライマが画質に与える影響や技術課題を整理し、その後の開発をどのような方針で進めるかを先行して検討することです。また、検討結果を基に、プライマ量を決定する評価フローの再構築にも取り組みました。</t>
+    <rPh sb="0" eb="1">
+      <t>カ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>コウセイ</t>
+    </rPh>
+    <rPh sb="5" eb="8">
+      <t>カンリショク</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>メイ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>シュニン</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>メイ</t>
+    </rPh>
+    <rPh sb="20" eb="23">
+      <t>イッパンショク</t>
+    </rPh>
+    <rPh sb="24" eb="25">
+      <t>メイ</t>
+    </rPh>
+    <rPh sb="245" eb="247">
+      <t>ショウギョウ</t>
+    </rPh>
+    <rPh sb="249" eb="251">
+      <t>インサツ</t>
+    </rPh>
+    <rPh sb="300" eb="302">
+      <t>ガシツ</t>
+    </rPh>
+    <rPh sb="303" eb="305">
+      <t>コウジョウ</t>
+    </rPh>
+    <rPh sb="311" eb="312">
+      <t>ウ</t>
+    </rPh>
+    <rPh sb="313" eb="315">
+      <t>トウメイ</t>
+    </rPh>
+    <rPh sb="320" eb="321">
+      <t>ウ</t>
+    </rPh>
+    <rPh sb="322" eb="323">
+      <t>リョウ</t>
+    </rPh>
+    <rPh sb="327" eb="329">
+      <t>ガシツ</t>
+    </rPh>
+    <rPh sb="330" eb="332">
+      <t>テイカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>デジタルビジネスプラットフォーム開発本部、ソフトウェア33開発室の中岫茉希と申します。
+私の所属する部門では、プリンタを高画質化するための、物理現象の解析を行っています。
+その中で私は、商業印刷向けのインクジェットプリンタを対象に、「プライマー」と呼ばれる透明なインクと画質との関係の解析を担当しています。
+このプライマーというのは、商業インクジェットプリンタで多種多様な用紙に対応するために、紙に下塗りするものです。
+このとき、プライマーの最適な量は、紙の種類やカラーインクの量によっても異なるため、設計の組み合わせが膨大になってしまいます。
+そこで、プライマーの量と画質との関係を解析することで、最小の評価工数でプライマー量を設計する手法を、デジプリ事業本部と連携して開発し、設計効率の向上に取り組んでいます。
+本日はよろしくお願いいたします。</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -5193,21 +5236,21 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:I62"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18.75"/>
   <cols>
-    <col min="1" max="1" width="10.6328125" style="2" customWidth="1"/>
-    <col min="2" max="2" width="50.36328125" style="1" customWidth="1"/>
-    <col min="3" max="3" width="52" customWidth="1"/>
+    <col min="1" max="1" width="10.625" style="2" customWidth="1"/>
+    <col min="2" max="2" width="50.375" style="1" customWidth="1"/>
+    <col min="3" max="3" width="107.125" customWidth="1"/>
     <col min="4" max="4" width="52" style="25" customWidth="1"/>
-    <col min="5" max="5" width="119.08984375" style="6" customWidth="1"/>
-    <col min="6" max="6" width="116.90625" style="6" customWidth="1"/>
-    <col min="7" max="7" width="35.90625" style="3" customWidth="1"/>
-    <col min="8" max="8" width="64.26953125" style="3" customWidth="1"/>
-    <col min="9" max="9" width="111.6328125" style="3" customWidth="1"/>
+    <col min="5" max="5" width="119.125" style="6" customWidth="1"/>
+    <col min="6" max="6" width="116.875" style="6" customWidth="1"/>
+    <col min="7" max="7" width="35.875" style="3" customWidth="1"/>
+    <col min="8" max="8" width="64.25" style="3" customWidth="1"/>
+    <col min="9" max="9" width="111.625" style="3" customWidth="1"/>
     <col min="10" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="13">
+    <row r="1" spans="1:9" ht="13.5">
       <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
@@ -5234,7 +5277,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="270">
+    <row r="2" spans="1:9" ht="262.5">
       <c r="A2" s="4">
         <v>0</v>
       </c>
@@ -5242,7 +5285,7 @@
         <v>180</v>
       </c>
       <c r="C2" s="18" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="D2" s="25" t="s">
         <v>172</v>
@@ -5260,7 +5303,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="409.5">
+    <row r="3" spans="1:9" ht="391.5">
       <c r="A3" s="28"/>
       <c r="B3" s="23" t="s">
         <v>181</v>
@@ -5271,7 +5314,7 @@
       <c r="E3" s="26"/>
       <c r="F3" s="20"/>
     </row>
-    <row r="4" spans="1:9" ht="252">
+    <row r="4" spans="1:9" ht="262.5">
       <c r="A4" s="4">
         <v>1</v>
       </c>
@@ -5279,7 +5322,7 @@
         <v>92</v>
       </c>
       <c r="C4" s="18" t="s">
-        <v>266</v>
+        <v>282</v>
       </c>
       <c r="D4" s="25" t="s">
         <v>173</v>
@@ -5292,7 +5335,7 @@
       </c>
       <c r="G4" s="6"/>
     </row>
-    <row r="5" spans="1:9" ht="78">
+    <row r="5" spans="1:9" ht="81">
       <c r="A5" s="4" t="s">
         <v>7</v>
       </c>
@@ -5307,7 +5350,7 @@
       </c>
       <c r="F5" s="20"/>
     </row>
-    <row r="6" spans="1:9" ht="91">
+    <row r="6" spans="1:9" ht="94.5">
       <c r="A6" s="4" t="s">
         <v>8</v>
       </c>
@@ -5322,7 +5365,7 @@
       </c>
       <c r="F6" s="13"/>
     </row>
-    <row r="7" spans="1:9" ht="78.75" customHeight="1">
+    <row r="7" spans="1:9" ht="121.5">
       <c r="A7" s="4" t="s">
         <v>9</v>
       </c>
@@ -5338,7 +5381,7 @@
       <c r="F7" s="14"/>
       <c r="I7" s="6"/>
     </row>
-    <row r="8" spans="1:9" ht="91">
+    <row r="8" spans="1:9" ht="54">
       <c r="A8" s="4" t="s">
         <v>10</v>
       </c>
@@ -5353,7 +5396,7 @@
       </c>
       <c r="F8" s="14"/>
     </row>
-    <row r="9" spans="1:9" ht="104">
+    <row r="9" spans="1:9" ht="108">
       <c r="A9" s="4">
         <v>2</v>
       </c>
@@ -5368,7 +5411,7 @@
       </c>
       <c r="F9" s="20"/>
     </row>
-    <row r="10" spans="1:9" ht="169">
+    <row r="10" spans="1:9" ht="108">
       <c r="A10" s="4">
         <v>3</v>
       </c>
@@ -5383,7 +5426,7 @@
       </c>
       <c r="F10" s="20"/>
     </row>
-    <row r="11" spans="1:9" ht="65">
+    <row r="11" spans="1:9" ht="40.5">
       <c r="A11" s="4" t="s">
         <v>11</v>
       </c>
@@ -5398,7 +5441,7 @@
       </c>
       <c r="F11" s="14"/>
     </row>
-    <row r="12" spans="1:9" ht="91">
+    <row r="12" spans="1:9" ht="67.5">
       <c r="A12" s="4" t="s">
         <v>12</v>
       </c>
@@ -5413,7 +5456,7 @@
       </c>
       <c r="F12" s="14"/>
     </row>
-    <row r="13" spans="1:9" ht="52">
+    <row r="13" spans="1:9" ht="27">
       <c r="A13" s="4" t="s">
         <v>13</v>
       </c>
@@ -5426,7 +5469,7 @@
       <c r="E13" s="13"/>
       <c r="F13" s="14"/>
     </row>
-    <row r="14" spans="1:9" ht="143">
+    <row r="14" spans="1:9" ht="135">
       <c r="A14" s="4">
         <v>4</v>
       </c>
@@ -5434,7 +5477,7 @@
         <v>101</v>
       </c>
       <c r="C14" s="36" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="E14" s="13" t="s">
         <v>192</v>
@@ -5442,7 +5485,7 @@
       <c r="F14" s="20"/>
       <c r="G14" s="10"/>
     </row>
-    <row r="15" spans="1:9" ht="65">
+    <row r="15" spans="1:9" ht="27">
       <c r="A15" s="4" t="s">
         <v>14</v>
       </c>
@@ -5457,7 +5500,7 @@
       </c>
       <c r="F15" s="20"/>
     </row>
-    <row r="16" spans="1:9" ht="65">
+    <row r="16" spans="1:9" ht="40.5">
       <c r="A16" s="4" t="s">
         <v>15</v>
       </c>
@@ -5472,7 +5515,7 @@
       </c>
       <c r="F16" s="20"/>
     </row>
-    <row r="17" spans="1:6" ht="91">
+    <row r="17" spans="1:6" ht="94.5">
       <c r="A17" s="4" t="s">
         <v>16</v>
       </c>
@@ -5487,7 +5530,7 @@
       </c>
       <c r="F17" s="20"/>
     </row>
-    <row r="18" spans="1:6" ht="65">
+    <row r="18" spans="1:6" ht="27">
       <c r="A18" s="4" t="s">
         <v>17</v>
       </c>
@@ -5502,7 +5545,7 @@
       </c>
       <c r="F18" s="20"/>
     </row>
-    <row r="19" spans="1:6" ht="65">
+    <row r="19" spans="1:6" ht="40.5">
       <c r="A19" s="4" t="s">
         <v>18</v>
       </c>
@@ -5515,7 +5558,7 @@
       <c r="E19" s="13"/>
       <c r="F19" s="20"/>
     </row>
-    <row r="20" spans="1:6" ht="91">
+    <row r="20" spans="1:6" ht="81">
       <c r="A20" s="4" t="s">
         <v>19</v>
       </c>
@@ -5530,7 +5573,7 @@
       </c>
       <c r="F20" s="20"/>
     </row>
-    <row r="21" spans="1:6" ht="169">
+    <row r="21" spans="1:6" ht="108">
       <c r="A21" s="4" t="s">
         <v>20</v>
       </c>
@@ -5544,7 +5587,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="22" spans="1:6" ht="26">
+    <row r="22" spans="1:6">
       <c r="A22" s="4" t="s">
         <v>21</v>
       </c>
@@ -5559,7 +5602,7 @@
       </c>
       <c r="F22" s="20"/>
     </row>
-    <row r="23" spans="1:6" ht="52">
+    <row r="23" spans="1:6" ht="54">
       <c r="A23" s="4" t="s">
         <v>22</v>
       </c>
@@ -5574,7 +5617,7 @@
       </c>
       <c r="F23" s="20"/>
     </row>
-    <row r="24" spans="1:6" ht="52">
+    <row r="24" spans="1:6" ht="27">
       <c r="A24" s="4" t="s">
         <v>23</v>
       </c>
@@ -5582,7 +5625,7 @@
         <v>110</v>
       </c>
       <c r="C24" s="18" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="E24" s="12" t="s">
         <v>201</v>
@@ -5600,7 +5643,7 @@
       <c r="E25" s="12"/>
       <c r="F25" s="20"/>
     </row>
-    <row r="26" spans="1:6" ht="52">
+    <row r="26" spans="1:6" ht="27">
       <c r="A26" s="4" t="s">
         <v>25</v>
       </c>
@@ -5613,7 +5656,7 @@
       <c r="E26" s="13"/>
       <c r="F26" s="20"/>
     </row>
-    <row r="27" spans="1:6" ht="130">
+    <row r="27" spans="1:6" ht="81">
       <c r="A27" s="4" t="s">
         <v>26</v>
       </c>
@@ -5626,7 +5669,7 @@
       <c r="E27" s="13"/>
       <c r="F27" s="14"/>
     </row>
-    <row r="28" spans="1:6" ht="104">
+    <row r="28" spans="1:6" ht="108">
       <c r="A28" s="4" t="s">
         <v>27</v>
       </c>
@@ -5641,7 +5684,7 @@
       </c>
       <c r="F28" s="20"/>
     </row>
-    <row r="29" spans="1:6" ht="52">
+    <row r="29" spans="1:6" ht="27">
       <c r="A29" s="4" t="s">
         <v>28</v>
       </c>
@@ -5656,7 +5699,7 @@
       </c>
       <c r="F29" s="20"/>
     </row>
-    <row r="30" spans="1:6" ht="52">
+    <row r="30" spans="1:6" ht="42">
       <c r="A30" s="4" t="s">
         <v>29</v>
       </c>
@@ -5682,7 +5725,7 @@
       <c r="E31" s="22"/>
       <c r="F31" s="20"/>
     </row>
-    <row r="32" spans="1:6" ht="52">
+    <row r="32" spans="1:6" ht="27">
       <c r="A32" s="4" t="s">
         <v>31</v>
       </c>
@@ -5697,7 +5740,7 @@
       </c>
       <c r="F32" s="20"/>
     </row>
-    <row r="33" spans="1:9" ht="65">
+    <row r="33" spans="1:9" ht="40.5">
       <c r="A33" s="4" t="s">
         <v>32</v>
       </c>
@@ -5713,7 +5756,7 @@
       <c r="F33" s="13"/>
       <c r="I33" s="6"/>
     </row>
-    <row r="34" spans="1:9" ht="52">
+    <row r="34" spans="1:9" ht="27">
       <c r="A34" s="4" t="s">
         <v>33</v>
       </c>
@@ -5728,7 +5771,7 @@
       </c>
       <c r="F34" s="20"/>
     </row>
-    <row r="35" spans="1:9" ht="52">
+    <row r="35" spans="1:9" ht="27">
       <c r="A35" s="4" t="s">
         <v>34</v>
       </c>
@@ -5741,7 +5784,7 @@
       <c r="E35" s="13"/>
       <c r="F35" s="20"/>
     </row>
-    <row r="36" spans="1:9" ht="52">
+    <row r="36" spans="1:9" ht="27">
       <c r="A36" s="4" t="s">
         <v>35</v>
       </c>
@@ -5756,7 +5799,7 @@
       </c>
       <c r="F36" s="20"/>
     </row>
-    <row r="37" spans="1:9" ht="65">
+    <row r="37" spans="1:9" ht="54">
       <c r="A37" s="4" t="s">
         <v>36</v>
       </c>
@@ -5771,7 +5814,7 @@
       </c>
       <c r="F37" s="20"/>
     </row>
-    <row r="38" spans="1:9" ht="65">
+    <row r="38" spans="1:9" ht="54">
       <c r="A38" s="4" t="s">
         <v>37</v>
       </c>
@@ -5786,7 +5829,7 @@
       </c>
       <c r="F38" s="20"/>
     </row>
-    <row r="39" spans="1:9" ht="81">
+    <row r="39" spans="1:9" ht="84">
       <c r="A39" s="4" t="s">
         <v>38</v>
       </c>
@@ -5801,7 +5844,7 @@
       </c>
       <c r="F39" s="14"/>
     </row>
-    <row r="40" spans="1:9" ht="78">
+    <row r="40" spans="1:9" ht="40.5">
       <c r="A40" s="4" t="s">
         <v>39</v>
       </c>
@@ -5814,7 +5857,7 @@
       <c r="E40" s="13"/>
       <c r="F40" s="15"/>
     </row>
-    <row r="41" spans="1:9" ht="65">
+    <row r="41" spans="1:9" ht="27">
       <c r="A41" s="4" t="s">
         <v>40</v>
       </c>
@@ -5827,7 +5870,7 @@
       <c r="E41" s="13"/>
       <c r="F41" s="13"/>
     </row>
-    <row r="42" spans="1:9" ht="65">
+    <row r="42" spans="1:9" ht="27">
       <c r="A42" s="4" t="s">
         <v>41</v>
       </c>
@@ -5840,7 +5883,7 @@
       <c r="E42" s="13"/>
       <c r="F42" s="13"/>
     </row>
-    <row r="43" spans="1:9" ht="26">
+    <row r="43" spans="1:9" ht="27">
       <c r="A43" s="4" t="s">
         <v>42</v>
       </c>
@@ -5851,7 +5894,7 @@
       <c r="E43" s="13"/>
       <c r="F43" s="13"/>
     </row>
-    <row r="44" spans="1:9" ht="65">
+    <row r="44" spans="1:9" ht="40.5">
       <c r="A44" s="4" t="s">
         <v>43</v>
       </c>
@@ -5866,7 +5909,7 @@
       </c>
       <c r="F44" s="13"/>
     </row>
-    <row r="45" spans="1:9" ht="78">
+    <row r="45" spans="1:9" ht="69">
       <c r="A45" s="4" t="s">
         <v>44</v>
       </c>
@@ -5881,7 +5924,7 @@
       </c>
       <c r="F45" s="13"/>
     </row>
-    <row r="46" spans="1:9" ht="65">
+    <row r="46" spans="1:9" ht="27">
       <c r="A46" s="4" t="s">
         <v>45</v>
       </c>
@@ -5896,7 +5939,7 @@
       </c>
       <c r="F46" s="13"/>
     </row>
-    <row r="47" spans="1:9" ht="26">
+    <row r="47" spans="1:9" ht="27">
       <c r="A47" s="4" t="s">
         <v>46</v>
       </c>
@@ -5907,7 +5950,7 @@
       <c r="E47" s="22"/>
       <c r="F47" s="13"/>
     </row>
-    <row r="48" spans="1:9" ht="26">
+    <row r="48" spans="1:9" ht="27">
       <c r="A48" s="4" t="s">
         <v>47</v>
       </c>
@@ -5918,7 +5961,7 @@
       <c r="E48" s="22"/>
       <c r="F48" s="13"/>
     </row>
-    <row r="49" spans="1:6" ht="52">
+    <row r="49" spans="1:6" ht="27">
       <c r="A49" s="4" t="s">
         <v>48</v>
       </c>
@@ -5931,7 +5974,7 @@
       <c r="E49" s="13"/>
       <c r="F49" s="13"/>
     </row>
-    <row r="50" spans="1:6" ht="52">
+    <row r="50" spans="1:6" ht="27">
       <c r="A50" s="4" t="s">
         <v>49</v>
       </c>
@@ -5946,7 +5989,7 @@
       </c>
       <c r="F50" s="13"/>
     </row>
-    <row r="51" spans="1:6" ht="65">
+    <row r="51" spans="1:6" ht="42">
       <c r="A51" s="4" t="s">
         <v>50</v>
       </c>
@@ -5961,7 +6004,7 @@
       </c>
       <c r="F51" s="13"/>
     </row>
-    <row r="52" spans="1:6" ht="65">
+    <row r="52" spans="1:6" ht="40.5">
       <c r="A52" s="4" t="s">
         <v>51</v>
       </c>
@@ -5976,7 +6019,7 @@
       </c>
       <c r="F52" s="13"/>
     </row>
-    <row r="53" spans="1:6" ht="91">
+    <row r="53" spans="1:6" ht="94.5">
       <c r="A53" s="4"/>
       <c r="B53" s="11" t="s">
         <v>139</v>
@@ -5998,7 +6041,7 @@
       <c r="E54" s="13"/>
       <c r="F54" s="13"/>
     </row>
-    <row r="55" spans="1:6" ht="26">
+    <row r="55" spans="1:6" ht="27">
       <c r="A55" s="4"/>
       <c r="B55" s="11" t="s">
         <v>141</v>
@@ -6020,7 +6063,7 @@
       </c>
       <c r="F56" s="13"/>
     </row>
-    <row r="57" spans="1:6" ht="39">
+    <row r="57" spans="1:6" ht="40.5">
       <c r="A57" s="4"/>
       <c r="B57" s="11" t="s">
         <v>143</v>
@@ -6031,7 +6074,7 @@
       </c>
       <c r="F57" s="13"/>
     </row>
-    <row r="58" spans="1:6" ht="39">
+    <row r="58" spans="1:6" ht="40.5">
       <c r="A58" s="4"/>
       <c r="B58" s="11" t="s">
         <v>144</v>
@@ -6042,7 +6085,7 @@
       </c>
       <c r="F58" s="13"/>
     </row>
-    <row r="59" spans="1:6" ht="52">
+    <row r="59" spans="1:6" ht="27">
       <c r="A59" s="4"/>
       <c r="B59" s="11" t="s">
         <v>145</v>
@@ -6053,7 +6096,7 @@
       <c r="E59" s="13"/>
       <c r="F59" s="13"/>
     </row>
-    <row r="60" spans="1:6" ht="65">
+    <row r="60" spans="1:6" ht="40.5">
       <c r="A60" s="4"/>
       <c r="B60" s="11" t="s">
         <v>146</v>
@@ -6066,7 +6109,7 @@
       </c>
       <c r="F60" s="13"/>
     </row>
-    <row r="61" spans="1:6" ht="39">
+    <row r="61" spans="1:6" ht="27">
       <c r="A61" s="4" t="s">
         <v>52</v>
       </c>
@@ -6078,7 +6121,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="62" spans="1:6" ht="39">
+    <row r="62" spans="1:6" ht="40.5">
       <c r="A62" s="4" t="s">
         <v>53</v>
       </c>
@@ -6100,7 +6143,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C945A8A3-E413-4358-BBE4-EF5A44242598}">
   <dimension ref="A1:A12"/>
-  <sheetFormatPr defaultRowHeight="13"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="34" t="s">
@@ -6124,17 +6167,17 @@
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
     </row>
     <row r="12" spans="1:1">
       <c r="A12" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
   </sheetData>
@@ -6146,10 +6189,10 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:B21"/>
-  <sheetFormatPr defaultRowHeight="13"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="150.36328125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="103.36328125" customWidth="1"/>
+    <col min="1" max="1" width="150.375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="103.375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
@@ -6186,7 +6229,7 @@
       </c>
       <c r="B6" s="24"/>
     </row>
-    <row r="7" spans="1:2" ht="52">
+    <row r="7" spans="1:2" ht="54">
       <c r="A7" s="24" t="s">
         <v>156</v>
       </c>
@@ -6266,7 +6309,7 @@
       </c>
       <c r="B19" s="24"/>
     </row>
-    <row r="20" spans="1:2" ht="65">
+    <row r="20" spans="1:2" ht="67.5">
       <c r="A20" s="24" t="s">
         <v>169</v>
       </c>
@@ -6289,13 +6332,13 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:B11"/>
-  <sheetFormatPr defaultRowHeight="13"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="69.6328125" customWidth="1"/>
-    <col min="2" max="2" width="66.36328125" customWidth="1"/>
+    <col min="1" max="1" width="69.625" customWidth="1"/>
+    <col min="2" max="2" width="66.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="58">
+    <row r="1" spans="1:2" ht="60">
       <c r="A1" s="31" t="s">
         <v>228</v>
       </c>
@@ -6303,7 +6346,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="55" customHeight="1">
+    <row r="2" spans="1:2" ht="54.95" customHeight="1">
       <c r="A2" s="31" t="s">
         <v>229</v>
       </c>
@@ -6311,7 +6354,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="55" customHeight="1">
+    <row r="3" spans="1:2" ht="54.95" customHeight="1">
       <c r="A3" s="31" t="s">
         <v>230</v>
       </c>
@@ -6319,7 +6362,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="87">
+    <row r="4" spans="1:2" ht="90">
       <c r="A4" s="31" t="s">
         <v>231</v>
       </c>
@@ -6327,7 +6370,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="55" customHeight="1">
+    <row r="5" spans="1:2" ht="54.95" customHeight="1">
       <c r="A5" s="31" t="s">
         <v>232</v>
       </c>
@@ -6335,7 +6378,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="55" customHeight="1">
+    <row r="6" spans="1:2" ht="54.95" customHeight="1">
       <c r="A6" s="31" t="s">
         <v>233</v>
       </c>
@@ -6343,7 +6386,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="58">
+    <row r="7" spans="1:2" ht="60">
       <c r="A7" s="31" t="s">
         <v>234</v>
       </c>
@@ -6351,7 +6394,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="58">
+    <row r="8" spans="1:2" ht="60">
       <c r="A8" s="31" t="s">
         <v>235</v>
       </c>
@@ -6359,7 +6402,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="9" spans="1:2" ht="55" customHeight="1">
+    <row r="9" spans="1:2" ht="54.95" customHeight="1">
       <c r="A9" s="31" t="s">
         <v>236</v>
       </c>
@@ -6367,7 +6410,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="10" spans="1:2" ht="55" customHeight="1">
+    <row r="10" spans="1:2" ht="54.95" customHeight="1">
       <c r="A10" s="31" t="s">
         <v>237</v>
       </c>
@@ -6375,7 +6418,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="11" spans="1:2" ht="55" customHeight="1">
+    <row r="11" spans="1:2" ht="54.95" customHeight="1">
       <c r="A11" s="31" t="s">
         <v>238</v>
       </c>
@@ -6392,10 +6435,10 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{05FA0C31-4B39-4CC9-AFFE-ADB97979182D}">
   <dimension ref="A1:B21"/>
-  <sheetFormatPr defaultRowHeight="13"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="150.36328125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="103.36328125" customWidth="1"/>
+    <col min="1" max="1" width="150.375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="103.375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
@@ -6420,7 +6463,7 @@
       </c>
       <c r="B4" s="24"/>
     </row>
-    <row r="5" spans="1:2" ht="65">
+    <row r="5" spans="1:2" ht="67.5">
       <c r="A5" s="33" t="s">
         <v>251</v>
       </c>
@@ -6434,7 +6477,7 @@
       </c>
       <c r="B6" s="24"/>
     </row>
-    <row r="7" spans="1:2" ht="52">
+    <row r="7" spans="1:2" ht="54">
       <c r="A7" s="33" t="s">
         <v>253</v>
       </c>
@@ -6490,7 +6533,7 @@
       <c r="A19" s="24"/>
       <c r="B19" s="24"/>
     </row>
-    <row r="20" spans="1:2" ht="65">
+    <row r="20" spans="1:2" ht="67.5">
       <c r="A20" s="24"/>
       <c r="B20" s="23" t="s">
         <v>178</v>
@@ -6509,10 +6552,10 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E3B1E147-F943-43CF-88AE-86DE70DEEA3B}">
   <dimension ref="A1:B21"/>
-  <sheetFormatPr defaultRowHeight="13"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="150.36328125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="103.36328125" customWidth="1"/>
+    <col min="1" max="1" width="150.375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="103.375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
@@ -6531,15 +6574,15 @@
       </c>
       <c r="B3" s="24"/>
     </row>
-    <row r="4" spans="1:2" ht="39">
+    <row r="4" spans="1:2" ht="40.5">
       <c r="A4" s="33" t="s">
         <v>261</v>
       </c>
       <c r="B4" s="23" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" ht="65">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" ht="67.5">
       <c r="A5" s="33" t="s">
         <v>262</v>
       </c>
@@ -6564,50 +6607,50 @@
         <v>265</v>
       </c>
       <c r="B8" s="33" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="33" t="s">
+        <v>266</v>
+      </c>
+      <c r="B9" s="24"/>
+    </row>
+    <row r="10" spans="1:2" ht="40.5">
+      <c r="A10" s="33" t="s">
         <v>267</v>
       </c>
-      <c r="B9" s="24"/>
-    </row>
-    <row r="10" spans="1:2" ht="39">
-      <c r="A10" s="33" t="s">
-        <v>268</v>
-      </c>
       <c r="B10" s="23" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="33" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B11" s="24"/>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="35" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B12" s="24"/>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="33" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="B13" s="24"/>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="33" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="B14" s="24"/>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="33" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B15" s="24"/>
     </row>
@@ -6627,7 +6670,7 @@
       <c r="A19" s="24"/>
       <c r="B19" s="24"/>
     </row>
-    <row r="20" spans="1:2" ht="65">
+    <row r="20" spans="1:2" ht="67.5">
       <c r="A20" s="24"/>
       <c r="B20" s="23" t="s">
         <v>178</v>
@@ -6647,7 +6690,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4E6BF410-1D86-4886-AF32-D2372AA65DBD}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="13"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
   <sheetData/>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/作業/面接練習/G3面接準備中岫.xlsx
+++ b/作業/面接練習/G3面接準備中岫.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aaa115298\Desktop\G3\G3\G3試験中岫作業\G3\作業\面接練習\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/df213c2b7ba35e42/デスクトップ/試験/G3/作業/面接練習/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2AEB519A-D76D-4323-8D4C-B1056013937A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="22" documentId="13_ncr:1_{2AEB519A-D76D-4323-8D4C-B1056013937A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6646B888-7793-4461-93D3-8CC8BF1FF9CA}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -19,7 +19,7 @@
     <sheet name="1014" sheetId="3" r:id="rId4"/>
     <sheet name="1015" sheetId="4" r:id="rId5"/>
     <sheet name="1016" sheetId="7" r:id="rId6"/>
-    <sheet name="Sheet2" sheetId="6" r:id="rId7"/>
+    <sheet name="1019" sheetId="6" r:id="rId7"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="294" uniqueCount="284">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="304" uniqueCount="296">
   <si>
     <t>No</t>
   </si>
@@ -4528,53 +4528,6 @@
     <t>本日はよろしくお願いいたします。</t>
   </si>
   <si>
-    <t>課の課題は、個別製品や担当者ごとに得られた知見が分散し、横展開しにくいことです。Mogamiで得た紙特性、評価結果、対応条件を共通の観点で整理し、他テーマ（IJにかかわらず電子写真）でも検索・再利用できる形にすることで、検討の重複を減らし開発速度を上げたいと考えています。
-IJ、電子写真同じような画質弊害が発生することがある。その場合、メカニズムの解析では両者のメンバーで、議論を行い効率的に得られるようにしている。</t>
-    <rPh sb="49" eb="50">
-      <t>カミ</t>
-    </rPh>
-    <rPh sb="86" eb="90">
-      <t>デンシシャシン</t>
-    </rPh>
-    <rPh sb="141" eb="145">
-      <t>デンシシャシン</t>
-    </rPh>
-    <rPh sb="145" eb="146">
-      <t>オナ</t>
-    </rPh>
-    <rPh sb="150" eb="152">
-      <t>ガシツ</t>
-    </rPh>
-    <rPh sb="152" eb="154">
-      <t>ヘイガイ</t>
-    </rPh>
-    <rPh sb="155" eb="157">
-      <t>ハッセイ</t>
-    </rPh>
-    <rPh sb="167" eb="169">
-      <t>バアイ</t>
-    </rPh>
-    <rPh sb="180" eb="182">
-      <t>リョウシャ</t>
-    </rPh>
-    <rPh sb="189" eb="191">
-      <t>ギロン</t>
-    </rPh>
-    <rPh sb="192" eb="193">
-      <t>オコナ</t>
-    </rPh>
-    <rPh sb="194" eb="196">
-      <t>コウリツ</t>
-    </rPh>
-    <rPh sb="196" eb="197">
-      <t>テキ</t>
-    </rPh>
-    <rPh sb="198" eb="199">
-      <t>エ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>答えだけを教えるのではなく、解析の方向性だけ示しタスクを進めるようにする。最初は評価計画と結果をこまめにレビューし、理解度に応じて任せる範囲を広げ、自力で次の検証を組み立てられるように育成します。</t>
     <rPh sb="14" eb="16">
       <t>カイセキ</t>
@@ -4671,6 +4624,212 @@
 このとき、プライマーの最適な量は、紙の種類やカラーインクの量によっても異なるため、設計の組み合わせが膨大になってしまいます。
 そこで、プライマーの量と画質との関係を解析することで、最小の評価工数でプライマー量を設計する手法を、デジプリ事業本部と連携して開発し、設計効率の向上に取り組んでいます。
 本日はよろしくお願いいたします。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>課の課題は、個別製品や担当者ごとに得られた知見が分散し、横展開しにくいことです。Mogamiで得た紙特性、評価結果、対応条件を共通の観点で整理し、他テーマ（IJにかかわらず電子写真）でも検索・再利用できる形にすることで、検討の重複を減らし開発速度を上げたいと考えています。例えば、自分のプロジェクトで起きた問題や課題の解決については、部会で共有する。
+IJ、電子写真同じような画質弊害が発生することがある。その場合、メカニズムの解析では両者のメンバーで、議論を行い効率的に得られるようにしている。</t>
+    <rPh sb="49" eb="50">
+      <t>カミ</t>
+    </rPh>
+    <rPh sb="86" eb="90">
+      <t>デンシシャシン</t>
+    </rPh>
+    <rPh sb="136" eb="137">
+      <t>タト</t>
+    </rPh>
+    <rPh sb="140" eb="142">
+      <t>ジブン</t>
+    </rPh>
+    <rPh sb="150" eb="151">
+      <t>オ</t>
+    </rPh>
+    <rPh sb="153" eb="155">
+      <t>モンダイ</t>
+    </rPh>
+    <rPh sb="156" eb="158">
+      <t>カダイ</t>
+    </rPh>
+    <rPh sb="159" eb="161">
+      <t>カイケツ</t>
+    </rPh>
+    <rPh sb="167" eb="169">
+      <t>ブカイ</t>
+    </rPh>
+    <rPh sb="170" eb="172">
+      <t>キョウユウ</t>
+    </rPh>
+    <rPh sb="180" eb="184">
+      <t>デンシシャシン</t>
+    </rPh>
+    <rPh sb="184" eb="185">
+      <t>オナ</t>
+    </rPh>
+    <rPh sb="189" eb="191">
+      <t>ガシツ</t>
+    </rPh>
+    <rPh sb="191" eb="193">
+      <t>ヘイガイ</t>
+    </rPh>
+    <rPh sb="194" eb="196">
+      <t>ハッセイ</t>
+    </rPh>
+    <rPh sb="206" eb="208">
+      <t>バアイ</t>
+    </rPh>
+    <rPh sb="219" eb="221">
+      <t>リョウシャ</t>
+    </rPh>
+    <rPh sb="228" eb="230">
+      <t>ギロン</t>
+    </rPh>
+    <rPh sb="231" eb="232">
+      <t>オコナ</t>
+    </rPh>
+    <rPh sb="233" eb="235">
+      <t>コウリツ</t>
+    </rPh>
+    <rPh sb="235" eb="236">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="237" eb="238">
+      <t>エ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>プロジェクトの最終ゴールは？</t>
+    <rPh sb="7" eb="9">
+      <t>サイシュウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>プライマの自動設計</t>
+    <rPh sb="5" eb="9">
+      <t>ジドウセッケイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>それは何年後なのか、それに対しての進捗は</t>
+    <rPh sb="3" eb="6">
+      <t>ナンネンゴ</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>タイ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>シンチョク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>失敗した経験は？</t>
+    <rPh sb="0" eb="2">
+      <t>シッパイ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ケイケン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>用語の定義や現象の捉え方が異なり、議論が進まないことがあった</t>
+    <rPh sb="0" eb="2">
+      <t>ヨウゴ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>テイギ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ゲンショウ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>トラ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>カタ</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>コト</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>ギロン</t>
+    </rPh>
+    <rPh sb="20" eb="21">
+      <t>スス</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>プライマのメカニズムを解明するのは具体的にどういうこと</t>
+    <rPh sb="11" eb="13">
+      <t>カイメイ</t>
+    </rPh>
+    <rPh sb="17" eb="20">
+      <t>グタイテキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>あなたの強みについて</t>
+    <rPh sb="4" eb="5">
+      <t>ツヨ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>G3として何が必要なのか、どういうことが求められるのか</t>
+    <rPh sb="5" eb="6">
+      <t>ナニ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ヒツヨウ</t>
+    </rPh>
+    <rPh sb="20" eb="21">
+      <t>モト</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>事業部とやりとりするときに心がけていること</t>
+    <rPh sb="0" eb="3">
+      <t>ジギョウブ</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>ココロ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>事業部を巻き込むためにどうすればいいか</t>
+    <rPh sb="0" eb="3">
+      <t>ジギョウブ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>マ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>コ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>上司と意見が異なったときはどうするか？</t>
+    <rPh sb="0" eb="2">
+      <t>ジョウシ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>イケン</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>コト</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>上司と意見が異なったときは、まず相手の考えや意見の背景を理解するように努めます。そのうえで、自分の考えも理由や根拠を明確にして、相手に伝えるようにします。お互いの意見をすり合わせ、より良い方法を見つけることが大切だと考えているからです。それでも意見が一致しない場合は、最終的な判断を尊重し、決定した方針に沿って責任を持って行動しま</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -4930,7 +5089,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -5041,6 +5200,9 @@
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -5236,21 +5398,21 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:I62"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18.75"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="10.625" style="2" customWidth="1"/>
-    <col min="2" max="2" width="50.375" style="1" customWidth="1"/>
-    <col min="3" max="3" width="107.125" customWidth="1"/>
+    <col min="1" max="1" width="10.6328125" style="2" customWidth="1"/>
+    <col min="2" max="2" width="50.36328125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="107.08984375" customWidth="1"/>
     <col min="4" max="4" width="52" style="25" customWidth="1"/>
-    <col min="5" max="5" width="119.125" style="6" customWidth="1"/>
-    <col min="6" max="6" width="116.875" style="6" customWidth="1"/>
-    <col min="7" max="7" width="35.875" style="3" customWidth="1"/>
-    <col min="8" max="8" width="64.25" style="3" customWidth="1"/>
-    <col min="9" max="9" width="111.625" style="3" customWidth="1"/>
+    <col min="5" max="5" width="119.08984375" style="6" customWidth="1"/>
+    <col min="6" max="6" width="116.90625" style="6" customWidth="1"/>
+    <col min="7" max="7" width="35.90625" style="3" customWidth="1"/>
+    <col min="8" max="8" width="64.26953125" style="3" customWidth="1"/>
+    <col min="9" max="9" width="111.6328125" style="3" customWidth="1"/>
     <col min="10" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="13.5">
+    <row r="1" spans="1:9" ht="13">
       <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
@@ -5277,7 +5439,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="262.5">
+    <row r="2" spans="1:9" ht="270">
       <c r="A2" s="4">
         <v>0</v>
       </c>
@@ -5285,7 +5447,7 @@
         <v>180</v>
       </c>
       <c r="C2" s="18" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="D2" s="25" t="s">
         <v>172</v>
@@ -5303,7 +5465,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="391.5">
+    <row r="3" spans="1:9" ht="390">
       <c r="A3" s="28"/>
       <c r="B3" s="23" t="s">
         <v>181</v>
@@ -5314,7 +5476,7 @@
       <c r="E3" s="26"/>
       <c r="F3" s="20"/>
     </row>
-    <row r="4" spans="1:9" ht="262.5">
+    <row r="4" spans="1:9" ht="252">
       <c r="A4" s="4">
         <v>1</v>
       </c>
@@ -5322,7 +5484,7 @@
         <v>92</v>
       </c>
       <c r="C4" s="18" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="D4" s="25" t="s">
         <v>173</v>
@@ -5335,7 +5497,7 @@
       </c>
       <c r="G4" s="6"/>
     </row>
-    <row r="5" spans="1:9" ht="81">
+    <row r="5" spans="1:9" ht="78">
       <c r="A5" s="4" t="s">
         <v>7</v>
       </c>
@@ -5350,7 +5512,7 @@
       </c>
       <c r="F5" s="20"/>
     </row>
-    <row r="6" spans="1:9" ht="94.5">
+    <row r="6" spans="1:9" ht="91">
       <c r="A6" s="4" t="s">
         <v>8</v>
       </c>
@@ -5365,7 +5527,7 @@
       </c>
       <c r="F6" s="13"/>
     </row>
-    <row r="7" spans="1:9" ht="121.5">
+    <row r="7" spans="1:9" ht="130">
       <c r="A7" s="4" t="s">
         <v>9</v>
       </c>
@@ -5373,7 +5535,7 @@
         <v>94</v>
       </c>
       <c r="C7" s="18" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="E7" s="21" t="s">
         <v>186</v>
@@ -5381,7 +5543,7 @@
       <c r="F7" s="14"/>
       <c r="I7" s="6"/>
     </row>
-    <row r="8" spans="1:9" ht="54">
+    <row r="8" spans="1:9" ht="52">
       <c r="A8" s="4" t="s">
         <v>10</v>
       </c>
@@ -5396,7 +5558,7 @@
       </c>
       <c r="F8" s="14"/>
     </row>
-    <row r="9" spans="1:9" ht="108">
+    <row r="9" spans="1:9" ht="104">
       <c r="A9" s="4">
         <v>2</v>
       </c>
@@ -5411,7 +5573,7 @@
       </c>
       <c r="F9" s="20"/>
     </row>
-    <row r="10" spans="1:9" ht="108">
+    <row r="10" spans="1:9" ht="117">
       <c r="A10" s="4">
         <v>3</v>
       </c>
@@ -5426,7 +5588,7 @@
       </c>
       <c r="F10" s="20"/>
     </row>
-    <row r="11" spans="1:9" ht="40.5">
+    <row r="11" spans="1:9" ht="52">
       <c r="A11" s="4" t="s">
         <v>11</v>
       </c>
@@ -5441,7 +5603,7 @@
       </c>
       <c r="F11" s="14"/>
     </row>
-    <row r="12" spans="1:9" ht="67.5">
+    <row r="12" spans="1:9" ht="91">
       <c r="A12" s="4" t="s">
         <v>12</v>
       </c>
@@ -5456,7 +5618,7 @@
       </c>
       <c r="F12" s="14"/>
     </row>
-    <row r="13" spans="1:9" ht="27">
+    <row r="13" spans="1:9" ht="26">
       <c r="A13" s="4" t="s">
         <v>13</v>
       </c>
@@ -5469,7 +5631,7 @@
       <c r="E13" s="13"/>
       <c r="F13" s="14"/>
     </row>
-    <row r="14" spans="1:9" ht="135">
+    <row r="14" spans="1:9" ht="143">
       <c r="A14" s="4">
         <v>4</v>
       </c>
@@ -5477,7 +5639,7 @@
         <v>101</v>
       </c>
       <c r="C14" s="36" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="E14" s="13" t="s">
         <v>192</v>
@@ -5485,7 +5647,7 @@
       <c r="F14" s="20"/>
       <c r="G14" s="10"/>
     </row>
-    <row r="15" spans="1:9" ht="27">
+    <row r="15" spans="1:9" ht="39">
       <c r="A15" s="4" t="s">
         <v>14</v>
       </c>
@@ -5500,7 +5662,7 @@
       </c>
       <c r="F15" s="20"/>
     </row>
-    <row r="16" spans="1:9" ht="40.5">
+    <row r="16" spans="1:9" ht="39">
       <c r="A16" s="4" t="s">
         <v>15</v>
       </c>
@@ -5515,7 +5677,7 @@
       </c>
       <c r="F16" s="20"/>
     </row>
-    <row r="17" spans="1:6" ht="94.5">
+    <row r="17" spans="1:6" ht="91">
       <c r="A17" s="4" t="s">
         <v>16</v>
       </c>
@@ -5530,7 +5692,7 @@
       </c>
       <c r="F17" s="20"/>
     </row>
-    <row r="18" spans="1:6" ht="27">
+    <row r="18" spans="1:6" ht="26">
       <c r="A18" s="4" t="s">
         <v>17</v>
       </c>
@@ -5545,7 +5707,7 @@
       </c>
       <c r="F18" s="20"/>
     </row>
-    <row r="19" spans="1:6" ht="40.5">
+    <row r="19" spans="1:6" ht="39">
       <c r="A19" s="4" t="s">
         <v>18</v>
       </c>
@@ -5558,7 +5720,7 @@
       <c r="E19" s="13"/>
       <c r="F19" s="20"/>
     </row>
-    <row r="20" spans="1:6" ht="81">
+    <row r="20" spans="1:6" ht="78">
       <c r="A20" s="4" t="s">
         <v>19</v>
       </c>
@@ -5573,7 +5735,7 @@
       </c>
       <c r="F20" s="20"/>
     </row>
-    <row r="21" spans="1:6" ht="108">
+    <row r="21" spans="1:6" ht="104">
       <c r="A21" s="4" t="s">
         <v>20</v>
       </c>
@@ -5587,7 +5749,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="22" spans="1:6">
+    <row r="22" spans="1:6" ht="26">
       <c r="A22" s="4" t="s">
         <v>21</v>
       </c>
@@ -5602,7 +5764,7 @@
       </c>
       <c r="F22" s="20"/>
     </row>
-    <row r="23" spans="1:6" ht="54">
+    <row r="23" spans="1:6" ht="52">
       <c r="A23" s="4" t="s">
         <v>22</v>
       </c>
@@ -5617,7 +5779,7 @@
       </c>
       <c r="F23" s="20"/>
     </row>
-    <row r="24" spans="1:6" ht="27">
+    <row r="24" spans="1:6" ht="26">
       <c r="A24" s="4" t="s">
         <v>23</v>
       </c>
@@ -5625,7 +5787,7 @@
         <v>110</v>
       </c>
       <c r="C24" s="18" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="E24" s="12" t="s">
         <v>201</v>
@@ -5643,7 +5805,7 @@
       <c r="E25" s="12"/>
       <c r="F25" s="20"/>
     </row>
-    <row r="26" spans="1:6" ht="27">
+    <row r="26" spans="1:6" ht="26">
       <c r="A26" s="4" t="s">
         <v>25</v>
       </c>
@@ -5656,7 +5818,7 @@
       <c r="E26" s="13"/>
       <c r="F26" s="20"/>
     </row>
-    <row r="27" spans="1:6" ht="81">
+    <row r="27" spans="1:6" ht="78">
       <c r="A27" s="4" t="s">
         <v>26</v>
       </c>
@@ -5669,7 +5831,7 @@
       <c r="E27" s="13"/>
       <c r="F27" s="14"/>
     </row>
-    <row r="28" spans="1:6" ht="108">
+    <row r="28" spans="1:6" ht="104">
       <c r="A28" s="4" t="s">
         <v>27</v>
       </c>
@@ -5684,7 +5846,7 @@
       </c>
       <c r="F28" s="20"/>
     </row>
-    <row r="29" spans="1:6" ht="27">
+    <row r="29" spans="1:6" ht="26">
       <c r="A29" s="4" t="s">
         <v>28</v>
       </c>
@@ -5699,7 +5861,7 @@
       </c>
       <c r="F29" s="20"/>
     </row>
-    <row r="30" spans="1:6" ht="42">
+    <row r="30" spans="1:6" ht="40.5">
       <c r="A30" s="4" t="s">
         <v>29</v>
       </c>
@@ -5725,7 +5887,7 @@
       <c r="E31" s="22"/>
       <c r="F31" s="20"/>
     </row>
-    <row r="32" spans="1:6" ht="27">
+    <row r="32" spans="1:6" ht="26">
       <c r="A32" s="4" t="s">
         <v>31</v>
       </c>
@@ -5740,7 +5902,7 @@
       </c>
       <c r="F32" s="20"/>
     </row>
-    <row r="33" spans="1:9" ht="40.5">
+    <row r="33" spans="1:9" ht="39">
       <c r="A33" s="4" t="s">
         <v>32</v>
       </c>
@@ -5756,7 +5918,7 @@
       <c r="F33" s="13"/>
       <c r="I33" s="6"/>
     </row>
-    <row r="34" spans="1:9" ht="27">
+    <row r="34" spans="1:9" ht="26">
       <c r="A34" s="4" t="s">
         <v>33</v>
       </c>
@@ -5771,7 +5933,7 @@
       </c>
       <c r="F34" s="20"/>
     </row>
-    <row r="35" spans="1:9" ht="27">
+    <row r="35" spans="1:9" ht="26">
       <c r="A35" s="4" t="s">
         <v>34</v>
       </c>
@@ -5784,7 +5946,7 @@
       <c r="E35" s="13"/>
       <c r="F35" s="20"/>
     </row>
-    <row r="36" spans="1:9" ht="27">
+    <row r="36" spans="1:9" ht="26">
       <c r="A36" s="4" t="s">
         <v>35</v>
       </c>
@@ -5799,7 +5961,7 @@
       </c>
       <c r="F36" s="20"/>
     </row>
-    <row r="37" spans="1:9" ht="54">
+    <row r="37" spans="1:9" ht="52">
       <c r="A37" s="4" t="s">
         <v>36</v>
       </c>
@@ -5814,7 +5976,7 @@
       </c>
       <c r="F37" s="20"/>
     </row>
-    <row r="38" spans="1:9" ht="54">
+    <row r="38" spans="1:9" ht="65">
       <c r="A38" s="4" t="s">
         <v>37</v>
       </c>
@@ -5829,7 +5991,7 @@
       </c>
       <c r="F38" s="20"/>
     </row>
-    <row r="39" spans="1:9" ht="84">
+    <row r="39" spans="1:9" ht="81">
       <c r="A39" s="4" t="s">
         <v>38</v>
       </c>
@@ -5844,7 +6006,7 @@
       </c>
       <c r="F39" s="14"/>
     </row>
-    <row r="40" spans="1:9" ht="40.5">
+    <row r="40" spans="1:9" ht="39">
       <c r="A40" s="4" t="s">
         <v>39</v>
       </c>
@@ -5857,11 +6019,11 @@
       <c r="E40" s="13"/>
       <c r="F40" s="15"/>
     </row>
-    <row r="41" spans="1:9" ht="27">
+    <row r="41" spans="1:9" ht="39">
       <c r="A41" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="B41" s="11" t="s">
+      <c r="B41" s="37" t="s">
         <v>127</v>
       </c>
       <c r="C41" s="5" t="s">
@@ -5870,7 +6032,7 @@
       <c r="E41" s="13"/>
       <c r="F41" s="13"/>
     </row>
-    <row r="42" spans="1:9" ht="27">
+    <row r="42" spans="1:9" ht="26">
       <c r="A42" s="4" t="s">
         <v>41</v>
       </c>
@@ -5883,7 +6045,7 @@
       <c r="E42" s="13"/>
       <c r="F42" s="13"/>
     </row>
-    <row r="43" spans="1:9" ht="27">
+    <row r="43" spans="1:9" ht="26">
       <c r="A43" s="4" t="s">
         <v>42</v>
       </c>
@@ -5894,7 +6056,7 @@
       <c r="E43" s="13"/>
       <c r="F43" s="13"/>
     </row>
-    <row r="44" spans="1:9" ht="40.5">
+    <row r="44" spans="1:9" ht="39">
       <c r="A44" s="4" t="s">
         <v>43</v>
       </c>
@@ -5909,7 +6071,7 @@
       </c>
       <c r="F44" s="13"/>
     </row>
-    <row r="45" spans="1:9" ht="69">
+    <row r="45" spans="1:9" ht="66.5">
       <c r="A45" s="4" t="s">
         <v>44</v>
       </c>
@@ -5924,7 +6086,7 @@
       </c>
       <c r="F45" s="13"/>
     </row>
-    <row r="46" spans="1:9" ht="27">
+    <row r="46" spans="1:9" ht="39">
       <c r="A46" s="4" t="s">
         <v>45</v>
       </c>
@@ -5939,7 +6101,7 @@
       </c>
       <c r="F46" s="13"/>
     </row>
-    <row r="47" spans="1:9" ht="27">
+    <row r="47" spans="1:9" ht="26">
       <c r="A47" s="4" t="s">
         <v>46</v>
       </c>
@@ -5950,7 +6112,7 @@
       <c r="E47" s="22"/>
       <c r="F47" s="13"/>
     </row>
-    <row r="48" spans="1:9" ht="27">
+    <row r="48" spans="1:9" ht="26">
       <c r="A48" s="4" t="s">
         <v>47</v>
       </c>
@@ -5961,7 +6123,7 @@
       <c r="E48" s="22"/>
       <c r="F48" s="13"/>
     </row>
-    <row r="49" spans="1:6" ht="27">
+    <row r="49" spans="1:6" ht="26">
       <c r="A49" s="4" t="s">
         <v>48</v>
       </c>
@@ -5974,7 +6136,7 @@
       <c r="E49" s="13"/>
       <c r="F49" s="13"/>
     </row>
-    <row r="50" spans="1:6" ht="27">
+    <row r="50" spans="1:6" ht="39">
       <c r="A50" s="4" t="s">
         <v>49</v>
       </c>
@@ -5989,7 +6151,7 @@
       </c>
       <c r="F50" s="13"/>
     </row>
-    <row r="51" spans="1:6" ht="42">
+    <row r="51" spans="1:6" ht="40.5">
       <c r="A51" s="4" t="s">
         <v>50</v>
       </c>
@@ -6004,7 +6166,7 @@
       </c>
       <c r="F51" s="13"/>
     </row>
-    <row r="52" spans="1:6" ht="40.5">
+    <row r="52" spans="1:6" ht="39">
       <c r="A52" s="4" t="s">
         <v>51</v>
       </c>
@@ -6019,7 +6181,7 @@
       </c>
       <c r="F52" s="13"/>
     </row>
-    <row r="53" spans="1:6" ht="94.5">
+    <row r="53" spans="1:6" ht="91">
       <c r="A53" s="4"/>
       <c r="B53" s="11" t="s">
         <v>139</v>
@@ -6041,7 +6203,7 @@
       <c r="E54" s="13"/>
       <c r="F54" s="13"/>
     </row>
-    <row r="55" spans="1:6" ht="27">
+    <row r="55" spans="1:6" ht="26">
       <c r="A55" s="4"/>
       <c r="B55" s="11" t="s">
         <v>141</v>
@@ -6063,7 +6225,7 @@
       </c>
       <c r="F56" s="13"/>
     </row>
-    <row r="57" spans="1:6" ht="40.5">
+    <row r="57" spans="1:6" ht="39">
       <c r="A57" s="4"/>
       <c r="B57" s="11" t="s">
         <v>143</v>
@@ -6074,7 +6236,7 @@
       </c>
       <c r="F57" s="13"/>
     </row>
-    <row r="58" spans="1:6" ht="40.5">
+    <row r="58" spans="1:6" ht="39">
       <c r="A58" s="4"/>
       <c r="B58" s="11" t="s">
         <v>144</v>
@@ -6085,7 +6247,7 @@
       </c>
       <c r="F58" s="13"/>
     </row>
-    <row r="59" spans="1:6" ht="27">
+    <row r="59" spans="1:6" ht="26">
       <c r="A59" s="4"/>
       <c r="B59" s="11" t="s">
         <v>145</v>
@@ -6096,7 +6258,7 @@
       <c r="E59" s="13"/>
       <c r="F59" s="13"/>
     </row>
-    <row r="60" spans="1:6" ht="40.5">
+    <row r="60" spans="1:6" ht="39">
       <c r="A60" s="4"/>
       <c r="B60" s="11" t="s">
         <v>146</v>
@@ -6109,7 +6271,7 @@
       </c>
       <c r="F60" s="13"/>
     </row>
-    <row r="61" spans="1:6" ht="27">
+    <row r="61" spans="1:6" ht="39">
       <c r="A61" s="4" t="s">
         <v>52</v>
       </c>
@@ -6121,7 +6283,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="62" spans="1:6" ht="40.5">
+    <row r="62" spans="1:6" ht="39">
       <c r="A62" s="4" t="s">
         <v>53</v>
       </c>
@@ -6143,7 +6305,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C945A8A3-E413-4358-BBE4-EF5A44242598}">
   <dimension ref="A1:A12"/>
-  <sheetFormatPr defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultRowHeight="13"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="34" t="s">
@@ -6189,10 +6351,10 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:B21"/>
-  <sheetFormatPr defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultRowHeight="13"/>
   <cols>
-    <col min="1" max="1" width="150.375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="103.375" customWidth="1"/>
+    <col min="1" max="1" width="150.36328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="103.36328125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
@@ -6229,7 +6391,7 @@
       </c>
       <c r="B6" s="24"/>
     </row>
-    <row r="7" spans="1:2" ht="54">
+    <row r="7" spans="1:2" ht="52">
       <c r="A7" s="24" t="s">
         <v>156</v>
       </c>
@@ -6309,7 +6471,7 @@
       </c>
       <c r="B19" s="24"/>
     </row>
-    <row r="20" spans="1:2" ht="67.5">
+    <row r="20" spans="1:2" ht="65">
       <c r="A20" s="24" t="s">
         <v>169</v>
       </c>
@@ -6332,13 +6494,13 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:B11"/>
-  <sheetFormatPr defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultRowHeight="13"/>
   <cols>
-    <col min="1" max="1" width="69.625" customWidth="1"/>
-    <col min="2" max="2" width="66.375" customWidth="1"/>
+    <col min="1" max="1" width="69.6328125" customWidth="1"/>
+    <col min="2" max="2" width="66.36328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="60">
+    <row r="1" spans="1:2" ht="58">
       <c r="A1" s="31" t="s">
         <v>228</v>
       </c>
@@ -6346,7 +6508,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="54.95" customHeight="1">
+    <row r="2" spans="1:2" ht="55" customHeight="1">
       <c r="A2" s="31" t="s">
         <v>229</v>
       </c>
@@ -6354,7 +6516,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="54.95" customHeight="1">
+    <row r="3" spans="1:2" ht="55" customHeight="1">
       <c r="A3" s="31" t="s">
         <v>230</v>
       </c>
@@ -6362,7 +6524,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="90">
+    <row r="4" spans="1:2" ht="87">
       <c r="A4" s="31" t="s">
         <v>231</v>
       </c>
@@ -6370,7 +6532,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="54.95" customHeight="1">
+    <row r="5" spans="1:2" ht="55" customHeight="1">
       <c r="A5" s="31" t="s">
         <v>232</v>
       </c>
@@ -6378,7 +6540,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="54.95" customHeight="1">
+    <row r="6" spans="1:2" ht="55" customHeight="1">
       <c r="A6" s="31" t="s">
         <v>233</v>
       </c>
@@ -6386,7 +6548,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="60">
+    <row r="7" spans="1:2" ht="58">
       <c r="A7" s="31" t="s">
         <v>234</v>
       </c>
@@ -6394,7 +6556,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="60">
+    <row r="8" spans="1:2" ht="58">
       <c r="A8" s="31" t="s">
         <v>235</v>
       </c>
@@ -6402,7 +6564,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="9" spans="1:2" ht="54.95" customHeight="1">
+    <row r="9" spans="1:2" ht="55" customHeight="1">
       <c r="A9" s="31" t="s">
         <v>236</v>
       </c>
@@ -6410,7 +6572,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="10" spans="1:2" ht="54.95" customHeight="1">
+    <row r="10" spans="1:2" ht="55" customHeight="1">
       <c r="A10" s="31" t="s">
         <v>237</v>
       </c>
@@ -6418,7 +6580,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="11" spans="1:2" ht="54.95" customHeight="1">
+    <row r="11" spans="1:2" ht="55" customHeight="1">
       <c r="A11" s="31" t="s">
         <v>238</v>
       </c>
@@ -6435,10 +6597,10 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{05FA0C31-4B39-4CC9-AFFE-ADB97979182D}">
   <dimension ref="A1:B21"/>
-  <sheetFormatPr defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultRowHeight="13"/>
   <cols>
-    <col min="1" max="1" width="150.375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="103.375" customWidth="1"/>
+    <col min="1" max="1" width="150.36328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="103.36328125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
@@ -6463,7 +6625,7 @@
       </c>
       <c r="B4" s="24"/>
     </row>
-    <row r="5" spans="1:2" ht="67.5">
+    <row r="5" spans="1:2" ht="65">
       <c r="A5" s="33" t="s">
         <v>251</v>
       </c>
@@ -6477,13 +6639,11 @@
       </c>
       <c r="B6" s="24"/>
     </row>
-    <row r="7" spans="1:2" ht="54">
+    <row r="7" spans="1:2">
       <c r="A7" s="33" t="s">
         <v>253</v>
       </c>
-      <c r="B7" s="23" t="s">
-        <v>171</v>
-      </c>
+      <c r="B7" s="23"/>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="24"/>
@@ -6533,7 +6693,7 @@
       <c r="A19" s="24"/>
       <c r="B19" s="24"/>
     </row>
-    <row r="20" spans="1:2" ht="67.5">
+    <row r="20" spans="1:2" ht="65">
       <c r="A20" s="24"/>
       <c r="B20" s="23" t="s">
         <v>178</v>
@@ -6552,10 +6712,10 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E3B1E147-F943-43CF-88AE-86DE70DEEA3B}">
   <dimension ref="A1:B21"/>
-  <sheetFormatPr defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultRowHeight="13"/>
   <cols>
-    <col min="1" max="1" width="150.375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="103.375" customWidth="1"/>
+    <col min="1" max="1" width="150.36328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="103.36328125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
@@ -6574,7 +6734,7 @@
       </c>
       <c r="B3" s="24"/>
     </row>
-    <row r="4" spans="1:2" ht="40.5">
+    <row r="4" spans="1:2" ht="39">
       <c r="A4" s="33" t="s">
         <v>261</v>
       </c>
@@ -6582,13 +6742,11 @@
         <v>273</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="67.5">
+    <row r="5" spans="1:2">
       <c r="A5" s="33" t="s">
         <v>262</v>
       </c>
-      <c r="B5" s="23" t="s">
-        <v>256</v>
-      </c>
+      <c r="B5" s="23"/>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="33" t="s">
@@ -6616,7 +6774,7 @@
       </c>
       <c r="B9" s="24"/>
     </row>
-    <row r="10" spans="1:2" ht="40.5">
+    <row r="10" spans="1:2" ht="39">
       <c r="A10" s="33" t="s">
         <v>267</v>
       </c>
@@ -6670,7 +6828,7 @@
       <c r="A19" s="24"/>
       <c r="B19" s="24"/>
     </row>
-    <row r="20" spans="1:2" ht="67.5">
+    <row r="20" spans="1:2" ht="65">
       <c r="A20" s="24"/>
       <c r="B20" s="23" t="s">
         <v>178</v>
@@ -6689,9 +6847,68 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4E6BF410-1D86-4886-AF32-D2372AA65DBD}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="13.5"/>
-  <sheetData/>
+  <dimension ref="A1:B9"/>
+  <sheetFormatPr defaultRowHeight="13"/>
+  <cols>
+    <col min="1" max="1" width="51.81640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="43.08984375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" s="34" t="s">
+        <v>284</v>
+      </c>
+      <c r="B1" s="34" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" s="34" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" s="34" t="s">
+        <v>287</v>
+      </c>
+      <c r="B3" s="34" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" s="34" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" s="34" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" s="34" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" s="34" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" s="34" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" s="34" t="s">
+        <v>294</v>
+      </c>
+      <c r="B9" s="34" t="s">
+        <v>295</v>
+      </c>
+    </row>
+  </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/作業/面接練習/G3面接準備中岫.xlsx
+++ b/作業/面接練習/G3面接準備中岫.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/df213c2b7ba35e42/デスクトップ/試験/G3/作業/面接練習/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aaa115298\Desktop\G3\G3\G3試験中岫作業\G3\作業\面接練習\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="22" documentId="13_ncr:1_{2AEB519A-D76D-4323-8D4C-B1056013937A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6646B888-7793-4461-93D3-8CC8BF1FF9CA}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F430D989-68B3-4586-B632-B88DA579EA80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="304" uniqueCount="296">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="365" uniqueCount="297">
   <si>
     <t>No</t>
   </si>
@@ -214,9 +214,6 @@
   </si>
   <si>
     <t>重要になるのは、課題の優先順位を定め、必要な評価と判断基準を明確にすることです。また、関係者の知見を集めて認識をそろえ、担当者が動きやすい形に作業を分解すること、得られた知見を次の開発に再利用できるよう整理することも重要です。</t>
-  </si>
-  <si>
-    <t>第一歩として、現在のメディア評価項目、判定基準、課題、関係者を一覧化します。どの情報が不足し、どこで判断に時間がかかっているかを明確にしたうえで、優先度の高いメディアから評価と対応の進め方を標準化します。</t>
   </si>
   <si>
     <t>グループの課題は、メディアごとの現象が複数の要因にまたがり、担当間で原因や優先順位の認識がずれやすいことです。評価結果を共通の指標で見える化し、事実・仮説・次の確認項目を分けて共有することで、議論と意思決定を早めようとしています。</t>
@@ -1700,22 +1697,6 @@
       <t>セイヒン</t>
     </rPh>
     <phoneticPr fontId="7"/>
-  </si>
-  <si>
-    <r>
-      <t>自分の担当評価を完遂する立場から、</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>Mogamiのメディア対応力全体を見て課題を設定し、周囲を動かす立場へ変わります。判断に必要な情報を整理し、関係者間の認識をそろえ、製品価値につながる結論まで責任を持つようになります。</t>
-    </r>
-    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>組織面では、メディア対応が画質、材料、搬送、制御など複数領域に関係するため、担当間の認識合わせに苦労します。単語の定義や現象の捉え方が異なるため、画質とプライマの関係の議論をしていても進まないことがあった。それに対して、単語の定義から行い、認識をすりあわせた。</t>
@@ -4092,27 +4073,6 @@
     <phoneticPr fontId="7"/>
   </si>
   <si>
-    <t>G3になったら、Mogamiの用紙対応力向上に向けて、個別の事象に対して画質改善を行うだけでなく、技術課題の優先順位を定め、チームの開発方針を示す役割を担いたいと考えています。
-現在、プライマ量の調整だけでは十分な画質が得られず、対応対象外としている紙があります。そのような紙に対して、画質が向上しない原因を多面的に分析し、必要な技術検討を関係者に働きかけながら、解決に向けた方針をまとめていきたいです。
-これまで対応できなかった紙にも対象を広げ、Mogamiの用紙対応力を高めることが、G3として実現したいことです。</t>
-    <rPh sb="30" eb="32">
-      <t>ジショウ</t>
-    </rPh>
-    <rPh sb="33" eb="34">
-      <t>タイ</t>
-    </rPh>
-    <rPh sb="36" eb="38">
-      <t>ガシツ</t>
-    </rPh>
-    <rPh sb="38" eb="40">
-      <t>カイゼン</t>
-    </rPh>
-    <rPh sb="41" eb="42">
-      <t>オコナ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>課は21名で、管理職2名、課員19名。チーム内では、
 私は用紙対応力向上のテーマに所属し、主にプライマに関する検討を行っています。私の役割は、文献調査や評価用チャートの分析を通じて、プライマが画質に与える影響や技術課題を整理し、その後の開発をどのような方針で進めるかを先行して検討することです。また、検討結果を基に、プライマ量を決定する評価フローの再構築にも取り組みました。</t>
     <phoneticPr fontId="1"/>
@@ -4557,66 +4517,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>課の構成は管理職2名、主任5名、G3、〇一般職〇名です。私たちのチームには、大きく二つのテーマがあります。一つはスジムラの発生メカニズムの解明、もう一つはMogamiの用紙対応力の向上です。
-ソフトウェア33開発室では、主に商業印刷機を対象に、測定・解析技術やAIを活用して、画質、安定性、用紙対応力を向上させる技術開発を行っています。具体的には、電子写真方式とインクジェット方式の両方について、画質劣化の原因を分析し、製品設計や画質改善につなげるプロジェクトに取り組んでいます。
-私は商業IJ印刷機Mogamiの用紙対応力向上のテーマに所属し、主にプライマに関する検討を行っています。プライマは画質を向上させるために打つ透明インクで、打つ量によって画質を低下させたりします。私の役割は、文献調査や評価用チャートの分析を通じて、プライマが画質に与える影響や技術課題を整理し、その後の開発をどのような方針で進めるかを先行して検討することです。また、検討結果を基に、プライマ量を決定する評価フローの再構築にも取り組みました。</t>
-    <rPh sb="0" eb="1">
-      <t>カ</t>
-    </rPh>
-    <rPh sb="2" eb="4">
-      <t>コウセイ</t>
-    </rPh>
-    <rPh sb="5" eb="8">
-      <t>カンリショク</t>
-    </rPh>
-    <rPh sb="9" eb="10">
-      <t>メイ</t>
-    </rPh>
-    <rPh sb="11" eb="13">
-      <t>シュニン</t>
-    </rPh>
-    <rPh sb="14" eb="15">
-      <t>メイ</t>
-    </rPh>
-    <rPh sb="20" eb="23">
-      <t>イッパンショク</t>
-    </rPh>
-    <rPh sb="24" eb="25">
-      <t>メイ</t>
-    </rPh>
-    <rPh sb="245" eb="247">
-      <t>ショウギョウ</t>
-    </rPh>
-    <rPh sb="249" eb="251">
-      <t>インサツ</t>
-    </rPh>
-    <rPh sb="300" eb="302">
-      <t>ガシツ</t>
-    </rPh>
-    <rPh sb="303" eb="305">
-      <t>コウジョウ</t>
-    </rPh>
-    <rPh sb="311" eb="312">
-      <t>ウ</t>
-    </rPh>
-    <rPh sb="313" eb="315">
-      <t>トウメイ</t>
-    </rPh>
-    <rPh sb="320" eb="321">
-      <t>ウ</t>
-    </rPh>
-    <rPh sb="322" eb="323">
-      <t>リョウ</t>
-    </rPh>
-    <rPh sb="327" eb="329">
-      <t>ガシツ</t>
-    </rPh>
-    <rPh sb="330" eb="332">
-      <t>テイカ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>デジタルビジネスプラットフォーム開発本部、ソフトウェア33開発室の中岫茉希と申します。
 私の所属する部門では、プリンタを高画質化するための、物理現象の解析を行っています。
 その中で私は、商業印刷向けのインクジェットプリンタを対象に、「プライマー」と呼ばれる透明なインクと画質との関係の解析を担当しています。
@@ -4627,77 +4527,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>課の課題は、個別製品や担当者ごとに得られた知見が分散し、横展開しにくいことです。Mogamiで得た紙特性、評価結果、対応条件を共通の観点で整理し、他テーマ（IJにかかわらず電子写真）でも検索・再利用できる形にすることで、検討の重複を減らし開発速度を上げたいと考えています。例えば、自分のプロジェクトで起きた問題や課題の解決については、部会で共有する。
-IJ、電子写真同じような画質弊害が発生することがある。その場合、メカニズムの解析では両者のメンバーで、議論を行い効率的に得られるようにしている。</t>
-    <rPh sb="49" eb="50">
-      <t>カミ</t>
-    </rPh>
-    <rPh sb="86" eb="90">
-      <t>デンシシャシン</t>
-    </rPh>
-    <rPh sb="136" eb="137">
-      <t>タト</t>
-    </rPh>
-    <rPh sb="140" eb="142">
-      <t>ジブン</t>
-    </rPh>
-    <rPh sb="150" eb="151">
-      <t>オ</t>
-    </rPh>
-    <rPh sb="153" eb="155">
-      <t>モンダイ</t>
-    </rPh>
-    <rPh sb="156" eb="158">
-      <t>カダイ</t>
-    </rPh>
-    <rPh sb="159" eb="161">
-      <t>カイケツ</t>
-    </rPh>
-    <rPh sb="167" eb="169">
-      <t>ブカイ</t>
-    </rPh>
-    <rPh sb="170" eb="172">
-      <t>キョウユウ</t>
-    </rPh>
-    <rPh sb="180" eb="184">
-      <t>デンシシャシン</t>
-    </rPh>
-    <rPh sb="184" eb="185">
-      <t>オナ</t>
-    </rPh>
-    <rPh sb="189" eb="191">
-      <t>ガシツ</t>
-    </rPh>
-    <rPh sb="191" eb="193">
-      <t>ヘイガイ</t>
-    </rPh>
-    <rPh sb="194" eb="196">
-      <t>ハッセイ</t>
-    </rPh>
-    <rPh sb="206" eb="208">
-      <t>バアイ</t>
-    </rPh>
-    <rPh sb="219" eb="221">
-      <t>リョウシャ</t>
-    </rPh>
-    <rPh sb="228" eb="230">
-      <t>ギロン</t>
-    </rPh>
-    <rPh sb="231" eb="232">
-      <t>オコナ</t>
-    </rPh>
-    <rPh sb="233" eb="235">
-      <t>コウリツ</t>
-    </rPh>
-    <rPh sb="235" eb="236">
-      <t>テキ</t>
-    </rPh>
-    <rPh sb="237" eb="238">
-      <t>エ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>プロジェクトの最終ゴールは？</t>
     <rPh sb="7" eb="9">
       <t>サイシュウ</t>
@@ -4830,6 +4659,532 @@
   </si>
   <si>
     <t>上司と意見が異なったときは、まず相手の考えや意見の背景を理解するように努めます。そのうえで、自分の考えも理由や根拠を明確にして、相手に伝えるようにします。お互いの意見をすり合わせ、より良い方法を見つけることが大切だと考えているからです。それでも意見が一致しない場合は、最終的な判断を尊重し、決定した方針に沿って責任を持って行動しま</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>課の構成は管理職2名、主任5名、G3、〇一般職〇名です。
+ソフトウェア33開発室では、主に商業印刷機を対象に、測定・解析技術やAIを活用して、画質、安定性、用紙対応力を向上させる技術開発を行っています。具体的には、電子写真方式とインクジェット方式の両方について、画質劣化の原因を分析し、製品設計や画質改善につなげるプロジェクトに取り組んでいます。私たちのチームには、大きく二つのテーマがあります。一つはスジムラの発生メカニズムの解明、もう一つはMogamiの用紙対応力の向上です。
+私は商業IJ印刷機Mogamiの用紙対応力向上のテーマに所属し、主にプライマに関する検討を行っています。プライマは画質を向上させるために打つ透明インクで、打つ量によって画質を低下させたりします。私の役割は、文献調査や評価用チャートの分析を通じて、プライマが画質に与える影響や技術課題を整理し、その後の開発をどのような方針で進めるかを先行して検討することです。また、検討結果を基に、プライマ量を決定する評価フローの再構築にも取り組みました。</t>
+    <rPh sb="0" eb="1">
+      <t>カ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>コウセイ</t>
+    </rPh>
+    <rPh sb="5" eb="8">
+      <t>カンリショク</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>メイ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>シュニン</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>メイ</t>
+    </rPh>
+    <rPh sb="20" eb="23">
+      <t>イッパンショク</t>
+    </rPh>
+    <rPh sb="24" eb="25">
+      <t>メイ</t>
+    </rPh>
+    <rPh sb="245" eb="247">
+      <t>ショウギョウ</t>
+    </rPh>
+    <rPh sb="249" eb="251">
+      <t>インサツ</t>
+    </rPh>
+    <rPh sb="300" eb="302">
+      <t>ガシツ</t>
+    </rPh>
+    <rPh sb="303" eb="305">
+      <t>コウジョウ</t>
+    </rPh>
+    <rPh sb="311" eb="312">
+      <t>ウ</t>
+    </rPh>
+    <rPh sb="313" eb="315">
+      <t>トウメイ</t>
+    </rPh>
+    <rPh sb="320" eb="321">
+      <t>ウ</t>
+    </rPh>
+    <rPh sb="322" eb="323">
+      <t>リョウ</t>
+    </rPh>
+    <rPh sb="327" eb="329">
+      <t>ガシツ</t>
+    </rPh>
+    <rPh sb="330" eb="332">
+      <t>テイカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>相手を尊敬すること、向こうからの意見をしっかり聞くこと
+本社の要素開発部門よりも、多くの課題を現場は持っている
+そのため、なぜ行われているのかというヒヤリングを適切に行う必要がある
+Ex）評価用チャートを使用してプライマ量を決定するときに、評価用チャートを左上から順番に見るのではなく、ランダムにチェックしているように見えていた
+理由を聞いたところ、その順番に見たほうが効率的にプライマ量を決定できると聞いた
+一見、素人からすると非効率的に見えるような方法でも、そこには何かしらの理由があるので、そこをしっかり聞き出すことが重要であると考えている</t>
+    <rPh sb="0" eb="2">
+      <t>アイテ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ソンケイ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>ム</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>イケン</t>
+    </rPh>
+    <rPh sb="23" eb="24">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="28" eb="30">
+      <t>ホンシャ</t>
+    </rPh>
+    <rPh sb="31" eb="35">
+      <t>ヨウソカイハツ</t>
+    </rPh>
+    <rPh sb="35" eb="37">
+      <t>ブモン</t>
+    </rPh>
+    <rPh sb="41" eb="42">
+      <t>オオ</t>
+    </rPh>
+    <rPh sb="44" eb="46">
+      <t>カダイ</t>
+    </rPh>
+    <rPh sb="47" eb="49">
+      <t>ゲンバ</t>
+    </rPh>
+    <rPh sb="50" eb="51">
+      <t>モ</t>
+    </rPh>
+    <rPh sb="63" eb="64">
+      <t>オコナ</t>
+    </rPh>
+    <rPh sb="80" eb="82">
+      <t>テキセツ</t>
+    </rPh>
+    <rPh sb="83" eb="84">
+      <t>オコナ</t>
+    </rPh>
+    <rPh sb="85" eb="87">
+      <t>ヒツヨウ</t>
+    </rPh>
+    <rPh sb="95" eb="97">
+      <t>ヒョウカ</t>
+    </rPh>
+    <rPh sb="97" eb="98">
+      <t>ヨウ</t>
+    </rPh>
+    <rPh sb="103" eb="105">
+      <t>シヨウ</t>
+    </rPh>
+    <rPh sb="111" eb="112">
+      <t>リョウ</t>
+    </rPh>
+    <rPh sb="113" eb="115">
+      <t>ケッテイ</t>
+    </rPh>
+    <rPh sb="121" eb="123">
+      <t>ヒョウカ</t>
+    </rPh>
+    <rPh sb="123" eb="124">
+      <t>ヨウ</t>
+    </rPh>
+    <rPh sb="129" eb="131">
+      <t>ヒダリウエ</t>
+    </rPh>
+    <rPh sb="133" eb="135">
+      <t>ジュンバン</t>
+    </rPh>
+    <rPh sb="136" eb="137">
+      <t>ミ</t>
+    </rPh>
+    <rPh sb="160" eb="161">
+      <t>ミ</t>
+    </rPh>
+    <rPh sb="166" eb="168">
+      <t>リユウ</t>
+    </rPh>
+    <rPh sb="169" eb="170">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="178" eb="180">
+      <t>ジュンバン</t>
+    </rPh>
+    <rPh sb="181" eb="182">
+      <t>ミ</t>
+    </rPh>
+    <rPh sb="186" eb="189">
+      <t>コウリツテキ</t>
+    </rPh>
+    <rPh sb="194" eb="195">
+      <t>リョウ</t>
+    </rPh>
+    <rPh sb="196" eb="198">
+      <t>ケッテイ</t>
+    </rPh>
+    <rPh sb="202" eb="203">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="206" eb="208">
+      <t>イッケン</t>
+    </rPh>
+    <rPh sb="209" eb="211">
+      <t>シロウト</t>
+    </rPh>
+    <rPh sb="216" eb="220">
+      <t>ヒコウリツテキ</t>
+    </rPh>
+    <rPh sb="221" eb="222">
+      <t>ミ</t>
+    </rPh>
+    <rPh sb="227" eb="229">
+      <t>ホウホウ</t>
+    </rPh>
+    <rPh sb="236" eb="237">
+      <t>ナニ</t>
+    </rPh>
+    <rPh sb="241" eb="243">
+      <t>リユウ</t>
+    </rPh>
+    <rPh sb="256" eb="257">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="258" eb="259">
+      <t>ダ</t>
+    </rPh>
+    <rPh sb="263" eb="265">
+      <t>ジュウヨウ</t>
+    </rPh>
+    <rPh sb="269" eb="270">
+      <t>カンガ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t xml:space="preserve">課の課題は、個別製品や担当者ごとに得られた知見が分散し、横展開しにくいことです。Mogamiで得た紙特性、評価結果、対応条件を共通の観点で整理し、他テーマ（IJにかかわらず電子写真）でも検索・再利用できる形にすることで、検討の重複を減らし開発速度を上げたいと考えています。例えば、自分のプロジェクトで起きた問題や課題の解決については、部会で共有する。
+</t>
+    <rPh sb="49" eb="50">
+      <t>カミ</t>
+    </rPh>
+    <rPh sb="86" eb="90">
+      <t>デンシシャシン</t>
+    </rPh>
+    <rPh sb="136" eb="137">
+      <t>タト</t>
+    </rPh>
+    <rPh sb="140" eb="142">
+      <t>ジブン</t>
+    </rPh>
+    <rPh sb="150" eb="151">
+      <t>オ</t>
+    </rPh>
+    <rPh sb="153" eb="155">
+      <t>モンダイ</t>
+    </rPh>
+    <rPh sb="156" eb="158">
+      <t>カダイ</t>
+    </rPh>
+    <rPh sb="159" eb="161">
+      <t>カイケツ</t>
+    </rPh>
+    <rPh sb="167" eb="169">
+      <t>ブカイ</t>
+    </rPh>
+    <rPh sb="170" eb="172">
+      <t>キョウユウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>G3になったら、ネットワークを作って他の人を巻き込みながらプロジェクトを牽引していきたいと思っている
+今回のプライマのプロジェクトも化学系の知識を必要とするため、画像処理技術を専門としている自部門や自分のチームメンバーだけで進めることは困難だった。そこで、デジプリのインクの専門家を巻き込んで、プライマの画質への寄与を解明できたと考えている
+そのため、課題を解決するために自分たちの領域で解決が難しいと思ったときに、適切な人を巻き込んでプロジェクトを進める役割を担いたい</t>
+    <rPh sb="15" eb="16">
+      <t>ツク</t>
+    </rPh>
+    <rPh sb="18" eb="19">
+      <t>ホカ</t>
+    </rPh>
+    <rPh sb="20" eb="21">
+      <t>ヒト</t>
+    </rPh>
+    <rPh sb="22" eb="23">
+      <t>マ</t>
+    </rPh>
+    <rPh sb="24" eb="25">
+      <t>コ</t>
+    </rPh>
+    <rPh sb="36" eb="38">
+      <t>ケンイン</t>
+    </rPh>
+    <rPh sb="45" eb="46">
+      <t>オモ</t>
+    </rPh>
+    <rPh sb="52" eb="54">
+      <t>コンカイ</t>
+    </rPh>
+    <rPh sb="67" eb="70">
+      <t>カガクケイ</t>
+    </rPh>
+    <rPh sb="71" eb="73">
+      <t>チシキ</t>
+    </rPh>
+    <rPh sb="74" eb="76">
+      <t>ヒツヨウ</t>
+    </rPh>
+    <rPh sb="89" eb="91">
+      <t>センモン</t>
+    </rPh>
+    <rPh sb="96" eb="99">
+      <t>ジブモン</t>
+    </rPh>
+    <rPh sb="177" eb="179">
+      <t>カダイ</t>
+    </rPh>
+    <rPh sb="180" eb="182">
+      <t>カイケツ</t>
+    </rPh>
+    <rPh sb="187" eb="189">
+      <t>ジブン</t>
+    </rPh>
+    <rPh sb="192" eb="194">
+      <t>リョウイキ</t>
+    </rPh>
+    <rPh sb="195" eb="197">
+      <t>カイケツ</t>
+    </rPh>
+    <rPh sb="198" eb="199">
+      <t>ムズカ</t>
+    </rPh>
+    <rPh sb="202" eb="203">
+      <t>オモ</t>
+    </rPh>
+    <rPh sb="209" eb="211">
+      <t>テキセツ</t>
+    </rPh>
+    <rPh sb="212" eb="213">
+      <t>ヒト</t>
+    </rPh>
+    <rPh sb="214" eb="215">
+      <t>マ</t>
+    </rPh>
+    <rPh sb="216" eb="217">
+      <t>コ</t>
+    </rPh>
+    <rPh sb="226" eb="227">
+      <t>スス</t>
+    </rPh>
+    <rPh sb="229" eb="231">
+      <t>ヤクワリ</t>
+    </rPh>
+    <rPh sb="232" eb="233">
+      <t>ニナ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>事業部の人を巻き込んで仕事を進める機会が多くなると思う。今でも適切な人を巻き込めるようにするために、自部門の他のメンバーが何をしていて、どの分野に強いかどうかはプロジェクトの週報を読むことで確認はしている。ただ、現場に行く機会がいまだ少ないので、事業部の人とのネットワークが薄いため、自部門の上司を介してつないでもらうことが多い。G3になったら、他部門との交渉事の機会が増えるため、現場に行く機会が増えそこで課題を見つけたり、現場の人と会話する機会が増えると思う。そうすると、事業部とのネットワークが増え、自分で巻き込んで仕事を進めていけるようになると考える</t>
+    <rPh sb="0" eb="3">
+      <t>ジギョウブ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>ヒト</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>マ</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>コ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>シゴト</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>スス</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>キカイ</t>
+    </rPh>
+    <rPh sb="20" eb="21">
+      <t>オオ</t>
+    </rPh>
+    <rPh sb="25" eb="26">
+      <t>オモ</t>
+    </rPh>
+    <rPh sb="28" eb="29">
+      <t>イマ</t>
+    </rPh>
+    <rPh sb="31" eb="33">
+      <t>テキセツ</t>
+    </rPh>
+    <rPh sb="34" eb="35">
+      <t>ヒト</t>
+    </rPh>
+    <rPh sb="36" eb="37">
+      <t>マ</t>
+    </rPh>
+    <rPh sb="38" eb="39">
+      <t>コ</t>
+    </rPh>
+    <rPh sb="50" eb="53">
+      <t>ジブモン</t>
+    </rPh>
+    <rPh sb="54" eb="55">
+      <t>ホカ</t>
+    </rPh>
+    <rPh sb="61" eb="62">
+      <t>ナニ</t>
+    </rPh>
+    <rPh sb="70" eb="72">
+      <t>ブンヤ</t>
+    </rPh>
+    <rPh sb="73" eb="74">
+      <t>ツヨ</t>
+    </rPh>
+    <rPh sb="87" eb="89">
+      <t>シュウホウ</t>
+    </rPh>
+    <rPh sb="90" eb="91">
+      <t>ヨ</t>
+    </rPh>
+    <rPh sb="95" eb="97">
+      <t>カクニン</t>
+    </rPh>
+    <rPh sb="106" eb="108">
+      <t>ゲンバ</t>
+    </rPh>
+    <rPh sb="109" eb="110">
+      <t>イ</t>
+    </rPh>
+    <rPh sb="111" eb="113">
+      <t>キカイ</t>
+    </rPh>
+    <rPh sb="117" eb="118">
+      <t>スク</t>
+    </rPh>
+    <rPh sb="123" eb="126">
+      <t>ジギョウブ</t>
+    </rPh>
+    <rPh sb="127" eb="128">
+      <t>ヒト</t>
+    </rPh>
+    <rPh sb="137" eb="138">
+      <t>ウス</t>
+    </rPh>
+    <rPh sb="142" eb="145">
+      <t>ジブモン</t>
+    </rPh>
+    <rPh sb="146" eb="148">
+      <t>ジョウシ</t>
+    </rPh>
+    <rPh sb="149" eb="150">
+      <t>カイ</t>
+    </rPh>
+    <rPh sb="162" eb="163">
+      <t>オオ</t>
+    </rPh>
+    <rPh sb="173" eb="176">
+      <t>タブモン</t>
+    </rPh>
+    <rPh sb="178" eb="181">
+      <t>コウショウゴト</t>
+    </rPh>
+    <rPh sb="182" eb="184">
+      <t>キカイ</t>
+    </rPh>
+    <rPh sb="185" eb="186">
+      <t>フ</t>
+    </rPh>
+    <rPh sb="191" eb="193">
+      <t>ゲンバ</t>
+    </rPh>
+    <rPh sb="194" eb="195">
+      <t>イ</t>
+    </rPh>
+    <rPh sb="196" eb="198">
+      <t>キカイ</t>
+    </rPh>
+    <rPh sb="199" eb="200">
+      <t>フ</t>
+    </rPh>
+    <rPh sb="204" eb="206">
+      <t>カダイ</t>
+    </rPh>
+    <rPh sb="207" eb="208">
+      <t>ミ</t>
+    </rPh>
+    <rPh sb="213" eb="215">
+      <t>ゲンバ</t>
+    </rPh>
+    <rPh sb="216" eb="217">
+      <t>ヒト</t>
+    </rPh>
+    <rPh sb="218" eb="220">
+      <t>カイワ</t>
+    </rPh>
+    <rPh sb="222" eb="224">
+      <t>キカイ</t>
+    </rPh>
+    <rPh sb="225" eb="226">
+      <t>フ</t>
+    </rPh>
+    <rPh sb="229" eb="230">
+      <t>オモ</t>
+    </rPh>
+    <rPh sb="238" eb="241">
+      <t>ジギョウブ</t>
+    </rPh>
+    <rPh sb="250" eb="251">
+      <t>フ</t>
+    </rPh>
+    <rPh sb="253" eb="255">
+      <t>ジブン</t>
+    </rPh>
+    <rPh sb="256" eb="257">
+      <t>マ</t>
+    </rPh>
+    <rPh sb="258" eb="259">
+      <t>コ</t>
+    </rPh>
+    <rPh sb="261" eb="263">
+      <t>シゴト</t>
+    </rPh>
+    <rPh sb="264" eb="265">
+      <t>スス</t>
+    </rPh>
+    <rPh sb="276" eb="277">
+      <t>カンガ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>課題を解決するためにどこの技術や情報が不足しているかを明らかにすることが</t>
+    <rPh sb="0" eb="2">
+      <t>カダイ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>カイケツ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>ギジュツ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>ジョウホウ</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>フソク</t>
+    </rPh>
+    <rPh sb="27" eb="28">
+      <t>アキ</t>
+    </rPh>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -5089,7 +5444,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -5202,6 +5557,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5397,22 +5755,22 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I62"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
+  <dimension ref="A1:I124"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18.75"/>
   <cols>
-    <col min="1" max="1" width="10.6328125" style="2" customWidth="1"/>
-    <col min="2" max="2" width="50.36328125" style="1" customWidth="1"/>
-    <col min="3" max="3" width="107.08984375" customWidth="1"/>
+    <col min="1" max="1" width="10.625" style="2" customWidth="1"/>
+    <col min="2" max="2" width="50.375" style="1" customWidth="1"/>
+    <col min="3" max="3" width="107.125" customWidth="1"/>
     <col min="4" max="4" width="52" style="25" customWidth="1"/>
-    <col min="5" max="5" width="119.08984375" style="6" customWidth="1"/>
-    <col min="6" max="6" width="116.90625" style="6" customWidth="1"/>
-    <col min="7" max="7" width="35.90625" style="3" customWidth="1"/>
-    <col min="8" max="8" width="64.26953125" style="3" customWidth="1"/>
-    <col min="9" max="9" width="111.6328125" style="3" customWidth="1"/>
+    <col min="5" max="5" width="119.125" style="6" customWidth="1"/>
+    <col min="6" max="6" width="116.875" style="6" customWidth="1"/>
+    <col min="7" max="7" width="35.875" style="3" customWidth="1"/>
+    <col min="8" max="8" width="64.25" style="3" customWidth="1"/>
+    <col min="9" max="9" width="111.625" style="3" customWidth="1"/>
     <col min="10" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="13">
+    <row r="1" spans="1:9" ht="13.5">
       <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
@@ -5439,24 +5797,24 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="270">
+    <row r="2" spans="1:9" ht="262.5">
       <c r="A2" s="4">
         <v>0</v>
       </c>
       <c r="B2" s="23" t="s">
+        <v>178</v>
+      </c>
+      <c r="C2" s="18" t="s">
+        <v>278</v>
+      </c>
+      <c r="D2" s="25" t="s">
+        <v>171</v>
+      </c>
+      <c r="E2" s="13" t="s">
         <v>180</v>
       </c>
-      <c r="C2" s="18" t="s">
-        <v>282</v>
-      </c>
-      <c r="D2" s="25" t="s">
-        <v>172</v>
-      </c>
-      <c r="E2" s="13" t="s">
-        <v>182</v>
-      </c>
       <c r="F2" s="20" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>5</v>
@@ -5465,332 +5823,332 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="390">
+    <row r="3" spans="1:9" ht="391.5">
       <c r="A3" s="28"/>
       <c r="B3" s="23" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="C3" s="29" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="E3" s="26"/>
       <c r="F3" s="20"/>
     </row>
-    <row r="4" spans="1:9" ht="252">
+    <row r="4" spans="1:9" ht="262.5">
       <c r="A4" s="4">
         <v>1</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C4" s="18" t="s">
-        <v>281</v>
+        <v>291</v>
       </c>
       <c r="D4" s="25" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E4" s="21" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="F4" s="20" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="G4" s="6"/>
     </row>
-    <row r="5" spans="1:9" ht="78">
+    <row r="5" spans="1:9" ht="81">
       <c r="A5" s="4" t="s">
         <v>7</v>
       </c>
       <c r="B5" s="23" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C5" s="5" t="s">
         <v>55</v>
       </c>
       <c r="E5" s="13" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="F5" s="20"/>
     </row>
-    <row r="6" spans="1:9" ht="91">
+    <row r="6" spans="1:9" ht="94.5">
       <c r="A6" s="4" t="s">
         <v>8</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C6" s="5" t="s">
         <v>56</v>
       </c>
       <c r="E6" s="13" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="F6" s="13"/>
     </row>
-    <row r="7" spans="1:9" ht="130">
+    <row r="7" spans="1:9" ht="121.5">
       <c r="A7" s="4" t="s">
         <v>9</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C7" s="18" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="E7" s="21" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="F7" s="14"/>
       <c r="I7" s="6"/>
     </row>
-    <row r="8" spans="1:9" ht="52">
+    <row r="8" spans="1:9" ht="54">
       <c r="A8" s="4" t="s">
         <v>10</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C8" s="18" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="E8" s="13" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="F8" s="14"/>
     </row>
-    <row r="9" spans="1:9" ht="104">
+    <row r="9" spans="1:9" ht="108">
       <c r="A9" s="4">
         <v>2</v>
       </c>
-      <c r="B9" s="11" t="s">
-        <v>96</v>
+      <c r="B9" s="23" t="s">
+        <v>95</v>
       </c>
       <c r="C9" s="5" t="s">
         <v>57</v>
       </c>
       <c r="E9" s="13" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="F9" s="20"/>
     </row>
-    <row r="10" spans="1:9" ht="117">
+    <row r="10" spans="1:9" ht="108">
       <c r="A10" s="4">
         <v>3</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C10" s="18" t="s">
-        <v>225</v>
+        <v>294</v>
       </c>
       <c r="E10" s="12" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="F10" s="20"/>
     </row>
-    <row r="11" spans="1:9" ht="52">
+    <row r="11" spans="1:9" ht="40.5">
       <c r="A11" s="4" t="s">
         <v>11</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C11" s="17" t="s">
         <v>58</v>
       </c>
       <c r="E11" s="12" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="F11" s="14"/>
     </row>
-    <row r="12" spans="1:9" ht="91">
+    <row r="12" spans="1:9" ht="67.5">
       <c r="A12" s="4" t="s">
         <v>12</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C12" s="18" t="s">
-        <v>175</v>
+        <v>295</v>
       </c>
       <c r="E12" s="13" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="F12" s="14"/>
     </row>
-    <row r="13" spans="1:9" ht="26">
+    <row r="13" spans="1:9">
       <c r="A13" s="4" t="s">
         <v>13</v>
       </c>
       <c r="B13" s="11" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C13" s="17" t="s">
-        <v>59</v>
+        <v>296</v>
       </c>
       <c r="E13" s="13"/>
       <c r="F13" s="14"/>
     </row>
-    <row r="14" spans="1:9" ht="143">
+    <row r="14" spans="1:9" ht="135">
       <c r="A14" s="4">
         <v>4</v>
       </c>
       <c r="B14" s="11" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C14" s="36" t="s">
-        <v>283</v>
+        <v>293</v>
       </c>
       <c r="E14" s="13" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="F14" s="20"/>
       <c r="G14" s="10"/>
     </row>
-    <row r="15" spans="1:9" ht="39">
+    <row r="15" spans="1:9" ht="27">
       <c r="A15" s="4" t="s">
         <v>14</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C15" s="17" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E15" s="13" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="F15" s="20"/>
     </row>
-    <row r="16" spans="1:9" ht="39">
+    <row r="16" spans="1:9" ht="40.5">
       <c r="A16" s="4" t="s">
         <v>15</v>
       </c>
       <c r="B16" s="11" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E16" s="13" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="F16" s="20"/>
     </row>
-    <row r="17" spans="1:6" ht="91">
+    <row r="17" spans="1:6" ht="94.5">
       <c r="A17" s="4" t="s">
         <v>16</v>
       </c>
       <c r="B17" s="11" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C17" s="18" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="E17" s="13" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="F17" s="20"/>
     </row>
-    <row r="18" spans="1:6" ht="26">
+    <row r="18" spans="1:6" ht="27">
       <c r="A18" s="4" t="s">
         <v>17</v>
       </c>
       <c r="B18" s="11" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E18" s="12" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="F18" s="20"/>
     </row>
-    <row r="19" spans="1:6" ht="39">
+    <row r="19" spans="1:6" ht="40.5">
       <c r="A19" s="4" t="s">
         <v>18</v>
       </c>
       <c r="B19" s="11" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C19" s="17" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E19" s="13"/>
       <c r="F19" s="20"/>
     </row>
-    <row r="20" spans="1:6" ht="78">
+    <row r="20" spans="1:6" ht="81">
       <c r="A20" s="4" t="s">
         <v>19</v>
       </c>
       <c r="B20" s="11" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E20" s="13" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="F20" s="20"/>
     </row>
-    <row r="21" spans="1:6" ht="104">
+    <row r="21" spans="1:6" ht="108">
       <c r="A21" s="4" t="s">
         <v>20</v>
       </c>
       <c r="B21" s="23" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="C21" s="18" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="E21" s="13" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" ht="26">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6">
       <c r="A22" s="4" t="s">
         <v>21</v>
       </c>
       <c r="B22" s="11" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E22" s="12" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="F22" s="20"/>
     </row>
-    <row r="23" spans="1:6" ht="52">
+    <row r="23" spans="1:6" ht="54">
       <c r="A23" s="4" t="s">
         <v>22</v>
       </c>
       <c r="B23" s="11" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C23" s="17" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E23" s="13" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="F23" s="20"/>
     </row>
-    <row r="24" spans="1:6" ht="26">
+    <row r="24" spans="1:6" ht="27">
       <c r="A24" s="4" t="s">
         <v>23</v>
       </c>
       <c r="B24" s="11" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C24" s="18" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="E24" s="12" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="F24" s="20"/>
     </row>
@@ -5799,80 +6157,80 @@
         <v>24</v>
       </c>
       <c r="B25" s="19" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C25" s="17"/>
       <c r="E25" s="12"/>
       <c r="F25" s="20"/>
     </row>
-    <row r="26" spans="1:6" ht="26">
+    <row r="26" spans="1:6" ht="27">
       <c r="A26" s="4" t="s">
         <v>25</v>
       </c>
       <c r="B26" s="11" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E26" s="13"/>
       <c r="F26" s="20"/>
     </row>
-    <row r="27" spans="1:6" ht="78">
+    <row r="27" spans="1:6" ht="81">
       <c r="A27" s="4" t="s">
         <v>26</v>
       </c>
       <c r="B27" s="11" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C27" s="30" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="E27" s="13"/>
       <c r="F27" s="14"/>
     </row>
-    <row r="28" spans="1:6" ht="104">
+    <row r="28" spans="1:6" ht="108">
       <c r="A28" s="4" t="s">
         <v>27</v>
       </c>
       <c r="B28" s="11" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E28" s="13" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="F28" s="20"/>
     </row>
-    <row r="29" spans="1:6" ht="26">
+    <row r="29" spans="1:6" ht="27">
       <c r="A29" s="4" t="s">
         <v>28</v>
       </c>
       <c r="B29" s="11" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E29" s="13" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="F29" s="20"/>
     </row>
-    <row r="30" spans="1:6" ht="40.5">
+    <row r="30" spans="1:6" ht="42">
       <c r="A30" s="4" t="s">
         <v>29</v>
       </c>
       <c r="B30" s="11" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E30" s="12" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="F30" s="20"/>
     </row>
@@ -5881,418 +6239,721 @@
         <v>30</v>
       </c>
       <c r="B31" s="11" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C31" s="5"/>
       <c r="E31" s="22"/>
       <c r="F31" s="20"/>
     </row>
-    <row r="32" spans="1:6" ht="26">
+    <row r="32" spans="1:6" ht="27">
       <c r="A32" s="4" t="s">
         <v>31</v>
       </c>
       <c r="B32" s="11" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E32" s="13" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="F32" s="20"/>
     </row>
-    <row r="33" spans="1:9" ht="39">
+    <row r="33" spans="1:9" ht="40.5">
       <c r="A33" s="4" t="s">
         <v>32</v>
       </c>
       <c r="B33" s="11" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E33" s="12" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="F33" s="13"/>
       <c r="I33" s="6"/>
     </row>
-    <row r="34" spans="1:9" ht="26">
+    <row r="34" spans="1:9" ht="27">
       <c r="A34" s="4" t="s">
         <v>33</v>
       </c>
       <c r="B34" s="11" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E34" s="12" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="F34" s="20"/>
     </row>
-    <row r="35" spans="1:9" ht="26">
+    <row r="35" spans="1:9" ht="27">
       <c r="A35" s="4" t="s">
         <v>34</v>
       </c>
       <c r="B35" s="11" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E35" s="13"/>
       <c r="F35" s="20"/>
     </row>
-    <row r="36" spans="1:9" ht="26">
+    <row r="36" spans="1:9" ht="27">
       <c r="A36" s="4" t="s">
         <v>35</v>
       </c>
       <c r="B36" s="11" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E36" s="13" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="F36" s="20"/>
     </row>
-    <row r="37" spans="1:9" ht="52">
+    <row r="37" spans="1:9" ht="54">
       <c r="A37" s="4" t="s">
         <v>36</v>
       </c>
       <c r="B37" s="11" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E37" s="13" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="F37" s="20"/>
     </row>
-    <row r="38" spans="1:9" ht="65">
+    <row r="38" spans="1:9" ht="54">
       <c r="A38" s="4" t="s">
         <v>37</v>
       </c>
       <c r="B38" s="11" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E38" s="13" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="F38" s="20"/>
     </row>
-    <row r="39" spans="1:9" ht="81">
+    <row r="39" spans="1:9" ht="84">
       <c r="A39" s="4" t="s">
         <v>38</v>
       </c>
       <c r="B39" s="11" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E39" s="13" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="F39" s="14"/>
     </row>
-    <row r="40" spans="1:9" ht="39">
+    <row r="40" spans="1:9" ht="40.5">
       <c r="A40" s="4" t="s">
         <v>39</v>
       </c>
       <c r="B40" s="11" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E40" s="13"/>
       <c r="F40" s="15"/>
     </row>
-    <row r="41" spans="1:9" ht="39">
+    <row r="41" spans="1:9" ht="27">
       <c r="A41" s="4" t="s">
         <v>40</v>
       </c>
       <c r="B41" s="37" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E41" s="13"/>
       <c r="F41" s="13"/>
     </row>
-    <row r="42" spans="1:9" ht="26">
+    <row r="42" spans="1:9" ht="27">
       <c r="A42" s="4" t="s">
         <v>41</v>
       </c>
       <c r="B42" s="11" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E42" s="13"/>
       <c r="F42" s="13"/>
     </row>
-    <row r="43" spans="1:9" ht="26">
+    <row r="43" spans="1:9" ht="27">
       <c r="A43" s="4" t="s">
         <v>42</v>
       </c>
       <c r="B43" s="11" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C43" s="5"/>
       <c r="E43" s="13"/>
       <c r="F43" s="13"/>
     </row>
-    <row r="44" spans="1:9" ht="39">
+    <row r="44" spans="1:9" ht="40.5">
       <c r="A44" s="4" t="s">
         <v>43</v>
       </c>
       <c r="B44" s="11" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E44" s="13" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="F44" s="13"/>
     </row>
-    <row r="45" spans="1:9" ht="66.5">
+    <row r="45" spans="1:9" ht="69">
       <c r="A45" s="4" t="s">
         <v>44</v>
       </c>
       <c r="B45" s="11" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C45" s="17" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E45" s="13" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="F45" s="13"/>
     </row>
-    <row r="46" spans="1:9" ht="39">
+    <row r="46" spans="1:9" ht="27">
       <c r="A46" s="4" t="s">
         <v>45</v>
       </c>
       <c r="B46" s="11" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C46" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E46" s="13" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="F46" s="13"/>
     </row>
-    <row r="47" spans="1:9" ht="26">
+    <row r="47" spans="1:9" ht="27">
       <c r="A47" s="4" t="s">
         <v>46</v>
       </c>
       <c r="B47" s="11" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C47" s="5"/>
       <c r="E47" s="22"/>
       <c r="F47" s="13"/>
     </row>
-    <row r="48" spans="1:9" ht="26">
+    <row r="48" spans="1:9" ht="27">
       <c r="A48" s="4" t="s">
         <v>47</v>
       </c>
       <c r="B48" s="11" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C48" s="5"/>
       <c r="E48" s="22"/>
       <c r="F48" s="13"/>
     </row>
-    <row r="49" spans="1:6" ht="26">
+    <row r="49" spans="1:6" ht="27">
       <c r="A49" s="4" t="s">
         <v>48</v>
       </c>
       <c r="B49" s="11" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E49" s="13"/>
       <c r="F49" s="13"/>
     </row>
-    <row r="50" spans="1:6" ht="39">
+    <row r="50" spans="1:6" ht="27">
       <c r="A50" s="4" t="s">
         <v>49</v>
       </c>
       <c r="B50" s="11" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C50" s="5" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E50" s="13" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="F50" s="13"/>
     </row>
-    <row r="51" spans="1:6" ht="40.5">
+    <row r="51" spans="1:6" ht="42">
       <c r="A51" s="4" t="s">
         <v>50</v>
       </c>
       <c r="B51" s="11" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C51" s="5" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E51" s="13" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="F51" s="13"/>
     </row>
-    <row r="52" spans="1:6" ht="39">
+    <row r="52" spans="1:6" ht="40.5">
       <c r="A52" s="4" t="s">
         <v>51</v>
       </c>
       <c r="B52" s="11" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C52" s="5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E52" s="13" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="F52" s="13"/>
     </row>
-    <row r="53" spans="1:6" ht="91">
+    <row r="53" spans="1:6" ht="94.5">
       <c r="A53" s="4"/>
       <c r="B53" s="11" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C53" s="5" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E53" s="12" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="F53" s="13"/>
     </row>
     <row r="54" spans="1:6">
       <c r="A54" s="4"/>
       <c r="B54" s="11" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C54" s="27"/>
       <c r="E54" s="13"/>
       <c r="F54" s="13"/>
     </row>
-    <row r="55" spans="1:6" ht="26">
+    <row r="55" spans="1:6" ht="27">
       <c r="A55" s="4"/>
       <c r="B55" s="11" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C55" s="5"/>
       <c r="E55" s="13" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="F55" s="13"/>
     </row>
     <row r="56" spans="1:6">
       <c r="A56" s="4"/>
       <c r="B56" s="11" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C56" s="5"/>
       <c r="E56" s="13" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="F56" s="13"/>
     </row>
-    <row r="57" spans="1:6" ht="39">
+    <row r="57" spans="1:6" ht="40.5">
       <c r="A57" s="4"/>
       <c r="B57" s="11" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C57" s="5"/>
       <c r="E57" s="13" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="F57" s="13"/>
     </row>
-    <row r="58" spans="1:6" ht="39">
+    <row r="58" spans="1:6" ht="40.5">
       <c r="A58" s="4"/>
       <c r="B58" s="11" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C58" s="5"/>
       <c r="E58" s="12" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="F58" s="13"/>
     </row>
-    <row r="59" spans="1:6" ht="26">
+    <row r="59" spans="1:6" ht="27">
       <c r="A59" s="4"/>
       <c r="B59" s="11" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C59" s="5" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E59" s="13"/>
       <c r="F59" s="13"/>
     </row>
-    <row r="60" spans="1:6" ht="39">
+    <row r="60" spans="1:6" ht="40.5">
       <c r="A60" s="4"/>
       <c r="B60" s="11" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C60" s="5" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E60" s="12" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="F60" s="13"/>
     </row>
-    <row r="61" spans="1:6" ht="39">
+    <row r="61" spans="1:6" ht="27">
       <c r="A61" s="4" t="s">
         <v>52</v>
       </c>
       <c r="B61" s="11" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C61" s="5"/>
       <c r="E61" s="13" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="62" spans="1:6" ht="39">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" ht="40.5">
       <c r="A62" s="4" t="s">
         <v>53</v>
       </c>
       <c r="B62" s="11" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C62" s="5"/>
       <c r="E62" s="13" t="s">
-        <v>224</v>
+        <v>222</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6">
+      <c r="B64" s="24" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="65" spans="2:2">
+      <c r="B65" s="24" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="66" spans="2:2">
+      <c r="B66" s="24" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="67" spans="2:2">
+      <c r="B67" s="24" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="68" spans="2:2">
+      <c r="B68" s="24" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="69" spans="2:2">
+      <c r="B69" s="24" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="70" spans="2:2">
+      <c r="B70" s="24" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="71" spans="2:2">
+      <c r="B71" s="24" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="72" spans="2:2">
+      <c r="B72" s="24" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="73" spans="2:2">
+      <c r="B73" s="24" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="74" spans="2:2">
+      <c r="B74" s="24" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="75" spans="2:2">
+      <c r="B75" s="24" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="76" spans="2:2">
+      <c r="B76" s="24" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="77" spans="2:2">
+      <c r="B77" s="24" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="78" spans="2:2">
+      <c r="B78" s="24" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="79" spans="2:2">
+      <c r="B79" s="24" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="80" spans="2:2">
+      <c r="B80" s="24" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="81" spans="2:2">
+      <c r="B81" s="24" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="82" spans="2:2">
+      <c r="B82" s="24" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="83" spans="2:2">
+      <c r="B83" s="24" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="84" spans="2:2" ht="30">
+      <c r="B84" s="31" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="85" spans="2:2">
+      <c r="B85" s="31" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="86" spans="2:2">
+      <c r="B86" s="31" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="87" spans="2:2">
+      <c r="B87" s="31" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="88" spans="2:2">
+      <c r="B88" s="31" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="89" spans="2:2">
+      <c r="B89" s="31" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="90" spans="2:2">
+      <c r="B90" s="31" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="91" spans="2:2">
+      <c r="B91" s="31" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="92" spans="2:2">
+      <c r="B92" s="31" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="93" spans="2:2">
+      <c r="B93" s="31" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="94" spans="2:2">
+      <c r="B94" s="31" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="95" spans="2:2">
+      <c r="B95" s="24" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="96" spans="2:2">
+      <c r="B96" s="33" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="97" spans="2:2">
+      <c r="B97" s="33" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="98" spans="2:2">
+      <c r="B98" s="33" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="99" spans="2:2">
+      <c r="B99" s="33" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="100" spans="2:2">
+      <c r="B100" s="33" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="101" spans="2:2">
+      <c r="B101" s="24" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="102" spans="2:2">
+      <c r="B102" s="33" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="103" spans="2:2">
+      <c r="B103" s="33" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="104" spans="2:2">
+      <c r="B104" s="33" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="105" spans="2:2">
+      <c r="B105" s="33" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="106" spans="2:2">
+      <c r="B106" s="33" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="107" spans="2:2">
+      <c r="B107" s="35" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="108" spans="2:2">
+      <c r="B108" s="33" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="109" spans="2:2">
+      <c r="B109" s="33" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="110" spans="2:2">
+      <c r="B110" s="33" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="111" spans="2:2">
+      <c r="B111" s="35" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="112" spans="2:2">
+      <c r="B112" s="33" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="113" spans="2:2">
+      <c r="B113" s="33" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="114" spans="2:2">
+      <c r="B114" s="33" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="115" spans="2:2">
+      <c r="B115" s="24"/>
+    </row>
+    <row r="116" spans="2:2">
+      <c r="B116" s="34" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="117" spans="2:2">
+      <c r="B117" s="34" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="118" spans="2:2">
+      <c r="B118" s="34" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="119" spans="2:2">
+      <c r="B119" s="34" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="120" spans="2:2">
+      <c r="B120" s="34" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="121" spans="2:2">
+      <c r="B121" s="34" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="122" spans="2:2">
+      <c r="B122" s="34" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="123" spans="2:2">
+      <c r="B123" s="34" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="124" spans="2:2">
+      <c r="B124" s="34" t="s">
+        <v>289</v>
       </c>
     </row>
   </sheetData>
@@ -6305,41 +6966,41 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C945A8A3-E413-4358-BBE4-EF5A44242598}">
   <dimension ref="A1:A12"/>
-  <sheetFormatPr defaultRowHeight="13"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="34" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
     </row>
     <row r="2" spans="1:1">
       <c r="A2" s="34" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="34" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" s="34" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
     </row>
     <row r="12" spans="1:1">
       <c r="A12" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
     </row>
   </sheetData>
@@ -6351,10 +7012,10 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:B21"/>
-  <sheetFormatPr defaultRowHeight="13"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="150.36328125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="103.36328125" customWidth="1"/>
+    <col min="1" max="1" width="150.375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="103.375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
@@ -6363,125 +7024,125 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="24" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B2" s="24"/>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="24" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B3" s="24"/>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="24" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B4" s="24"/>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="24" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B5" s="24"/>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="24" t="s">
+        <v>154</v>
+      </c>
+      <c r="B6" s="24"/>
+    </row>
+    <row r="7" spans="1:2" ht="54">
+      <c r="A7" s="24" t="s">
         <v>155</v>
       </c>
-      <c r="B6" s="24"/>
-    </row>
-    <row r="7" spans="1:2" ht="52">
-      <c r="A7" s="24" t="s">
-        <v>156</v>
-      </c>
       <c r="B7" s="23" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="24" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B8" s="24"/>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="24" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B9" s="24"/>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="24" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B10" s="24"/>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="24" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B11" s="24"/>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="24" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B12" s="24"/>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="24" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B13" s="24"/>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="24" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B14" s="24"/>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="24" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B15" s="24"/>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="24" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B16" s="24"/>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="24" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B17" s="24"/>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="24" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B18" s="24"/>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="24" t="s">
+        <v>167</v>
+      </c>
+      <c r="B19" s="24"/>
+    </row>
+    <row r="20" spans="1:2" ht="67.5">
+      <c r="A20" s="24" t="s">
         <v>168</v>
       </c>
-      <c r="B19" s="24"/>
-    </row>
-    <row r="20" spans="1:2" ht="65">
-      <c r="A20" s="24" t="s">
-        <v>169</v>
-      </c>
       <c r="B20" s="23" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="24" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B21" s="24"/>
     </row>
@@ -6494,98 +7155,98 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:B11"/>
-  <sheetFormatPr defaultRowHeight="13"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="69.6328125" customWidth="1"/>
-    <col min="2" max="2" width="66.36328125" customWidth="1"/>
+    <col min="1" max="1" width="69.625" customWidth="1"/>
+    <col min="2" max="2" width="66.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="58">
+    <row r="1" spans="1:2" ht="60">
       <c r="A1" s="31" t="s">
+        <v>225</v>
+      </c>
+      <c r="B1" s="32" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" ht="54.95" customHeight="1">
+      <c r="A2" s="31" t="s">
+        <v>226</v>
+      </c>
+      <c r="B2" s="32" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="54.95" customHeight="1">
+      <c r="A3" s="31" t="s">
+        <v>227</v>
+      </c>
+      <c r="B3" s="32" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="90">
+      <c r="A4" s="31" t="s">
         <v>228</v>
       </c>
-      <c r="B1" s="32" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" ht="55" customHeight="1">
-      <c r="A2" s="31" t="s">
+      <c r="B4" s="32" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" ht="54.95" customHeight="1">
+      <c r="A5" s="31" t="s">
         <v>229</v>
       </c>
-      <c r="B2" s="32" t="s">
+      <c r="B5" s="32" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" ht="54.95" customHeight="1">
+      <c r="A6" s="31" t="s">
+        <v>230</v>
+      </c>
+      <c r="B6" s="32" t="s">
         <v>239</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="55" customHeight="1">
-      <c r="A3" s="31" t="s">
-        <v>230</v>
-      </c>
-      <c r="B3" s="32" t="s">
+    <row r="7" spans="1:2" ht="60">
+      <c r="A7" s="31" t="s">
+        <v>231</v>
+      </c>
+      <c r="B7" s="32" t="s">
         <v>240</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="87">
-      <c r="A4" s="31" t="s">
-        <v>231</v>
-      </c>
-      <c r="B4" s="32" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" ht="55" customHeight="1">
-      <c r="A5" s="31" t="s">
+    <row r="8" spans="1:2" ht="60">
+      <c r="A8" s="31" t="s">
         <v>232</v>
       </c>
-      <c r="B5" s="32" t="s">
+      <c r="B8" s="32" t="s">
         <v>241</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="55" customHeight="1">
-      <c r="A6" s="31" t="s">
+    <row r="9" spans="1:2" ht="54.95" customHeight="1">
+      <c r="A9" s="31" t="s">
         <v>233</v>
       </c>
-      <c r="B6" s="32" t="s">
+      <c r="B9" s="32" t="s">
         <v>242</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="58">
-      <c r="A7" s="31" t="s">
+    <row r="10" spans="1:2" ht="54.95" customHeight="1">
+      <c r="A10" s="31" t="s">
         <v>234</v>
       </c>
-      <c r="B7" s="32" t="s">
+      <c r="B10" s="32" t="s">
         <v>243</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="58">
-      <c r="A8" s="31" t="s">
+    <row r="11" spans="1:2" ht="54.95" customHeight="1">
+      <c r="A11" s="31" t="s">
         <v>235</v>
       </c>
-      <c r="B8" s="32" t="s">
+      <c r="B11" s="32" t="s">
         <v>244</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" ht="55" customHeight="1">
-      <c r="A9" s="31" t="s">
-        <v>236</v>
-      </c>
-      <c r="B9" s="32" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" ht="55" customHeight="1">
-      <c r="A10" s="31" t="s">
-        <v>237</v>
-      </c>
-      <c r="B10" s="32" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" ht="55" customHeight="1">
-      <c r="A11" s="31" t="s">
-        <v>238</v>
-      </c>
-      <c r="B11" s="32" t="s">
-        <v>247</v>
       </c>
     </row>
   </sheetData>
@@ -6597,10 +7258,10 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{05FA0C31-4B39-4CC9-AFFE-ADB97979182D}">
   <dimension ref="A1:B21"/>
-  <sheetFormatPr defaultRowHeight="13"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="150.36328125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="103.36328125" customWidth="1"/>
+    <col min="1" max="1" width="150.375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="103.375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
@@ -6609,39 +7270,39 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="24" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B2" s="24"/>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="33" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="B3" s="24"/>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="33" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="B4" s="24"/>
     </row>
-    <row r="5" spans="1:2" ht="65">
+    <row r="5" spans="1:2" ht="67.5">
       <c r="A5" s="33" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="B5" s="23" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="33" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="B6" s="24"/>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="33" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="B7" s="23"/>
     </row>
@@ -6693,10 +7354,10 @@
       <c r="A19" s="24"/>
       <c r="B19" s="24"/>
     </row>
-    <row r="20" spans="1:2" ht="65">
+    <row r="20" spans="1:2" ht="67.5">
       <c r="A20" s="24"/>
       <c r="B20" s="23" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -6712,10 +7373,10 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E3B1E147-F943-43CF-88AE-86DE70DEEA3B}">
   <dimension ref="A1:B21"/>
-  <sheetFormatPr defaultRowHeight="13"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="150.36328125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="103.36328125" customWidth="1"/>
+    <col min="1" max="1" width="150.375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="103.375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
@@ -6724,91 +7385,91 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="24" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B2" s="24"/>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="33" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="B3" s="24"/>
     </row>
-    <row r="4" spans="1:2" ht="39">
+    <row r="4" spans="1:2" ht="40.5">
       <c r="A4" s="33" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="B4" s="23" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="33" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="B5" s="23"/>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="33" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="B6" s="24"/>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="33" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="B7" s="23"/>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="35" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="B8" s="33" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="33" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="B9" s="24"/>
     </row>
-    <row r="10" spans="1:2" ht="39">
+    <row r="10" spans="1:2" ht="40.5">
       <c r="A10" s="33" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="B10" s="23" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="33" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="B11" s="24"/>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="35" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="B12" s="24"/>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="33" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="B13" s="24"/>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="33" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="B14" s="24"/>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="33" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="B15" s="24"/>
     </row>
@@ -6828,10 +7489,10 @@
       <c r="A19" s="24"/>
       <c r="B19" s="24"/>
     </row>
-    <row r="20" spans="1:2" ht="65">
+    <row r="20" spans="1:2" ht="67.5">
       <c r="A20" s="24"/>
       <c r="B20" s="23" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -6848,64 +7509,67 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4E6BF410-1D86-4886-AF32-D2372AA65DBD}">
   <dimension ref="A1:B9"/>
-  <sheetFormatPr defaultRowHeight="13"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="51.81640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="43.08984375" customWidth="1"/>
+    <col min="1" max="1" width="51.875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="119.375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="34" t="s">
-        <v>284</v>
+        <v>279</v>
       </c>
       <c r="B1" s="34" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="34" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="34" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="B3" s="34" t="s">
-        <v>288</v>
+        <v>283</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="34" t="s">
-        <v>289</v>
+        <v>284</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="34" t="s">
-        <v>290</v>
+        <v>285</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="34" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" ht="108">
       <c r="A7" s="34" t="s">
+        <v>287</v>
+      </c>
+      <c r="B7" s="38" t="s">
         <v>292</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="34" t="s">
-        <v>293</v>
+        <v>288</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="34" t="s">
-        <v>294</v>
+        <v>289</v>
       </c>
       <c r="B9" s="34" t="s">
-        <v>295</v>
+        <v>290</v>
       </c>
     </row>
   </sheetData>

--- a/作業/面接練習/G3面接準備中岫.xlsx
+++ b/作業/面接練習/G3面接準備中岫.xlsx
@@ -8,18 +8,19 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aaa115298\Desktop\G3\G3\G3試験中岫作業\G3\作業\面接練習\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F430D989-68B3-4586-B632-B88DA579EA80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05812F14-A61D-49CD-962A-264C407D2F11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet3" sheetId="5" r:id="rId2"/>
-    <sheet name="1013" sheetId="2" r:id="rId3"/>
-    <sheet name="1014" sheetId="3" r:id="rId4"/>
-    <sheet name="1015" sheetId="4" r:id="rId5"/>
-    <sheet name="1016" sheetId="7" r:id="rId6"/>
-    <sheet name="1019" sheetId="6" r:id="rId7"/>
+    <sheet name="Sheet2" sheetId="8" r:id="rId2"/>
+    <sheet name="Sheet3" sheetId="5" r:id="rId3"/>
+    <sheet name="1013" sheetId="2" r:id="rId4"/>
+    <sheet name="1014" sheetId="3" r:id="rId5"/>
+    <sheet name="1015" sheetId="4" r:id="rId6"/>
+    <sheet name="1016" sheetId="7" r:id="rId7"/>
+    <sheet name="1019" sheetId="6" r:id="rId8"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="365" uniqueCount="297">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="493" uniqueCount="404">
   <si>
     <t>No</t>
   </si>
@@ -5186,6 +5187,327 @@
       <t>アキ</t>
     </rPh>
     <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>◆質問内容</t>
+  </si>
+  <si>
+    <t>・自己紹介をお願いします。</t>
+  </si>
+  <si>
+    <t>・G3とG2の役割の違いは何だと思いますか？</t>
+  </si>
+  <si>
+    <t>・課の構成を教えて下さい。</t>
+  </si>
+  <si>
+    <t>・センター外とも関わってると思うがどんなところと連携していますか？</t>
+  </si>
+  <si>
+    <t>・質感プリントは他社技術と比較してどの位置にいるのですか？</t>
+  </si>
+  <si>
+    <t>・上手くいった、やりがいを感じた経験はありますか？</t>
+  </si>
+  <si>
+    <t>・いつからこのテーマに取り組んでいますか？</t>
+  </si>
+  <si>
+    <t>・グループ内でモチベーションを維持するためにどんなことをしていますか？</t>
+  </si>
+  <si>
+    <t>・今後の展開をどう考えていますか？（技術的な展開</t>
+  </si>
+  <si>
+    <t>・ビジネスに向けて実際に客先に聞いたりすると</t>
+  </si>
+  <si>
+    <t>　コスト等の面で詰められて困ったりしてませんか？</t>
+  </si>
+  <si>
+    <t>・今と異なる仕事に就くことも考えていますか？</t>
+  </si>
+  <si>
+    <t>　例えば営業なんかやれと言われたらどう考えますか？</t>
+  </si>
+  <si>
+    <t>・連携で困ったこと、困ったときに工夫したことなどはありますか？</t>
+  </si>
+  <si>
+    <t>・連携先と上手くやるにはどうしたら良いと思いますか？</t>
+  </si>
+  <si>
+    <t>・最後に進取の気性とは何だと思いますか？よろしければ一言で</t>
+  </si>
+  <si>
+    <t>◆メモ</t>
+  </si>
+  <si>
+    <t>・記憶に漏れがあるかもしれませんが、最後の質問（進取の気性）以外は</t>
+  </si>
+  <si>
+    <t>　過去質問内容メモで見た様なオーソドックスな質問で、雰囲気も和やかでした。</t>
+  </si>
+  <si>
+    <t>・技術開発を行う上で、あなたが一番苦労した点はなんですか？</t>
+  </si>
+  <si>
+    <t>・それをどのように解決しましたか？</t>
+  </si>
+  <si>
+    <t>・後輩と仕事をする上で後輩は言うことを聞いてくれますか？</t>
+  </si>
+  <si>
+    <t>・聞いてくれないときは、どのように解決していますか？</t>
+  </si>
+  <si>
+    <t>・上司と仕事をする上での意見の食い違いはどうしていますか？</t>
+  </si>
+  <si>
+    <t>・進歩の著しい分野の仕事をされていると思いますが、進歩の速さに対し、なに</t>
+  </si>
+  <si>
+    <t>か工夫していることはありますか？</t>
+  </si>
+  <si>
+    <t>・ＣｉＳＲＡとの連携があるという話がありましたが、定期的なやりとりはして</t>
+  </si>
+  <si>
+    <t>いるのですか？</t>
+  </si>
+  <si>
+    <t>・芸術家を相手にしなければならない仕事だと思いますが、そういう面でなにか</t>
+  </si>
+  <si>
+    <t>自己啓発のようなものに取り組んでいますか？</t>
+  </si>
+  <si>
+    <t>・将来のキャリアプランについてお聞きしますが、今の技術をつづけていくか、</t>
+  </si>
+  <si>
+    <t>その他のことをやってみたいか、どのように考えていますか？</t>
+  </si>
+  <si>
+    <t>・質問は以上になりますが、最後に言い残したことや伝えたいことがあれば言っ</t>
+  </si>
+  <si>
+    <t>てください。</t>
+  </si>
+  <si>
+    <t>・想定内の質問で、和やかな雰囲気でした。</t>
+  </si>
+  <si>
+    <t>（人事）</t>
+  </si>
+  <si>
+    <t>・自己紹介を1分程度でしてください</t>
+  </si>
+  <si>
+    <t>・チーム構成を教えてください</t>
+  </si>
+  <si>
+    <t>・あなたの役割を教えてください</t>
+  </si>
+  <si>
+    <t>（技術１）</t>
+  </si>
+  <si>
+    <t>・役割シートの課業にスケジュール立案やリソース管理とありますが何をやっていますか？</t>
+  </si>
+  <si>
+    <t>・現在、ソニーのカメラがシェアを伸ばしてきますよね？ソニーの凄さって何？</t>
+  </si>
+  <si>
+    <t>・それに対してどう対策すべき？</t>
+  </si>
+  <si>
+    <t>・どのようにソニーと自社のカメラ性能を比較しているの？</t>
+  </si>
+  <si>
+    <t>・それはセンサ単体の話？それとも画像処理全体を含めた話？</t>
+  </si>
+  <si>
+    <t>・キヤノンのセンサをどうしていくべきだと考えていますか？</t>
+  </si>
+  <si>
+    <t>（技術２）</t>
+  </si>
+  <si>
+    <t>・他部門と連携していく上で最も重要なことはなんですか？</t>
+  </si>
+  <si>
+    <t>・イメコミとの連携で情報共有はどのように行っているのですか？</t>
+  </si>
+  <si>
+    <t>・川崎-下丸子と場所が離れているため情報共有が大変と思うのですが、工夫していることは？</t>
+  </si>
+  <si>
+    <t>・上司や先輩と仕事を進める上で意見が合わなかったらどうする？</t>
+  </si>
+  <si>
+    <t>・現在の仕事で解決しなければならない最大の課題はなんですか？</t>
+  </si>
+  <si>
+    <t>・それに対してどのように取り組むべきですか？</t>
+  </si>
+  <si>
+    <t>・最後にキャリアプランを教えてください</t>
+  </si>
+  <si>
+    <t>・G3に必要なものは何だと思いますか？</t>
+  </si>
+  <si>
+    <t>（技術）</t>
+  </si>
+  <si>
+    <t>・業務を行う上での課題は何ですか？</t>
+  </si>
+  <si>
+    <t>・技術開発の優先順位を探るのが課題だということでしたが、その優先順位の基</t>
+  </si>
+  <si>
+    <t>　準は何ですか？</t>
+  </si>
+  <si>
+    <t>・開発の課題は何ですか？</t>
+  </si>
+  <si>
+    <t>・技術的な課題は何ですか？</t>
+  </si>
+  <si>
+    <t>・どのような発想でその課題を見つけてきますか？</t>
+  </si>
+  <si>
+    <t>・業務を行う上で困ったことはありましたか？また、今後どのように対応してい</t>
+  </si>
+  <si>
+    <t>　きますか？</t>
+  </si>
+  <si>
+    <t>・あなたが今後の展望として抱いている野望のようなものはありますか？</t>
+  </si>
+  <si>
+    <t>・最後に、進取の気性を一言で表すとどうだと思いますか？</t>
+  </si>
+  <si>
+    <t>・自由視点映像にかかわる圧縮技術についての話が多かった。</t>
+  </si>
+  <si>
+    <t>・基本的には話したいことを話させてもらった印象</t>
+  </si>
+  <si>
+    <t>・課の構成を教えてください。</t>
+  </si>
+  <si>
+    <t>・グループの構成とそこでの役割について教えてください。</t>
+  </si>
+  <si>
+    <t>・G2とG3の違いはなんだと思いますか？</t>
+  </si>
+  <si>
+    <t>・あなたのどういった部分にG3として期待されていると思いますか？</t>
+  </si>
+  <si>
+    <t>・技術開発をするうえで困ったことはなんですか？</t>
+  </si>
+  <si>
+    <t>・今後そういったことが起きないように、何か決めましたか？</t>
+  </si>
+  <si>
+    <t>・SVの最終的な目標はなんですか？</t>
+  </si>
+  <si>
+    <t>・SVの自由視点の現在の技術的な課題を教えてください。</t>
+  </si>
+  <si>
+    <t>・今までの技術開発で周りを巻き込んで課題を解決した事例を教えてください。</t>
+  </si>
+  <si>
+    <t>・先輩と業務に取り組んでいるという話でしたが、コミュニケーションするときにどのようなことに気を付けていますか？</t>
+  </si>
+  <si>
+    <t>・後輩とコミュニケーションするときにどのようなことに気をつけていますか？</t>
+  </si>
+  <si>
+    <t>・後輩が言うこと聞いてくれない時はどうしますか？</t>
+  </si>
+  <si>
+    <t>・特許リーダーをされているということで、昨今なかなかアイデアが出ない状況にあると思いますが、どう工夫していますか？</t>
+  </si>
+  <si>
+    <t>・キャリアプランを教えてください。今やってる技術開発を続けたいですか？</t>
+  </si>
+  <si>
+    <t>・最後に言い残したことや補充したいことがあれば言ってください。</t>
+  </si>
+  <si>
+    <t>・オーソドックスな質問が多く、和やかな雰囲気でした。</t>
+  </si>
+  <si>
+    <t>・技術の内容よりはコミュニケーション系の質問が多かったです。</t>
+  </si>
+  <si>
+    <t>・業務内容について1分程度で教えてください</t>
+  </si>
+  <si>
+    <t>・G2とG3の違いは何と考えていますか？</t>
+  </si>
+  <si>
+    <t>・G3になったときには上司とのコミュニケーションはどのように変化しますか？</t>
+  </si>
+  <si>
+    <t>・ではあなたが考えるG3として行動したことはありますか？</t>
+  </si>
+  <si>
+    <t>・そもそも、職場として臆せず意見を言えるような雰囲気なんですか？</t>
+  </si>
+  <si>
+    <t>・お互いに意見を言い合える状態にするために意識的に行っていることはありますか？</t>
+  </si>
+  <si>
+    <t>(技術１？)</t>
+  </si>
+  <si>
+    <t>・イメージングを進めるためにどのような課題があると考えていますか？（業務上でも、会社としてもなんでも）</t>
+  </si>
+  <si>
+    <t>・上司は↑のあなたの考えについて知っているのですか？</t>
+  </si>
+  <si>
+    <t>・業務を進める上で大きな失敗をしてしまったことはありますか？</t>
+  </si>
+  <si>
+    <t>(技術２？)</t>
+  </si>
+  <si>
+    <t>・チームを動かすためにどのように行動していますか？</t>
+  </si>
+  <si>
+    <t>・コミュニケーションをする上で心がけていることはありますか？</t>
+  </si>
+  <si>
+    <t>・コミュニケーションが上手くできなくて失敗してしまったという例はありますか？</t>
+  </si>
+  <si>
+    <t>・その失敗に対してはどのように対応しましたか？</t>
+  </si>
+  <si>
+    <t>(人事)</t>
+  </si>
+  <si>
+    <t>・最後に今後のキャリアについてどうしていきたいかを教えてください</t>
+  </si>
+  <si>
+    <t>最初に面接官の方に「緊張せず普段通りに話をした方が良い結果につながると思う」</t>
+  </si>
+  <si>
+    <t>と念を押されたのもあり、リラックスして話ができるように心がけました。</t>
+  </si>
+  <si>
+    <t>基本的に、最初に話したところから話題が広がるように展開していたので、</t>
+  </si>
+  <si>
+    <t>突拍子な質問もなく、面接といよりは面談という雰囲気でした。</t>
   </si>
 </sst>
 </file>
@@ -6964,6 +7286,657 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{40E537D0-355C-44F6-821F-B309AC3764BF}">
+  <dimension ref="A1:A139"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1">
+      <c r="A2" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1">
+      <c r="A4" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1">
+      <c r="A5" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1">
+      <c r="A6" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1">
+      <c r="A7" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1">
+      <c r="A8" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1">
+      <c r="A9" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1">
+      <c r="A10" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1">
+      <c r="A11" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1">
+      <c r="A12" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1">
+      <c r="A13" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1">
+      <c r="A14" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1">
+      <c r="A15" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1">
+      <c r="A16" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1">
+      <c r="A17" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1">
+      <c r="A18" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1">
+      <c r="A19" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1">
+      <c r="A20" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1">
+      <c r="A23" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1">
+      <c r="A24" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1">
+      <c r="A25" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1">
+      <c r="A26" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1">
+      <c r="A27" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1">
+      <c r="A28" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1">
+      <c r="A29" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1">
+      <c r="A30" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1">
+      <c r="A31" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1">
+      <c r="A32" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1">
+      <c r="A33" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1">
+      <c r="A34" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1">
+      <c r="A35" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1">
+      <c r="A36" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1">
+      <c r="A37" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1">
+      <c r="A38" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1">
+      <c r="A39" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1">
+      <c r="A40" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1">
+      <c r="A41" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1">
+      <c r="A42" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1">
+      <c r="A43" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1">
+      <c r="A46" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1">
+      <c r="A47" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1">
+      <c r="A48" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1">
+      <c r="A49" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1">
+      <c r="A50" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1">
+      <c r="A51" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1">
+      <c r="A52" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1">
+      <c r="A53" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1">
+      <c r="A54" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="55" spans="1:1">
+      <c r="A55" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="56" spans="1:1">
+      <c r="A56" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="57" spans="1:1">
+      <c r="A57" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="58" spans="1:1">
+      <c r="A58" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="59" spans="1:1">
+      <c r="A59" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="60" spans="1:1">
+      <c r="A60" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="61" spans="1:1">
+      <c r="A61" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="62" spans="1:1">
+      <c r="A62" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="63" spans="1:1">
+      <c r="A63" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="64" spans="1:1">
+      <c r="A64" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="65" spans="1:1">
+      <c r="A65" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="66" spans="1:1">
+      <c r="A66" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="69" spans="1:1">
+      <c r="A69" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="70" spans="1:1">
+      <c r="A70" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="71" spans="1:1">
+      <c r="A71" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="72" spans="1:1">
+      <c r="A72" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="73" spans="1:1">
+      <c r="A73" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="74" spans="1:1">
+      <c r="A74" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="75" spans="1:1">
+      <c r="A75" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="76" spans="1:1">
+      <c r="A76" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="77" spans="1:1">
+      <c r="A77" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="78" spans="1:1">
+      <c r="A78" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="79" spans="1:1">
+      <c r="A79" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="80" spans="1:1">
+      <c r="A80" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="81" spans="1:1">
+      <c r="A81" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="82" spans="1:1">
+      <c r="A82" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="83" spans="1:1">
+      <c r="A83" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="84" spans="1:1">
+      <c r="A84" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="85" spans="1:1">
+      <c r="A85" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="86" spans="1:1">
+      <c r="A86" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="87" spans="1:1">
+      <c r="A87" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="88" spans="1:1">
+      <c r="A88" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="92" spans="1:1">
+      <c r="A92" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="93" spans="1:1">
+      <c r="A93" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="94" spans="1:1">
+      <c r="A94" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="95" spans="1:1">
+      <c r="A95" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="96" spans="1:1">
+      <c r="A96" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="97" spans="1:1">
+      <c r="A97" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="98" spans="1:1">
+      <c r="A98" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="99" spans="1:1">
+      <c r="A99" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="100" spans="1:1">
+      <c r="A100" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="101" spans="1:1">
+      <c r="A101" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="102" spans="1:1">
+      <c r="A102" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="103" spans="1:1">
+      <c r="A103" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="104" spans="1:1">
+      <c r="A104" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="105" spans="1:1">
+      <c r="A105" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="106" spans="1:1">
+      <c r="A106" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="107" spans="1:1">
+      <c r="A107" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="108" spans="1:1">
+      <c r="A108" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="109" spans="1:1">
+      <c r="A109" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="110" spans="1:1">
+      <c r="A110" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="111" spans="1:1">
+      <c r="A111" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="112" spans="1:1">
+      <c r="A112" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="113" spans="1:1">
+      <c r="A113" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="114" spans="1:1">
+      <c r="A114" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="117" spans="1:1">
+      <c r="A117" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="118" spans="1:1">
+      <c r="A118" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="119" spans="1:1">
+      <c r="A119" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="120" spans="1:1">
+      <c r="A120" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="121" spans="1:1">
+      <c r="A121" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="122" spans="1:1">
+      <c r="A122" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="123" spans="1:1">
+      <c r="A123" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="124" spans="1:1">
+      <c r="A124" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="125" spans="1:1">
+      <c r="A125" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="126" spans="1:1">
+      <c r="A126" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="127" spans="1:1">
+      <c r="A127" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="128" spans="1:1">
+      <c r="A128" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="129" spans="1:1">
+      <c r="A129" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="130" spans="1:1">
+      <c r="A130" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="131" spans="1:1">
+      <c r="A131" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="132" spans="1:1">
+      <c r="A132" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="133" spans="1:1">
+      <c r="A133" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="134" spans="1:1">
+      <c r="A134" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="135" spans="1:1">
+      <c r="A135" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="136" spans="1:1">
+      <c r="A136" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="137" spans="1:1">
+      <c r="A137" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="138" spans="1:1">
+      <c r="A138" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="139" spans="1:1">
+      <c r="A139" t="s">
+        <v>403</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C945A8A3-E413-4358-BBE4-EF5A44242598}">
   <dimension ref="A1:A12"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
@@ -7009,7 +7982,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:B21"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
@@ -7152,7 +8125,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:B11"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
@@ -7255,7 +8228,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{05FA0C31-4B39-4CC9-AFFE-ADB97979182D}">
   <dimension ref="A1:B21"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
@@ -7370,7 +8343,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E3B1E147-F943-43CF-88AE-86DE70DEEA3B}">
   <dimension ref="A1:B21"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
@@ -7506,7 +8479,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4E6BF410-1D86-4886-AF32-D2372AA65DBD}">
   <dimension ref="A1:B9"/>
   <sheetFormatPr defaultRowHeight="13.5"/>

--- a/作業/面接練習/G3面接準備中岫.xlsx
+++ b/作業/面接練習/G3面接準備中岫.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aaa115298\Desktop\G3\G3\G3試験中岫作業\G3\作業\面接練習\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05812F14-A61D-49CD-962A-264C407D2F11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{612C5AFA-B74B-4E4B-83AC-8A39F0ED668D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -21,6 +21,8 @@
     <sheet name="1015" sheetId="4" r:id="rId6"/>
     <sheet name="1016" sheetId="7" r:id="rId7"/>
     <sheet name="1019" sheetId="6" r:id="rId8"/>
+    <sheet name="1021" sheetId="9" r:id="rId9"/>
+    <sheet name="Sheet5" sheetId="10" r:id="rId10"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="493" uniqueCount="404">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="519" uniqueCount="430">
   <si>
     <t>No</t>
   </si>
@@ -4518,16 +4520,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>デジタルビジネスプラットフォーム開発本部、ソフトウェア33開発室の中岫茉希と申します。
-私の所属する部門では、プリンタを高画質化するための、物理現象の解析を行っています。
-その中で私は、商業印刷向けのインクジェットプリンタを対象に、「プライマー」と呼ばれる透明なインクと画質との関係の解析を担当しています。
-このプライマーというのは、商業インクジェットプリンタで多種多様な用紙に対応するために、紙に下塗りするものです。
-このとき、プライマーの最適な量は、紙の種類やカラーインクの量によっても異なるため、設計の組み合わせが膨大になってしまいます。
-そこで、プライマーの量と画質との関係を解析することで、最小の評価工数でプライマー量を設計する手法を、デジプリ事業本部と連携して開発し、設計効率の向上に取り組んでいます。
-本日はよろしくお願いいたします。</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>プロジェクトの最終ゴールは？</t>
     <rPh sb="7" eb="9">
       <t>サイシュウ</t>
@@ -5508,6 +5500,199 @@
   </si>
   <si>
     <t>突拍子な質問もなく、面接といよりは面談という雰囲気でした。</t>
+  </si>
+  <si>
+    <t>・サブリーダーとして気をつけていること</t>
+  </si>
+  <si>
+    <t>・評価は自分自身だけ、他のメンバーもやっている？</t>
+  </si>
+  <si>
+    <t>・やりとりで困ったことは？</t>
+  </si>
+  <si>
+    <t>・失敗した経験は？今後それを対策するには？</t>
+  </si>
+  <si>
+    <t>・要求しようと違うものが届いたこと、事前対策としてどうするか？</t>
+  </si>
+  <si>
+    <t>・チームや組織の課題</t>
+  </si>
+  <si>
+    <t>・リーダー像、ロールモデルは？</t>
+  </si>
+  <si>
+    <t>・リーダー像に近づくためにやっていることは？</t>
+  </si>
+  <si>
+    <t>・先輩とやっているときに気をつけていること</t>
+    <rPh sb="1" eb="3">
+      <t>センパイ</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>キ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・メカニズムの解明って具体的に何？</t>
+    <rPh sb="7" eb="9">
+      <t>カイメイ</t>
+    </rPh>
+    <rPh sb="11" eb="14">
+      <t>グタイテキ</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>ナニ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・部のMissionは</t>
+    <rPh sb="1" eb="2">
+      <t>ブ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・商業IJにおける画質とは</t>
+    <rPh sb="1" eb="3">
+      <t>ショウギョウ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>ガシツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・事業部とのトラブル</t>
+    <rPh sb="1" eb="4">
+      <t>ジギョウブ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t xml:space="preserve">先輩と一緒に取り組む場合でも、単にサポートを受けるのではなく、自分がその業務を前に進める当事者であることを意識しています。
+ 例えば、事業部やチーム外のメンバーと連携する際には、自分から課題や論点を整理して関係者に提示し、専門の異なるメンバーの認識をそろえながら議論を進めています。一方で、自分だけで判断せず、重要な方向性については先輩と早めに認識を合わせることで、手戻りが生じないようにしています。具体例として、Mogamiの画質改善では、私はプライマ量と画質の関係整理を担当していました。一方、同じプロジェクト内では、別のチームがスジムラの発生メカニズムを整理していました。
+</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t xml:space="preserve">
+プライマ量を変えると粒状性や発色だけでなく、インクの広がり方や被覆状態を通じてスジムラにも影響する可能性があり、自分の担当範囲だけで整理すると、要因を見落とす懸念があると考えました。そこで、私からスジムラチームに働きかけ、これまでに整理していたスジムラの発生要因や物理現象を共有してもらいました。
+そのうえで、スジムラチームの整理方法を参考にしながら、プライマ量、カラーインク量、紙特性、インクの広がりや被覆状態、最終的な画質のつながりを整理しました。また、認識が異なる部分は打ち合わせで論点を提示し、用語や因果関係をすり合わせました。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>→具体的には？</t>
+    <rPh sb="1" eb="4">
+      <t>グタイテキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>メカニズム解明の共通点は、**「目に見える画質の良し悪しを、画像を構成する物理的な特徴まで分解し、発生要因との因果関係を整理すること」</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・上流工程・下流工程とは？</t>
+    <rPh sb="1" eb="3">
+      <t>ジョウリュウ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>コウテイ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>カリュウ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>コウテイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>年頭方針でいう上流工程とは、製品開発の早い段階で、画質に影響する要因を解析し、必要な設計要件を決める工程です。下流工程とは、試作機や実機を使って、設計した製品が目標画質を満たしているかを検証する工程です。
+ 私たちの部門には、画質課題が下流工程で発覚して手戻りになることを防ぐため、上流工程から画質を定量的・理論的に解析し、設計判断につなげることが求められています。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・事業部を巻き込むためにやること</t>
+    <rPh sb="1" eb="4">
+      <t>ジギョウブ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>マ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>コ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>事業部の課題を見つけるためには、資料や会議だけでなく、実際の設計現場に足を運び、業務の進め方を直接確認することが重要だと考えています。
+ 例えば、事業部で行っているプライマの最適量を決める評価フローを実際に見せてもらい、どの工程に時間がかかっているのか、どの判断が担当者の経験に依存しているのか、どこで評価のやり直しが発生しているのかを確認します。
+ そこで得た情報を、評価方法の不足や設計条件と画質の関係が整理できていないといった技術課題に置き換え、自部門の解析技術で解決できるテーマとして提案したいと考えています。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>デジタルビジネスプラットフォーム開発本部、ソフトウェア33開発室の中岫茉希と申します。
+私の所属する部門では、商業印刷向けインクジェットプリンタの高画質化に向けて、印刷画質がどのような要因によって決まるのか、その仕組みを解析しています。
+その中で私は、商業印刷向けのインクジェットプリンタ、Mogamiを対象に、「プライマー」と呼ばれる透明なインクと画質との関係の解析を担当しています。
+プライマーとは、さまざまな用紙に対応するため、印刷前に用紙へ打つ透明な液体です。適切な量は用紙の種類やカラーインク量によって異なるため、評価すべき条件の組み合わせが膨大になることが課題です。
+そこで、プライマー量と画質の関係を明らかにし、少ない評価工数で適切なプライマー量を設計する手法を、デジプリ事業本部と連携して開発しています。これにより、事業部の設計の効率化に貢献してます。
+本日はよろしくお願いいたします。</t>
+    <rPh sb="226" eb="227">
+      <t>ウ</t>
+    </rPh>
+    <rPh sb="381" eb="383">
+      <t>コウケン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>週報や技術報告会は知見者を見つけるきっかけとして活用しますが、読むだけではなく、先輩にも確認して適切な人を特定し、自分から直接相談するようにしています。その際は、相手に最初から答えを求めるのではなく、自分で仮説や関係図のたたき台を用意し、確認したい論点を具体化して持ち込みます。得られた意見を成果物に反映して再度確認することで、単発の相談で終わらず、継続的に協力してもらえる関係を作ることを意識しています。</t>
+    <rPh sb="3" eb="5">
+      <t>ギジュツ</t>
+    </rPh>
+    <rPh sb="5" eb="8">
+      <t>ホウコクカイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>必要な人を巻き込むのでは？</t>
+    <rPh sb="0" eb="2">
+      <t>ヒツヨウ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>ヒト</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>マ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>コ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>私の強みは、データをもとに現象を客観的に捉え、仮説を立てて分析できることです。
+ この力を高めるために統計検定2級を取得し、平均値だけで判断するのではなく、データのばらつきや条件間の差、要因同士の関係を見ることを意識しています。
+ 業務では、プライマ量、カラーインク量、用紙の違いによる画質データを整理し、どの条件が画質変化に関係しているのかを分析しています。さらに、分析結果を関係図として構造化し、評価条件や設計方針を検討する際の根拠として活用しています。
+ このように、感覚や経験だけに頼らず、データと物理的な仕組みの両面から課題を整理できることが私の強みです。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>あなたの強み？</t>
+    <rPh sb="4" eb="5">
+      <t>ツヨ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>私の強みは、データを定量的に分析し、課題を客観的に示せることです。関係者を巻き込む際にも、感覚だけで協力を求めるのではなく、課題の大きさや改善効果を数値で示し、取り組む必要性を納得してもらうことを意識しています。G3になったら、データを共通言語として専門の異なるメンバーの認識をそろえ、課題解決を主導したいです。</t>
+    <phoneticPr fontId="1"/>
   </si>
 </sst>
 </file>
@@ -6127,7 +6312,7 @@
         <v>178</v>
       </c>
       <c r="C2" s="18" t="s">
-        <v>278</v>
+        <v>424</v>
       </c>
       <c r="D2" s="25" t="s">
         <v>171</v>
@@ -6164,7 +6349,7 @@
         <v>91</v>
       </c>
       <c r="C4" s="18" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="D4" s="25" t="s">
         <v>172</v>
@@ -6261,7 +6446,7 @@
         <v>96</v>
       </c>
       <c r="C10" s="18" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="E10" s="12" t="s">
         <v>187</v>
@@ -6291,7 +6476,7 @@
         <v>98</v>
       </c>
       <c r="C12" s="18" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="E12" s="13" t="s">
         <v>189</v>
@@ -6306,7 +6491,7 @@
         <v>99</v>
       </c>
       <c r="C13" s="17" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="E13" s="13"/>
       <c r="F13" s="14"/>
@@ -6319,7 +6504,7 @@
         <v>100</v>
       </c>
       <c r="C14" s="36" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="E14" s="13" t="s">
         <v>190</v>
@@ -7235,53 +7420,63 @@
     </row>
     <row r="116" spans="2:2">
       <c r="B116" s="34" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
     <row r="117" spans="2:2">
       <c r="B117" s="34" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="118" spans="2:2">
       <c r="B118" s="34" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
     </row>
     <row r="119" spans="2:2">
       <c r="B119" s="34" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
     </row>
     <row r="120" spans="2:2">
       <c r="B120" s="34" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
     </row>
     <row r="121" spans="2:2">
       <c r="B121" s="34" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
     </row>
     <row r="122" spans="2:2">
       <c r="B122" s="34" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="123" spans="2:2">
       <c r="B123" s="34" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="124" spans="2:2">
       <c r="B124" s="34" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="8" scale="50" orientation="landscape" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7016FA33-FF68-4C3D-B093-FADADA8DE1A9}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
+  <sheetData/>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
@@ -7292,642 +7487,642 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="2" spans="1:1">
       <c r="A2" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
     <row r="10" spans="1:1">
       <c r="A10" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
     </row>
     <row r="12" spans="1:1">
       <c r="A12" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
     </row>
     <row r="14" spans="1:1">
       <c r="A14" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
     </row>
     <row r="16" spans="1:1">
       <c r="A16" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="18" spans="1:1">
       <c r="A18" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="24" spans="1:1">
       <c r="A24" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="26" spans="1:1">
       <c r="A26" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
     </row>
     <row r="28" spans="1:1">
       <c r="A28" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
     </row>
     <row r="30" spans="1:1">
       <c r="A30" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
     </row>
     <row r="32" spans="1:1">
       <c r="A32" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="34" spans="1:1">
       <c r="A34" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="36" spans="1:1">
       <c r="A36" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
     </row>
     <row r="37" spans="1:1">
       <c r="A37" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="38" spans="1:1">
       <c r="A38" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
     </row>
     <row r="40" spans="1:1">
       <c r="A40" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="42" spans="1:1">
       <c r="A42" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="43" spans="1:1">
       <c r="A43" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="46" spans="1:1">
       <c r="A46" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="47" spans="1:1">
       <c r="A47" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
     </row>
     <row r="49" spans="1:1">
       <c r="A49" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="50" spans="1:1">
       <c r="A50" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
     </row>
     <row r="51" spans="1:1">
       <c r="A51" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="52" spans="1:1">
       <c r="A52" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
     </row>
     <row r="53" spans="1:1">
       <c r="A53" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
     </row>
     <row r="54" spans="1:1">
       <c r="A54" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
     </row>
     <row r="55" spans="1:1">
       <c r="A55" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="56" spans="1:1">
       <c r="A56" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="57" spans="1:1">
       <c r="A57" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="58" spans="1:1">
       <c r="A58" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
     </row>
     <row r="59" spans="1:1">
       <c r="A59" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
     </row>
     <row r="60" spans="1:1">
       <c r="A60" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="61" spans="1:1">
       <c r="A61" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="62" spans="1:1">
       <c r="A62" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
     </row>
     <row r="63" spans="1:1">
       <c r="A63" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
     </row>
     <row r="64" spans="1:1">
       <c r="A64" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
     </row>
     <row r="65" spans="1:1">
       <c r="A65" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="66" spans="1:1">
       <c r="A66" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="69" spans="1:1">
       <c r="A69" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="70" spans="1:1">
       <c r="A70" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="71" spans="1:1">
       <c r="A71" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
     </row>
     <row r="72" spans="1:1">
       <c r="A72" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="73" spans="1:1">
       <c r="A73" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="74" spans="1:1">
       <c r="A74" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
     </row>
     <row r="75" spans="1:1">
       <c r="A75" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="76" spans="1:1">
       <c r="A76" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="77" spans="1:1">
       <c r="A77" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
     </row>
     <row r="78" spans="1:1">
       <c r="A78" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
     </row>
     <row r="79" spans="1:1">
       <c r="A79" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
     </row>
     <row r="80" spans="1:1">
       <c r="A80" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
     </row>
     <row r="81" spans="1:1">
       <c r="A81" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
     </row>
     <row r="82" spans="1:1">
       <c r="A82" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
     </row>
     <row r="83" spans="1:1">
       <c r="A83" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="84" spans="1:1">
       <c r="A84" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
     </row>
     <row r="85" spans="1:1">
       <c r="A85" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
     </row>
     <row r="86" spans="1:1">
       <c r="A86" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="87" spans="1:1">
       <c r="A87" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
     </row>
     <row r="88" spans="1:1">
       <c r="A88" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
     </row>
     <row r="92" spans="1:1">
       <c r="A92" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="93" spans="1:1">
       <c r="A93" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="94" spans="1:1">
       <c r="A94" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="95" spans="1:1">
       <c r="A95" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="96" spans="1:1">
       <c r="A96" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="97" spans="1:1">
       <c r="A97" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
     <row r="98" spans="1:1">
       <c r="A98" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="99" spans="1:1">
       <c r="A99" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
     </row>
     <row r="100" spans="1:1">
       <c r="A100" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="101" spans="1:1">
       <c r="A101" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
     </row>
     <row r="102" spans="1:1">
       <c r="A102" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="103" spans="1:1">
       <c r="A103" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
     </row>
     <row r="104" spans="1:1">
       <c r="A104" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="105" spans="1:1">
       <c r="A105" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="106" spans="1:1">
       <c r="A106" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="107" spans="1:1">
       <c r="A107" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="108" spans="1:1">
       <c r="A108" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="109" spans="1:1">
       <c r="A109" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="110" spans="1:1">
       <c r="A110" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
     </row>
     <row r="111" spans="1:1">
       <c r="A111" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
     </row>
     <row r="112" spans="1:1">
       <c r="A112" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="113" spans="1:1">
       <c r="A113" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="114" spans="1:1">
       <c r="A114" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="117" spans="1:1">
       <c r="A117" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="118" spans="1:1">
       <c r="A118" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="119" spans="1:1">
       <c r="A119" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
     </row>
     <row r="120" spans="1:1">
       <c r="A120" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
     </row>
     <row r="121" spans="1:1">
       <c r="A121" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
     </row>
     <row r="122" spans="1:1">
       <c r="A122" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
     </row>
     <row r="123" spans="1:1">
       <c r="A123" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
     </row>
     <row r="124" spans="1:1">
       <c r="A124" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
     </row>
     <row r="125" spans="1:1">
       <c r="A125" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
     </row>
     <row r="126" spans="1:1">
       <c r="A126" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
     </row>
     <row r="127" spans="1:1">
       <c r="A127" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
     </row>
     <row r="128" spans="1:1">
       <c r="A128" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="129" spans="1:1">
       <c r="A129" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
     </row>
     <row r="130" spans="1:1">
       <c r="A130" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
     </row>
     <row r="131" spans="1:1">
       <c r="A131" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
     </row>
     <row r="132" spans="1:1">
       <c r="A132" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
     </row>
     <row r="133" spans="1:1">
       <c r="A133" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
     </row>
     <row r="134" spans="1:1">
       <c r="A134" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
     </row>
     <row r="135" spans="1:1">
       <c r="A135" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="136" spans="1:1">
       <c r="A136" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="137" spans="1:1">
       <c r="A137" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
     </row>
     <row r="138" spans="1:1">
       <c r="A138" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
     </row>
     <row r="139" spans="1:1">
       <c r="A139" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
     </row>
   </sheetData>
@@ -8490,59 +8685,191 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="34" t="s">
+        <v>278</v>
+      </c>
+      <c r="B1" s="34" t="s">
         <v>279</v>
-      </c>
-      <c r="B1" s="34" t="s">
-        <v>280</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="34" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="34" t="s">
+        <v>281</v>
+      </c>
+      <c r="B3" s="34" t="s">
         <v>282</v>
-      </c>
-      <c r="B3" s="34" t="s">
-        <v>283</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="34" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="34" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="34" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="108">
       <c r="A7" s="34" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B7" s="38" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="34" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="34" t="s">
+        <v>288</v>
+      </c>
+      <c r="B9" s="34" t="s">
         <v>289</v>
       </c>
-      <c r="B9" s="34" t="s">
-        <v>290</v>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AF701674-7A60-413B-8525-5F23C4EF17DB}">
+  <dimension ref="A1:B19"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
+  <cols>
+    <col min="1" max="1" width="63.125" customWidth="1"/>
+    <col min="2" max="2" width="73.875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" ht="121.5">
+      <c r="A1" s="34" t="s">
+        <v>411</v>
+      </c>
+      <c r="B1" s="38" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" ht="121.5">
+      <c r="A2" s="34" t="s">
+        <v>418</v>
+      </c>
+      <c r="B2" s="38" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" s="34" t="s">
+        <v>412</v>
+      </c>
+      <c r="B3" s="34" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" s="34" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" ht="67.5">
+      <c r="A5" s="34" t="s">
+        <v>420</v>
+      </c>
+      <c r="B5" s="38" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" s="34" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" s="34" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" ht="102" customHeight="1">
+      <c r="A8" s="34" t="s">
+        <v>422</v>
+      </c>
+      <c r="B8" s="38" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" ht="102" customHeight="1">
+      <c r="A9" s="34" t="s">
+        <v>426</v>
+      </c>
+      <c r="B9" s="38" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" ht="102" customHeight="1">
+      <c r="A10" s="34" t="s">
+        <v>428</v>
+      </c>
+      <c r="B10" s="38" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" ht="102" customHeight="1">
+      <c r="A11" s="34"/>
+      <c r="B11" s="38" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2">
+      <c r="A12" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
+      <c r="A13" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2">
+      <c r="A14" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2">
+      <c r="A15" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2">
+      <c r="A16" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1">
+      <c r="A17" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1">
+      <c r="A18" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1">
+      <c r="A19" t="s">
+        <v>410</v>
       </c>
     </row>
   </sheetData>

--- a/作業/面接練習/G3面接準備中岫.xlsx
+++ b/作業/面接練習/G3面接準備中岫.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aaa115298\Desktop\G3\G3\G3試験中岫作業\G3\作業\面接練習\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{612C5AFA-B74B-4E4B-83AC-8A39F0ED668D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0122B0F2-1340-4BB2-9411-EF3E8BB6C6E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
     <sheet name="1016" sheetId="7" r:id="rId7"/>
     <sheet name="1019" sheetId="6" r:id="rId8"/>
     <sheet name="1021" sheetId="9" r:id="rId9"/>
-    <sheet name="Sheet5" sheetId="10" r:id="rId10"/>
+    <sheet name="1022" sheetId="10" r:id="rId10"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="519" uniqueCount="430">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="665" uniqueCount="552">
   <si>
     <t>No</t>
   </si>
@@ -5694,12 +5694,378 @@
     <t>私の強みは、データを定量的に分析し、課題を客観的に示せることです。関係者を巻き込む際にも、感覚だけで協力を求めるのではなく、課題の大きさや改善効果を数値で示し、取り組む必要性を納得してもらうことを意識しています。G3になったら、データを共通言語として専門の異なるメンバーの認識をそろえ、課題解決を主導したいです。</t>
     <phoneticPr fontId="1"/>
   </si>
+  <si>
+    <t>質問1：自己紹介をお願いします</t>
+  </si>
+  <si>
+    <t>回答</t>
+  </si>
+  <si>
+    <t>デジタルビジネスプラットフォーム開発本部 ソフトウェア33開発室所属。</t>
+  </si>
+  <si>
+    <t>商業印刷向け電子写真プリンターの高画質化に取り組んでいる。</t>
+  </si>
+  <si>
+    <t>印刷物の計測解析技術をデジプリ本部へ提案・開発している。</t>
+  </si>
+  <si>
+    <t>粒状性（画像のざらつき感）の改善をテーマとしている。</t>
+  </si>
+  <si>
+    <t>トナー配置と粒状性の関係を解析し、目標粒状性を実現する設計指針の構築に貢献した。</t>
+  </si>
+  <si>
+    <t>5名チームの中で解析技術開発の主担当を務めている。</t>
+  </si>
+  <si>
+    <t>質問2：ソフトウェア33開発室の構成を教えてください</t>
+  </si>
+  <si>
+    <t>室長1名</t>
+  </si>
+  <si>
+    <t>主幹1名</t>
+  </si>
+  <si>
+    <t>一般職21名</t>
+  </si>
+  <si>
+    <t>合計23名</t>
+  </si>
+  <si>
+    <t>内訳：</t>
+  </si>
+  <si>
+    <t>電子写真プリンター担当：16名</t>
+  </si>
+  <si>
+    <t>インクジェットプリンター担当：5名</t>
+  </si>
+  <si>
+    <t>質問3：電子写真プリンター担当16名の体制について詳しく教えてください</t>
+  </si>
+  <si>
+    <t>16名は大きく3チームに分かれている。</t>
+  </si>
+  <si>
+    <t>1. 計測解析技術開発チーム（5名）</t>
+  </si>
+  <si>
+    <t>2. ツール開発チーム（6名）</t>
+  </si>
+  <si>
+    <t>計測解析アルゴリズムを事業部内で活用するためのツール化を担当</t>
+  </si>
+  <si>
+    <t>3. 印刷検品アルゴリズム開発チーム（5名）</t>
+  </si>
+  <si>
+    <t>印刷中に発生する欠陥を自動検出する技術を開発</t>
+  </si>
+  <si>
+    <t>質問4：印刷検品とは何ですか</t>
+  </si>
+  <si>
+    <t>印刷工程の途中で画像を取得する。</t>
+  </si>
+  <si>
+    <t>良品か不良品かをリアルタイム判定する。</t>
+  </si>
+  <si>
+    <t>傷や異常を自動検出することで検品作業を効率化する。</t>
+  </si>
+  <si>
+    <t>質問5：5名のチームの構成を教えてください</t>
+  </si>
+  <si>
+    <t>チームはさらに、</t>
+  </si>
+  <si>
+    <t>計測技術開発チーム（2名）</t>
+  </si>
+  <si>
+    <t>解析技術開発チーム（2名）</t>
+  </si>
+  <si>
+    <t>チームリーダー（1名）</t>
+  </si>
+  <si>
+    <t>で構成される。</t>
+  </si>
+  <si>
+    <t>市場さんは解析技術開発チーム所属。</t>
+  </si>
+  <si>
+    <t>質問6：解析技術開発チーム内での立場を教えてください</t>
+  </si>
+  <si>
+    <t>もう1名は年次上では先輩。</t>
+  </si>
+  <si>
+    <t>ただしチーム在籍期間は市場さんの方が長い。</t>
+  </si>
+  <si>
+    <t>実質的には解析技術開発を主導する立場に近い。</t>
+  </si>
+  <si>
+    <t>質問7：普段どのように業務を進めていますか</t>
+  </si>
+  <si>
+    <t>事業部から計測解析依頼を受ける。</t>
+  </si>
+  <si>
+    <t>まず5名全員で課題を整理する。</t>
+  </si>
+  <si>
+    <t>計測チームが必要なデータ取得手法を検討する。</t>
+  </si>
+  <si>
+    <t>取得データを解析チームが分析する。</t>
+  </si>
+  <si>
+    <t>結果を事業部へフィードバックする。</t>
+  </si>
+  <si>
+    <t>質問8：チームメンバーが困っているときはどのように対応しますか</t>
+  </si>
+  <si>
+    <t>まず困っている内容をヒアリングする。</t>
+  </si>
+  <si>
+    <t>自身が知識を持っている場合は技術指導を行う。</t>
+  </si>
+  <si>
+    <t>自分では対応できない場合は有識者につなぐ。</t>
+  </si>
+  <si>
+    <t>プロジェクト進行上の課題であればリーダーと連携して解決する。</t>
+  </si>
+  <si>
+    <t>質問9：チームの技術力向上のために取り組んでいることはありますか</t>
+  </si>
+  <si>
+    <t>技術的な不足を自発的に発見する。</t>
+  </si>
+  <si>
+    <t>自ら学習する。</t>
+  </si>
+  <si>
+    <t>得た知識を周囲へ共有する。</t>
+  </si>
+  <si>
+    <t>チーム全体の技術レベル向上を意識している。</t>
+  </si>
+  <si>
+    <t>質問10：どのように情報収集していますか</t>
+  </si>
+  <si>
+    <t>軽微な内容はインターネット調査。</t>
+  </si>
+  <si>
+    <t>深く学ぶ必要がある内容は書籍等で体系的に学習する。</t>
+  </si>
+  <si>
+    <t>質問11：解析結果は事業部でそのまま活用されていますか</t>
+  </si>
+  <si>
+    <t>必ずしも活用されているわけではない。</t>
+  </si>
+  <si>
+    <t>開発した技術をいかに現場に定着させるかが課題である。</t>
+  </si>
+  <si>
+    <t>質問12：活用されない原因をどのように調べましたか</t>
+  </si>
+  <si>
+    <t>事業部へ出向きヒアリングを実施した。</t>
+  </si>
+  <si>
+    <t>開発会議にも参加した。</t>
+  </si>
+  <si>
+    <t>実際の運用状況を確認した。</t>
+  </si>
+  <si>
+    <t>質問13：どのような原因が分かりましたか</t>
+  </si>
+  <si>
+    <t>粒状性とトナー配置の相関関係は理解してもらえていた。</t>
+  </si>
+  <si>
+    <t>しかし「なぜそのトナー配置で粒状性が変わるのか」が説明できていなかった。</t>
+  </si>
+  <si>
+    <t>メカニズムへの納得感不足が利用されない原因だった。</t>
+  </si>
+  <si>
+    <t>質問14：その課題にどう対応しましたか</t>
+  </si>
+  <si>
+    <t>因果関係を説明するための数理モデルを提案した。</t>
+  </si>
+  <si>
+    <t>前例が少ないテーマだったが、自ら主導して開発した。</t>
+  </si>
+  <si>
+    <t>メカニズム説明を可能にした。</t>
+  </si>
+  <si>
+    <t>質問15：結果はどうなりましたか</t>
+  </si>
+  <si>
+    <t>事業部から高い評価を得た。</t>
+  </si>
+  <si>
+    <t>「腹落ちした」と評価された。</t>
+  </si>
+  <si>
+    <t>提案した設計指標が実際に活用されるようになった。</t>
+  </si>
+  <si>
+    <t>山本さん参加後の面接練習</t>
+  </si>
+  <si>
+    <t>質問16：部屋の役割は何ですか</t>
+  </si>
+  <si>
+    <t>当初の回答</t>
+  </si>
+  <si>
+    <t>デジプリ本部向けにツールを提供し設計効率化を行う組織。</t>
+  </si>
+  <si>
+    <t>議論後に整理された回答</t>
+  </si>
+  <si>
+    <t>DBPのプリンティング向け高画質化技術を担当する。</t>
+  </si>
+  <si>
+    <t>ソフトウェア31開発室が「定量化」担当。</t>
+  </si>
+  <si>
+    <t>ソフトウェア33開発室が「解析」担当。</t>
+  </si>
+  <si>
+    <t>人が感じる画質、印刷物、プリンターの関係を解明し、高画質化技術へつなげる。</t>
+  </si>
+  <si>
+    <t>質問17：16名チームの中での自分の立場は何ですか</t>
+  </si>
+  <si>
+    <t>電子写真プリンターの計測解析技術開発チーム所属。</t>
+  </si>
+  <si>
+    <t>解析技術開発担当。</t>
+  </si>
+  <si>
+    <t>解析技術の中心メンバーとして活動している。</t>
+  </si>
+  <si>
+    <t>質問18：組織課題はありますか</t>
+  </si>
+  <si>
+    <t>チームごとに扱う技術が異なる。</t>
+  </si>
+  <si>
+    <t>技術交流が十分でない。</t>
+  </si>
+  <si>
+    <t>横展開可能な技術が十分共有されていない。</t>
+  </si>
+  <si>
+    <t>質問19：なぜ技術共有が進まないと思いますか</t>
+  </si>
+  <si>
+    <t>どの技術が横展開可能か整理できていない。</t>
+  </si>
+  <si>
+    <t>各チームが自分の業務に閉じがちである。</t>
+  </si>
+  <si>
+    <t>他チームでの活用可能性が見えづらい。</t>
+  </si>
+  <si>
+    <t>質問20：どのように改善したいですか</t>
+  </si>
+  <si>
+    <t>技術の棚卸しを行う。</t>
+  </si>
+  <si>
+    <t>技術カンファレンスなどを活用して共有する。</t>
+  </si>
+  <si>
+    <t>自らも積極的に発信していきたい。</t>
+  </si>
+  <si>
+    <t>質問21：リーダーシップで最も重要なことは何ですか</t>
+  </si>
+  <si>
+    <t>組織のビジョンを示すこと。</t>
+  </si>
+  <si>
+    <t>自分たちの組織がどうあるべきかを示すこと。</t>
+  </si>
+  <si>
+    <t>質問22：リーダーになったら何をしたいですか</t>
+  </si>
+  <si>
+    <t>事業部へ積極的に入り込む。</t>
+  </si>
+  <si>
+    <t>現場課題を把握する。</t>
+  </si>
+  <si>
+    <t>課題解決へ向けて周囲を巻き込む。</t>
+  </si>
+  <si>
+    <t>ビジョンを示して組織を導く。</t>
+  </si>
+  <si>
+    <t>質問23：将来やりたいことは何ですか</t>
+  </si>
+  <si>
+    <t>現在の電子写真解析技術をさらに深めたい。</t>
+  </si>
+  <si>
+    <t>電子写真分野の第一人者になりたい。</t>
+  </si>
+  <si>
+    <t>電子写真解析技術をインクジェットや他分野へ展開したい。</t>
+  </si>
+  <si>
+    <t>複雑なシステムを解析する技術として横展開したい。</t>
+  </si>
+  <si>
+    <t>質問24：それを実現するために何を学んでいますか</t>
+  </si>
+  <si>
+    <t>統計解析を自主的に勉強している。</t>
+  </si>
+  <si>
+    <t>解析技術の基盤になると考えている。</t>
+  </si>
+  <si>
+    <t>自分だけでなく組織全体へ波及させたいと考えている。</t>
+  </si>
+  <si>
+    <t>質問25：本部の役割と自分の役割の関係は何ですか</t>
+  </si>
+  <si>
+    <t>DBPは差別化技術を事業部へ提供する組織。</t>
+  </si>
+  <si>
+    <t>その中で画像処理技術による価値提供を行う。</t>
+  </si>
+  <si>
+    <t>自身はプリンティングの高画質化を通じて事業へ貢献している。</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="20">
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -5840,6 +6206,30 @@
       <family val="3"/>
       <charset val="128"/>
     </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13.5"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="24"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
   </fonts>
   <fills count="8">
     <fill>
@@ -5951,7 +6341,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -6068,6 +6458,27 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -7472,9 +7883,821 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7016FA33-FF68-4C3D-B093-FADADA8DE1A9}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:A278"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1" spans="1:1" ht="21">
+      <c r="A1" s="39" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" ht="16.5">
+      <c r="A3" s="40" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1">
+      <c r="A4" s="41"/>
+    </row>
+    <row r="5" spans="1:1">
+      <c r="A5" s="42" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1">
+      <c r="A6" s="42" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1">
+      <c r="A7" s="42" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1">
+      <c r="A8" s="42" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1">
+      <c r="A9" s="42" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1">
+      <c r="A10" s="42" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1" ht="21">
+      <c r="A14" s="39" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1" ht="16.5">
+      <c r="A16" s="40" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1">
+      <c r="A17" s="41"/>
+    </row>
+    <row r="18" spans="1:1">
+      <c r="A18" s="42" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1">
+      <c r="A19" s="42" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1">
+      <c r="A20" s="42" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1">
+      <c r="A21" s="42" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1">
+      <c r="A23" s="34" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1">
+      <c r="A24" s="41"/>
+    </row>
+    <row r="25" spans="1:1">
+      <c r="A25" s="42" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1">
+      <c r="A26" s="42" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1" ht="21">
+      <c r="A30" s="39" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1" ht="16.5">
+      <c r="A32" s="40" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1">
+      <c r="A34" s="34" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1">
+      <c r="A35" s="41"/>
+    </row>
+    <row r="36" spans="1:1">
+      <c r="A36" s="42" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1">
+      <c r="A37" s="42" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1">
+      <c r="A38" s="43" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1">
+      <c r="A39" s="42" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1">
+      <c r="A40" s="43" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1" ht="21">
+      <c r="A44" s="39" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1" ht="16.5">
+      <c r="A46" s="40" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1">
+      <c r="A47" s="41"/>
+    </row>
+    <row r="48" spans="1:1">
+      <c r="A48" s="42" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1">
+      <c r="A49" s="42" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1">
+      <c r="A50" s="42" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1" ht="21">
+      <c r="A54" s="39" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="56" spans="1:1" ht="16.5">
+      <c r="A56" s="40" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="58" spans="1:1">
+      <c r="A58" s="34" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="59" spans="1:1">
+      <c r="A59" s="41"/>
+    </row>
+    <row r="60" spans="1:1">
+      <c r="A60" s="42" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="61" spans="1:1">
+      <c r="A61" s="42" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="62" spans="1:1">
+      <c r="A62" s="42" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="64" spans="1:1">
+      <c r="A64" s="34" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="66" spans="1:1">
+      <c r="A66" s="34" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="70" spans="1:1" ht="21">
+      <c r="A70" s="39" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="72" spans="1:1" ht="16.5">
+      <c r="A72" s="40" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="73" spans="1:1">
+      <c r="A73" s="41"/>
+    </row>
+    <row r="74" spans="1:1">
+      <c r="A74" s="42" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="75" spans="1:1">
+      <c r="A75" s="42" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="76" spans="1:1">
+      <c r="A76" s="42" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="80" spans="1:1" ht="21">
+      <c r="A80" s="39" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="82" spans="1:1" ht="16.5">
+      <c r="A82" s="40" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="83" spans="1:1">
+      <c r="A83" s="41"/>
+    </row>
+    <row r="84" spans="1:1">
+      <c r="A84" s="42" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="85" spans="1:1">
+      <c r="A85" s="42" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="86" spans="1:1">
+      <c r="A86" s="42" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="87" spans="1:1">
+      <c r="A87" s="42" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="88" spans="1:1">
+      <c r="A88" s="42" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="92" spans="1:1" ht="21">
+      <c r="A92" s="39" t="s">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="94" spans="1:1" ht="16.5">
+      <c r="A94" s="40" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="95" spans="1:1">
+      <c r="A95" s="41"/>
+    </row>
+    <row r="96" spans="1:1">
+      <c r="A96" s="42" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="97" spans="1:1">
+      <c r="A97" s="42" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="98" spans="1:1">
+      <c r="A98" s="42" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="99" spans="1:1">
+      <c r="A99" s="42" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="103" spans="1:1" ht="21">
+      <c r="A103" s="39" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="105" spans="1:1" ht="16.5">
+      <c r="A105" s="40" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="106" spans="1:1">
+      <c r="A106" s="41"/>
+    </row>
+    <row r="107" spans="1:1">
+      <c r="A107" s="42" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="108" spans="1:1">
+      <c r="A108" s="42" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="109" spans="1:1">
+      <c r="A109" s="42" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="110" spans="1:1">
+      <c r="A110" s="42" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="114" spans="1:1" ht="21">
+      <c r="A114" s="39" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="116" spans="1:1" ht="16.5">
+      <c r="A116" s="40" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="117" spans="1:1">
+      <c r="A117" s="41"/>
+    </row>
+    <row r="118" spans="1:1">
+      <c r="A118" s="42" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="119" spans="1:1">
+      <c r="A119" s="42" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="123" spans="1:1" ht="21">
+      <c r="A123" s="39" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="125" spans="1:1" ht="16.5">
+      <c r="A125" s="40" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="126" spans="1:1">
+      <c r="A126" s="41"/>
+    </row>
+    <row r="127" spans="1:1">
+      <c r="A127" s="42" t="s">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="128" spans="1:1">
+      <c r="A128" s="42" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="132" spans="1:1" ht="21">
+      <c r="A132" s="39" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="134" spans="1:1" ht="16.5">
+      <c r="A134" s="40" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="135" spans="1:1">
+      <c r="A135" s="41"/>
+    </row>
+    <row r="136" spans="1:1">
+      <c r="A136" s="42" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="137" spans="1:1">
+      <c r="A137" s="42" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="138" spans="1:1">
+      <c r="A138" s="42" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="142" spans="1:1" ht="21">
+      <c r="A142" s="39" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="144" spans="1:1" ht="16.5">
+      <c r="A144" s="40" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="145" spans="1:1">
+      <c r="A145" s="41"/>
+    </row>
+    <row r="146" spans="1:1">
+      <c r="A146" s="42" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="147" spans="1:1">
+      <c r="A147" s="42" t="s">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="148" spans="1:1">
+      <c r="A148" s="42" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="152" spans="1:1" ht="21">
+      <c r="A152" s="39" t="s">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="154" spans="1:1" ht="16.5">
+      <c r="A154" s="40" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="155" spans="1:1">
+      <c r="A155" s="41"/>
+    </row>
+    <row r="156" spans="1:1">
+      <c r="A156" s="42" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="157" spans="1:1">
+      <c r="A157" s="42" t="s">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="158" spans="1:1">
+      <c r="A158" s="42" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="162" spans="1:1" ht="21">
+      <c r="A162" s="39" t="s">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="164" spans="1:1" ht="16.5">
+      <c r="A164" s="40" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="165" spans="1:1">
+      <c r="A165" s="41"/>
+    </row>
+    <row r="166" spans="1:1">
+      <c r="A166" s="42" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="167" spans="1:1">
+      <c r="A167" s="42" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="168" spans="1:1">
+      <c r="A168" s="42" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="172" spans="1:1" ht="28.5">
+      <c r="A172" s="44" t="s">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="174" spans="1:1" ht="21">
+      <c r="A174" s="39" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="176" spans="1:1" ht="16.5">
+      <c r="A176" s="40" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="178" spans="1:1">
+      <c r="A178" s="34" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="179" spans="1:1">
+      <c r="A179" s="41"/>
+    </row>
+    <row r="180" spans="1:1">
+      <c r="A180" s="42" t="s">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="182" spans="1:1">
+      <c r="A182" s="34" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="183" spans="1:1">
+      <c r="A183" s="41"/>
+    </row>
+    <row r="184" spans="1:1">
+      <c r="A184" s="42" t="s">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="185" spans="1:1">
+      <c r="A185" s="42" t="s">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="186" spans="1:1">
+      <c r="A186" s="42" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="187" spans="1:1">
+      <c r="A187" s="42" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="191" spans="1:1" ht="21">
+      <c r="A191" s="39" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="193" spans="1:1" ht="16.5">
+      <c r="A193" s="40" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="194" spans="1:1">
+      <c r="A194" s="41"/>
+    </row>
+    <row r="195" spans="1:1">
+      <c r="A195" s="42" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="196" spans="1:1">
+      <c r="A196" s="42" t="s">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="197" spans="1:1">
+      <c r="A197" s="42" t="s">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="201" spans="1:1" ht="21">
+      <c r="A201" s="39" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="203" spans="1:1" ht="16.5">
+      <c r="A203" s="40" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="204" spans="1:1">
+      <c r="A204" s="41"/>
+    </row>
+    <row r="205" spans="1:1">
+      <c r="A205" s="42" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="206" spans="1:1">
+      <c r="A206" s="42" t="s">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="207" spans="1:1">
+      <c r="A207" s="42" t="s">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="211" spans="1:1" ht="21">
+      <c r="A211" s="39" t="s">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="213" spans="1:1" ht="16.5">
+      <c r="A213" s="40" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="214" spans="1:1">
+      <c r="A214" s="41"/>
+    </row>
+    <row r="215" spans="1:1">
+      <c r="A215" s="42" t="s">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="216" spans="1:1">
+      <c r="A216" s="42" t="s">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="217" spans="1:1">
+      <c r="A217" s="42" t="s">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="221" spans="1:1" ht="21">
+      <c r="A221" s="39" t="s">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="223" spans="1:1" ht="16.5">
+      <c r="A223" s="40" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="224" spans="1:1">
+      <c r="A224" s="41"/>
+    </row>
+    <row r="225" spans="1:1">
+      <c r="A225" s="45" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="226" spans="1:1">
+      <c r="A226" s="45" t="s">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="227" spans="1:1">
+      <c r="A227" s="45" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="231" spans="1:1" ht="21">
+      <c r="A231" s="39" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="233" spans="1:1" ht="16.5">
+      <c r="A233" s="40" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="234" spans="1:1">
+      <c r="A234" s="41"/>
+    </row>
+    <row r="235" spans="1:1">
+      <c r="A235" s="42" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="236" spans="1:1">
+      <c r="A236" s="42" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="240" spans="1:1" ht="21">
+      <c r="A240" s="39" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="242" spans="1:1" ht="16.5">
+      <c r="A242" s="40" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="243" spans="1:1">
+      <c r="A243" s="41"/>
+    </row>
+    <row r="244" spans="1:1">
+      <c r="A244" s="42" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="245" spans="1:1">
+      <c r="A245" s="42" t="s">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="246" spans="1:1">
+      <c r="A246" s="42" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="247" spans="1:1">
+      <c r="A247" s="42" t="s">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="251" spans="1:1" ht="21">
+      <c r="A251" s="39" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="253" spans="1:1" ht="16.5">
+      <c r="A253" s="40" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="254" spans="1:1">
+      <c r="A254" s="41"/>
+    </row>
+    <row r="255" spans="1:1">
+      <c r="A255" s="42" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="256" spans="1:1">
+      <c r="A256" s="42" t="s">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="257" spans="1:1">
+      <c r="A257" s="42" t="s">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="258" spans="1:1">
+      <c r="A258" s="42" t="s">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="262" spans="1:1" ht="21">
+      <c r="A262" s="39" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="264" spans="1:1" ht="16.5">
+      <c r="A264" s="40" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="265" spans="1:1">
+      <c r="A265" s="41"/>
+    </row>
+    <row r="266" spans="1:1">
+      <c r="A266" s="42" t="s">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="267" spans="1:1">
+      <c r="A267" s="42" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="268" spans="1:1">
+      <c r="A268" s="42" t="s">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="272" spans="1:1" ht="21">
+      <c r="A272" s="39" t="s">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="274" spans="1:1" ht="16.5">
+      <c r="A274" s="40" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="275" spans="1:1">
+      <c r="A275" s="41"/>
+    </row>
+    <row r="276" spans="1:1">
+      <c r="A276" s="45" t="s">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="277" spans="1:1">
+      <c r="A277" s="45" t="s">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="278" spans="1:1">
+      <c r="A278" s="45" t="s">
+        <v>551</v>
+      </c>
+    </row>
+  </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/作業/面接練習/G3面接準備中岫.xlsx
+++ b/作業/面接練習/G3面接準備中岫.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aaa115298\Desktop\G3\G3\G3試験中岫作業\G3\作業\面接練習\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0122B0F2-1340-4BB2-9411-EF3E8BB6C6E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40B73C56-5A46-4589-B6E8-85E2C2A8C972}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="665" uniqueCount="552">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="666" uniqueCount="553">
   <si>
     <t>No</t>
   </si>
@@ -6059,6 +6059,12 @@
   </si>
   <si>
     <t>自身はプリンティングの高画質化を通じて事業へ貢献している。</t>
+  </si>
+  <si>
+    <t>プライマが画質に与える影響のメカニズムを解析するというのは、プライマとインクが反応してから、最終的な画質が形成されるまでの一連の流れを明らかにすることだと考えています。
+ 具体的には、プライマとインクが反応することで、インク中の成分が凝集し、その結果、紙上でのインクの広がり方や定着状態が変化します。
+ そうした現象が、スジムラなどの画質にどのようにつながっているのかを定量的に整理することで、最終的には用紙に応じた適切なプライマ量を判断できるようにすることを目指しています。</t>
+    <phoneticPr fontId="1"/>
   </si>
 </sst>
 </file>
@@ -9927,9 +9933,12 @@
         <v>282</v>
       </c>
     </row>
-    <row r="4" spans="1:2">
+    <row r="4" spans="1:2" ht="67.5">
       <c r="A4" s="34" t="s">
         <v>283</v>
+      </c>
+      <c r="B4" s="38" t="s">
+        <v>552</v>
       </c>
     </row>
     <row r="5" spans="1:2">

--- a/作業/面接練習/G3面接準備中岫.xlsx
+++ b/作業/面接練習/G3面接準備中岫.xlsx
@@ -8,21 +8,24 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aaa115298\Desktop\G3\G3\G3試験中岫作業\G3\作業\面接練習\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40B73C56-5A46-4589-B6E8-85E2C2A8C972}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20E12783-3F2A-469D-89EF-A5034C76BFE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="8" r:id="rId2"/>
-    <sheet name="Sheet3" sheetId="5" r:id="rId3"/>
-    <sheet name="1013" sheetId="2" r:id="rId4"/>
-    <sheet name="1014" sheetId="3" r:id="rId5"/>
-    <sheet name="1015" sheetId="4" r:id="rId6"/>
-    <sheet name="1016" sheetId="7" r:id="rId7"/>
-    <sheet name="1019" sheetId="6" r:id="rId8"/>
-    <sheet name="1021" sheetId="9" r:id="rId9"/>
-    <sheet name="1022" sheetId="10" r:id="rId10"/>
+    <sheet name="Sheet5" sheetId="12" r:id="rId2"/>
+    <sheet name="Sheet6" sheetId="13" r:id="rId3"/>
+    <sheet name="Sheet4" sheetId="11" r:id="rId4"/>
+    <sheet name="Sheet2" sheetId="8" r:id="rId5"/>
+    <sheet name="Sheet3" sheetId="5" r:id="rId6"/>
+    <sheet name="1013" sheetId="2" r:id="rId7"/>
+    <sheet name="1014" sheetId="3" r:id="rId8"/>
+    <sheet name="1015" sheetId="4" r:id="rId9"/>
+    <sheet name="1016" sheetId="7" r:id="rId10"/>
+    <sheet name="1019" sheetId="6" r:id="rId11"/>
+    <sheet name="1021" sheetId="9" r:id="rId12"/>
+    <sheet name="1022" sheetId="10" r:id="rId13"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="666" uniqueCount="553">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="938" uniqueCount="763">
   <si>
     <t>No</t>
   </si>
@@ -4655,66 +4658,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>課の構成は管理職2名、主任5名、G3、〇一般職〇名です。
-ソフトウェア33開発室では、主に商業印刷機を対象に、測定・解析技術やAIを活用して、画質、安定性、用紙対応力を向上させる技術開発を行っています。具体的には、電子写真方式とインクジェット方式の両方について、画質劣化の原因を分析し、製品設計や画質改善につなげるプロジェクトに取り組んでいます。私たちのチームには、大きく二つのテーマがあります。一つはスジムラの発生メカニズムの解明、もう一つはMogamiの用紙対応力の向上です。
-私は商業IJ印刷機Mogamiの用紙対応力向上のテーマに所属し、主にプライマに関する検討を行っています。プライマは画質を向上させるために打つ透明インクで、打つ量によって画質を低下させたりします。私の役割は、文献調査や評価用チャートの分析を通じて、プライマが画質に与える影響や技術課題を整理し、その後の開発をどのような方針で進めるかを先行して検討することです。また、検討結果を基に、プライマ量を決定する評価フローの再構築にも取り組みました。</t>
-    <rPh sb="0" eb="1">
-      <t>カ</t>
-    </rPh>
-    <rPh sb="2" eb="4">
-      <t>コウセイ</t>
-    </rPh>
-    <rPh sb="5" eb="8">
-      <t>カンリショク</t>
-    </rPh>
-    <rPh sb="9" eb="10">
-      <t>メイ</t>
-    </rPh>
-    <rPh sb="11" eb="13">
-      <t>シュニン</t>
-    </rPh>
-    <rPh sb="14" eb="15">
-      <t>メイ</t>
-    </rPh>
-    <rPh sb="20" eb="23">
-      <t>イッパンショク</t>
-    </rPh>
-    <rPh sb="24" eb="25">
-      <t>メイ</t>
-    </rPh>
-    <rPh sb="245" eb="247">
-      <t>ショウギョウ</t>
-    </rPh>
-    <rPh sb="249" eb="251">
-      <t>インサツ</t>
-    </rPh>
-    <rPh sb="300" eb="302">
-      <t>ガシツ</t>
-    </rPh>
-    <rPh sb="303" eb="305">
-      <t>コウジョウ</t>
-    </rPh>
-    <rPh sb="311" eb="312">
-      <t>ウ</t>
-    </rPh>
-    <rPh sb="313" eb="315">
-      <t>トウメイ</t>
-    </rPh>
-    <rPh sb="320" eb="321">
-      <t>ウ</t>
-    </rPh>
-    <rPh sb="322" eb="323">
-      <t>リョウ</t>
-    </rPh>
-    <rPh sb="327" eb="329">
-      <t>ガシツ</t>
-    </rPh>
-    <rPh sb="330" eb="332">
-      <t>テイカ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>相手を尊敬すること、向こうからの意見をしっかり聞くこと
 本社の要素開発部門よりも、多くの課題を現場は持っている
 そのため、なぜ行われているのかというヒヤリングを適切に行う必要がある
@@ -4862,41 +4805,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t xml:space="preserve">課の課題は、個別製品や担当者ごとに得られた知見が分散し、横展開しにくいことです。Mogamiで得た紙特性、評価結果、対応条件を共通の観点で整理し、他テーマ（IJにかかわらず電子写真）でも検索・再利用できる形にすることで、検討の重複を減らし開発速度を上げたいと考えています。例えば、自分のプロジェクトで起きた問題や課題の解決については、部会で共有する。
-</t>
-    <rPh sb="49" eb="50">
-      <t>カミ</t>
-    </rPh>
-    <rPh sb="86" eb="90">
-      <t>デンシシャシン</t>
-    </rPh>
-    <rPh sb="136" eb="137">
-      <t>タト</t>
-    </rPh>
-    <rPh sb="140" eb="142">
-      <t>ジブン</t>
-    </rPh>
-    <rPh sb="150" eb="151">
-      <t>オ</t>
-    </rPh>
-    <rPh sb="153" eb="155">
-      <t>モンダイ</t>
-    </rPh>
-    <rPh sb="156" eb="158">
-      <t>カダイ</t>
-    </rPh>
-    <rPh sb="159" eb="161">
-      <t>カイケツ</t>
-    </rPh>
-    <rPh sb="167" eb="169">
-      <t>ブカイ</t>
-    </rPh>
-    <rPh sb="170" eb="172">
-      <t>キョウユウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>G3になったら、ネットワークを作って他の人を巻き込みながらプロジェクトを牽引していきたいと思っている
 今回のプライマのプロジェクトも化学系の知識を必要とするため、画像処理技術を専門としている自部門や自分のチームメンバーだけで進めることは困難だった。そこで、デジプリのインクの専門家を巻き込んで、プライマの画質への寄与を解明できたと考えている
 そのため、課題を解決するために自分たちの領域で解決が難しいと思ったときに、適切な人を巻き込んでプロジェクトを進める役割を担いたい</t>
@@ -5573,12 +5481,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t xml:space="preserve">先輩と一緒に取り組む場合でも、単にサポートを受けるのではなく、自分がその業務を前に進める当事者であることを意識しています。
- 例えば、事業部やチーム外のメンバーと連携する際には、自分から課題や論点を整理して関係者に提示し、専門の異なるメンバーの認識をそろえながら議論を進めています。一方で、自分だけで判断せず、重要な方向性については先輩と早めに認識を合わせることで、手戻りが生じないようにしています。具体例として、Mogamiの画質改善では、私はプライマ量と画質の関係整理を担当していました。一方、同じプロジェクト内では、別のチームがスジムラの発生メカニズムを整理していました。
-</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t xml:space="preserve">
 プライマ量を変えると粒状性や発色だけでなく、インクの広がり方や被覆状態を通じてスジムラにも影響する可能性があり、自分の担当範囲だけで整理すると、要因を見落とす懸念があると考えました。そこで、私からスジムラチームに働きかけ、これまでに整理していたスジムラの発生要因や物理現象を共有してもらいました。
 そのうえで、スジムラチームの整理方法を参考にしながら、プライマ量、カラーインク量、紙特性、インクの広がりや被覆状態、最終的な画質のつながりを整理しました。また、認識が異なる部分は打ち合わせで論点を提示し、用語や因果関係をすり合わせました。</t>
@@ -5633,21 +5535,6 @@
     <t>事業部の課題を見つけるためには、資料や会議だけでなく、実際の設計現場に足を運び、業務の進め方を直接確認することが重要だと考えています。
  例えば、事業部で行っているプライマの最適量を決める評価フローを実際に見せてもらい、どの工程に時間がかかっているのか、どの判断が担当者の経験に依存しているのか、どこで評価のやり直しが発生しているのかを確認します。
  そこで得た情報を、評価方法の不足や設計条件と画質の関係が整理できていないといった技術課題に置き換え、自部門の解析技術で解決できるテーマとして提案したいと考えています。</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>デジタルビジネスプラットフォーム開発本部、ソフトウェア33開発室の中岫茉希と申します。
-私の所属する部門では、商業印刷向けインクジェットプリンタの高画質化に向けて、印刷画質がどのような要因によって決まるのか、その仕組みを解析しています。
-その中で私は、商業印刷向けのインクジェットプリンタ、Mogamiを対象に、「プライマー」と呼ばれる透明なインクと画質との関係の解析を担当しています。
-プライマーとは、さまざまな用紙に対応するため、印刷前に用紙へ打つ透明な液体です。適切な量は用紙の種類やカラーインク量によって異なるため、評価すべき条件の組み合わせが膨大になることが課題です。
-そこで、プライマー量と画質の関係を明らかにし、少ない評価工数で適切なプライマー量を設計する手法を、デジプリ事業本部と連携して開発しています。これにより、事業部の設計の効率化に貢献してます。
-本日はよろしくお願いいたします。</t>
-    <rPh sb="226" eb="227">
-      <t>ウ</t>
-    </rPh>
-    <rPh sb="381" eb="383">
-      <t>コウケン</t>
-    </rPh>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -5977,9 +5864,6 @@
     <t>質問19：なぜ技術共有が進まないと思いますか</t>
   </si>
   <si>
-    <t>どの技術が横展開可能か整理できていない。</t>
-  </si>
-  <si>
     <t>各チームが自分の業務に閉じがちである。</t>
   </si>
   <si>
@@ -6065,13 +5949,1034 @@
  具体的には、プライマとインクが反応することで、インク中の成分が凝集し、その結果、紙上でのインクの広がり方や定着状態が変化します。
  そうした現象が、スジムラなどの画質にどのようにつながっているのかを定量的に整理することで、最終的には用紙に応じた適切なプライマ量を判断できるようにすることを目指しています。</t>
     <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>先輩と一緒に取り組む場合でも、単にサポートを受けるのではなく、主体的に自分で考えて行動することを心がけています。
+ 例えば、自分たちの知見だけでは進められないことや、他のチームと協力することでより深く検討できることについては、自分から積極的に打ち合わせを設定するようにしています。
+ 実際に、同じプロジェクト内でスジムラの発生メカニズムを解析しているチームがあり、スジムラにはプライマも関係しているため、共通する課題については自分から情報共有や議論の場を設け、お互いの知見を活用して検討を進めています。
+ このように、先輩から指示を受けて動くだけではなく、自分から必要な人を巻き込み、課題解決を前に進めることを意識しています。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>課の構成は管理職2名、主任5名、G3、〇一般職〇名です。
+私の開発室では、電子写真とインクジェットの両方について高画質化を実現するプロジェクトがあり、私hあインクジェットのほうに所属している。私のプロジェクトでは、２つのテーマがあって私の所属しているテーマは主任と私の２人で進めている。先輩は、チームのとりまとめ計画を担っていて、私の役割は、文献調査や評価用チャートの分析を通じて、プライマが画質に与える影響や技術課題を整理し、その後の開発をどのような方針で進めるかを先行して検討することです。また、２人のチームですので、主任が忙しいときに関しては、同じプロジェクトの別テーマの人と連携したり、事業部との対応も積極的に担っている。</t>
+    <rPh sb="0" eb="1">
+      <t>カ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>コウセイ</t>
+    </rPh>
+    <rPh sb="5" eb="8">
+      <t>カンリショク</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>メイ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>シュニン</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>メイ</t>
+    </rPh>
+    <rPh sb="20" eb="23">
+      <t>イッパンショク</t>
+    </rPh>
+    <rPh sb="24" eb="25">
+      <t>メイ</t>
+    </rPh>
+    <rPh sb="30" eb="31">
+      <t>ワタシ</t>
+    </rPh>
+    <rPh sb="32" eb="35">
+      <t>カイハツシツ</t>
+    </rPh>
+    <rPh sb="38" eb="42">
+      <t>デンシシャシン</t>
+    </rPh>
+    <rPh sb="51" eb="53">
+      <t>リョウホウ</t>
+    </rPh>
+    <rPh sb="57" eb="61">
+      <t>コウガシツカ</t>
+    </rPh>
+    <rPh sb="62" eb="64">
+      <t>ジツゲン</t>
+    </rPh>
+    <rPh sb="76" eb="77">
+      <t>ワタシ</t>
+    </rPh>
+    <rPh sb="90" eb="92">
+      <t>ショゾク</t>
+    </rPh>
+    <rPh sb="97" eb="98">
+      <t>ワタシ</t>
+    </rPh>
+    <rPh sb="118" eb="119">
+      <t>ワタシ</t>
+    </rPh>
+    <rPh sb="120" eb="122">
+      <t>ショゾク</t>
+    </rPh>
+    <rPh sb="130" eb="132">
+      <t>シュニン</t>
+    </rPh>
+    <rPh sb="133" eb="134">
+      <t>ワタシ</t>
+    </rPh>
+    <rPh sb="136" eb="137">
+      <t>リ</t>
+    </rPh>
+    <rPh sb="138" eb="139">
+      <t>スス</t>
+    </rPh>
+    <rPh sb="144" eb="146">
+      <t>センパイ</t>
+    </rPh>
+    <rPh sb="157" eb="159">
+      <t>ケイカク</t>
+    </rPh>
+    <rPh sb="160" eb="161">
+      <t>ニナ</t>
+    </rPh>
+    <rPh sb="166" eb="167">
+      <t>ワタシ</t>
+    </rPh>
+    <rPh sb="252" eb="253">
+      <t>リ</t>
+    </rPh>
+    <rPh sb="262" eb="264">
+      <t>シュニン</t>
+    </rPh>
+    <rPh sb="265" eb="266">
+      <t>イソガ</t>
+    </rPh>
+    <rPh sb="271" eb="272">
+      <t>カン</t>
+    </rPh>
+    <rPh sb="276" eb="277">
+      <t>オナ</t>
+    </rPh>
+    <rPh sb="285" eb="286">
+      <t>ベツ</t>
+    </rPh>
+    <rPh sb="290" eb="291">
+      <t>ヒト</t>
+    </rPh>
+    <rPh sb="292" eb="294">
+      <t>レンケイ</t>
+    </rPh>
+    <rPh sb="298" eb="301">
+      <t>ジギョウブ</t>
+    </rPh>
+    <rPh sb="303" eb="305">
+      <t>タイオウ</t>
+    </rPh>
+    <rPh sb="306" eb="309">
+      <t>セッキョクテキ</t>
+    </rPh>
+    <rPh sb="310" eb="311">
+      <t>ニナ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t xml:space="preserve">G3以降は、Mogamiに携わった経験を活かしながら、技術者としての専門性をさらに高め、将来的には高画質化に関わる技術の先駆者になりたいと考えています。
+ また、自分の担当領域だけに閉じず、CPPなど商業印刷に関わる部門とも連携しながら、海外で活躍できる人材になりたいと考えている。
+ そのために現在は、商業印刷に関する知識を深めることに加えて、現象を定量的に捉えるための統計的な知識や、将来の活躍の幅を広げるための英語の習得にも取り組んでいます。
+</t>
+    <rPh sb="119" eb="121">
+      <t>カイガイ</t>
+    </rPh>
+    <rPh sb="122" eb="124">
+      <t>カツヤク</t>
+    </rPh>
+    <rPh sb="127" eb="129">
+      <t>ジンザイ</t>
+    </rPh>
+    <rPh sb="135" eb="136">
+      <t>カンガ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>どの技術が横展開可能か整理できていない。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t xml:space="preserve">
+組織の課題として、プロジェクトが縦割りになり、得られた技術や知見が十分に横展開されていないことがあると考えています。
+ 原因として、各チームが自分たちの業務に閉じがちなこと、また他チームがどのような課題を抱えているのか見えにくいことがあると考えています。
+自分のプロジェクトで出た課題を共有</t>
+    <rPh sb="131" eb="133">
+      <t>ジブン</t>
+    </rPh>
+    <rPh sb="141" eb="142">
+      <t>デ</t>
+    </rPh>
+    <rPh sb="143" eb="145">
+      <t>カダイ</t>
+    </rPh>
+    <rPh sb="146" eb="148">
+      <t>キョウユウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>デジタルビジネスプラットフォーム開発本部、ソフトウェア33開発室の中岫茉希と申します。
+私の所属する部門では、商業印刷向けプリンタの高画質化に向けて、印刷画質がどのような要因によって決まるのか、その仕組みを解析しています。
+商業印刷分野では、顧客に応じて多様な紙に対して高画質で印刷されることが求められます。
+そのため、印刷前に「プライマ」と呼ばれる透明な液体を紙に打つことで、画質を向上させています。
+ただプライマ量は紙によって適切な量が異なるため、その調整には多くの評価が必要です。
+そこで、私はプライマ量と画質の関係を解明することで、少ない評価で適切な量を決められる手法を、デジプリ事業本部と連携して開発し、設計の効率化につなげています。
+本日はよろしくお願いいたします。</t>
+    <rPh sb="114" eb="116">
+      <t>ショウギョウ</t>
+    </rPh>
+    <rPh sb="116" eb="118">
+      <t>インサツ</t>
+    </rPh>
+    <rPh sb="118" eb="120">
+      <t>ブンヤ</t>
+    </rPh>
+    <rPh sb="123" eb="125">
+      <t>コキャク</t>
+    </rPh>
+    <rPh sb="126" eb="127">
+      <t>オウ</t>
+    </rPh>
+    <rPh sb="129" eb="131">
+      <t>タヨウ</t>
+    </rPh>
+    <rPh sb="132" eb="133">
+      <t>カミ</t>
+    </rPh>
+    <rPh sb="134" eb="135">
+      <t>タイ</t>
+    </rPh>
+    <rPh sb="137" eb="140">
+      <t>コウガシツ</t>
+    </rPh>
+    <rPh sb="141" eb="143">
+      <t>インサツ</t>
+    </rPh>
+    <rPh sb="149" eb="150">
+      <t>モト</t>
+    </rPh>
+    <rPh sb="185" eb="186">
+      <t>ウ</t>
+    </rPh>
+    <rPh sb="194" eb="196">
+      <t>コウジョウ</t>
+    </rPh>
+    <rPh sb="210" eb="211">
+      <t>リョウ</t>
+    </rPh>
+    <rPh sb="250" eb="251">
+      <t>ワタシ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <r>
+      <t>事業部と伴走するうえでは、</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>自分たちの技術を一方的に提案するのではなく、まず事業部が何に困っていて、何を実現したいのかを理解すること</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>を意識しています。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>そのうえで、例えばプライマと画質の関係を整理する場合も、解析すること自体を目的にせず、</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>設計工数の削減など、実際の設計にどう役立てられるかを事業部とすり合わせながら進める</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>ことを心がけています。</t>
+    </r>
+  </si>
+  <si>
+    <t>「具体的に何種類まで増えるかは一概には言えませんが、商業印刷では顧客ごとに使用する用紙が異なり、今後さらに多品種への対応が求められると考えています。そのため、一枚一枚の用紙に個別対応するのではなく、紙物性と画質の関係を整理して、未知の用紙にも効率よく条件設計できるようにすることが重要です。」</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>どれだけ紙の種類増えるの</t>
+    <rPh sb="4" eb="5">
+      <t>カミ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>シュルイ</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>フ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>プロジェクトの苦労した点</t>
+    <rPh sb="7" eb="9">
+      <t>クロウ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>テン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>プライマ量を増減させて画質の良し悪しを見るだけではなく、紙の種類やインク量など複数の条件が絡む中で、プライマが各画質特性にどう影響するのかを整理しています。特に、ある画質を改善すると別の画質が悪化するトレードオフもあるため、複数の画質特性を定量的に評価し、どの条件なら最適になるかを明らかにしようとしている点に技術的な難しさがあります。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>関係図作成。すべての画質に対して、どのようなメカニズムで画質が悪くなるのかを関連図を作ったため、要素数が多くてとても分かりにくくなってしまった。それに対して、どのように事業部でも利用してもらえるかを考えたときに、関連するものがクリックされたらその要素だけが抽出されるツールを作った。このツール作成のときに、クリックされて残ってほしいものが消えてしまったり、いらないものが残ってしまったりした。その要因をひとつずつかみ砕いて、ツールを最終的に完成させた。→新たなものを作るハードルは高かったが、実際に使ってもらいやすいツールを作れてよかった</t>
+    <rPh sb="0" eb="3">
+      <t>カンケイズ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>サクセイ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>ガシツ</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>タイ</t>
+    </rPh>
+    <rPh sb="28" eb="30">
+      <t>ガシツ</t>
+    </rPh>
+    <rPh sb="31" eb="32">
+      <t>ワル</t>
+    </rPh>
+    <rPh sb="38" eb="41">
+      <t>カンレンズ</t>
+    </rPh>
+    <rPh sb="42" eb="43">
+      <t>ツク</t>
+    </rPh>
+    <rPh sb="48" eb="50">
+      <t>ヨウソ</t>
+    </rPh>
+    <rPh sb="50" eb="51">
+      <t>スウ</t>
+    </rPh>
+    <rPh sb="52" eb="53">
+      <t>オオ</t>
+    </rPh>
+    <rPh sb="58" eb="59">
+      <t>ワ</t>
+    </rPh>
+    <rPh sb="75" eb="76">
+      <t>タイ</t>
+    </rPh>
+    <rPh sb="84" eb="87">
+      <t>ジギョウブ</t>
+    </rPh>
+    <rPh sb="89" eb="91">
+      <t>リヨウ</t>
+    </rPh>
+    <rPh sb="99" eb="100">
+      <t>カンガ</t>
+    </rPh>
+    <rPh sb="106" eb="108">
+      <t>カンレン</t>
+    </rPh>
+    <rPh sb="123" eb="125">
+      <t>ヨウソ</t>
+    </rPh>
+    <rPh sb="128" eb="130">
+      <t>チュウシュツ</t>
+    </rPh>
+    <rPh sb="137" eb="138">
+      <t>ツク</t>
+    </rPh>
+    <rPh sb="146" eb="148">
+      <t>サクセイ</t>
+    </rPh>
+    <rPh sb="160" eb="161">
+      <t>ノコ</t>
+    </rPh>
+    <rPh sb="169" eb="170">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="185" eb="186">
+      <t>ノコ</t>
+    </rPh>
+    <rPh sb="198" eb="200">
+      <t>ヨウイン</t>
+    </rPh>
+    <rPh sb="208" eb="209">
+      <t>クダ</t>
+    </rPh>
+    <rPh sb="216" eb="218">
+      <t>サイシュウ</t>
+    </rPh>
+    <rPh sb="218" eb="219">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="220" eb="222">
+      <t>カンセイ</t>
+    </rPh>
+    <rPh sb="227" eb="228">
+      <t>アラ</t>
+    </rPh>
+    <rPh sb="233" eb="234">
+      <t>ツク</t>
+    </rPh>
+    <rPh sb="240" eb="241">
+      <t>タカ</t>
+    </rPh>
+    <rPh sb="246" eb="248">
+      <t>ジッサイ</t>
+    </rPh>
+    <rPh sb="249" eb="250">
+      <t>ツカ</t>
+    </rPh>
+    <rPh sb="262" eb="263">
+      <t>ツク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>プロジェクトごとに専門性を高め、担当領域を明確にできることは縦割りのメリットだと考えています。一方で、各プロジェクトで得られた知見が閉じてしまうと、他のプロジェクトで活用できる技術まで共有されにくくなります。そのため、縦割りをなくすのではなく、専門性は維持しながら、横断的に知見を共有できる仕組みが必要だと考えています。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>① 中岫さん</t>
+  </si>
+  <si>
+    <t>自己紹介</t>
+  </si>
+  <si>
+    <t>Q</t>
+  </si>
+  <si>
+    <t>名前と1分間自己紹介をお願いします。</t>
+  </si>
+  <si>
+    <t>A</t>
+  </si>
+  <si>
+    <t>DBP開発本部ソフトウェア33開発室所属。</t>
+  </si>
+  <si>
+    <t>商業印刷プリンターの高画質化に向けて画質決定要因の解析を担当。</t>
+  </si>
+  <si>
+    <t>多様な紙への対応のためプライマーを使用するが、紙種ごとに最適量が異なり調整に時間がかかる。</t>
+  </si>
+  <si>
+    <t>プライマーと画質の関係を解析し、デジプリ事業部と連携して設計効率化に貢献している。</t>
+  </si>
+  <si>
+    <t>Q1</t>
+  </si>
+  <si>
+    <t>所属している課の構成とあなたの役割について説明してください。</t>
+  </si>
+  <si>
+    <t>課は21名（管理職2名、主任5名、会員14名）。</t>
+  </si>
+  <si>
+    <t>インクジェット商業印刷と電子写真の高画質化プロジェクトがある。</t>
+  </si>
+  <si>
+    <t>自分はインクジェット商業印刷のプロジェクト担当。</t>
+  </si>
+  <si>
+    <t>自チームは主任と2名体制。</t>
+  </si>
+  <si>
+    <t>主任は計画立案・チーム運営担当。</t>
+  </si>
+  <si>
+    <t>自分は文献や論文を用いたプライマーと画質の関係調査を担当。</t>
+  </si>
+  <si>
+    <t>必要時には他チームとの連携も担当。</t>
+  </si>
+  <si>
+    <t>Q2</t>
+  </si>
+  <si>
+    <t>G2とG3の違いは何ですか。またG3になったらどういう役割を担いたいですか。</t>
+  </si>
+  <si>
+    <t>G2は与えられたタスクを確実に遂行して成果を出す役割。</t>
+  </si>
+  <si>
+    <t>G3は課題に対して必要な人を巻き込みながら推進する役割。</t>
+  </si>
+  <si>
+    <t>自身は適切な人を巻き込んでプロジェクト推進を行いたい。</t>
+  </si>
+  <si>
+    <t>Q3</t>
+  </si>
+  <si>
+    <t>G3になったら何を重点的にやりたいですか。</t>
+  </si>
+  <si>
+    <t>専門家を巻き込んで推進する役割を担いたい。</t>
+  </si>
+  <si>
+    <t>プライマー解析ではインク知識や化学知識が必要だった。</t>
+  </si>
+  <si>
+    <t>デジプリ事業部の専門家を巻き込みながらメカニズム解明を行った。</t>
+  </si>
+  <si>
+    <t>今後も自分の専門外の知見を積極的に取り込みたい。</t>
+  </si>
+  <si>
+    <t>Q4</t>
+  </si>
+  <si>
+    <t>そのような活動で難しかったことと克服方法を教えてください。</t>
+  </si>
+  <si>
+    <t>自分の専門外知識を把握することが難しかった。</t>
+  </si>
+  <si>
+    <t>事業部と用語定義や現象の捉え方が異なった。</t>
+  </si>
+  <si>
+    <t>議論開始時に認識合わせを行い、定義を明確化した。</t>
+  </si>
+  <si>
+    <t>Q5</t>
+  </si>
+  <si>
+    <t>チームや部門の一番の課題は何ですか。</t>
+  </si>
+  <si>
+    <t>プロジェクトが縦割りで知見共有が不十分なこと。</t>
+  </si>
+  <si>
+    <t>部会等で知見共有を進めるべき。</t>
+  </si>
+  <si>
+    <t>重複開発の防止につながる。</t>
+  </si>
+  <si>
+    <t>Q6</t>
+  </si>
+  <si>
+    <t>縦割り体制の良い面についてはどう思いますか。</t>
+  </si>
+  <si>
+    <t>同じ製品を継続的に担当できるため知識が蓄積できる。</t>
+  </si>
+  <si>
+    <t>一方で考え方が偏る可能性がある。</t>
+  </si>
+  <si>
+    <t>IJと電子写真間でジョブローテーションがあると良い。</t>
+  </si>
+  <si>
+    <t>Q7</t>
+  </si>
+  <si>
+    <t>今までで最も達成感があったことは何ですか。</t>
+  </si>
+  <si>
+    <t>プライマー量決定の評価フローを新方式として提案し、事業部に受け入れられたこと。</t>
+  </si>
+  <si>
+    <t>現行手法は手作業が多く時間がかかっていた。</t>
+  </si>
+  <si>
+    <t>事業部知見と解析技術を組み合わせて改善案を提案した。</t>
+  </si>
+  <si>
+    <t>Q8</t>
+  </si>
+  <si>
+    <t>最も失敗した経験は何ですか。</t>
+  </si>
+  <si>
+    <t>用語や現象の認識差により議論が噛み合わず時間を浪費した。</t>
+  </si>
+  <si>
+    <t>今後はプロジェクト初期に共通認識形成を行う。</t>
+  </si>
+  <si>
+    <t>Q9</t>
+  </si>
+  <si>
+    <t>事業部と本部で根本的な考え方の違いはありますか。</t>
+  </si>
+  <si>
+    <t>事業部は製品リリースなど短期目標を重視。</t>
+  </si>
+  <si>
+    <t>本部は長期的な効率化や将来技術を重視。</t>
+  </si>
+  <si>
+    <t>その視点差から意見の違いが生じる。</t>
+  </si>
+  <si>
+    <t>Q10</t>
+  </si>
+  <si>
+    <t>プライマーはキャノン独自技術ですか。</t>
+  </si>
+  <si>
+    <t>他社でも使われている。</t>
+  </si>
+  <si>
+    <t>前処理液など別名称の場合もある。</t>
+  </si>
+  <si>
+    <t>Q11</t>
+  </si>
+  <si>
+    <t>新しい設計フローは事業部に受け入れられましたか。</t>
+  </si>
+  <si>
+    <t>最終的には受け入れられた。</t>
+  </si>
+  <si>
+    <t>当初は現行手法維持の意見もあった。</t>
+  </si>
+  <si>
+    <t>将来の紙種増加への対応必要性を理解してもらえた。</t>
+  </si>
+  <si>
+    <t>Q12</t>
+  </si>
+  <si>
+    <t>今後紙種は増えるのですか。</t>
+  </si>
+  <si>
+    <t>現在は約300種類。</t>
+  </si>
+  <si>
+    <t>高画質要件により対象紙は今後増える可能性がある。</t>
+  </si>
+  <si>
+    <t>後継機ではより多くの紙種への対応が必要。</t>
+  </si>
+  <si>
+    <t>中岫さんへのアドバイス</t>
+  </si>
+  <si>
+    <t>課構成説明は定番質問なので、もっとコンパクトに整理するとよい。細部より全体像が伝わる粒度を意識する。</t>
+  </si>
+  <si>
+    <t>用語定義の話では「なぜそれを重要だと思ったのか」という上位視点を加えるとよい。G4や管理職レベルの視点で語れると評価されやすい。</t>
+  </si>
+  <si>
+    <t>紙種拡大の必要性については、顧客価値やキャノンブランド向上という高い視座で語ると説得力が増す。</t>
+  </si>
+  <si>
+    <t>育成質問への備えをしておく。よく出るテーマなので回答例を準備しておくべき。</t>
+  </si>
+  <si>
+    <t>仕事内容が順調に進んだ話だけでなく、技術的難しさや困難さをもっとアピールした方がよい。課題をどう乗り越えたかが評価される。</t>
+  </si>
+  <si>
+    <t>対外折衝や事業部との調整で苦労したエピソードがあるとG3らしさが出る。困難→工夫→成果の流れで語れるとよい。</t>
+  </si>
+  <si>
+    <t>新フロー提案時の工夫や定量効果をもっと具体的に話してよい。事業部との利害調整も良い題材になる。</t>
+  </si>
+  <si>
+    <t>聞かれていないことを話しすぎる必要はない。質問への回答を優先しつつ、少しだけ付加価値を加えるくらいがよい。</t>
+  </si>
+  <si>
+    <t>② 新家さん</t>
+  </si>
+  <si>
+    <t>名前と1分自己紹介をお願いします。</t>
+  </si>
+  <si>
+    <t>DBP開発本部ソフトウェア12開発室所属。</t>
+  </si>
+  <si>
+    <t>EOS VRシステム向け画像処理開発担当。</t>
+  </si>
+  <si>
+    <t>デュアルフィッシュアイレンズ映像をVR映像へ変換するシステム。</t>
+  </si>
+  <si>
+    <t>TPP側でアルゴリズム開発を担当。</t>
+  </si>
+  <si>
+    <t>プロジェクトのメンバー構成とあなたの役割を説明してください。</t>
+  </si>
+  <si>
+    <t>室長がPM。</t>
+  </si>
+  <si>
+    <t>主幹がプロジェクトリーダー。</t>
+  </si>
+  <si>
+    <t>実務担当2名。</t>
+  </si>
+  <si>
+    <t>自分はアルゴリズム開発・実装を担当。</t>
+  </si>
+  <si>
+    <t>部下とのやり取りで苦労したことはありますか。</t>
+  </si>
+  <si>
+    <t>後輩は優秀で大きな問題はなかった。</t>
+  </si>
+  <si>
+    <t>むしろ事業部への技術移管・育成の方が苦労した。</t>
+  </si>
+  <si>
+    <t>AI学習環境の使い方を一から説明する必要があった。</t>
+  </si>
+  <si>
+    <t>どうやって解決しましたか。</t>
+  </si>
+  <si>
+    <t>相手の知識レベルを把握した。</t>
+  </si>
+  <si>
+    <t>Linuxコマンドレベルから説明した。</t>
+  </si>
+  <si>
+    <t>相手に合わせて資料や説明を調整した。</t>
+  </si>
+  <si>
+    <t>AI技術はどのように学びましたか。</t>
+  </si>
+  <si>
+    <t>大学・大学院から画像処理を専攻。</t>
+  </si>
+  <si>
+    <t>AIブーム初期から学習していた世代。</t>
+  </si>
+  <si>
+    <t>業務経験と自主学習で習得した。</t>
+  </si>
+  <si>
+    <t>EOS VRは他のカメラ画像処理と何が違いますか。</t>
+  </si>
+  <si>
+    <t>デュアルフィッシュアイという特殊な入力。</t>
+  </si>
+  <si>
+    <t>180度超の魚眼画像を扱う。</t>
+  </si>
+  <si>
+    <t>特殊な座標系変換が必要。</t>
+  </si>
+  <si>
+    <t>左右視差補正も必要。</t>
+  </si>
+  <si>
+    <t>その技術的な難しさは何ですか。</t>
+  </si>
+  <si>
+    <t>一般的な左右マッチング技術は通常画像前提。</t>
+  </si>
+  <si>
+    <t>デュアルフィッシュアイ向け学習データが存在しない。</t>
+  </si>
+  <si>
+    <t>独自に学習データセットを作成した。</t>
+  </si>
+  <si>
+    <t>新規技術開発で工夫していることは何ですか。</t>
+  </si>
+  <si>
+    <t>広く知識を収集すること。</t>
+  </si>
+  <si>
+    <t>異分野技術も調査すること。</t>
+  </si>
+  <si>
+    <t>異なる分野の技術を融合して活用すること。</t>
+  </si>
+  <si>
+    <t>失敗経験を教えてください。</t>
+  </si>
+  <si>
+    <t>CG素材利用時の指示不足。</t>
+  </si>
+  <si>
+    <t>部下が利用不可素材を使用してしまった。</t>
+  </si>
+  <si>
+    <t>手戻りが発生した。</t>
+  </si>
+  <si>
+    <t>指示と確認の重要性を学んだ。</t>
+  </si>
+  <si>
+    <t>EOS VRを普及させるにはどうすればよいですか。</t>
+  </si>
+  <si>
+    <t>スマートグラス普及が前提。</t>
+  </si>
+  <si>
+    <t>キラーコンテンツが重要。</t>
+  </si>
+  <si>
+    <t>EOS VRならではの体験価値を提供する必要がある。</t>
+  </si>
+  <si>
+    <t>新家さんへのアドバイス</t>
+  </si>
+  <si>
+    <t>話し方や回答は安定しており全体的に良い。上位視点へ自然に話を繋げられていた点も評価できる。</t>
+  </si>
+  <si>
+    <t>アルゴリズム開発では「自分がどう工夫したか」をもっと強調した方がよい。作業報告ではなく主体性を見せるべき。</t>
+  </si>
+  <si>
+    <t>自分で考えたこと、調べたこと、周囲を納得させたことをエピソードに入れるとポテンシャルが伝わる。</t>
+  </si>
+  <si>
+    <t>縦ずれ補正の意義をもっと説明してよい。技術だけでなく「なぜ必要なのか」を伝えるべき。</t>
+  </si>
+  <si>
+    <t>巻き込みや展開のエピソードをもう一つ持っておくと強い。社内への知見共有や啓蒙活動は良い題材になる。</t>
+  </si>
+  <si>
+    <t>コンプライアンス問題発見と部内共有の話は非常に良いエピソード。育成や再発防止と結びつけるとさらに評価される。</t>
+  </si>
+  <si>
+    <t>質問への回答が途中でずれることがある。まず結論を答え、その後に詳細説明することを意識すると良い。</t>
+  </si>
+  <si>
+    <t>以前より大幅に改善している。話がそれても元に戻せるようになっており安心感がある。</t>
+  </si>
+  <si>
+    <t>③ 市場さん</t>
+  </si>
+  <si>
+    <t>商業印刷向け電子写真プリンタの画質改善業務を担当。</t>
+  </si>
+  <si>
+    <t>計測解析技術をデジプリ設計部門へ提案。</t>
+  </si>
+  <si>
+    <t>粒状性とトナー配置の関係を解析。</t>
+  </si>
+  <si>
+    <t>目標粒状性を達成するためのトナー配置条件を解明。</t>
+  </si>
+  <si>
+    <t>5名チームで解析技術開発を担当。</t>
+  </si>
+  <si>
+    <t>課の構成とあなたの役割を教えてください。</t>
+  </si>
+  <si>
+    <t>室全体23名。</t>
+  </si>
+  <si>
+    <t>室長1名、主幹1名、一般職21名。</t>
+  </si>
+  <si>
+    <t>EPとIJの高画質化を担当する4チーム構成。</t>
+  </si>
+  <si>
+    <t>自身は電子写真向け計測解析技術チーム所属。</t>
+  </si>
+  <si>
+    <t>5名チームで解析サブチーム担当。</t>
+  </si>
+  <si>
+    <t>技術開発のサブリーダー。</t>
+  </si>
+  <si>
+    <t>大きな苦労はない。</t>
+  </si>
+  <si>
+    <t>背景知識や経緯を意識して共有している。</t>
+  </si>
+  <si>
+    <t>主体的に検討に入れる環境作りを意識している。</t>
+  </si>
+  <si>
+    <t>上司との関係で困ったことはありますか。</t>
+  </si>
+  <si>
+    <t>特にない。</t>
+  </si>
+  <si>
+    <t>情報共有を密に行っている。</t>
+  </si>
+  <si>
+    <t>認識差を早期に解消できている。</t>
+  </si>
+  <si>
+    <t>事業部との関係で苦労したことはありますか。</t>
+  </si>
+  <si>
+    <t>提供した解析技術が活用されなかった。</t>
+  </si>
+  <si>
+    <t>なぜ使われないか調査した。</t>
+  </si>
+  <si>
+    <t>開発会議に参加しヒアリングした。</t>
+  </si>
+  <si>
+    <t>どう解決したのですか。</t>
+  </si>
+  <si>
+    <t>原因は因果関係への納得感不足だった。</t>
+  </si>
+  <si>
+    <t>トナー配置と粒状性の因果関係を説明する数理モデルを提案。</t>
+  </si>
+  <si>
+    <t>納得してもらい開発指標として活用してもらえた。</t>
+  </si>
+  <si>
+    <t>グループの目指すべき姿は何ですか。</t>
+  </si>
+  <si>
+    <t>依頼をそのまま開発するのではなく課題の本質を理解する。</t>
+  </si>
+  <si>
+    <t>将来展開も考えた事業部の資産となる技術を提供する。</t>
+  </si>
+  <si>
+    <t>G3になったらどのような役割を果たしますか。</t>
+  </si>
+  <si>
+    <t>事業部内部に入り課題を発掘する。</t>
+  </si>
+  <si>
+    <t>連携先以外の部門にもヒアリングする。</t>
+  </si>
+  <si>
+    <t>デジプリ全体の課題解決に貢献したい。</t>
+  </si>
+  <si>
+    <t>G3として十分な点と不足している点は何ですか。</t>
+  </si>
+  <si>
+    <t>十分な点</t>
+  </si>
+  <si>
+    <t>論理的説明力。</t>
+  </si>
+  <si>
+    <t>数学的手法による説明。</t>
+  </si>
+  <si>
+    <t>相手を納得させる能力。</t>
+  </si>
+  <si>
+    <t>不足している点</t>
+  </si>
+  <si>
+    <t>事業部ドメイン知識。</t>
+  </si>
+  <si>
+    <t>より深い課題発掘能力。</t>
+  </si>
+  <si>
+    <t>仕事で大事にしていることは何ですか。</t>
+  </si>
+  <si>
+    <t>事業部目線で使いやすいことを第一に考えること。</t>
+  </si>
+  <si>
+    <t>それが行動に結びついた具体例はありますか。</t>
+  </si>
+  <si>
+    <t>ヒアリングを行い利用者目線で課題を把握した。</t>
+  </si>
+  <si>
+    <t>その結果として改善策提案につながった。</t>
+  </si>
+  <si>
+    <t>粒状性を改善すれば目標達成ですか。</t>
+  </si>
+  <si>
+    <t>粒状性が最大の課題。</t>
+  </si>
+  <si>
+    <t>ただし光沢ムラなど他課題も存在する。</t>
+  </si>
+  <si>
+    <t>今後もメカニズム解明アプローチで改善を進める。</t>
+  </si>
+  <si>
+    <t>情報共有で工夫していることはありますか。</t>
+  </si>
+  <si>
+    <t>結論だけでなく背景や目的も共有する。</t>
+  </si>
+  <si>
+    <t>相手に納得してもらうことを重視している。</t>
+  </si>
+  <si>
+    <t>市場さんへのアドバイス</t>
+  </si>
+  <si>
+    <t>全体的には内容もしっかりしており回答も安定している。苦労した点の質問は自慢話につなげる意図だと理解して活用すると良い。</t>
+  </si>
+  <si>
+    <t>論理性や数理モデルの話では、会社に与えるメリットまで説明するとさらに強くなる。属人性排除や開発効率向上まで語れると良い。</t>
+  </si>
+  <si>
+    <t>「目指す姿」「G3として何をするか」はもっと端的な結論から話した方がよい。定番質問なので短く明確な回答を準備しておくべき。</t>
+  </si>
+  <si>
+    <t>質問文を繰り返してから答えると伝わりやすい。「目指す姿は」「G3としては」など主題を明確にすると良い。</t>
+  </si>
+  <si>
+    <t>役割説明では先に全体説明する理由を一言添えると聞き手が安心する。組織説明もやや長いため整理した方がよい。</t>
+  </si>
+  <si>
+    <t>数理モデルの価値をもっと強くアピールしてよい。普遍性や再利用性、機種変更後も使える点は強力な訴求材料。</t>
+  </si>
+  <si>
+    <t>部門課題やG3の役割の質問から数理モデルの話へ自然につなげる準備をしておくと良い。持ち込みたい強みを意図的に話せるようにする。</t>
+  </si>
+  <si>
+    <t>面接官は「将来もっと上に行きたい人か」を見ている。野望や信念、組織をこう変えたいという思いをもっと前面に出した方がよい。</t>
+  </si>
+  <si>
+    <t>質問パターンごとに使いたいキラーワードを準備しておくと良い。事前に引き出しを作っておけば本番でも安定して話せる。</t>
+  </si>
+  <si>
+    <t>全体として以前よりかなり改善している。今後は回答精度よりも、強みや将来性を印象付ける段階に入っている。</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="23">
+  <fonts count="28">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -6236,6 +7141,40 @@
       <family val="3"/>
       <charset val="128"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="24"/>
+      <color theme="1"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="1"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13.5"/>
+      <color theme="1"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="8">
     <fill>
@@ -6347,7 +7286,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="46">
+  <cellXfs count="52">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -6485,6 +7424,24 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -6729,7 +7686,7 @@
         <v>178</v>
       </c>
       <c r="C2" s="18" t="s">
-        <v>424</v>
+        <v>553</v>
       </c>
       <c r="D2" s="25" t="s">
         <v>171</v>
@@ -6766,7 +7723,7 @@
         <v>91</v>
       </c>
       <c r="C4" s="18" t="s">
-        <v>290</v>
+        <v>549</v>
       </c>
       <c r="D4" s="25" t="s">
         <v>172</v>
@@ -6863,7 +7820,7 @@
         <v>96</v>
       </c>
       <c r="C10" s="18" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="E10" s="12" t="s">
         <v>187</v>
@@ -6893,7 +7850,7 @@
         <v>98</v>
       </c>
       <c r="C12" s="18" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="E12" s="13" t="s">
         <v>189</v>
@@ -6908,7 +7865,7 @@
         <v>99</v>
       </c>
       <c r="C13" s="17" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="E13" s="13"/>
       <c r="F13" s="14"/>
@@ -6921,7 +7878,7 @@
         <v>100</v>
       </c>
       <c r="C14" s="36" t="s">
-        <v>292</v>
+        <v>552</v>
       </c>
       <c r="E14" s="13" t="s">
         <v>190</v>
@@ -7888,18 +8845,361 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E3B1E147-F943-43CF-88AE-86DE70DEEA3B}">
+  <dimension ref="A1:B21"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
+  <cols>
+    <col min="1" max="1" width="150.375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="103.375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" s="24"/>
+      <c r="B1" s="24"/>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" s="24" t="s">
+        <v>150</v>
+      </c>
+      <c r="B2" s="24"/>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" s="33" t="s">
+        <v>251</v>
+      </c>
+      <c r="B3" s="24"/>
+    </row>
+    <row r="4" spans="1:2" ht="40.5">
+      <c r="A4" s="33" t="s">
+        <v>258</v>
+      </c>
+      <c r="B4" s="23" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" s="33" t="s">
+        <v>259</v>
+      </c>
+      <c r="B5" s="23"/>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" s="33" t="s">
+        <v>260</v>
+      </c>
+      <c r="B6" s="24"/>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" s="33" t="s">
+        <v>261</v>
+      </c>
+      <c r="B7" s="23"/>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" s="35" t="s">
+        <v>262</v>
+      </c>
+      <c r="B8" s="33" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" s="33" t="s">
+        <v>263</v>
+      </c>
+      <c r="B9" s="24"/>
+    </row>
+    <row r="10" spans="1:2" ht="40.5">
+      <c r="A10" s="33" t="s">
+        <v>264</v>
+      </c>
+      <c r="B10" s="23" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" s="33" t="s">
+        <v>265</v>
+      </c>
+      <c r="B11" s="24"/>
+    </row>
+    <row r="12" spans="1:2">
+      <c r="A12" s="35" t="s">
+        <v>266</v>
+      </c>
+      <c r="B12" s="24"/>
+    </row>
+    <row r="13" spans="1:2">
+      <c r="A13" s="33" t="s">
+        <v>267</v>
+      </c>
+      <c r="B13" s="24"/>
+    </row>
+    <row r="14" spans="1:2">
+      <c r="A14" s="33" t="s">
+        <v>268</v>
+      </c>
+      <c r="B14" s="24"/>
+    </row>
+    <row r="15" spans="1:2">
+      <c r="A15" s="33" t="s">
+        <v>269</v>
+      </c>
+      <c r="B15" s="24"/>
+    </row>
+    <row r="16" spans="1:2">
+      <c r="A16" s="24"/>
+      <c r="B16" s="24"/>
+    </row>
+    <row r="17" spans="1:2">
+      <c r="A17" s="24"/>
+      <c r="B17" s="24"/>
+    </row>
+    <row r="18" spans="1:2">
+      <c r="A18" s="24"/>
+      <c r="B18" s="24"/>
+    </row>
+    <row r="19" spans="1:2">
+      <c r="A19" s="24"/>
+      <c r="B19" s="24"/>
+    </row>
+    <row r="20" spans="1:2" ht="67.5">
+      <c r="A20" s="24"/>
+      <c r="B20" s="23" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2">
+      <c r="A21" s="24"/>
+      <c r="B21" s="24"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4E6BF410-1D86-4886-AF32-D2372AA65DBD}">
+  <dimension ref="A1:B9"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
+  <cols>
+    <col min="1" max="1" width="51.875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="119.375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" s="34" t="s">
+        <v>278</v>
+      </c>
+      <c r="B1" s="34" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" s="34" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" s="34" t="s">
+        <v>281</v>
+      </c>
+      <c r="B3" s="34" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="67.5">
+      <c r="A4" s="34" t="s">
+        <v>283</v>
+      </c>
+      <c r="B4" s="38" t="s">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" s="34" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" s="34" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" ht="108">
+      <c r="A7" s="34" t="s">
+        <v>286</v>
+      </c>
+      <c r="B7" s="38" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" s="34" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" s="34" t="s">
+        <v>288</v>
+      </c>
+      <c r="B9" s="34" t="s">
+        <v>289</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AF701674-7A60-413B-8525-5F23C4EF17DB}">
+  <dimension ref="A1:B19"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
+  <cols>
+    <col min="1" max="1" width="63.125" customWidth="1"/>
+    <col min="2" max="2" width="73.875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" ht="121.5">
+      <c r="A1" s="34" t="s">
+        <v>409</v>
+      </c>
+      <c r="B1" s="38" t="s">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" ht="121.5">
+      <c r="A2" s="34" t="s">
+        <v>415</v>
+      </c>
+      <c r="B2" s="38" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" s="34" t="s">
+        <v>410</v>
+      </c>
+      <c r="B3" s="34" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" s="34" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" ht="67.5">
+      <c r="A5" s="34" t="s">
+        <v>417</v>
+      </c>
+      <c r="B5" s="38" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" s="34" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" s="34" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" ht="102" customHeight="1">
+      <c r="A8" s="34" t="s">
+        <v>419</v>
+      </c>
+      <c r="B8" s="38" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" ht="102" customHeight="1">
+      <c r="A9" s="34" t="s">
+        <v>422</v>
+      </c>
+      <c r="B9" s="38" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" ht="102" customHeight="1">
+      <c r="A10" s="34" t="s">
+        <v>424</v>
+      </c>
+      <c r="B10" s="38" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" ht="102" customHeight="1">
+      <c r="A11" s="34"/>
+      <c r="B11" s="38" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2">
+      <c r="A12" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
+      <c r="A13" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2">
+      <c r="A14" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2">
+      <c r="A15" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2">
+      <c r="A16" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1">
+      <c r="A17" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1">
+      <c r="A18" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1">
+      <c r="A19" t="s">
+        <v>408</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7016FA33-FF68-4C3D-B093-FADADA8DE1A9}">
   <dimension ref="A1:A278"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <sheetData>
     <row r="1" spans="1:1" ht="21">
       <c r="A1" s="39" t="s">
-        <v>430</v>
+        <v>426</v>
       </c>
     </row>
     <row r="3" spans="1:1" ht="16.5">
       <c r="A3" s="40" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
     </row>
     <row r="4" spans="1:1">
@@ -7907,42 +9207,42 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" s="42" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" s="42" t="s">
-        <v>433</v>
+        <v>429</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" s="42" t="s">
-        <v>434</v>
+        <v>430</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" s="42" t="s">
-        <v>435</v>
+        <v>431</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" s="42" t="s">
-        <v>436</v>
+        <v>432</v>
       </c>
     </row>
     <row r="10" spans="1:1">
       <c r="A10" s="42" t="s">
-        <v>437</v>
+        <v>433</v>
       </c>
     </row>
     <row r="14" spans="1:1" ht="21">
       <c r="A14" s="39" t="s">
-        <v>438</v>
+        <v>434</v>
       </c>
     </row>
     <row r="16" spans="1:1" ht="16.5">
       <c r="A16" s="40" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
     </row>
     <row r="17" spans="1:1">
@@ -7950,27 +9250,27 @@
     </row>
     <row r="18" spans="1:1">
       <c r="A18" s="42" t="s">
-        <v>439</v>
+        <v>435</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" s="42" t="s">
-        <v>440</v>
+        <v>436</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" s="42" t="s">
-        <v>441</v>
+        <v>437</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" s="42" t="s">
-        <v>442</v>
+        <v>438</v>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23" s="34" t="s">
-        <v>443</v>
+        <v>439</v>
       </c>
     </row>
     <row r="24" spans="1:1">
@@ -7978,27 +9278,27 @@
     </row>
     <row r="25" spans="1:1">
       <c r="A25" s="42" t="s">
-        <v>444</v>
+        <v>440</v>
       </c>
     </row>
     <row r="26" spans="1:1">
       <c r="A26" s="42" t="s">
-        <v>445</v>
+        <v>441</v>
       </c>
     </row>
     <row r="30" spans="1:1" ht="21">
       <c r="A30" s="39" t="s">
-        <v>446</v>
+        <v>442</v>
       </c>
     </row>
     <row r="32" spans="1:1" ht="16.5">
       <c r="A32" s="40" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
     </row>
     <row r="34" spans="1:1">
       <c r="A34" s="34" t="s">
-        <v>447</v>
+        <v>443</v>
       </c>
     </row>
     <row r="35" spans="1:1">
@@ -8006,37 +9306,37 @@
     </row>
     <row r="36" spans="1:1">
       <c r="A36" s="42" t="s">
-        <v>448</v>
+        <v>444</v>
       </c>
     </row>
     <row r="37" spans="1:1">
       <c r="A37" s="42" t="s">
-        <v>449</v>
+        <v>445</v>
       </c>
     </row>
     <row r="38" spans="1:1">
       <c r="A38" s="43" t="s">
-        <v>450</v>
+        <v>446</v>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39" s="42" t="s">
-        <v>451</v>
+        <v>447</v>
       </c>
     </row>
     <row r="40" spans="1:1">
       <c r="A40" s="43" t="s">
-        <v>452</v>
+        <v>448</v>
       </c>
     </row>
     <row r="44" spans="1:1" ht="21">
       <c r="A44" s="39" t="s">
-        <v>453</v>
+        <v>449</v>
       </c>
     </row>
     <row r="46" spans="1:1" ht="16.5">
       <c r="A46" s="40" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
     </row>
     <row r="47" spans="1:1">
@@ -8044,32 +9344,32 @@
     </row>
     <row r="48" spans="1:1">
       <c r="A48" s="42" t="s">
-        <v>454</v>
+        <v>450</v>
       </c>
     </row>
     <row r="49" spans="1:1">
       <c r="A49" s="42" t="s">
-        <v>455</v>
+        <v>451</v>
       </c>
     </row>
     <row r="50" spans="1:1">
       <c r="A50" s="42" t="s">
-        <v>456</v>
+        <v>452</v>
       </c>
     </row>
     <row r="54" spans="1:1" ht="21">
       <c r="A54" s="39" t="s">
-        <v>457</v>
+        <v>453</v>
       </c>
     </row>
     <row r="56" spans="1:1" ht="16.5">
       <c r="A56" s="40" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
     </row>
     <row r="58" spans="1:1">
       <c r="A58" s="34" t="s">
-        <v>458</v>
+        <v>454</v>
       </c>
     </row>
     <row r="59" spans="1:1">
@@ -8077,37 +9377,37 @@
     </row>
     <row r="60" spans="1:1">
       <c r="A60" s="42" t="s">
-        <v>459</v>
+        <v>455</v>
       </c>
     </row>
     <row r="61" spans="1:1">
       <c r="A61" s="42" t="s">
-        <v>460</v>
+        <v>456</v>
       </c>
     </row>
     <row r="62" spans="1:1">
       <c r="A62" s="42" t="s">
-        <v>461</v>
+        <v>457</v>
       </c>
     </row>
     <row r="64" spans="1:1">
       <c r="A64" s="34" t="s">
-        <v>462</v>
+        <v>458</v>
       </c>
     </row>
     <row r="66" spans="1:1">
       <c r="A66" s="34" t="s">
-        <v>463</v>
+        <v>459</v>
       </c>
     </row>
     <row r="70" spans="1:1" ht="21">
       <c r="A70" s="39" t="s">
-        <v>464</v>
+        <v>460</v>
       </c>
     </row>
     <row r="72" spans="1:1" ht="16.5">
       <c r="A72" s="40" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
     </row>
     <row r="73" spans="1:1">
@@ -8115,27 +9415,27 @@
     </row>
     <row r="74" spans="1:1">
       <c r="A74" s="42" t="s">
-        <v>465</v>
+        <v>461</v>
       </c>
     </row>
     <row r="75" spans="1:1">
       <c r="A75" s="42" t="s">
-        <v>466</v>
+        <v>462</v>
       </c>
     </row>
     <row r="76" spans="1:1">
       <c r="A76" s="42" t="s">
-        <v>467</v>
+        <v>463</v>
       </c>
     </row>
     <row r="80" spans="1:1" ht="21">
       <c r="A80" s="39" t="s">
-        <v>468</v>
+        <v>464</v>
       </c>
     </row>
     <row r="82" spans="1:1" ht="16.5">
       <c r="A82" s="40" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
     </row>
     <row r="83" spans="1:1">
@@ -8143,37 +9443,37 @@
     </row>
     <row r="84" spans="1:1">
       <c r="A84" s="42" t="s">
-        <v>469</v>
+        <v>465</v>
       </c>
     </row>
     <row r="85" spans="1:1">
       <c r="A85" s="42" t="s">
-        <v>470</v>
+        <v>466</v>
       </c>
     </row>
     <row r="86" spans="1:1">
       <c r="A86" s="42" t="s">
-        <v>471</v>
+        <v>467</v>
       </c>
     </row>
     <row r="87" spans="1:1">
       <c r="A87" s="42" t="s">
-        <v>472</v>
+        <v>468</v>
       </c>
     </row>
     <row r="88" spans="1:1">
       <c r="A88" s="42" t="s">
-        <v>473</v>
+        <v>469</v>
       </c>
     </row>
     <row r="92" spans="1:1" ht="21">
       <c r="A92" s="39" t="s">
-        <v>474</v>
+        <v>470</v>
       </c>
     </row>
     <row r="94" spans="1:1" ht="16.5">
       <c r="A94" s="40" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
     </row>
     <row r="95" spans="1:1">
@@ -8181,32 +9481,32 @@
     </row>
     <row r="96" spans="1:1">
       <c r="A96" s="42" t="s">
-        <v>475</v>
+        <v>471</v>
       </c>
     </row>
     <row r="97" spans="1:1">
       <c r="A97" s="42" t="s">
-        <v>476</v>
+        <v>472</v>
       </c>
     </row>
     <row r="98" spans="1:1">
       <c r="A98" s="42" t="s">
-        <v>477</v>
+        <v>473</v>
       </c>
     </row>
     <row r="99" spans="1:1">
       <c r="A99" s="42" t="s">
-        <v>478</v>
+        <v>474</v>
       </c>
     </row>
     <row r="103" spans="1:1" ht="21">
       <c r="A103" s="39" t="s">
-        <v>479</v>
+        <v>475</v>
       </c>
     </row>
     <row r="105" spans="1:1" ht="16.5">
       <c r="A105" s="40" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
     </row>
     <row r="106" spans="1:1">
@@ -8214,32 +9514,32 @@
     </row>
     <row r="107" spans="1:1">
       <c r="A107" s="42" t="s">
-        <v>480</v>
+        <v>476</v>
       </c>
     </row>
     <row r="108" spans="1:1">
       <c r="A108" s="42" t="s">
-        <v>481</v>
+        <v>477</v>
       </c>
     </row>
     <row r="109" spans="1:1">
       <c r="A109" s="42" t="s">
-        <v>482</v>
+        <v>478</v>
       </c>
     </row>
     <row r="110" spans="1:1">
       <c r="A110" s="42" t="s">
-        <v>483</v>
+        <v>479</v>
       </c>
     </row>
     <row r="114" spans="1:1" ht="21">
       <c r="A114" s="39" t="s">
-        <v>484</v>
+        <v>480</v>
       </c>
     </row>
     <row r="116" spans="1:1" ht="16.5">
       <c r="A116" s="40" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
     </row>
     <row r="117" spans="1:1">
@@ -8247,22 +9547,22 @@
     </row>
     <row r="118" spans="1:1">
       <c r="A118" s="42" t="s">
-        <v>485</v>
+        <v>481</v>
       </c>
     </row>
     <row r="119" spans="1:1">
       <c r="A119" s="42" t="s">
-        <v>486</v>
+        <v>482</v>
       </c>
     </row>
     <row r="123" spans="1:1" ht="21">
       <c r="A123" s="39" t="s">
-        <v>487</v>
+        <v>483</v>
       </c>
     </row>
     <row r="125" spans="1:1" ht="16.5">
       <c r="A125" s="40" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
     </row>
     <row r="126" spans="1:1">
@@ -8270,22 +9570,22 @@
     </row>
     <row r="127" spans="1:1">
       <c r="A127" s="42" t="s">
-        <v>488</v>
+        <v>484</v>
       </c>
     </row>
     <row r="128" spans="1:1">
       <c r="A128" s="42" t="s">
-        <v>489</v>
+        <v>485</v>
       </c>
     </row>
     <row r="132" spans="1:1" ht="21">
       <c r="A132" s="39" t="s">
-        <v>490</v>
+        <v>486</v>
       </c>
     </row>
     <row r="134" spans="1:1" ht="16.5">
       <c r="A134" s="40" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
     </row>
     <row r="135" spans="1:1">
@@ -8293,27 +9593,27 @@
     </row>
     <row r="136" spans="1:1">
       <c r="A136" s="42" t="s">
-        <v>491</v>
+        <v>487</v>
       </c>
     </row>
     <row r="137" spans="1:1">
       <c r="A137" s="42" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
     </row>
     <row r="138" spans="1:1">
       <c r="A138" s="42" t="s">
-        <v>493</v>
+        <v>489</v>
       </c>
     </row>
     <row r="142" spans="1:1" ht="21">
       <c r="A142" s="39" t="s">
-        <v>494</v>
+        <v>490</v>
       </c>
     </row>
     <row r="144" spans="1:1" ht="16.5">
       <c r="A144" s="40" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
     </row>
     <row r="145" spans="1:1">
@@ -8321,27 +9621,27 @@
     </row>
     <row r="146" spans="1:1">
       <c r="A146" s="42" t="s">
-        <v>495</v>
+        <v>491</v>
       </c>
     </row>
     <row r="147" spans="1:1">
       <c r="A147" s="42" t="s">
-        <v>496</v>
+        <v>492</v>
       </c>
     </row>
     <row r="148" spans="1:1">
       <c r="A148" s="42" t="s">
-        <v>497</v>
+        <v>493</v>
       </c>
     </row>
     <row r="152" spans="1:1" ht="21">
       <c r="A152" s="39" t="s">
-        <v>498</v>
+        <v>494</v>
       </c>
     </row>
     <row r="154" spans="1:1" ht="16.5">
       <c r="A154" s="40" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
     </row>
     <row r="155" spans="1:1">
@@ -8349,27 +9649,27 @@
     </row>
     <row r="156" spans="1:1">
       <c r="A156" s="42" t="s">
-        <v>499</v>
+        <v>495</v>
       </c>
     </row>
     <row r="157" spans="1:1">
       <c r="A157" s="42" t="s">
-        <v>500</v>
+        <v>496</v>
       </c>
     </row>
     <row r="158" spans="1:1">
       <c r="A158" s="42" t="s">
-        <v>501</v>
+        <v>497</v>
       </c>
     </row>
     <row r="162" spans="1:1" ht="21">
       <c r="A162" s="39" t="s">
-        <v>502</v>
+        <v>498</v>
       </c>
     </row>
     <row r="164" spans="1:1" ht="16.5">
       <c r="A164" s="40" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
     </row>
     <row r="165" spans="1:1">
@@ -8377,37 +9677,37 @@
     </row>
     <row r="166" spans="1:1">
       <c r="A166" s="42" t="s">
-        <v>503</v>
+        <v>499</v>
       </c>
     </row>
     <row r="167" spans="1:1">
       <c r="A167" s="42" t="s">
-        <v>504</v>
+        <v>500</v>
       </c>
     </row>
     <row r="168" spans="1:1">
       <c r="A168" s="42" t="s">
-        <v>505</v>
+        <v>501</v>
       </c>
     </row>
     <row r="172" spans="1:1" ht="28.5">
       <c r="A172" s="44" t="s">
-        <v>506</v>
+        <v>502</v>
       </c>
     </row>
     <row r="174" spans="1:1" ht="21">
       <c r="A174" s="39" t="s">
-        <v>507</v>
+        <v>503</v>
       </c>
     </row>
     <row r="176" spans="1:1" ht="16.5">
       <c r="A176" s="40" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
     </row>
     <row r="178" spans="1:1">
       <c r="A178" s="34" t="s">
-        <v>508</v>
+        <v>504</v>
       </c>
     </row>
     <row r="179" spans="1:1">
@@ -8415,12 +9715,12 @@
     </row>
     <row r="180" spans="1:1">
       <c r="A180" s="42" t="s">
-        <v>509</v>
+        <v>505</v>
       </c>
     </row>
     <row r="182" spans="1:1">
       <c r="A182" s="34" t="s">
-        <v>510</v>
+        <v>506</v>
       </c>
     </row>
     <row r="183" spans="1:1">
@@ -8428,32 +9728,32 @@
     </row>
     <row r="184" spans="1:1">
       <c r="A184" s="42" t="s">
-        <v>511</v>
+        <v>507</v>
       </c>
     </row>
     <row r="185" spans="1:1">
       <c r="A185" s="42" t="s">
-        <v>512</v>
+        <v>508</v>
       </c>
     </row>
     <row r="186" spans="1:1">
       <c r="A186" s="42" t="s">
-        <v>513</v>
+        <v>509</v>
       </c>
     </row>
     <row r="187" spans="1:1">
       <c r="A187" s="42" t="s">
-        <v>514</v>
+        <v>510</v>
       </c>
     </row>
     <row r="191" spans="1:1" ht="21">
       <c r="A191" s="39" t="s">
-        <v>515</v>
+        <v>511</v>
       </c>
     </row>
     <row r="193" spans="1:1" ht="16.5">
       <c r="A193" s="40" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
     </row>
     <row r="194" spans="1:1">
@@ -8461,27 +9761,27 @@
     </row>
     <row r="195" spans="1:1">
       <c r="A195" s="42" t="s">
-        <v>516</v>
+        <v>512</v>
       </c>
     </row>
     <row r="196" spans="1:1">
       <c r="A196" s="42" t="s">
-        <v>517</v>
+        <v>513</v>
       </c>
     </row>
     <row r="197" spans="1:1">
       <c r="A197" s="42" t="s">
-        <v>518</v>
+        <v>514</v>
       </c>
     </row>
     <row r="201" spans="1:1" ht="21">
       <c r="A201" s="39" t="s">
-        <v>519</v>
+        <v>515</v>
       </c>
     </row>
     <row r="203" spans="1:1" ht="16.5">
       <c r="A203" s="40" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
     </row>
     <row r="204" spans="1:1">
@@ -8489,27 +9789,27 @@
     </row>
     <row r="205" spans="1:1">
       <c r="A205" s="42" t="s">
-        <v>520</v>
+        <v>516</v>
       </c>
     </row>
     <row r="206" spans="1:1">
       <c r="A206" s="42" t="s">
-        <v>521</v>
+        <v>517</v>
       </c>
     </row>
     <row r="207" spans="1:1">
       <c r="A207" s="42" t="s">
-        <v>522</v>
+        <v>518</v>
       </c>
     </row>
     <row r="211" spans="1:1" ht="21">
       <c r="A211" s="39" t="s">
-        <v>523</v>
+        <v>519</v>
       </c>
     </row>
     <row r="213" spans="1:1" ht="16.5">
       <c r="A213" s="40" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
     </row>
     <row r="214" spans="1:1">
@@ -8517,27 +9817,27 @@
     </row>
     <row r="215" spans="1:1">
       <c r="A215" s="42" t="s">
-        <v>524</v>
+        <v>551</v>
       </c>
     </row>
     <row r="216" spans="1:1">
       <c r="A216" s="42" t="s">
-        <v>525</v>
+        <v>520</v>
       </c>
     </row>
     <row r="217" spans="1:1">
       <c r="A217" s="42" t="s">
-        <v>526</v>
+        <v>521</v>
       </c>
     </row>
     <row r="221" spans="1:1" ht="21">
       <c r="A221" s="39" t="s">
-        <v>527</v>
+        <v>522</v>
       </c>
     </row>
     <row r="223" spans="1:1" ht="16.5">
       <c r="A223" s="40" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
     </row>
     <row r="224" spans="1:1">
@@ -8545,27 +9845,27 @@
     </row>
     <row r="225" spans="1:1">
       <c r="A225" s="45" t="s">
-        <v>528</v>
+        <v>523</v>
       </c>
     </row>
     <row r="226" spans="1:1">
       <c r="A226" s="45" t="s">
-        <v>529</v>
+        <v>524</v>
       </c>
     </row>
     <row r="227" spans="1:1">
       <c r="A227" s="45" t="s">
-        <v>530</v>
+        <v>525</v>
       </c>
     </row>
     <row r="231" spans="1:1" ht="21">
       <c r="A231" s="39" t="s">
-        <v>531</v>
+        <v>526</v>
       </c>
     </row>
     <row r="233" spans="1:1" ht="16.5">
       <c r="A233" s="40" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
     </row>
     <row r="234" spans="1:1">
@@ -8573,22 +9873,22 @@
     </row>
     <row r="235" spans="1:1">
       <c r="A235" s="42" t="s">
-        <v>532</v>
+        <v>527</v>
       </c>
     </row>
     <row r="236" spans="1:1">
       <c r="A236" s="42" t="s">
-        <v>533</v>
+        <v>528</v>
       </c>
     </row>
     <row r="240" spans="1:1" ht="21">
       <c r="A240" s="39" t="s">
-        <v>534</v>
+        <v>529</v>
       </c>
     </row>
     <row r="242" spans="1:1" ht="16.5">
       <c r="A242" s="40" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
     </row>
     <row r="243" spans="1:1">
@@ -8596,32 +9896,32 @@
     </row>
     <row r="244" spans="1:1">
       <c r="A244" s="42" t="s">
-        <v>535</v>
+        <v>530</v>
       </c>
     </row>
     <row r="245" spans="1:1">
       <c r="A245" s="42" t="s">
-        <v>536</v>
+        <v>531</v>
       </c>
     </row>
     <row r="246" spans="1:1">
       <c r="A246" s="42" t="s">
-        <v>537</v>
+        <v>532</v>
       </c>
     </row>
     <row r="247" spans="1:1">
       <c r="A247" s="42" t="s">
-        <v>538</v>
+        <v>533</v>
       </c>
     </row>
     <row r="251" spans="1:1" ht="21">
       <c r="A251" s="39" t="s">
-        <v>539</v>
+        <v>534</v>
       </c>
     </row>
     <row r="253" spans="1:1" ht="16.5">
       <c r="A253" s="40" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
     </row>
     <row r="254" spans="1:1">
@@ -8629,32 +9929,32 @@
     </row>
     <row r="255" spans="1:1">
       <c r="A255" s="42" t="s">
-        <v>540</v>
+        <v>535</v>
       </c>
     </row>
     <row r="256" spans="1:1">
       <c r="A256" s="42" t="s">
-        <v>541</v>
+        <v>536</v>
       </c>
     </row>
     <row r="257" spans="1:1">
       <c r="A257" s="42" t="s">
-        <v>542</v>
+        <v>537</v>
       </c>
     </row>
     <row r="258" spans="1:1">
       <c r="A258" s="42" t="s">
-        <v>543</v>
+        <v>538</v>
       </c>
     </row>
     <row r="262" spans="1:1" ht="21">
       <c r="A262" s="39" t="s">
-        <v>544</v>
+        <v>539</v>
       </c>
     </row>
     <row r="264" spans="1:1" ht="16.5">
       <c r="A264" s="40" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
     </row>
     <row r="265" spans="1:1">
@@ -8662,27 +9962,27 @@
     </row>
     <row r="266" spans="1:1">
       <c r="A266" s="42" t="s">
-        <v>545</v>
+        <v>540</v>
       </c>
     </row>
     <row r="267" spans="1:1">
       <c r="A267" s="42" t="s">
-        <v>546</v>
+        <v>541</v>
       </c>
     </row>
     <row r="268" spans="1:1">
       <c r="A268" s="42" t="s">
-        <v>547</v>
+        <v>542</v>
       </c>
     </row>
     <row r="272" spans="1:1" ht="21">
       <c r="A272" s="39" t="s">
-        <v>548</v>
+        <v>543</v>
       </c>
     </row>
     <row r="274" spans="1:1" ht="16.5">
       <c r="A274" s="40" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
     </row>
     <row r="275" spans="1:1">
@@ -8690,17 +9990,17 @@
     </row>
     <row r="276" spans="1:1">
       <c r="A276" s="45" t="s">
-        <v>549</v>
+        <v>544</v>
       </c>
     </row>
     <row r="277" spans="1:1">
       <c r="A277" s="45" t="s">
-        <v>550</v>
+        <v>545</v>
       </c>
     </row>
     <row r="278" spans="1:1">
       <c r="A278" s="45" t="s">
-        <v>551</v>
+        <v>546</v>
       </c>
     </row>
   </sheetData>
@@ -8710,648 +10010,38 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{40E537D0-355C-44F6-821F-B309AC3764BF}">
-  <dimension ref="A1:A139"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{18E79AA2-39D8-469F-B011-2D82F20D6FA2}">
+  <dimension ref="A2:B5"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
+  <cols>
+    <col min="1" max="1" width="43" customWidth="1"/>
+    <col min="2" max="2" width="68.625" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:1">
-      <c r="A1" t="s">
-        <v>296</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1">
-      <c r="A2" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" t="s">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1">
-      <c r="A4" t="s">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1">
-      <c r="A5" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1">
-      <c r="A6" t="s">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1">
-      <c r="A7" t="s">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1">
-      <c r="A8" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1">
-      <c r="A9" t="s">
-        <v>304</v>
-      </c>
-    </row>
-    <row r="10" spans="1:1">
-      <c r="A10" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1">
-      <c r="A11" t="s">
-        <v>306</v>
-      </c>
-    </row>
-    <row r="12" spans="1:1">
-      <c r="A12" t="s">
-        <v>307</v>
-      </c>
-    </row>
-    <row r="13" spans="1:1">
-      <c r="A13" t="s">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="14" spans="1:1">
-      <c r="A14" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="15" spans="1:1">
-      <c r="A15" t="s">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="16" spans="1:1">
-      <c r="A16" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1">
-      <c r="A17" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1">
-      <c r="A18" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1">
-      <c r="A19" t="s">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="20" spans="1:1">
-      <c r="A20" t="s">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="23" spans="1:1">
-      <c r="A23" t="s">
-        <v>296</v>
-      </c>
-    </row>
-    <row r="24" spans="1:1">
-      <c r="A24" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="25" spans="1:1">
-      <c r="A25" t="s">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="26" spans="1:1">
-      <c r="A26" t="s">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="27" spans="1:1">
-      <c r="A27" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="28" spans="1:1">
-      <c r="A28" t="s">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="29" spans="1:1">
-      <c r="A29" t="s">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="30" spans="1:1">
-      <c r="A30" t="s">
-        <v>319</v>
-      </c>
-    </row>
-    <row r="31" spans="1:1">
-      <c r="A31" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="32" spans="1:1">
-      <c r="A32" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="33" spans="1:1">
-      <c r="A33" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="34" spans="1:1">
-      <c r="A34" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="35" spans="1:1">
-      <c r="A35" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="36" spans="1:1">
-      <c r="A36" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="37" spans="1:1">
-      <c r="A37" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="38" spans="1:1">
-      <c r="A38" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="39" spans="1:1">
-      <c r="A39" t="s">
-        <v>328</v>
-      </c>
-    </row>
-    <row r="40" spans="1:1">
-      <c r="A40" t="s">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="41" spans="1:1">
-      <c r="A41" t="s">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="42" spans="1:1">
-      <c r="A42" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="43" spans="1:1">
-      <c r="A43" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="46" spans="1:1">
-      <c r="A46" t="s">
-        <v>296</v>
-      </c>
-    </row>
-    <row r="47" spans="1:1">
-      <c r="A47" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="48" spans="1:1">
-      <c r="A48" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="49" spans="1:1">
-      <c r="A49" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="50" spans="1:1">
-      <c r="A50" t="s">
-        <v>335</v>
-      </c>
-    </row>
-    <row r="51" spans="1:1">
-      <c r="A51" t="s">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="52" spans="1:1">
-      <c r="A52" t="s">
-        <v>337</v>
-      </c>
-    </row>
-    <row r="53" spans="1:1">
-      <c r="A53" t="s">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="54" spans="1:1">
-      <c r="A54" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="55" spans="1:1">
-      <c r="A55" t="s">
-        <v>340</v>
-      </c>
-    </row>
-    <row r="56" spans="1:1">
-      <c r="A56" t="s">
-        <v>341</v>
-      </c>
-    </row>
-    <row r="57" spans="1:1">
-      <c r="A57" t="s">
-        <v>342</v>
-      </c>
-    </row>
-    <row r="58" spans="1:1">
-      <c r="A58" t="s">
-        <v>343</v>
-      </c>
-    </row>
-    <row r="59" spans="1:1">
-      <c r="A59" t="s">
-        <v>344</v>
-      </c>
-    </row>
-    <row r="60" spans="1:1">
-      <c r="A60" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="61" spans="1:1">
-      <c r="A61" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="62" spans="1:1">
-      <c r="A62" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="63" spans="1:1">
-      <c r="A63" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="64" spans="1:1">
-      <c r="A64" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="65" spans="1:1">
-      <c r="A65" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="66" spans="1:1">
-      <c r="A66" t="s">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="69" spans="1:1">
-      <c r="A69" t="s">
-        <v>296</v>
-      </c>
-    </row>
-    <row r="70" spans="1:1">
-      <c r="A70" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="71" spans="1:1">
-      <c r="A71" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="72" spans="1:1">
-      <c r="A72" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="73" spans="1:1">
-      <c r="A73" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="74" spans="1:1">
-      <c r="A74" t="s">
-        <v>352</v>
-      </c>
-    </row>
-    <row r="75" spans="1:1">
-      <c r="A75" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="76" spans="1:1">
-      <c r="A76" t="s">
-        <v>354</v>
-      </c>
-    </row>
-    <row r="77" spans="1:1">
-      <c r="A77" t="s">
-        <v>355</v>
-      </c>
-    </row>
-    <row r="78" spans="1:1">
-      <c r="A78" t="s">
-        <v>356</v>
-      </c>
-    </row>
-    <row r="79" spans="1:1">
-      <c r="A79" t="s">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="80" spans="1:1">
-      <c r="A80" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="81" spans="1:1">
-      <c r="A81" t="s">
-        <v>359</v>
-      </c>
-    </row>
-    <row r="82" spans="1:1">
-      <c r="A82" t="s">
-        <v>360</v>
-      </c>
-    </row>
-    <row r="83" spans="1:1">
-      <c r="A83" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="84" spans="1:1">
-      <c r="A84" t="s">
-        <v>361</v>
-      </c>
-    </row>
-    <row r="85" spans="1:1">
-      <c r="A85" t="s">
-        <v>362</v>
-      </c>
-    </row>
-    <row r="86" spans="1:1">
-      <c r="A86" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="87" spans="1:1">
-      <c r="A87" t="s">
-        <v>363</v>
-      </c>
-    </row>
-    <row r="88" spans="1:1">
-      <c r="A88" t="s">
-        <v>364</v>
-      </c>
-    </row>
-    <row r="92" spans="1:1">
-      <c r="A92" t="s">
-        <v>296</v>
-      </c>
-    </row>
-    <row r="93" spans="1:1">
-      <c r="A93" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="94" spans="1:1">
-      <c r="A94" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="95" spans="1:1">
-      <c r="A95" t="s">
-        <v>365</v>
-      </c>
-    </row>
-    <row r="96" spans="1:1">
-      <c r="A96" t="s">
-        <v>366</v>
-      </c>
-    </row>
-    <row r="97" spans="1:1">
-      <c r="A97" t="s">
-        <v>367</v>
-      </c>
-    </row>
-    <row r="98" spans="1:1">
-      <c r="A98" t="s">
-        <v>368</v>
-      </c>
-    </row>
-    <row r="99" spans="1:1">
-      <c r="A99" t="s">
-        <v>352</v>
-      </c>
-    </row>
-    <row r="100" spans="1:1">
-      <c r="A100" t="s">
-        <v>369</v>
-      </c>
-    </row>
-    <row r="101" spans="1:1">
-      <c r="A101" t="s">
-        <v>370</v>
-      </c>
-    </row>
-    <row r="102" spans="1:1">
-      <c r="A102" t="s">
-        <v>371</v>
-      </c>
-    </row>
-    <row r="103" spans="1:1">
-      <c r="A103" t="s">
-        <v>372</v>
-      </c>
-    </row>
-    <row r="104" spans="1:1">
-      <c r="A104" t="s">
-        <v>373</v>
-      </c>
-    </row>
-    <row r="105" spans="1:1">
-      <c r="A105" t="s">
-        <v>374</v>
-      </c>
-    </row>
-    <row r="106" spans="1:1">
-      <c r="A106" t="s">
-        <v>375</v>
-      </c>
-    </row>
-    <row r="107" spans="1:1">
-      <c r="A107" t="s">
-        <v>376</v>
-      </c>
-    </row>
-    <row r="108" spans="1:1">
-      <c r="A108" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="109" spans="1:1">
-      <c r="A109" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="110" spans="1:1">
-      <c r="A110" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="111" spans="1:1">
-      <c r="A111" t="s">
-        <v>379</v>
-      </c>
-    </row>
-    <row r="112" spans="1:1">
-      <c r="A112" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="113" spans="1:1">
-      <c r="A113" t="s">
-        <v>380</v>
-      </c>
-    </row>
-    <row r="114" spans="1:1">
-      <c r="A114" t="s">
-        <v>381</v>
-      </c>
-    </row>
-    <row r="117" spans="1:1">
-      <c r="A117" t="s">
-        <v>296</v>
-      </c>
-    </row>
-    <row r="118" spans="1:1">
-      <c r="A118" t="s">
-        <v>382</v>
-      </c>
-    </row>
-    <row r="119" spans="1:1">
-      <c r="A119" t="s">
-        <v>383</v>
-      </c>
-    </row>
-    <row r="120" spans="1:1">
-      <c r="A120" t="s">
-        <v>384</v>
-      </c>
-    </row>
-    <row r="121" spans="1:1">
-      <c r="A121" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="122" spans="1:1">
-      <c r="A122" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="123" spans="1:1">
-      <c r="A123" t="s">
-        <v>387</v>
-      </c>
-    </row>
-    <row r="124" spans="1:1">
-      <c r="A124" t="s">
-        <v>388</v>
-      </c>
-    </row>
-    <row r="125" spans="1:1">
-      <c r="A125" t="s">
-        <v>389</v>
-      </c>
-    </row>
-    <row r="126" spans="1:1">
-      <c r="A126" t="s">
-        <v>390</v>
-      </c>
-    </row>
-    <row r="127" spans="1:1">
-      <c r="A127" t="s">
-        <v>391</v>
-      </c>
-    </row>
-    <row r="128" spans="1:1">
-      <c r="A128" t="s">
-        <v>392</v>
-      </c>
-    </row>
-    <row r="129" spans="1:1">
-      <c r="A129" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="130" spans="1:1">
-      <c r="A130" t="s">
-        <v>394</v>
-      </c>
-    </row>
-    <row r="131" spans="1:1">
-      <c r="A131" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="132" spans="1:1">
-      <c r="A132" t="s">
-        <v>396</v>
-      </c>
-    </row>
-    <row r="133" spans="1:1">
-      <c r="A133" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="134" spans="1:1">
-      <c r="A134" t="s">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="135" spans="1:1">
-      <c r="A135" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="136" spans="1:1">
-      <c r="A136" t="s">
-        <v>399</v>
-      </c>
-    </row>
-    <row r="137" spans="1:1">
-      <c r="A137" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="138" spans="1:1">
-      <c r="A138" t="s">
-        <v>401</v>
-      </c>
-    </row>
-    <row r="139" spans="1:1">
-      <c r="A139" t="s">
-        <v>402</v>
+    <row r="2" spans="1:2" ht="54">
+      <c r="A2" s="34" t="s">
+        <v>557</v>
+      </c>
+      <c r="B2" s="38" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="67.5">
+      <c r="A3" s="34" t="s">
+        <v>558</v>
+      </c>
+      <c r="B3" s="38" t="s">
+        <v>559</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="94.5">
+      <c r="B4" s="38" t="s">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" ht="54">
+      <c r="B5" s="38" t="s">
+        <v>561</v>
       </c>
     </row>
   </sheetData>
@@ -9361,6 +10051,2262 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2D50A871-9D78-407F-ADF0-E93D7C884AF1}">
+  <dimension ref="B2:B576"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
+  <sheetData>
+    <row r="2" spans="2:2" ht="37.5">
+      <c r="B2" s="47" t="s">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="4" spans="2:2" ht="26.25">
+      <c r="B4" s="48" t="s">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="6" spans="2:2" ht="21">
+      <c r="B6" s="49" t="s">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="8" spans="2:2" ht="16.5">
+      <c r="B8" s="46" t="s">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="10" spans="2:2" ht="21">
+      <c r="B10" s="49" t="s">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="11" spans="2:2">
+      <c r="B11" s="41"/>
+    </row>
+    <row r="12" spans="2:2" ht="16.5">
+      <c r="B12" s="50" t="s">
+        <v>567</v>
+      </c>
+    </row>
+    <row r="13" spans="2:2" ht="16.5">
+      <c r="B13" s="50" t="s">
+        <v>568</v>
+      </c>
+    </row>
+    <row r="14" spans="2:2" ht="16.5">
+      <c r="B14" s="50" t="s">
+        <v>569</v>
+      </c>
+    </row>
+    <row r="15" spans="2:2" ht="16.5">
+      <c r="B15" s="50" t="s">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="19" spans="2:2" ht="26.25">
+      <c r="B19" s="48" t="s">
+        <v>571</v>
+      </c>
+    </row>
+    <row r="21" spans="2:2" ht="16.5">
+      <c r="B21" s="46" t="s">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="23" spans="2:2" ht="21">
+      <c r="B23" s="49" t="s">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="24" spans="2:2">
+      <c r="B24" s="41"/>
+    </row>
+    <row r="25" spans="2:2" ht="16.5">
+      <c r="B25" s="50" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="26" spans="2:2" ht="16.5">
+      <c r="B26" s="50" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="27" spans="2:2" ht="16.5">
+      <c r="B27" s="50" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="28" spans="2:2" ht="16.5">
+      <c r="B28" s="50" t="s">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="29" spans="2:2" ht="16.5">
+      <c r="B29" s="50" t="s">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="30" spans="2:2" ht="16.5">
+      <c r="B30" s="50" t="s">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="31" spans="2:2" ht="16.5">
+      <c r="B31" s="50" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="35" spans="2:2" ht="26.25">
+      <c r="B35" s="48" t="s">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="37" spans="2:2" ht="16.5">
+      <c r="B37" s="46" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="39" spans="2:2" ht="21">
+      <c r="B39" s="49" t="s">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="40" spans="2:2">
+      <c r="B40" s="41"/>
+    </row>
+    <row r="41" spans="2:2" ht="16.5">
+      <c r="B41" s="50" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="42" spans="2:2" ht="16.5">
+      <c r="B42" s="50" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="43" spans="2:2" ht="16.5">
+      <c r="B43" s="50" t="s">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="47" spans="2:2" ht="26.25">
+      <c r="B47" s="48" t="s">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="49" spans="2:2" ht="16.5">
+      <c r="B49" s="46" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="51" spans="2:2" ht="21">
+      <c r="B51" s="49" t="s">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="52" spans="2:2">
+      <c r="B52" s="41"/>
+    </row>
+    <row r="53" spans="2:2" ht="16.5">
+      <c r="B53" s="50" t="s">
+        <v>587</v>
+      </c>
+    </row>
+    <row r="54" spans="2:2" ht="16.5">
+      <c r="B54" s="50" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="55" spans="2:2" ht="16.5">
+      <c r="B55" s="50" t="s">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="56" spans="2:2" ht="16.5">
+      <c r="B56" s="50" t="s">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="60" spans="2:2" ht="26.25">
+      <c r="B60" s="48" t="s">
+        <v>591</v>
+      </c>
+    </row>
+    <row r="62" spans="2:2" ht="16.5">
+      <c r="B62" s="46" t="s">
+        <v>592</v>
+      </c>
+    </row>
+    <row r="64" spans="2:2" ht="21">
+      <c r="B64" s="49" t="s">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="65" spans="2:2">
+      <c r="B65" s="41"/>
+    </row>
+    <row r="66" spans="2:2" ht="16.5">
+      <c r="B66" s="50" t="s">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="67" spans="2:2" ht="16.5">
+      <c r="B67" s="50" t="s">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="68" spans="2:2" ht="16.5">
+      <c r="B68" s="50" t="s">
+        <v>595</v>
+      </c>
+    </row>
+    <row r="72" spans="2:2" ht="26.25">
+      <c r="B72" s="48" t="s">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="74" spans="2:2" ht="16.5">
+      <c r="B74" s="46" t="s">
+        <v>597</v>
+      </c>
+    </row>
+    <row r="76" spans="2:2" ht="21">
+      <c r="B76" s="49" t="s">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="77" spans="2:2">
+      <c r="B77" s="41"/>
+    </row>
+    <row r="78" spans="2:2" ht="16.5">
+      <c r="B78" s="50" t="s">
+        <v>598</v>
+      </c>
+    </row>
+    <row r="79" spans="2:2" ht="16.5">
+      <c r="B79" s="50" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="80" spans="2:2" ht="16.5">
+      <c r="B80" s="50" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="84" spans="2:2" ht="26.25">
+      <c r="B84" s="48" t="s">
+        <v>601</v>
+      </c>
+    </row>
+    <row r="86" spans="2:2" ht="16.5">
+      <c r="B86" s="46" t="s">
+        <v>602</v>
+      </c>
+    </row>
+    <row r="88" spans="2:2" ht="21">
+      <c r="B88" s="49" t="s">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="89" spans="2:2">
+      <c r="B89" s="41"/>
+    </row>
+    <row r="90" spans="2:2" ht="16.5">
+      <c r="B90" s="50" t="s">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="91" spans="2:2" ht="16.5">
+      <c r="B91" s="50" t="s">
+        <v>604</v>
+      </c>
+    </row>
+    <row r="92" spans="2:2" ht="16.5">
+      <c r="B92" s="50" t="s">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="96" spans="2:2" ht="26.25">
+      <c r="B96" s="48" t="s">
+        <v>606</v>
+      </c>
+    </row>
+    <row r="98" spans="2:2" ht="16.5">
+      <c r="B98" s="46" t="s">
+        <v>607</v>
+      </c>
+    </row>
+    <row r="100" spans="2:2" ht="21">
+      <c r="B100" s="49" t="s">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="101" spans="2:2">
+      <c r="B101" s="41"/>
+    </row>
+    <row r="102" spans="2:2" ht="16.5">
+      <c r="B102" s="50" t="s">
+        <v>608</v>
+      </c>
+    </row>
+    <row r="103" spans="2:2" ht="16.5">
+      <c r="B103" s="50" t="s">
+        <v>609</v>
+      </c>
+    </row>
+    <row r="104" spans="2:2" ht="16.5">
+      <c r="B104" s="50" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="108" spans="2:2" ht="26.25">
+      <c r="B108" s="48" t="s">
+        <v>611</v>
+      </c>
+    </row>
+    <row r="110" spans="2:2" ht="16.5">
+      <c r="B110" s="46" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="112" spans="2:2" ht="21">
+      <c r="B112" s="49" t="s">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="113" spans="2:2">
+      <c r="B113" s="41"/>
+    </row>
+    <row r="114" spans="2:2" ht="16.5">
+      <c r="B114" s="50" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="115" spans="2:2" ht="16.5">
+      <c r="B115" s="50" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="119" spans="2:2" ht="26.25">
+      <c r="B119" s="48" t="s">
+        <v>615</v>
+      </c>
+    </row>
+    <row r="121" spans="2:2" ht="16.5">
+      <c r="B121" s="46" t="s">
+        <v>616</v>
+      </c>
+    </row>
+    <row r="123" spans="2:2" ht="21">
+      <c r="B123" s="49" t="s">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="124" spans="2:2">
+      <c r="B124" s="41"/>
+    </row>
+    <row r="125" spans="2:2" ht="16.5">
+      <c r="B125" s="50" t="s">
+        <v>617</v>
+      </c>
+    </row>
+    <row r="126" spans="2:2" ht="16.5">
+      <c r="B126" s="50" t="s">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="127" spans="2:2" ht="16.5">
+      <c r="B127" s="50" t="s">
+        <v>619</v>
+      </c>
+    </row>
+    <row r="131" spans="2:2" ht="26.25">
+      <c r="B131" s="48" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="133" spans="2:2" ht="16.5">
+      <c r="B133" s="46" t="s">
+        <v>621</v>
+      </c>
+    </row>
+    <row r="135" spans="2:2" ht="21">
+      <c r="B135" s="49" t="s">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="136" spans="2:2">
+      <c r="B136" s="41"/>
+    </row>
+    <row r="137" spans="2:2" ht="16.5">
+      <c r="B137" s="50" t="s">
+        <v>622</v>
+      </c>
+    </row>
+    <row r="138" spans="2:2" ht="16.5">
+      <c r="B138" s="50" t="s">
+        <v>623</v>
+      </c>
+    </row>
+    <row r="142" spans="2:2" ht="26.25">
+      <c r="B142" s="48" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="144" spans="2:2" ht="16.5">
+      <c r="B144" s="46" t="s">
+        <v>625</v>
+      </c>
+    </row>
+    <row r="146" spans="2:2" ht="21">
+      <c r="B146" s="49" t="s">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="147" spans="2:2">
+      <c r="B147" s="41"/>
+    </row>
+    <row r="148" spans="2:2" ht="16.5">
+      <c r="B148" s="50" t="s">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="149" spans="2:2" ht="16.5">
+      <c r="B149" s="50" t="s">
+        <v>627</v>
+      </c>
+    </row>
+    <row r="150" spans="2:2" ht="16.5">
+      <c r="B150" s="50" t="s">
+        <v>628</v>
+      </c>
+    </row>
+    <row r="154" spans="2:2" ht="26.25">
+      <c r="B154" s="48" t="s">
+        <v>629</v>
+      </c>
+    </row>
+    <row r="156" spans="2:2" ht="16.5">
+      <c r="B156" s="46" t="s">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="158" spans="2:2" ht="21">
+      <c r="B158" s="49" t="s">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="159" spans="2:2">
+      <c r="B159" s="41"/>
+    </row>
+    <row r="160" spans="2:2" ht="16.5">
+      <c r="B160" s="50" t="s">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="161" spans="2:2" ht="16.5">
+      <c r="B161" s="50" t="s">
+        <v>632</v>
+      </c>
+    </row>
+    <row r="162" spans="2:2" ht="16.5">
+      <c r="B162" s="50" t="s">
+        <v>633</v>
+      </c>
+    </row>
+    <row r="166" spans="2:2" ht="37.5">
+      <c r="B166" s="47" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="168" spans="2:2" ht="21">
+      <c r="B168" s="49">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="170" spans="2:2" ht="16.5">
+      <c r="B170" s="46" t="s">
+        <v>635</v>
+      </c>
+    </row>
+    <row r="172" spans="2:2" ht="21">
+      <c r="B172" s="49">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="174" spans="2:2" ht="16.5">
+      <c r="B174" s="46" t="s">
+        <v>636</v>
+      </c>
+    </row>
+    <row r="176" spans="2:2" ht="21">
+      <c r="B176" s="49">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="178" spans="2:2" ht="16.5">
+      <c r="B178" s="46" t="s">
+        <v>637</v>
+      </c>
+    </row>
+    <row r="180" spans="2:2" ht="21">
+      <c r="B180" s="49">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="182" spans="2:2" ht="16.5">
+      <c r="B182" s="46" t="s">
+        <v>638</v>
+      </c>
+    </row>
+    <row r="184" spans="2:2" ht="21">
+      <c r="B184" s="49">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="186" spans="2:2" ht="16.5">
+      <c r="B186" s="46" t="s">
+        <v>639</v>
+      </c>
+    </row>
+    <row r="188" spans="2:2" ht="21">
+      <c r="B188" s="49">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="190" spans="2:2" ht="16.5">
+      <c r="B190" s="46" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="192" spans="2:2" ht="21">
+      <c r="B192" s="49">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="194" spans="2:2" ht="16.5">
+      <c r="B194" s="46" t="s">
+        <v>641</v>
+      </c>
+    </row>
+    <row r="196" spans="2:2" ht="21">
+      <c r="B196" s="49">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="198" spans="2:2" ht="16.5">
+      <c r="B198" s="46" t="s">
+        <v>642</v>
+      </c>
+    </row>
+    <row r="200" spans="2:2" ht="16.5">
+      <c r="B200" s="46"/>
+    </row>
+    <row r="202" spans="2:2" ht="37.5">
+      <c r="B202" s="47" t="s">
+        <v>643</v>
+      </c>
+    </row>
+    <row r="204" spans="2:2" ht="26.25">
+      <c r="B204" s="48" t="s">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="206" spans="2:2" ht="21">
+      <c r="B206" s="49" t="s">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="208" spans="2:2" ht="16.5">
+      <c r="B208" s="46" t="s">
+        <v>644</v>
+      </c>
+    </row>
+    <row r="210" spans="2:2" ht="21">
+      <c r="B210" s="49" t="s">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="211" spans="2:2">
+      <c r="B211" s="41"/>
+    </row>
+    <row r="212" spans="2:2" ht="16.5">
+      <c r="B212" s="50" t="s">
+        <v>645</v>
+      </c>
+    </row>
+    <row r="213" spans="2:2" ht="16.5">
+      <c r="B213" s="50" t="s">
+        <v>646</v>
+      </c>
+    </row>
+    <row r="214" spans="2:2" ht="16.5">
+      <c r="B214" s="50" t="s">
+        <v>647</v>
+      </c>
+    </row>
+    <row r="215" spans="2:2" ht="16.5">
+      <c r="B215" s="50" t="s">
+        <v>648</v>
+      </c>
+    </row>
+    <row r="219" spans="2:2" ht="26.25">
+      <c r="B219" s="48" t="s">
+        <v>571</v>
+      </c>
+    </row>
+    <row r="221" spans="2:2" ht="16.5">
+      <c r="B221" s="46" t="s">
+        <v>649</v>
+      </c>
+    </row>
+    <row r="223" spans="2:2" ht="21">
+      <c r="B223" s="49" t="s">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="224" spans="2:2">
+      <c r="B224" s="41"/>
+    </row>
+    <row r="225" spans="2:2" ht="16.5">
+      <c r="B225" s="50" t="s">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="226" spans="2:2" ht="16.5">
+      <c r="B226" s="50" t="s">
+        <v>651</v>
+      </c>
+    </row>
+    <row r="227" spans="2:2" ht="16.5">
+      <c r="B227" s="50" t="s">
+        <v>652</v>
+      </c>
+    </row>
+    <row r="228" spans="2:2" ht="16.5">
+      <c r="B228" s="50" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="232" spans="2:2" ht="26.25">
+      <c r="B232" s="48" t="s">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="234" spans="2:2" ht="16.5">
+      <c r="B234" s="46" t="s">
+        <v>654</v>
+      </c>
+    </row>
+    <row r="236" spans="2:2" ht="21">
+      <c r="B236" s="49" t="s">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="237" spans="2:2">
+      <c r="B237" s="41"/>
+    </row>
+    <row r="238" spans="2:2" ht="16.5">
+      <c r="B238" s="50" t="s">
+        <v>655</v>
+      </c>
+    </row>
+    <row r="239" spans="2:2" ht="16.5">
+      <c r="B239" s="50" t="s">
+        <v>656</v>
+      </c>
+    </row>
+    <row r="240" spans="2:2" ht="16.5">
+      <c r="B240" s="50" t="s">
+        <v>657</v>
+      </c>
+    </row>
+    <row r="244" spans="2:2" ht="26.25">
+      <c r="B244" s="48" t="s">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="246" spans="2:2" ht="16.5">
+      <c r="B246" s="46" t="s">
+        <v>658</v>
+      </c>
+    </row>
+    <row r="248" spans="2:2" ht="21">
+      <c r="B248" s="49" t="s">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="249" spans="2:2">
+      <c r="B249" s="41"/>
+    </row>
+    <row r="250" spans="2:2" ht="16.5">
+      <c r="B250" s="50" t="s">
+        <v>659</v>
+      </c>
+    </row>
+    <row r="251" spans="2:2" ht="16.5">
+      <c r="B251" s="50" t="s">
+        <v>660</v>
+      </c>
+    </row>
+    <row r="252" spans="2:2" ht="16.5">
+      <c r="B252" s="50" t="s">
+        <v>661</v>
+      </c>
+    </row>
+    <row r="256" spans="2:2" ht="26.25">
+      <c r="B256" s="48" t="s">
+        <v>591</v>
+      </c>
+    </row>
+    <row r="258" spans="2:2" ht="16.5">
+      <c r="B258" s="46" t="s">
+        <v>662</v>
+      </c>
+    </row>
+    <row r="260" spans="2:2" ht="21">
+      <c r="B260" s="49" t="s">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="261" spans="2:2">
+      <c r="B261" s="41"/>
+    </row>
+    <row r="262" spans="2:2" ht="16.5">
+      <c r="B262" s="50" t="s">
+        <v>663</v>
+      </c>
+    </row>
+    <row r="263" spans="2:2" ht="16.5">
+      <c r="B263" s="50" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="264" spans="2:2" ht="16.5">
+      <c r="B264" s="50" t="s">
+        <v>665</v>
+      </c>
+    </row>
+    <row r="268" spans="2:2" ht="26.25">
+      <c r="B268" s="48" t="s">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="270" spans="2:2" ht="16.5">
+      <c r="B270" s="46" t="s">
+        <v>666</v>
+      </c>
+    </row>
+    <row r="272" spans="2:2" ht="21">
+      <c r="B272" s="49" t="s">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="273" spans="2:2">
+      <c r="B273" s="41"/>
+    </row>
+    <row r="274" spans="2:2" ht="16.5">
+      <c r="B274" s="50" t="s">
+        <v>667</v>
+      </c>
+    </row>
+    <row r="275" spans="2:2" ht="16.5">
+      <c r="B275" s="50" t="s">
+        <v>668</v>
+      </c>
+    </row>
+    <row r="276" spans="2:2" ht="16.5">
+      <c r="B276" s="50" t="s">
+        <v>669</v>
+      </c>
+    </row>
+    <row r="277" spans="2:2" ht="16.5">
+      <c r="B277" s="50" t="s">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="281" spans="2:2" ht="26.25">
+      <c r="B281" s="48" t="s">
+        <v>601</v>
+      </c>
+    </row>
+    <row r="283" spans="2:2" ht="16.5">
+      <c r="B283" s="46" t="s">
+        <v>671</v>
+      </c>
+    </row>
+    <row r="285" spans="2:2" ht="21">
+      <c r="B285" s="49" t="s">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="286" spans="2:2">
+      <c r="B286" s="41"/>
+    </row>
+    <row r="287" spans="2:2" ht="16.5">
+      <c r="B287" s="50" t="s">
+        <v>672</v>
+      </c>
+    </row>
+    <row r="288" spans="2:2" ht="16.5">
+      <c r="B288" s="50" t="s">
+        <v>673</v>
+      </c>
+    </row>
+    <row r="289" spans="2:2" ht="16.5">
+      <c r="B289" s="50" t="s">
+        <v>674</v>
+      </c>
+    </row>
+    <row r="293" spans="2:2" ht="26.25">
+      <c r="B293" s="48" t="s">
+        <v>606</v>
+      </c>
+    </row>
+    <row r="295" spans="2:2" ht="16.5">
+      <c r="B295" s="46" t="s">
+        <v>675</v>
+      </c>
+    </row>
+    <row r="297" spans="2:2" ht="21">
+      <c r="B297" s="49" t="s">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="298" spans="2:2">
+      <c r="B298" s="41"/>
+    </row>
+    <row r="299" spans="2:2" ht="16.5">
+      <c r="B299" s="50" t="s">
+        <v>676</v>
+      </c>
+    </row>
+    <row r="300" spans="2:2" ht="16.5">
+      <c r="B300" s="50" t="s">
+        <v>677</v>
+      </c>
+    </row>
+    <row r="301" spans="2:2" ht="16.5">
+      <c r="B301" s="50" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="305" spans="2:2" ht="26.25">
+      <c r="B305" s="48" t="s">
+        <v>611</v>
+      </c>
+    </row>
+    <row r="307" spans="2:2" ht="16.5">
+      <c r="B307" s="46" t="s">
+        <v>679</v>
+      </c>
+    </row>
+    <row r="309" spans="2:2" ht="21">
+      <c r="B309" s="49" t="s">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="310" spans="2:2">
+      <c r="B310" s="41"/>
+    </row>
+    <row r="311" spans="2:2" ht="16.5">
+      <c r="B311" s="50" t="s">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="312" spans="2:2" ht="16.5">
+      <c r="B312" s="50" t="s">
+        <v>681</v>
+      </c>
+    </row>
+    <row r="313" spans="2:2" ht="16.5">
+      <c r="B313" s="50" t="s">
+        <v>682</v>
+      </c>
+    </row>
+    <row r="314" spans="2:2" ht="16.5">
+      <c r="B314" s="50" t="s">
+        <v>683</v>
+      </c>
+    </row>
+    <row r="318" spans="2:2" ht="26.25">
+      <c r="B318" s="48" t="s">
+        <v>615</v>
+      </c>
+    </row>
+    <row r="320" spans="2:2" ht="16.5">
+      <c r="B320" s="46" t="s">
+        <v>684</v>
+      </c>
+    </row>
+    <row r="322" spans="2:2" ht="21">
+      <c r="B322" s="49" t="s">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="323" spans="2:2">
+      <c r="B323" s="41"/>
+    </row>
+    <row r="324" spans="2:2" ht="16.5">
+      <c r="B324" s="50" t="s">
+        <v>685</v>
+      </c>
+    </row>
+    <row r="325" spans="2:2" ht="16.5">
+      <c r="B325" s="50" t="s">
+        <v>686</v>
+      </c>
+    </row>
+    <row r="326" spans="2:2" ht="16.5">
+      <c r="B326" s="50" t="s">
+        <v>687</v>
+      </c>
+    </row>
+    <row r="330" spans="2:2" ht="37.5">
+      <c r="B330" s="47" t="s">
+        <v>688</v>
+      </c>
+    </row>
+    <row r="332" spans="2:2" ht="21">
+      <c r="B332" s="49">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="334" spans="2:2" ht="16.5">
+      <c r="B334" s="46" t="s">
+        <v>689</v>
+      </c>
+    </row>
+    <row r="336" spans="2:2" ht="21">
+      <c r="B336" s="49">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="338" spans="2:2" ht="16.5">
+      <c r="B338" s="46" t="s">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="340" spans="2:2" ht="21">
+      <c r="B340" s="49">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="342" spans="2:2" ht="16.5">
+      <c r="B342" s="46" t="s">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="344" spans="2:2" ht="21">
+      <c r="B344" s="49">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="346" spans="2:2" ht="16.5">
+      <c r="B346" s="46" t="s">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="348" spans="2:2" ht="21">
+      <c r="B348" s="49">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="350" spans="2:2" ht="16.5">
+      <c r="B350" s="46" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="352" spans="2:2" ht="21">
+      <c r="B352" s="49">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="354" spans="2:2" ht="16.5">
+      <c r="B354" s="46" t="s">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="356" spans="2:2" ht="21">
+      <c r="B356" s="49">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="358" spans="2:2" ht="16.5">
+      <c r="B358" s="46" t="s">
+        <v>695</v>
+      </c>
+    </row>
+    <row r="360" spans="2:2" ht="21">
+      <c r="B360" s="49">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="362" spans="2:2" ht="16.5">
+      <c r="B362" s="46" t="s">
+        <v>696</v>
+      </c>
+    </row>
+    <row r="364" spans="2:2" ht="16.5">
+      <c r="B364" s="46"/>
+    </row>
+    <row r="366" spans="2:2" ht="37.5">
+      <c r="B366" s="47" t="s">
+        <v>697</v>
+      </c>
+    </row>
+    <row r="368" spans="2:2" ht="26.25">
+      <c r="B368" s="48" t="s">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="370" spans="2:2" ht="21">
+      <c r="B370" s="49" t="s">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="372" spans="2:2" ht="16.5">
+      <c r="B372" s="46" t="s">
+        <v>644</v>
+      </c>
+    </row>
+    <row r="374" spans="2:2" ht="21">
+      <c r="B374" s="49" t="s">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="375" spans="2:2">
+      <c r="B375" s="41"/>
+    </row>
+    <row r="376" spans="2:2" ht="16.5">
+      <c r="B376" s="50" t="s">
+        <v>567</v>
+      </c>
+    </row>
+    <row r="377" spans="2:2" ht="16.5">
+      <c r="B377" s="50" t="s">
+        <v>698</v>
+      </c>
+    </row>
+    <row r="378" spans="2:2" ht="16.5">
+      <c r="B378" s="50" t="s">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="379" spans="2:2" ht="16.5">
+      <c r="B379" s="50" t="s">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="380" spans="2:2" ht="16.5">
+      <c r="B380" s="50" t="s">
+        <v>701</v>
+      </c>
+    </row>
+    <row r="381" spans="2:2" ht="16.5">
+      <c r="B381" s="50" t="s">
+        <v>702</v>
+      </c>
+    </row>
+    <row r="385" spans="2:2" ht="26.25">
+      <c r="B385" s="48" t="s">
+        <v>571</v>
+      </c>
+    </row>
+    <row r="387" spans="2:2" ht="16.5">
+      <c r="B387" s="46" t="s">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="389" spans="2:2" ht="21">
+      <c r="B389" s="49" t="s">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="390" spans="2:2">
+      <c r="B390" s="41"/>
+    </row>
+    <row r="391" spans="2:2" ht="16.5">
+      <c r="B391" s="50" t="s">
+        <v>704</v>
+      </c>
+    </row>
+    <row r="392" spans="2:2" ht="16.5">
+      <c r="B392" s="50" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="393" spans="2:2" ht="16.5">
+      <c r="B393" s="50" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="394" spans="2:2" ht="16.5">
+      <c r="B394" s="50" t="s">
+        <v>707</v>
+      </c>
+    </row>
+    <row r="395" spans="2:2" ht="16.5">
+      <c r="B395" s="50" t="s">
+        <v>708</v>
+      </c>
+    </row>
+    <row r="396" spans="2:2" ht="16.5">
+      <c r="B396" s="50" t="s">
+        <v>709</v>
+      </c>
+    </row>
+    <row r="400" spans="2:2" ht="26.25">
+      <c r="B400" s="48" t="s">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="402" spans="2:2" ht="16.5">
+      <c r="B402" s="46" t="s">
+        <v>654</v>
+      </c>
+    </row>
+    <row r="404" spans="2:2" ht="21">
+      <c r="B404" s="49" t="s">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="405" spans="2:2">
+      <c r="B405" s="41"/>
+    </row>
+    <row r="406" spans="2:2" ht="16.5">
+      <c r="B406" s="50" t="s">
+        <v>710</v>
+      </c>
+    </row>
+    <row r="407" spans="2:2" ht="16.5">
+      <c r="B407" s="50" t="s">
+        <v>711</v>
+      </c>
+    </row>
+    <row r="408" spans="2:2" ht="16.5">
+      <c r="B408" s="50" t="s">
+        <v>712</v>
+      </c>
+    </row>
+    <row r="412" spans="2:2" ht="26.25">
+      <c r="B412" s="48" t="s">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="414" spans="2:2" ht="16.5">
+      <c r="B414" s="46" t="s">
+        <v>713</v>
+      </c>
+    </row>
+    <row r="416" spans="2:2" ht="21">
+      <c r="B416" s="49" t="s">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="417" spans="2:2">
+      <c r="B417" s="41"/>
+    </row>
+    <row r="418" spans="2:2" ht="16.5">
+      <c r="B418" s="50" t="s">
+        <v>714</v>
+      </c>
+    </row>
+    <row r="419" spans="2:2" ht="16.5">
+      <c r="B419" s="50" t="s">
+        <v>715</v>
+      </c>
+    </row>
+    <row r="420" spans="2:2" ht="16.5">
+      <c r="B420" s="50" t="s">
+        <v>716</v>
+      </c>
+    </row>
+    <row r="424" spans="2:2" ht="26.25">
+      <c r="B424" s="48" t="s">
+        <v>591</v>
+      </c>
+    </row>
+    <row r="426" spans="2:2" ht="16.5">
+      <c r="B426" s="46" t="s">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="428" spans="2:2" ht="21">
+      <c r="B428" s="49" t="s">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="429" spans="2:2">
+      <c r="B429" s="41"/>
+    </row>
+    <row r="430" spans="2:2" ht="16.5">
+      <c r="B430" s="50" t="s">
+        <v>718</v>
+      </c>
+    </row>
+    <row r="431" spans="2:2" ht="16.5">
+      <c r="B431" s="50" t="s">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="432" spans="2:2" ht="16.5">
+      <c r="B432" s="50" t="s">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="436" spans="2:2" ht="26.25">
+      <c r="B436" s="48" t="s">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="438" spans="2:2" ht="16.5">
+      <c r="B438" s="46" t="s">
+        <v>721</v>
+      </c>
+    </row>
+    <row r="440" spans="2:2" ht="21">
+      <c r="B440" s="49" t="s">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="441" spans="2:2">
+      <c r="B441" s="41"/>
+    </row>
+    <row r="442" spans="2:2" ht="16.5">
+      <c r="B442" s="50" t="s">
+        <v>722</v>
+      </c>
+    </row>
+    <row r="443" spans="2:2" ht="16.5">
+      <c r="B443" s="50" t="s">
+        <v>723</v>
+      </c>
+    </row>
+    <row r="444" spans="2:2" ht="16.5">
+      <c r="B444" s="50" t="s">
+        <v>724</v>
+      </c>
+    </row>
+    <row r="448" spans="2:2" ht="26.25">
+      <c r="B448" s="48" t="s">
+        <v>601</v>
+      </c>
+    </row>
+    <row r="450" spans="2:2" ht="16.5">
+      <c r="B450" s="46" t="s">
+        <v>725</v>
+      </c>
+    </row>
+    <row r="452" spans="2:2" ht="21">
+      <c r="B452" s="49" t="s">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="453" spans="2:2">
+      <c r="B453" s="41"/>
+    </row>
+    <row r="454" spans="2:2" ht="16.5">
+      <c r="B454" s="50" t="s">
+        <v>726</v>
+      </c>
+    </row>
+    <row r="455" spans="2:2" ht="16.5">
+      <c r="B455" s="50" t="s">
+        <v>727</v>
+      </c>
+    </row>
+    <row r="459" spans="2:2" ht="26.25">
+      <c r="B459" s="48" t="s">
+        <v>606</v>
+      </c>
+    </row>
+    <row r="461" spans="2:2" ht="16.5">
+      <c r="B461" s="46" t="s">
+        <v>728</v>
+      </c>
+    </row>
+    <row r="463" spans="2:2" ht="21">
+      <c r="B463" s="49" t="s">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="464" spans="2:2">
+      <c r="B464" s="41"/>
+    </row>
+    <row r="465" spans="2:2" ht="16.5">
+      <c r="B465" s="50" t="s">
+        <v>729</v>
+      </c>
+    </row>
+    <row r="466" spans="2:2" ht="16.5">
+      <c r="B466" s="50" t="s">
+        <v>730</v>
+      </c>
+    </row>
+    <row r="467" spans="2:2" ht="16.5">
+      <c r="B467" s="50" t="s">
+        <v>731</v>
+      </c>
+    </row>
+    <row r="471" spans="2:2" ht="26.25">
+      <c r="B471" s="48" t="s">
+        <v>611</v>
+      </c>
+    </row>
+    <row r="473" spans="2:2" ht="16.5">
+      <c r="B473" s="46" t="s">
+        <v>732</v>
+      </c>
+    </row>
+    <row r="475" spans="2:2" ht="21">
+      <c r="B475" s="49" t="s">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="477" spans="2:2" ht="16.5">
+      <c r="B477" s="51" t="s">
+        <v>733</v>
+      </c>
+    </row>
+    <row r="478" spans="2:2">
+      <c r="B478" s="41"/>
+    </row>
+    <row r="479" spans="2:2" ht="16.5">
+      <c r="B479" s="50" t="s">
+        <v>734</v>
+      </c>
+    </row>
+    <row r="480" spans="2:2" ht="16.5">
+      <c r="B480" s="50" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="481" spans="2:2" ht="16.5">
+      <c r="B481" s="50" t="s">
+        <v>736</v>
+      </c>
+    </row>
+    <row r="483" spans="2:2" ht="16.5">
+      <c r="B483" s="51" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="484" spans="2:2">
+      <c r="B484" s="41"/>
+    </row>
+    <row r="485" spans="2:2" ht="16.5">
+      <c r="B485" s="50" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="486" spans="2:2" ht="16.5">
+      <c r="B486" s="50" t="s">
+        <v>739</v>
+      </c>
+    </row>
+    <row r="490" spans="2:2" ht="26.25">
+      <c r="B490" s="48" t="s">
+        <v>615</v>
+      </c>
+    </row>
+    <row r="492" spans="2:2" ht="16.5">
+      <c r="B492" s="46" t="s">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="494" spans="2:2" ht="21">
+      <c r="B494" s="49" t="s">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="495" spans="2:2">
+      <c r="B495" s="41"/>
+    </row>
+    <row r="496" spans="2:2" ht="16.5">
+      <c r="B496" s="50" t="s">
+        <v>741</v>
+      </c>
+    </row>
+    <row r="500" spans="2:2" ht="26.25">
+      <c r="B500" s="48" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="502" spans="2:2" ht="16.5">
+      <c r="B502" s="46" t="s">
+        <v>742</v>
+      </c>
+    </row>
+    <row r="504" spans="2:2" ht="21">
+      <c r="B504" s="49" t="s">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="505" spans="2:2">
+      <c r="B505" s="41"/>
+    </row>
+    <row r="506" spans="2:2" ht="16.5">
+      <c r="B506" s="50" t="s">
+        <v>743</v>
+      </c>
+    </row>
+    <row r="507" spans="2:2" ht="16.5">
+      <c r="B507" s="50" t="s">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="511" spans="2:2" ht="26.25">
+      <c r="B511" s="48" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="513" spans="2:2" ht="16.5">
+      <c r="B513" s="46" t="s">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="515" spans="2:2" ht="21">
+      <c r="B515" s="49" t="s">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="516" spans="2:2">
+      <c r="B516" s="41"/>
+    </row>
+    <row r="517" spans="2:2" ht="16.5">
+      <c r="B517" s="50" t="s">
+        <v>746</v>
+      </c>
+    </row>
+    <row r="518" spans="2:2" ht="16.5">
+      <c r="B518" s="50" t="s">
+        <v>747</v>
+      </c>
+    </row>
+    <row r="519" spans="2:2" ht="16.5">
+      <c r="B519" s="50" t="s">
+        <v>748</v>
+      </c>
+    </row>
+    <row r="523" spans="2:2" ht="26.25">
+      <c r="B523" s="48" t="s">
+        <v>629</v>
+      </c>
+    </row>
+    <row r="525" spans="2:2" ht="16.5">
+      <c r="B525" s="46" t="s">
+        <v>749</v>
+      </c>
+    </row>
+    <row r="527" spans="2:2" ht="21">
+      <c r="B527" s="49" t="s">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="528" spans="2:2">
+      <c r="B528" s="41"/>
+    </row>
+    <row r="529" spans="2:2" ht="16.5">
+      <c r="B529" s="50" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="530" spans="2:2" ht="16.5">
+      <c r="B530" s="50" t="s">
+        <v>751</v>
+      </c>
+    </row>
+    <row r="534" spans="2:2" ht="37.5">
+      <c r="B534" s="47" t="s">
+        <v>752</v>
+      </c>
+    </row>
+    <row r="536" spans="2:2" ht="21">
+      <c r="B536" s="49">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="538" spans="2:2" ht="16.5">
+      <c r="B538" s="46" t="s">
+        <v>753</v>
+      </c>
+    </row>
+    <row r="540" spans="2:2" ht="21">
+      <c r="B540" s="49">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="542" spans="2:2" ht="16.5">
+      <c r="B542" s="46" t="s">
+        <v>754</v>
+      </c>
+    </row>
+    <row r="544" spans="2:2" ht="21">
+      <c r="B544" s="49">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="546" spans="2:2" ht="16.5">
+      <c r="B546" s="46" t="s">
+        <v>755</v>
+      </c>
+    </row>
+    <row r="548" spans="2:2" ht="21">
+      <c r="B548" s="49">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="550" spans="2:2" ht="16.5">
+      <c r="B550" s="46" t="s">
+        <v>756</v>
+      </c>
+    </row>
+    <row r="552" spans="2:2" ht="21">
+      <c r="B552" s="49">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="554" spans="2:2" ht="16.5">
+      <c r="B554" s="46" t="s">
+        <v>757</v>
+      </c>
+    </row>
+    <row r="556" spans="2:2" ht="21">
+      <c r="B556" s="49">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="558" spans="2:2" ht="16.5">
+      <c r="B558" s="46" t="s">
+        <v>758</v>
+      </c>
+    </row>
+    <row r="560" spans="2:2" ht="21">
+      <c r="B560" s="49">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="562" spans="2:2" ht="16.5">
+      <c r="B562" s="46" t="s">
+        <v>759</v>
+      </c>
+    </row>
+    <row r="564" spans="2:2" ht="21">
+      <c r="B564" s="49">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="566" spans="2:2" ht="16.5">
+      <c r="B566" s="46" t="s">
+        <v>760</v>
+      </c>
+    </row>
+    <row r="568" spans="2:2" ht="21">
+      <c r="B568" s="49">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="570" spans="2:2" ht="16.5">
+      <c r="B570" s="46" t="s">
+        <v>761</v>
+      </c>
+    </row>
+    <row r="572" spans="2:2" ht="21">
+      <c r="B572" s="49">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="574" spans="2:2" ht="16.5">
+      <c r="B574" s="46" t="s">
+        <v>762</v>
+      </c>
+    </row>
+    <row r="575" spans="2:2" ht="16.5">
+      <c r="B575" s="46"/>
+    </row>
+    <row r="576" spans="2:2" ht="16.5">
+      <c r="B576" s="46"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EFC6BB78-2366-4CBC-BDE4-AE3B7D4D0F5C}">
+  <dimension ref="B2:B3"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
+  <sheetData>
+    <row r="2" spans="2:2" ht="16.5">
+      <c r="B2" s="46" t="s">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="3" spans="2:2" ht="16.5">
+      <c r="B3" s="46" t="s">
+        <v>555</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{40E537D0-355C-44F6-821F-B309AC3764BF}">
+  <dimension ref="A1:A139"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1">
+      <c r="A2" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1">
+      <c r="A4" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1">
+      <c r="A5" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1">
+      <c r="A6" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1">
+      <c r="A7" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1">
+      <c r="A8" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1">
+      <c r="A9" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1">
+      <c r="A10" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1">
+      <c r="A11" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1">
+      <c r="A12" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1">
+      <c r="A13" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1">
+      <c r="A14" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1">
+      <c r="A15" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1">
+      <c r="A16" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1">
+      <c r="A17" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1">
+      <c r="A18" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1">
+      <c r="A19" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1">
+      <c r="A20" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1">
+      <c r="A23" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1">
+      <c r="A24" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1">
+      <c r="A25" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1">
+      <c r="A26" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1">
+      <c r="A27" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1">
+      <c r="A28" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1">
+      <c r="A29" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1">
+      <c r="A30" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1">
+      <c r="A31" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1">
+      <c r="A32" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1">
+      <c r="A33" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1">
+      <c r="A34" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1">
+      <c r="A35" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1">
+      <c r="A36" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1">
+      <c r="A37" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1">
+      <c r="A38" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1">
+      <c r="A39" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1">
+      <c r="A40" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1">
+      <c r="A41" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1">
+      <c r="A42" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1">
+      <c r="A43" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1">
+      <c r="A46" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1">
+      <c r="A47" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1">
+      <c r="A48" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1">
+      <c r="A49" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1">
+      <c r="A50" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1">
+      <c r="A51" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1">
+      <c r="A52" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1">
+      <c r="A53" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1">
+      <c r="A54" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="55" spans="1:1">
+      <c r="A55" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="56" spans="1:1">
+      <c r="A56" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="57" spans="1:1">
+      <c r="A57" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="58" spans="1:1">
+      <c r="A58" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="59" spans="1:1">
+      <c r="A59" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="60" spans="1:1">
+      <c r="A60" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="61" spans="1:1">
+      <c r="A61" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="62" spans="1:1">
+      <c r="A62" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="63" spans="1:1">
+      <c r="A63" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="64" spans="1:1">
+      <c r="A64" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="65" spans="1:1">
+      <c r="A65" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="66" spans="1:1">
+      <c r="A66" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="69" spans="1:1">
+      <c r="A69" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="70" spans="1:1">
+      <c r="A70" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="71" spans="1:1">
+      <c r="A71" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="72" spans="1:1">
+      <c r="A72" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="73" spans="1:1">
+      <c r="A73" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="74" spans="1:1">
+      <c r="A74" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="75" spans="1:1">
+      <c r="A75" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="76" spans="1:1">
+      <c r="A76" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="77" spans="1:1">
+      <c r="A77" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="78" spans="1:1">
+      <c r="A78" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="79" spans="1:1">
+      <c r="A79" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="80" spans="1:1">
+      <c r="A80" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="81" spans="1:1">
+      <c r="A81" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="82" spans="1:1">
+      <c r="A82" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="83" spans="1:1">
+      <c r="A83" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="84" spans="1:1">
+      <c r="A84" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="85" spans="1:1">
+      <c r="A85" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="86" spans="1:1">
+      <c r="A86" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="87" spans="1:1">
+      <c r="A87" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="88" spans="1:1">
+      <c r="A88" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="92" spans="1:1">
+      <c r="A92" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="93" spans="1:1">
+      <c r="A93" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="94" spans="1:1">
+      <c r="A94" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="95" spans="1:1">
+      <c r="A95" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="96" spans="1:1">
+      <c r="A96" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="97" spans="1:1">
+      <c r="A97" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="98" spans="1:1">
+      <c r="A98" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="99" spans="1:1">
+      <c r="A99" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="100" spans="1:1">
+      <c r="A100" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="101" spans="1:1">
+      <c r="A101" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="102" spans="1:1">
+      <c r="A102" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="103" spans="1:1">
+      <c r="A103" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="104" spans="1:1">
+      <c r="A104" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="105" spans="1:1">
+      <c r="A105" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="106" spans="1:1">
+      <c r="A106" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="107" spans="1:1">
+      <c r="A107" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="108" spans="1:1">
+      <c r="A108" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="109" spans="1:1">
+      <c r="A109" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="110" spans="1:1">
+      <c r="A110" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="111" spans="1:1">
+      <c r="A111" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="112" spans="1:1">
+      <c r="A112" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="113" spans="1:1">
+      <c r="A113" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="114" spans="1:1">
+      <c r="A114" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="117" spans="1:1">
+      <c r="A117" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="118" spans="1:1">
+      <c r="A118" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="119" spans="1:1">
+      <c r="A119" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="120" spans="1:1">
+      <c r="A120" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="121" spans="1:1">
+      <c r="A121" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="122" spans="1:1">
+      <c r="A122" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="123" spans="1:1">
+      <c r="A123" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="124" spans="1:1">
+      <c r="A124" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="125" spans="1:1">
+      <c r="A125" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="126" spans="1:1">
+      <c r="A126" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="127" spans="1:1">
+      <c r="A127" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="128" spans="1:1">
+      <c r="A128" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="129" spans="1:1">
+      <c r="A129" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="130" spans="1:1">
+      <c r="A130" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="131" spans="1:1">
+      <c r="A131" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="132" spans="1:1">
+      <c r="A132" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="133" spans="1:1">
+      <c r="A133" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="134" spans="1:1">
+      <c r="A134" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="135" spans="1:1">
+      <c r="A135" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="136" spans="1:1">
+      <c r="A136" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="137" spans="1:1">
+      <c r="A137" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="138" spans="1:1">
+      <c r="A138" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="139" spans="1:1">
+      <c r="A139" t="s">
+        <v>400</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C945A8A3-E413-4358-BBE4-EF5A44242598}">
   <dimension ref="A1:A12"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
@@ -9406,7 +12352,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:B21"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
@@ -9529,12 +12475,12 @@
       </c>
       <c r="B19" s="24"/>
     </row>
-    <row r="20" spans="1:2" ht="67.5">
+    <row r="20" spans="1:2" ht="94.5">
       <c r="A20" s="24" t="s">
         <v>168</v>
       </c>
       <c r="B20" s="23" t="s">
-        <v>176</v>
+        <v>550</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -9549,7 +12495,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:B11"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
@@ -9652,7 +12598,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{05FA0C31-4B39-4CC9-AFFE-ADB97979182D}">
   <dimension ref="A1:B21"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
@@ -9765,347 +12711,4 @@
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E3B1E147-F943-43CF-88AE-86DE70DEEA3B}">
-  <dimension ref="A1:B21"/>
-  <sheetFormatPr defaultRowHeight="13.5"/>
-  <cols>
-    <col min="1" max="1" width="150.375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="103.375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:2">
-      <c r="A1" s="24"/>
-      <c r="B1" s="24"/>
-    </row>
-    <row r="2" spans="1:2">
-      <c r="A2" s="24" t="s">
-        <v>150</v>
-      </c>
-      <c r="B2" s="24"/>
-    </row>
-    <row r="3" spans="1:2">
-      <c r="A3" s="33" t="s">
-        <v>251</v>
-      </c>
-      <c r="B3" s="24"/>
-    </row>
-    <row r="4" spans="1:2" ht="40.5">
-      <c r="A4" s="33" t="s">
-        <v>258</v>
-      </c>
-      <c r="B4" s="23" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2">
-      <c r="A5" s="33" t="s">
-        <v>259</v>
-      </c>
-      <c r="B5" s="23"/>
-    </row>
-    <row r="6" spans="1:2">
-      <c r="A6" s="33" t="s">
-        <v>260</v>
-      </c>
-      <c r="B6" s="24"/>
-    </row>
-    <row r="7" spans="1:2">
-      <c r="A7" s="33" t="s">
-        <v>261</v>
-      </c>
-      <c r="B7" s="23"/>
-    </row>
-    <row r="8" spans="1:2">
-      <c r="A8" s="35" t="s">
-        <v>262</v>
-      </c>
-      <c r="B8" s="33" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2">
-      <c r="A9" s="33" t="s">
-        <v>263</v>
-      </c>
-      <c r="B9" s="24"/>
-    </row>
-    <row r="10" spans="1:2" ht="40.5">
-      <c r="A10" s="33" t="s">
-        <v>264</v>
-      </c>
-      <c r="B10" s="23" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2">
-      <c r="A11" s="33" t="s">
-        <v>265</v>
-      </c>
-      <c r="B11" s="24"/>
-    </row>
-    <row r="12" spans="1:2">
-      <c r="A12" s="35" t="s">
-        <v>266</v>
-      </c>
-      <c r="B12" s="24"/>
-    </row>
-    <row r="13" spans="1:2">
-      <c r="A13" s="33" t="s">
-        <v>267</v>
-      </c>
-      <c r="B13" s="24"/>
-    </row>
-    <row r="14" spans="1:2">
-      <c r="A14" s="33" t="s">
-        <v>268</v>
-      </c>
-      <c r="B14" s="24"/>
-    </row>
-    <row r="15" spans="1:2">
-      <c r="A15" s="33" t="s">
-        <v>269</v>
-      </c>
-      <c r="B15" s="24"/>
-    </row>
-    <row r="16" spans="1:2">
-      <c r="A16" s="24"/>
-      <c r="B16" s="24"/>
-    </row>
-    <row r="17" spans="1:2">
-      <c r="A17" s="24"/>
-      <c r="B17" s="24"/>
-    </row>
-    <row r="18" spans="1:2">
-      <c r="A18" s="24"/>
-      <c r="B18" s="24"/>
-    </row>
-    <row r="19" spans="1:2">
-      <c r="A19" s="24"/>
-      <c r="B19" s="24"/>
-    </row>
-    <row r="20" spans="1:2" ht="67.5">
-      <c r="A20" s="24"/>
-      <c r="B20" s="23" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2">
-      <c r="A21" s="24"/>
-      <c r="B21" s="24"/>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="1"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4E6BF410-1D86-4886-AF32-D2372AA65DBD}">
-  <dimension ref="A1:B9"/>
-  <sheetFormatPr defaultRowHeight="13.5"/>
-  <cols>
-    <col min="1" max="1" width="51.875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="119.375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:2">
-      <c r="A1" s="34" t="s">
-        <v>278</v>
-      </c>
-      <c r="B1" s="34" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2">
-      <c r="A2" s="34" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2">
-      <c r="A3" s="34" t="s">
-        <v>281</v>
-      </c>
-      <c r="B3" s="34" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" ht="67.5">
-      <c r="A4" s="34" t="s">
-        <v>283</v>
-      </c>
-      <c r="B4" s="38" t="s">
-        <v>552</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2">
-      <c r="A5" s="34" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2">
-      <c r="A6" s="34" t="s">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" ht="108">
-      <c r="A7" s="34" t="s">
-        <v>286</v>
-      </c>
-      <c r="B7" s="38" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2">
-      <c r="A8" s="34" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2">
-      <c r="A9" s="34" t="s">
-        <v>288</v>
-      </c>
-      <c r="B9" s="34" t="s">
-        <v>289</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="1"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AF701674-7A60-413B-8525-5F23C4EF17DB}">
-  <dimension ref="A1:B19"/>
-  <sheetFormatPr defaultRowHeight="13.5"/>
-  <cols>
-    <col min="1" max="1" width="63.125" customWidth="1"/>
-    <col min="2" max="2" width="73.875" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:2" ht="121.5">
-      <c r="A1" s="34" t="s">
-        <v>411</v>
-      </c>
-      <c r="B1" s="38" t="s">
-        <v>416</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" ht="121.5">
-      <c r="A2" s="34" t="s">
-        <v>418</v>
-      </c>
-      <c r="B2" s="38" t="s">
-        <v>417</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2">
-      <c r="A3" s="34" t="s">
-        <v>412</v>
-      </c>
-      <c r="B3" s="34" t="s">
-        <v>419</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2">
-      <c r="A4" s="34" t="s">
-        <v>413</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" ht="67.5">
-      <c r="A5" s="34" t="s">
-        <v>420</v>
-      </c>
-      <c r="B5" s="38" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2">
-      <c r="A6" s="34" t="s">
-        <v>414</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2">
-      <c r="A7" s="34" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" ht="102" customHeight="1">
-      <c r="A8" s="34" t="s">
-        <v>422</v>
-      </c>
-      <c r="B8" s="38" t="s">
-        <v>423</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" ht="102" customHeight="1">
-      <c r="A9" s="34" t="s">
-        <v>426</v>
-      </c>
-      <c r="B9" s="38" t="s">
-        <v>425</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" ht="102" customHeight="1">
-      <c r="A10" s="34" t="s">
-        <v>428</v>
-      </c>
-      <c r="B10" s="38" t="s">
-        <v>427</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" ht="102" customHeight="1">
-      <c r="A11" s="34"/>
-      <c r="B11" s="38" t="s">
-        <v>429</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2">
-      <c r="A12" t="s">
-        <v>403</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2">
-      <c r="A13" t="s">
-        <v>404</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2">
-      <c r="A14" t="s">
-        <v>405</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2">
-      <c r="A15" t="s">
-        <v>406</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2">
-      <c r="A16" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1">
-      <c r="A17" t="s">
-        <v>408</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1">
-      <c r="A18" t="s">
-        <v>409</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1">
-      <c r="A19" t="s">
-        <v>410</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="1"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>
--- a/作業/面接練習/G3面接準備中岫.xlsx
+++ b/作業/面接練習/G3面接準備中岫.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aaa115298\Desktop\G3\G3\G3試験中岫作業\G3\作業\面接練習\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/df213c2b7ba35e42/デスクトップ/試験/G3/作業/面接練習/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20E12783-3F2A-469D-89EF-A5034C76BFE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="22" documentId="13_ncr:1_{20E12783-3F2A-469D-89EF-A5034C76BFE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{25FDD01F-B175-418B-8C29-818855BD1DAB}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -18,14 +18,13 @@
     <sheet name="Sheet6" sheetId="13" r:id="rId3"/>
     <sheet name="Sheet4" sheetId="11" r:id="rId4"/>
     <sheet name="Sheet2" sheetId="8" r:id="rId5"/>
-    <sheet name="Sheet3" sheetId="5" r:id="rId6"/>
-    <sheet name="1013" sheetId="2" r:id="rId7"/>
-    <sheet name="1014" sheetId="3" r:id="rId8"/>
-    <sheet name="1015" sheetId="4" r:id="rId9"/>
-    <sheet name="1016" sheetId="7" r:id="rId10"/>
-    <sheet name="1019" sheetId="6" r:id="rId11"/>
-    <sheet name="1021" sheetId="9" r:id="rId12"/>
-    <sheet name="1022" sheetId="10" r:id="rId13"/>
+    <sheet name="1013" sheetId="2" r:id="rId6"/>
+    <sheet name="1014" sheetId="3" r:id="rId7"/>
+    <sheet name="1015" sheetId="4" r:id="rId8"/>
+    <sheet name="1016" sheetId="7" r:id="rId9"/>
+    <sheet name="1019" sheetId="6" r:id="rId10"/>
+    <sheet name="1021" sheetId="9" r:id="rId11"/>
+    <sheet name="1022" sheetId="10" r:id="rId12"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -43,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="938" uniqueCount="763">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="942" uniqueCount="767">
   <si>
     <t>No</t>
   </si>
@@ -1903,18 +1902,6 @@
     <rPh sb="162" eb="163">
       <t>カンガ</t>
     </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>私は、デジタルビジネスプラットフォーム開発本部、ソフトウェア33開発室の中岫茉希と申します。
-私は、デジタルプリンティング事業本部と連携し、商業印刷向けインクジェットプリンターMogamiの高画質化に向けた技術開発を担当しています。
-商業印刷の分野では、従来のオフセット印刷で使用されてきたさまざまな用紙を、デジタル印刷でも使用したいというニーズがあります。そのため、商業印刷機には、多様な用紙に対応しながら、安定した高画質を実現することが求められています。Mogamiにおいても、高画質化と用紙対応力の向上が重要な開発課題の一つとなっています。社内資料では、Mogamiの顧客価値として、高画質・高品位に加え、幅広い用紙への対応が挙げられています。
-私が担当しているのは、プライマに関する画質評価と設計支援です。プライマとは、カラーインクの定着性を高めるために、印刷前に用紙へ付与する透明な液体です。プライマの付与量によって、発色やムラ、にじみなどの画質が変化するため、画質全体を考慮して適切な量を決めることが重要です。
-一方で、プライマ量を変えると複数の画質項目がそれぞれ異なる形で変化します。ある画質項目が良くなっても、別の画質項目が悪化する場合があり、単一の評価結果だけで適切な量を決めることはできません。また、従来の評価では、複数のチャートや画質項目を確認しながら総合的に判断する必要があり、評価者の経験に依存しやすいという課題がありました。
-そこで私は、まず、プライマ量の変化がそれぞれの画質項目にどのような影響を与えるのかを分析し、プライマと画質の関係を整理しました。さらに、その結果を実際の設計判断につなげるため、評価項目や判断方法を見直し、適切なプライマ量を効率的に決定するための評価フローを再構築しました。
-具体的には、複数の評価結果を比較しやすくするために評価方法を整理するとともに、評価者によらず、同じ考え方でプライマ量を選択できるよう判断手順を明確にしました。これにより、従来は経験や勘に依存しやすかった評価を、より再現性のある形で進めるための基盤を整えました。
-私は、こうした画質の分析と評価フローの改善を通じて、商業印刷機の安定した高画質化と、開発・評価の効率化に貢献しています。
-本日はよろしくお願いいたします。</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -4084,11 +4071,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>私が目標としているのは、自分たちの専門領域だけでは解決が難しい課題に対して、他部署の専門家を適切に巻き込み、チームとして解決に導ける先輩です。
-Mogamiのメディア対応では複数領域の知見が必要となるため、専門の異なる関係者が集まると、同じ用語でも定義が異なったり、現象の捉え方がずれたりすることがあります。そのような場面で、議論の前提や用語の定義をそろえ、各担当者の知見をつなぎながら、判断すべき論点を明確にする姿勢を見習いたいと考えています。</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>Q1. あなたの検討しているチームの編成と状況を教えてください</t>
   </si>
   <si>
@@ -4245,18 +4227,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>デジタルビジネスプラットフォーム開発本部ソフトウェア12開発室の森本と申します。</t>
-  </si>
-  <si>
-    <t>2023年に入社し、入社当初はイメージング事業本部に配属され、ボリュメトリックビデオの開発、DBPに異動してからはカメラやCT装置といった画像処理技術に関わる開発を行ってきました。</t>
-  </si>
-  <si>
-    <t>そのように入社して以来、一貫して三次元画像処理やメディカル領域といったキヤノンにとって新しい領域の画像処理に携わっています。</t>
-  </si>
-  <si>
-    <t>直近ではイメージング事業本部と連携し、少数のカメラで人間の3Dモデルを生成する技術の開発を担当しています。</t>
-  </si>
-  <si>
     <t>スジムラチームとの関係？どのように協力しながらやっているのか</t>
     <rPh sb="9" eb="11">
       <t>カンケイ</t>
@@ -4483,15 +4453,6 @@
       <t>モト</t>
     </rPh>
     <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>私は、デジタルビジネスプラットフォーム開発本部、ソフトウェア33開発室の中岫茉希と申します。</t>
-  </si>
-  <si>
-    <t>画質定量化技術をコアとして、プリンティング製品の開発を支援しています。直近では、デジタルプリンティング事業本部と連携し、商業印刷機Mogamiの画質向上に向けた技術開発を担当しており、画質劣化の原因を解析することで、画質の向上を実現するための設計効率化を目指しています。</t>
-  </si>
-  <si>
-    <t>本日はよろしくお願いいたします。</t>
   </si>
   <si>
     <t>答えだけを教えるのではなく、解析の方向性だけ示しタスクを進めるようにする。最初は評価計画と結果をこまめにレビューし、理解度に応じて任せる範囲を広げ、自力で次の検証を組み立てられるように育成します。</t>
@@ -6970,6 +6931,339 @@
   </si>
   <si>
     <t>全体として以前よりかなり改善している。今後は回答精度よりも、強みや将来性を印象付ける段階に入っている。</t>
+  </si>
+  <si>
+    <t>他事業部と技術的な議論をする際には、最初に用語の定義や現象の捉え方を合わせておくことが重要だと考えています。
+例えば、プライマの効果を議論するときに「溶剤」という言葉が出てきても、ある人は有機溶剤を指し、別の人は液体全般を指していることがあります。そうすると、同じ言葉を使っていても、想定している作用やメカニズムが異なり、議論がかみ合わなくなってしまいます。
+その結果、原因の捉え方を誤ったり、効果の評価や対策の方向性がずれたりする可能性があります。
+だからこそ、議論の最初に、用語が何を指すのか、どの範囲の現象を扱うのかを明確にしておくことが大切です。
+これは単にコミュニケーションを円滑にするためではなく、正しい現象解析と、合理的な開発判断につなげるために必要なことだと考えています。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>他事業部と心がけていること</t>
+    <rPh sb="0" eb="4">
+      <t>タジギョウブ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>ココロ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>印刷会社	受注可能な案件が増える。用紙の選択肢が広がり、売上や利益の拡大を狙える
+発注者（企業など）	希望する紙質や仕上がりで印刷物を制作できる。表現や商品訴求の幅が広がる
+キヤノン	印刷会社への提案力が高まり、製品の差別化や販売機会の拡大につながる</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>紙種が増えることによるメリット</t>
+    <rPh sb="0" eb="2">
+      <t>カミシュ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>フ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ix1700を拡大するためには</t>
+    <rPh sb="7" eb="9">
+      <t>カクダイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>マーケ：展示会などで実際に印刷されたサンプルを見せて、どれだけ高画質に印刷できるかをアピールする
+技術：対応品種の安定、紙種の拡大</t>
+    <rPh sb="4" eb="7">
+      <t>テンジカイ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>ジッサイ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>インサツ</t>
+    </rPh>
+    <rPh sb="23" eb="24">
+      <t>ミ</t>
+    </rPh>
+    <rPh sb="31" eb="34">
+      <t>コウガシツ</t>
+    </rPh>
+    <rPh sb="35" eb="37">
+      <t>インサツ</t>
+    </rPh>
+    <rPh sb="49" eb="51">
+      <t>ギジュツ</t>
+    </rPh>
+    <rPh sb="52" eb="56">
+      <t>タイオウヒンシュ</t>
+    </rPh>
+    <rPh sb="57" eb="59">
+      <t>アンテイ</t>
+    </rPh>
+    <rPh sb="60" eb="62">
+      <t>カミシュ</t>
+    </rPh>
+    <rPh sb="63" eb="65">
+      <t>カクダイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>印刷業界は斜陽産業なのでは</t>
+    <rPh sb="0" eb="2">
+      <t>インサツ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ギョウカイ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>シャヨウ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>サンギョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>報を伝えるだけの印刷物はデジタルに置き換わりやすい一方、紙の質感や見栄えが商品価値を高めるカタログ、高付加価値の販促物、パッケージなどは、紙ならではの価値を提供できる余地があります。そのような高画質に印刷するのが難しい紙に対しても、安定して高い画質で印刷できるようにしていくことで、キヤノンが顧客から選ばれると考えている</t>
+    <rPh sb="96" eb="99">
+      <t>コウガシツ</t>
+    </rPh>
+    <rPh sb="100" eb="102">
+      <t>インサツ</t>
+    </rPh>
+    <rPh sb="106" eb="107">
+      <t>ムズカ</t>
+    </rPh>
+    <rPh sb="109" eb="110">
+      <t>カミ</t>
+    </rPh>
+    <rPh sb="111" eb="112">
+      <t>タイ</t>
+    </rPh>
+    <rPh sb="116" eb="118">
+      <t>アンテイ</t>
+    </rPh>
+    <rPh sb="120" eb="121">
+      <t>タカ</t>
+    </rPh>
+    <rPh sb="122" eb="124">
+      <t>ガシツ</t>
+    </rPh>
+    <rPh sb="125" eb="127">
+      <t>インサツ</t>
+    </rPh>
+    <rPh sb="146" eb="148">
+      <t>コキャク</t>
+    </rPh>
+    <rPh sb="150" eb="151">
+      <t>エラ</t>
+    </rPh>
+    <rPh sb="155" eb="156">
+      <t>カンガ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>私は、デジタルビジネスプラットフォーム開発本部、ソフトウェア33開発室の中岫茉希と申します。
+商業印刷向けプリンタの高画質化に向けて、印刷画質がどのような要因によって決まるのか、その仕組みを解析しています。
+商業印刷の分野では、従来のオフセット印刷で使用されてきたさまざまな用紙を、デジタル印刷でも使用したいというニーズがあります。そのため、商業印刷機には、多様な用紙に対応しながら、安定した高画質を実現することが求められています。
+さまざまな用紙に対応するため、カラーインクを打つ前に、用紙へ透明な液体であるプライマを付与します。プライマは、用紙の種類に応じて適切な量を調整する必要がありますが、その量によって粒状性やもやむらなど、複数の画質項目が異なる影響を受けます。そのため、ある画質項目を改善しようとすると別の項目が悪化する場合もあり、複数の画質項目を総合的に評価して、適切な量を判断する必要があります。
+従来は、複数のチャートや画質項目を個別に確認しながら総合的に判断していたため、評価に時間がかかるだけでなく、評価者の経験に依存しやすいという課題がありました。
+そこで私は、まず、プライマ量の変化がそれぞれの画質項目にどのような影響を与えるのかを分析し、プライマと画質の関係を整理しました。さらに、その結果を実際の設計判断につなげるため、評価項目や判断方法を見直し、適切なプライマ量を効率的に決定するための評価フローを再構築しました。
+具体的には、複数の評価結果を比較しやすくするために評価方法を整理するとともに、評価者によらず、同じ考え方でプライマ量を選択できるよう判断手順を明確にしました。これにより、従来は経験や勘に依存しやすかった評価を、より再現性のある形で進めるための基盤を整えました。
+私は、こうした画質の分析と評価フローの改善を通じて、商業印刷機の安定した高画質化と、開発・評価の効率化に貢献しています。
+本日はよろしくお願いいたします。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>私がロールモデルの先輩を見習いたいと思う点は、事業部全体の視点から課題を発見し、解決に向けたプロジェクトを自ら立案できることです。
+特に、現場に足を運んで実際の業務フローを把握し、事業部がまだ気づいていない課題を発見したうえで、自部門が持つ画像処理技術やAI解析、定量評価といった技術を組み合わせ、解決につなげている点を尊敬しています。
+私自身も、与えられた問題を自分の担当領域だけで解決するのではなく、実際に現場に足を運び、業務の流れを確認したり、自分自身で体験したりすることで、問題の根本原因や潜在的な課題を見つけることを意識したいと考えています。
+今後は、現場で得た気づきを課題の発見につなげ、自部門の技術を活用した解決策を自ら提案し、プロジェクトとして推進できる人材を目指したいです。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t xml:space="preserve">プライマとインクが反応して、インクが定着するまでは化学的な反応が起きているので、化学の知見が必要
+インクが紙に定着し画像が形成されたら、スキャンして見え方を定量化できたり、解析できるのでソフト解析
+後者は第三部が得意とする分野
+</t>
+    <rPh sb="9" eb="11">
+      <t>ハンノウ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>テイチャク</t>
+    </rPh>
+    <rPh sb="25" eb="28">
+      <t>カガクテキ</t>
+    </rPh>
+    <rPh sb="29" eb="31">
+      <t>ハンノウ</t>
+    </rPh>
+    <rPh sb="32" eb="33">
+      <t>オ</t>
+    </rPh>
+    <rPh sb="40" eb="42">
+      <t>カガク</t>
+    </rPh>
+    <rPh sb="43" eb="45">
+      <t>チケン</t>
+    </rPh>
+    <rPh sb="46" eb="48">
+      <t>ヒツヨウ</t>
+    </rPh>
+    <rPh sb="53" eb="54">
+      <t>カミ</t>
+    </rPh>
+    <rPh sb="55" eb="57">
+      <t>テイチャク</t>
+    </rPh>
+    <rPh sb="58" eb="60">
+      <t>ガゾウ</t>
+    </rPh>
+    <rPh sb="61" eb="63">
+      <t>ケイセイ</t>
+    </rPh>
+    <rPh sb="86" eb="88">
+      <t>カイセキ</t>
+    </rPh>
+    <rPh sb="96" eb="98">
+      <t>カイセキ</t>
+    </rPh>
+    <rPh sb="99" eb="101">
+      <t>コウシャ</t>
+    </rPh>
+    <rPh sb="102" eb="105">
+      <t>ダイサンブ</t>
+    </rPh>
+    <rPh sb="106" eb="108">
+      <t>トクイ</t>
+    </rPh>
+    <rPh sb="111" eb="113">
+      <t>ブンヤ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>特にはない
+リクルーター活動で就活生の面倒を見たりしている
+先輩は解析の方針を示して、あとは自分で考えるようにしていて、そのかわり進捗はこまめに確認してくれていた
+自分で考える力もついたし、先輩が忙しいときでも朝会で確認できたので、遅れないように進めることができた。</t>
+    <rPh sb="0" eb="1">
+      <t>トク</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>カツドウ</t>
+    </rPh>
+    <rPh sb="15" eb="18">
+      <t>シュウカツセイ</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>メンドウ</t>
+    </rPh>
+    <rPh sb="22" eb="23">
+      <t>ミ</t>
+    </rPh>
+    <rPh sb="30" eb="32">
+      <t>センパイ</t>
+    </rPh>
+    <rPh sb="33" eb="35">
+      <t>カイセキ</t>
+    </rPh>
+    <rPh sb="36" eb="38">
+      <t>ホウシン</t>
+    </rPh>
+    <rPh sb="39" eb="40">
+      <t>シメ</t>
+    </rPh>
+    <rPh sb="46" eb="48">
+      <t>ジブン</t>
+    </rPh>
+    <rPh sb="49" eb="50">
+      <t>カンガ</t>
+    </rPh>
+    <rPh sb="65" eb="67">
+      <t>シンチョク</t>
+    </rPh>
+    <rPh sb="72" eb="74">
+      <t>カクニン</t>
+    </rPh>
+    <rPh sb="82" eb="84">
+      <t>ジブン</t>
+    </rPh>
+    <rPh sb="85" eb="86">
+      <t>カンガ</t>
+    </rPh>
+    <rPh sb="88" eb="89">
+      <t>チカラ</t>
+    </rPh>
+    <rPh sb="95" eb="97">
+      <t>センパイ</t>
+    </rPh>
+    <rPh sb="98" eb="99">
+      <t>イソガ</t>
+    </rPh>
+    <rPh sb="105" eb="107">
+      <t>アサカイ</t>
+    </rPh>
+    <rPh sb="108" eb="110">
+      <t>カクニン</t>
+    </rPh>
+    <rPh sb="116" eb="117">
+      <t>オク</t>
+    </rPh>
+    <rPh sb="123" eb="124">
+      <t>スス</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>高画質化を実現するための設計を効率化するプロジェクトをやりたいと思っている
+紙の特性とプライマ量の関係がわかっていないから、そこを勉強している
+またコニカミノルタが自動設計では進んでいるから、そこの技術調査もしている</t>
+    <rPh sb="0" eb="4">
+      <t>コウガシツカ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>ジツゲン</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>セッケイ</t>
+    </rPh>
+    <rPh sb="15" eb="18">
+      <t>コウリツカ</t>
+    </rPh>
+    <rPh sb="32" eb="33">
+      <t>オモ</t>
+    </rPh>
+    <rPh sb="38" eb="39">
+      <t>カミ</t>
+    </rPh>
+    <rPh sb="40" eb="42">
+      <t>トクセイ</t>
+    </rPh>
+    <rPh sb="47" eb="48">
+      <t>リョウ</t>
+    </rPh>
+    <rPh sb="49" eb="51">
+      <t>カンケイ</t>
+    </rPh>
+    <rPh sb="65" eb="67">
+      <t>ベンキョウ</t>
+    </rPh>
+    <rPh sb="82" eb="86">
+      <t>ジドウセッケイ</t>
+    </rPh>
+    <rPh sb="88" eb="89">
+      <t>スス</t>
+    </rPh>
+    <rPh sb="99" eb="103">
+      <t>ギジュツチョウサ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
   </si>
 </sst>
 </file>
@@ -7637,21 +7931,21 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:I124"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18.75"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="10.625" style="2" customWidth="1"/>
-    <col min="2" max="2" width="50.375" style="1" customWidth="1"/>
-    <col min="3" max="3" width="107.125" customWidth="1"/>
+    <col min="1" max="1" width="10.6328125" style="2" customWidth="1"/>
+    <col min="2" max="2" width="50.36328125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="107.08984375" customWidth="1"/>
     <col min="4" max="4" width="52" style="25" customWidth="1"/>
-    <col min="5" max="5" width="119.125" style="6" customWidth="1"/>
-    <col min="6" max="6" width="116.875" style="6" customWidth="1"/>
-    <col min="7" max="7" width="35.875" style="3" customWidth="1"/>
-    <col min="8" max="8" width="64.25" style="3" customWidth="1"/>
-    <col min="9" max="9" width="111.625" style="3" customWidth="1"/>
+    <col min="5" max="5" width="119.08984375" style="6" customWidth="1"/>
+    <col min="6" max="6" width="116.90625" style="6" customWidth="1"/>
+    <col min="7" max="7" width="35.90625" style="3" customWidth="1"/>
+    <col min="8" max="8" width="64.26953125" style="3" customWidth="1"/>
+    <col min="9" max="9" width="111.6328125" style="3" customWidth="1"/>
     <col min="10" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="13.5">
+    <row r="1" spans="1:9" ht="13">
       <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
@@ -7678,21 +7972,21 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="262.5">
+    <row r="2" spans="1:9" ht="270">
       <c r="A2" s="4">
         <v>0</v>
       </c>
       <c r="B2" s="23" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C2" s="18" t="s">
-        <v>553</v>
+        <v>544</v>
       </c>
       <c r="D2" s="25" t="s">
         <v>171</v>
       </c>
       <c r="E2" s="13" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="F2" s="20" t="s">
         <v>148</v>
@@ -7704,18 +7998,18 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="391.5">
+    <row r="3" spans="1:9" ht="351">
       <c r="A3" s="28"/>
       <c r="B3" s="23" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C3" s="29" t="s">
-        <v>177</v>
+        <v>762</v>
       </c>
       <c r="E3" s="26"/>
       <c r="F3" s="20"/>
     </row>
-    <row r="4" spans="1:9" ht="262.5">
+    <row r="4" spans="1:9" ht="252">
       <c r="A4" s="4">
         <v>1</v>
       </c>
@@ -7723,20 +8017,20 @@
         <v>91</v>
       </c>
       <c r="C4" s="18" t="s">
-        <v>549</v>
+        <v>540</v>
       </c>
       <c r="D4" s="25" t="s">
         <v>172</v>
       </c>
       <c r="E4" s="21" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F4" s="20" t="s">
         <v>149</v>
       </c>
       <c r="G4" s="6"/>
     </row>
-    <row r="5" spans="1:9" ht="81">
+    <row r="5" spans="1:9" ht="78">
       <c r="A5" s="4" t="s">
         <v>7</v>
       </c>
@@ -7747,11 +8041,11 @@
         <v>55</v>
       </c>
       <c r="E5" s="13" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="F5" s="20"/>
     </row>
-    <row r="6" spans="1:9" ht="94.5">
+    <row r="6" spans="1:9" ht="91">
       <c r="A6" s="4" t="s">
         <v>8</v>
       </c>
@@ -7762,11 +8056,11 @@
         <v>56</v>
       </c>
       <c r="E6" s="13" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="F6" s="13"/>
     </row>
-    <row r="7" spans="1:9" ht="121.5">
+    <row r="7" spans="1:9" ht="130">
       <c r="A7" s="4" t="s">
         <v>9</v>
       </c>
@@ -7774,15 +8068,15 @@
         <v>93</v>
       </c>
       <c r="C7" s="18" t="s">
-        <v>277</v>
+        <v>268</v>
       </c>
       <c r="E7" s="21" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="F7" s="14"/>
       <c r="I7" s="6"/>
     </row>
-    <row r="8" spans="1:9" ht="54">
+    <row r="8" spans="1:9" ht="52">
       <c r="A8" s="4" t="s">
         <v>10</v>
       </c>
@@ -7790,14 +8084,14 @@
         <v>94</v>
       </c>
       <c r="C8" s="18" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E8" s="13" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="F8" s="14"/>
     </row>
-    <row r="9" spans="1:9" ht="108">
+    <row r="9" spans="1:9" ht="104">
       <c r="A9" s="4">
         <v>2</v>
       </c>
@@ -7808,11 +8102,11 @@
         <v>57</v>
       </c>
       <c r="E9" s="13" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="F9" s="20"/>
     </row>
-    <row r="10" spans="1:9" ht="108">
+    <row r="10" spans="1:9" ht="117">
       <c r="A10" s="4">
         <v>3</v>
       </c>
@@ -7820,14 +8114,14 @@
         <v>96</v>
       </c>
       <c r="C10" s="18" t="s">
-        <v>291</v>
+        <v>282</v>
       </c>
       <c r="E10" s="12" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="F10" s="20"/>
     </row>
-    <row r="11" spans="1:9" ht="40.5">
+    <row r="11" spans="1:9" ht="52">
       <c r="A11" s="4" t="s">
         <v>11</v>
       </c>
@@ -7838,11 +8132,11 @@
         <v>58</v>
       </c>
       <c r="E11" s="12" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="F11" s="14"/>
     </row>
-    <row r="12" spans="1:9" ht="67.5">
+    <row r="12" spans="1:9" ht="91">
       <c r="A12" s="4" t="s">
         <v>12</v>
       </c>
@@ -7850,10 +8144,10 @@
         <v>98</v>
       </c>
       <c r="C12" s="18" t="s">
-        <v>292</v>
+        <v>283</v>
       </c>
       <c r="E12" s="13" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F12" s="14"/>
     </row>
@@ -7865,12 +8159,12 @@
         <v>99</v>
       </c>
       <c r="C13" s="17" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="E13" s="13"/>
       <c r="F13" s="14"/>
     </row>
-    <row r="14" spans="1:9" ht="135">
+    <row r="14" spans="1:9" ht="143">
       <c r="A14" s="4">
         <v>4</v>
       </c>
@@ -7878,15 +8172,15 @@
         <v>100</v>
       </c>
       <c r="C14" s="36" t="s">
-        <v>552</v>
+        <v>543</v>
       </c>
       <c r="E14" s="13" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F14" s="20"/>
       <c r="G14" s="10"/>
     </row>
-    <row r="15" spans="1:9" ht="27">
+    <row r="15" spans="1:9" ht="39">
       <c r="A15" s="4" t="s">
         <v>14</v>
       </c>
@@ -7897,11 +8191,11 @@
         <v>59</v>
       </c>
       <c r="E15" s="13" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F15" s="20"/>
     </row>
-    <row r="16" spans="1:9" ht="40.5">
+    <row r="16" spans="1:9" ht="39">
       <c r="A16" s="4" t="s">
         <v>15</v>
       </c>
@@ -7912,11 +8206,11 @@
         <v>60</v>
       </c>
       <c r="E16" s="13" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F16" s="20"/>
     </row>
-    <row r="17" spans="1:6" ht="94.5">
+    <row r="17" spans="1:6" ht="91">
       <c r="A17" s="4" t="s">
         <v>16</v>
       </c>
@@ -7927,11 +8221,11 @@
         <v>174</v>
       </c>
       <c r="E17" s="13" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="F17" s="20"/>
     </row>
-    <row r="18" spans="1:6" ht="27">
+    <row r="18" spans="1:6" ht="26">
       <c r="A18" s="4" t="s">
         <v>17</v>
       </c>
@@ -7942,11 +8236,11 @@
         <v>61</v>
       </c>
       <c r="E18" s="12" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="F18" s="20"/>
     </row>
-    <row r="19" spans="1:6" ht="40.5">
+    <row r="19" spans="1:6" ht="39">
       <c r="A19" s="4" t="s">
         <v>18</v>
       </c>
@@ -7959,7 +8253,7 @@
       <c r="E19" s="13"/>
       <c r="F19" s="20"/>
     </row>
-    <row r="20" spans="1:6" ht="81">
+    <row r="20" spans="1:6" ht="78">
       <c r="A20" s="4" t="s">
         <v>19</v>
       </c>
@@ -7970,11 +8264,11 @@
         <v>63</v>
       </c>
       <c r="E20" s="13" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F20" s="20"/>
     </row>
-    <row r="21" spans="1:6" ht="108">
+    <row r="21" spans="1:6" ht="104">
       <c r="A21" s="4" t="s">
         <v>20</v>
       </c>
@@ -7982,13 +8276,13 @@
         <v>175</v>
       </c>
       <c r="C21" s="18" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="E21" s="13" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" ht="26">
       <c r="A22" s="4" t="s">
         <v>21</v>
       </c>
@@ -7999,11 +8293,11 @@
         <v>64</v>
       </c>
       <c r="E22" s="12" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F22" s="20"/>
     </row>
-    <row r="23" spans="1:6" ht="54">
+    <row r="23" spans="1:6" ht="52">
       <c r="A23" s="4" t="s">
         <v>22</v>
       </c>
@@ -8014,11 +8308,11 @@
         <v>65</v>
       </c>
       <c r="E23" s="13" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="F23" s="20"/>
     </row>
-    <row r="24" spans="1:6" ht="27">
+    <row r="24" spans="1:6" ht="26">
       <c r="A24" s="4" t="s">
         <v>23</v>
       </c>
@@ -8026,10 +8320,10 @@
         <v>109</v>
       </c>
       <c r="C24" s="18" t="s">
-        <v>276</v>
+        <v>267</v>
       </c>
       <c r="E24" s="12" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="F24" s="20"/>
     </row>
@@ -8044,7 +8338,7 @@
       <c r="E25" s="12"/>
       <c r="F25" s="20"/>
     </row>
-    <row r="26" spans="1:6" ht="27">
+    <row r="26" spans="1:6" ht="26">
       <c r="A26" s="4" t="s">
         <v>25</v>
       </c>
@@ -8057,7 +8351,7 @@
       <c r="E26" s="13"/>
       <c r="F26" s="20"/>
     </row>
-    <row r="27" spans="1:6" ht="81">
+    <row r="27" spans="1:6" ht="143">
       <c r="A27" s="4" t="s">
         <v>26</v>
       </c>
@@ -8065,12 +8359,12 @@
         <v>112</v>
       </c>
       <c r="C27" s="30" t="s">
-        <v>224</v>
+        <v>763</v>
       </c>
       <c r="E27" s="13"/>
       <c r="F27" s="14"/>
     </row>
-    <row r="28" spans="1:6" ht="108">
+    <row r="28" spans="1:6" ht="104">
       <c r="A28" s="4" t="s">
         <v>27</v>
       </c>
@@ -8081,11 +8375,11 @@
         <v>67</v>
       </c>
       <c r="E28" s="13" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="F28" s="20"/>
     </row>
-    <row r="29" spans="1:6" ht="27">
+    <row r="29" spans="1:6" ht="26">
       <c r="A29" s="4" t="s">
         <v>28</v>
       </c>
@@ -8096,11 +8390,11 @@
         <v>68</v>
       </c>
       <c r="E29" s="13" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F29" s="20"/>
     </row>
-    <row r="30" spans="1:6" ht="42">
+    <row r="30" spans="1:6" ht="40.5">
       <c r="A30" s="4" t="s">
         <v>29</v>
       </c>
@@ -8111,7 +8405,7 @@
         <v>69</v>
       </c>
       <c r="E30" s="12" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="F30" s="20"/>
     </row>
@@ -8126,7 +8420,7 @@
       <c r="E31" s="22"/>
       <c r="F31" s="20"/>
     </row>
-    <row r="32" spans="1:6" ht="27">
+    <row r="32" spans="1:6" ht="26">
       <c r="A32" s="4" t="s">
         <v>31</v>
       </c>
@@ -8137,11 +8431,11 @@
         <v>70</v>
       </c>
       <c r="E32" s="13" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="F32" s="20"/>
     </row>
-    <row r="33" spans="1:9" ht="40.5">
+    <row r="33" spans="1:9" ht="39">
       <c r="A33" s="4" t="s">
         <v>32</v>
       </c>
@@ -8152,12 +8446,12 @@
         <v>71</v>
       </c>
       <c r="E33" s="12" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="F33" s="13"/>
       <c r="I33" s="6"/>
     </row>
-    <row r="34" spans="1:9" ht="27">
+    <row r="34" spans="1:9" ht="26">
       <c r="A34" s="4" t="s">
         <v>33</v>
       </c>
@@ -8168,11 +8462,11 @@
         <v>72</v>
       </c>
       <c r="E34" s="12" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="F34" s="20"/>
     </row>
-    <row r="35" spans="1:9" ht="27">
+    <row r="35" spans="1:9" ht="26">
       <c r="A35" s="4" t="s">
         <v>34</v>
       </c>
@@ -8185,7 +8479,7 @@
       <c r="E35" s="13"/>
       <c r="F35" s="20"/>
     </row>
-    <row r="36" spans="1:9" ht="27">
+    <row r="36" spans="1:9" ht="26">
       <c r="A36" s="4" t="s">
         <v>35</v>
       </c>
@@ -8196,11 +8490,11 @@
         <v>74</v>
       </c>
       <c r="E36" s="13" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="F36" s="20"/>
     </row>
-    <row r="37" spans="1:9" ht="54">
+    <row r="37" spans="1:9" ht="52">
       <c r="A37" s="4" t="s">
         <v>36</v>
       </c>
@@ -8211,11 +8505,11 @@
         <v>75</v>
       </c>
       <c r="E37" s="13" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F37" s="20"/>
     </row>
-    <row r="38" spans="1:9" ht="54">
+    <row r="38" spans="1:9" ht="65">
       <c r="A38" s="4" t="s">
         <v>37</v>
       </c>
@@ -8226,11 +8520,11 @@
         <v>76</v>
       </c>
       <c r="E38" s="13" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F38" s="20"/>
     </row>
-    <row r="39" spans="1:9" ht="84">
+    <row r="39" spans="1:9" ht="81">
       <c r="A39" s="4" t="s">
         <v>38</v>
       </c>
@@ -8241,11 +8535,11 @@
         <v>77</v>
       </c>
       <c r="E39" s="13" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="F39" s="14"/>
     </row>
-    <row r="40" spans="1:9" ht="40.5">
+    <row r="40" spans="1:9" ht="39">
       <c r="A40" s="4" t="s">
         <v>39</v>
       </c>
@@ -8258,7 +8552,7 @@
       <c r="E40" s="13"/>
       <c r="F40" s="15"/>
     </row>
-    <row r="41" spans="1:9" ht="27">
+    <row r="41" spans="1:9" ht="39">
       <c r="A41" s="4" t="s">
         <v>40</v>
       </c>
@@ -8271,7 +8565,7 @@
       <c r="E41" s="13"/>
       <c r="F41" s="13"/>
     </row>
-    <row r="42" spans="1:9" ht="27">
+    <row r="42" spans="1:9" ht="26">
       <c r="A42" s="4" t="s">
         <v>41</v>
       </c>
@@ -8284,7 +8578,7 @@
       <c r="E42" s="13"/>
       <c r="F42" s="13"/>
     </row>
-    <row r="43" spans="1:9" ht="27">
+    <row r="43" spans="1:9" ht="26">
       <c r="A43" s="4" t="s">
         <v>42</v>
       </c>
@@ -8295,7 +8589,7 @@
       <c r="E43" s="13"/>
       <c r="F43" s="13"/>
     </row>
-    <row r="44" spans="1:9" ht="40.5">
+    <row r="44" spans="1:9" ht="39">
       <c r="A44" s="4" t="s">
         <v>43</v>
       </c>
@@ -8306,11 +8600,11 @@
         <v>81</v>
       </c>
       <c r="E44" s="13" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="F44" s="13"/>
     </row>
-    <row r="45" spans="1:9" ht="69">
+    <row r="45" spans="1:9" ht="66.5">
       <c r="A45" s="4" t="s">
         <v>44</v>
       </c>
@@ -8321,11 +8615,11 @@
         <v>82</v>
       </c>
       <c r="E45" s="13" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="F45" s="13"/>
     </row>
-    <row r="46" spans="1:9" ht="27">
+    <row r="46" spans="1:9" ht="39">
       <c r="A46" s="4" t="s">
         <v>45</v>
       </c>
@@ -8336,11 +8630,11 @@
         <v>83</v>
       </c>
       <c r="E46" s="13" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F46" s="13"/>
     </row>
-    <row r="47" spans="1:9" ht="27">
+    <row r="47" spans="1:9" ht="26">
       <c r="A47" s="4" t="s">
         <v>46</v>
       </c>
@@ -8351,7 +8645,7 @@
       <c r="E47" s="22"/>
       <c r="F47" s="13"/>
     </row>
-    <row r="48" spans="1:9" ht="27">
+    <row r="48" spans="1:9" ht="26">
       <c r="A48" s="4" t="s">
         <v>47</v>
       </c>
@@ -8362,7 +8656,7 @@
       <c r="E48" s="22"/>
       <c r="F48" s="13"/>
     </row>
-    <row r="49" spans="1:6" ht="27">
+    <row r="49" spans="1:6" ht="26">
       <c r="A49" s="4" t="s">
         <v>48</v>
       </c>
@@ -8375,7 +8669,7 @@
       <c r="E49" s="13"/>
       <c r="F49" s="13"/>
     </row>
-    <row r="50" spans="1:6" ht="27">
+    <row r="50" spans="1:6" ht="39">
       <c r="A50" s="4" t="s">
         <v>49</v>
       </c>
@@ -8386,11 +8680,11 @@
         <v>85</v>
       </c>
       <c r="E50" s="13" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="F50" s="13"/>
     </row>
-    <row r="51" spans="1:6" ht="42">
+    <row r="51" spans="1:6" ht="40.5">
       <c r="A51" s="4" t="s">
         <v>50</v>
       </c>
@@ -8401,11 +8695,11 @@
         <v>86</v>
       </c>
       <c r="E51" s="13" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F51" s="13"/>
     </row>
-    <row r="52" spans="1:6" ht="40.5">
+    <row r="52" spans="1:6" ht="39">
       <c r="A52" s="4" t="s">
         <v>51</v>
       </c>
@@ -8416,11 +8710,11 @@
         <v>87</v>
       </c>
       <c r="E52" s="13" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="F52" s="13"/>
     </row>
-    <row r="53" spans="1:6" ht="94.5">
+    <row r="53" spans="1:6" ht="91">
       <c r="A53" s="4"/>
       <c r="B53" s="11" t="s">
         <v>138</v>
@@ -8429,7 +8723,7 @@
         <v>88</v>
       </c>
       <c r="E53" s="12" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="F53" s="13"/>
     </row>
@@ -8442,14 +8736,14 @@
       <c r="E54" s="13"/>
       <c r="F54" s="13"/>
     </row>
-    <row r="55" spans="1:6" ht="27">
+    <row r="55" spans="1:6" ht="26">
       <c r="A55" s="4"/>
       <c r="B55" s="11" t="s">
         <v>140</v>
       </c>
       <c r="C55" s="5"/>
       <c r="E55" s="13" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="F55" s="13"/>
     </row>
@@ -8460,33 +8754,33 @@
       </c>
       <c r="C56" s="5"/>
       <c r="E56" s="13" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F56" s="13"/>
     </row>
-    <row r="57" spans="1:6" ht="40.5">
+    <row r="57" spans="1:6" ht="39">
       <c r="A57" s="4"/>
       <c r="B57" s="11" t="s">
         <v>142</v>
       </c>
       <c r="C57" s="5"/>
       <c r="E57" s="13" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="F57" s="13"/>
     </row>
-    <row r="58" spans="1:6" ht="40.5">
+    <row r="58" spans="1:6" ht="39">
       <c r="A58" s="4"/>
       <c r="B58" s="11" t="s">
         <v>143</v>
       </c>
       <c r="C58" s="5"/>
       <c r="E58" s="12" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="F58" s="13"/>
     </row>
-    <row r="59" spans="1:6" ht="27">
+    <row r="59" spans="1:6" ht="26">
       <c r="A59" s="4"/>
       <c r="B59" s="11" t="s">
         <v>144</v>
@@ -8497,7 +8791,7 @@
       <c r="E59" s="13"/>
       <c r="F59" s="13"/>
     </row>
-    <row r="60" spans="1:6" ht="40.5">
+    <row r="60" spans="1:6" ht="39">
       <c r="A60" s="4"/>
       <c r="B60" s="11" t="s">
         <v>145</v>
@@ -8506,11 +8800,11 @@
         <v>90</v>
       </c>
       <c r="E60" s="12" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="F60" s="13"/>
     </row>
-    <row r="61" spans="1:6" ht="27">
+    <row r="61" spans="1:6" ht="39">
       <c r="A61" s="4" t="s">
         <v>52</v>
       </c>
@@ -8519,10 +8813,10 @@
       </c>
       <c r="C61" s="5"/>
       <c r="E61" s="13" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="62" spans="1:6" ht="40.5">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" ht="39">
       <c r="A62" s="4" t="s">
         <v>53</v>
       </c>
@@ -8531,7 +8825,7 @@
       </c>
       <c r="C62" s="5"/>
       <c r="E62" s="13" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="64" spans="1:6">
@@ -8634,59 +8928,59 @@
         <v>169</v>
       </c>
     </row>
-    <row r="84" spans="2:2" ht="30">
+    <row r="84" spans="2:2" ht="29">
       <c r="B84" s="31" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
     </row>
     <row r="85" spans="2:2">
       <c r="B85" s="31" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
     </row>
     <row r="86" spans="2:2">
       <c r="B86" s="31" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
     </row>
     <row r="87" spans="2:2">
       <c r="B87" s="31" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="88" spans="2:2">
       <c r="B88" s="31" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
     </row>
     <row r="89" spans="2:2">
       <c r="B89" s="31" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
     </row>
     <row r="90" spans="2:2">
       <c r="B90" s="31" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
     </row>
     <row r="91" spans="2:2">
       <c r="B91" s="31" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
     </row>
     <row r="92" spans="2:2">
       <c r="B92" s="31" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
     </row>
     <row r="93" spans="2:2">
       <c r="B93" s="31" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
     </row>
     <row r="94" spans="2:2">
       <c r="B94" s="31" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
     </row>
     <row r="95" spans="2:2">
@@ -8696,27 +8990,27 @@
     </row>
     <row r="96" spans="2:2">
       <c r="B96" s="33" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
     </row>
     <row r="97" spans="2:2">
       <c r="B97" s="33" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
     </row>
     <row r="98" spans="2:2">
       <c r="B98" s="33" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
     </row>
     <row r="99" spans="2:2">
       <c r="B99" s="33" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
     </row>
     <row r="100" spans="2:2">
       <c r="B100" s="33" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
     </row>
     <row r="101" spans="2:2">
@@ -8726,67 +9020,67 @@
     </row>
     <row r="102" spans="2:2">
       <c r="B102" s="33" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
     </row>
     <row r="103" spans="2:2">
       <c r="B103" s="33" t="s">
-        <v>258</v>
+        <v>252</v>
       </c>
     </row>
     <row r="104" spans="2:2">
       <c r="B104" s="33" t="s">
-        <v>259</v>
+        <v>253</v>
       </c>
     </row>
     <row r="105" spans="2:2">
       <c r="B105" s="33" t="s">
-        <v>260</v>
+        <v>254</v>
       </c>
     </row>
     <row r="106" spans="2:2">
       <c r="B106" s="33" t="s">
-        <v>261</v>
+        <v>255</v>
       </c>
     </row>
     <row r="107" spans="2:2">
       <c r="B107" s="35" t="s">
-        <v>262</v>
+        <v>256</v>
       </c>
     </row>
     <row r="108" spans="2:2">
       <c r="B108" s="33" t="s">
-        <v>263</v>
+        <v>257</v>
       </c>
     </row>
     <row r="109" spans="2:2">
       <c r="B109" s="33" t="s">
-        <v>264</v>
+        <v>258</v>
       </c>
     </row>
     <row r="110" spans="2:2">
       <c r="B110" s="33" t="s">
-        <v>265</v>
+        <v>259</v>
       </c>
     </row>
     <row r="111" spans="2:2">
       <c r="B111" s="35" t="s">
-        <v>266</v>
+        <v>260</v>
       </c>
     </row>
     <row r="112" spans="2:2">
       <c r="B112" s="33" t="s">
-        <v>267</v>
+        <v>261</v>
       </c>
     </row>
     <row r="113" spans="2:2">
       <c r="B113" s="33" t="s">
-        <v>268</v>
+        <v>262</v>
       </c>
     </row>
     <row r="114" spans="2:2">
       <c r="B114" s="33" t="s">
-        <v>269</v>
+        <v>263</v>
       </c>
     </row>
     <row r="115" spans="2:2">
@@ -8794,47 +9088,47 @@
     </row>
     <row r="116" spans="2:2">
       <c r="B116" s="34" t="s">
-        <v>278</v>
+        <v>269</v>
       </c>
     </row>
     <row r="117" spans="2:2">
       <c r="B117" s="34" t="s">
-        <v>280</v>
+        <v>271</v>
       </c>
     </row>
     <row r="118" spans="2:2">
       <c r="B118" s="34" t="s">
-        <v>281</v>
+        <v>272</v>
       </c>
     </row>
     <row r="119" spans="2:2">
       <c r="B119" s="34" t="s">
-        <v>283</v>
+        <v>274</v>
       </c>
     </row>
     <row r="120" spans="2:2">
       <c r="B120" s="34" t="s">
-        <v>284</v>
+        <v>275</v>
       </c>
     </row>
     <row r="121" spans="2:2">
       <c r="B121" s="34" t="s">
-        <v>285</v>
+        <v>276</v>
       </c>
     </row>
     <row r="122" spans="2:2">
       <c r="B122" s="34" t="s">
-        <v>286</v>
+        <v>277</v>
       </c>
     </row>
     <row r="123" spans="2:2">
       <c r="B123" s="34" t="s">
-        <v>287</v>
+        <v>278</v>
       </c>
     </row>
     <row r="124" spans="2:2">
       <c r="B124" s="34" t="s">
-        <v>288</v>
+        <v>279</v>
       </c>
     </row>
   </sheetData>
@@ -8845,208 +9139,204 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E3B1E147-F943-43CF-88AE-86DE70DEEA3B}">
-  <dimension ref="A1:B21"/>
-  <sheetFormatPr defaultRowHeight="13.5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4E6BF410-1D86-4886-AF32-D2372AA65DBD}">
+  <dimension ref="A1:B9"/>
+  <sheetFormatPr defaultRowHeight="13"/>
   <cols>
-    <col min="1" max="1" width="150.375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="103.375" customWidth="1"/>
+    <col min="1" max="1" width="51.90625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="119.36328125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
-      <c r="A1" s="24"/>
-      <c r="B1" s="24"/>
+      <c r="A1" s="34" t="s">
+        <v>269</v>
+      </c>
+      <c r="B1" s="34" t="s">
+        <v>270</v>
+      </c>
     </row>
     <row r="2" spans="1:2">
-      <c r="A2" s="24" t="s">
-        <v>150</v>
-      </c>
-      <c r="B2" s="24"/>
+      <c r="A2" s="34" t="s">
+        <v>271</v>
+      </c>
     </row>
     <row r="3" spans="1:2">
-      <c r="A3" s="33" t="s">
-        <v>251</v>
-      </c>
-      <c r="B3" s="24"/>
-    </row>
-    <row r="4" spans="1:2" ht="40.5">
-      <c r="A4" s="33" t="s">
-        <v>258</v>
-      </c>
-      <c r="B4" s="23" t="s">
-        <v>270</v>
+      <c r="A3" s="34" t="s">
+        <v>272</v>
+      </c>
+      <c r="B3" s="34" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="65">
+      <c r="A4" s="34" t="s">
+        <v>274</v>
+      </c>
+      <c r="B4" s="38" t="s">
+        <v>538</v>
       </c>
     </row>
     <row r="5" spans="1:2">
-      <c r="A5" s="33" t="s">
-        <v>259</v>
-      </c>
-      <c r="B5" s="23"/>
+      <c r="A5" s="34" t="s">
+        <v>275</v>
+      </c>
     </row>
     <row r="6" spans="1:2">
-      <c r="A6" s="33" t="s">
-        <v>260</v>
-      </c>
-      <c r="B6" s="24"/>
-    </row>
-    <row r="7" spans="1:2">
-      <c r="A7" s="33" t="s">
-        <v>261</v>
-      </c>
-      <c r="B7" s="23"/>
+      <c r="A6" s="34" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" ht="117">
+      <c r="A7" s="34" t="s">
+        <v>277</v>
+      </c>
+      <c r="B7" s="38" t="s">
+        <v>281</v>
+      </c>
     </row>
     <row r="8" spans="1:2">
-      <c r="A8" s="35" t="s">
-        <v>262</v>
-      </c>
-      <c r="B8" s="33" t="s">
-        <v>271</v>
+      <c r="A8" s="34" t="s">
+        <v>278</v>
       </c>
     </row>
     <row r="9" spans="1:2">
-      <c r="A9" s="33" t="s">
-        <v>263</v>
-      </c>
-      <c r="B9" s="24"/>
-    </row>
-    <row r="10" spans="1:2" ht="40.5">
-      <c r="A10" s="33" t="s">
-        <v>264</v>
-      </c>
-      <c r="B10" s="23" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2">
-      <c r="A11" s="33" t="s">
-        <v>265</v>
-      </c>
-      <c r="B11" s="24"/>
-    </row>
-    <row r="12" spans="1:2">
-      <c r="A12" s="35" t="s">
-        <v>266</v>
-      </c>
-      <c r="B12" s="24"/>
-    </row>
-    <row r="13" spans="1:2">
-      <c r="A13" s="33" t="s">
-        <v>267</v>
-      </c>
-      <c r="B13" s="24"/>
-    </row>
-    <row r="14" spans="1:2">
-      <c r="A14" s="33" t="s">
-        <v>268</v>
-      </c>
-      <c r="B14" s="24"/>
-    </row>
-    <row r="15" spans="1:2">
-      <c r="A15" s="33" t="s">
-        <v>269</v>
-      </c>
-      <c r="B15" s="24"/>
-    </row>
-    <row r="16" spans="1:2">
-      <c r="A16" s="24"/>
-      <c r="B16" s="24"/>
-    </row>
-    <row r="17" spans="1:2">
-      <c r="A17" s="24"/>
-      <c r="B17" s="24"/>
-    </row>
-    <row r="18" spans="1:2">
-      <c r="A18" s="24"/>
-      <c r="B18" s="24"/>
-    </row>
-    <row r="19" spans="1:2">
-      <c r="A19" s="24"/>
-      <c r="B19" s="24"/>
-    </row>
-    <row r="20" spans="1:2" ht="67.5">
-      <c r="A20" s="24"/>
-      <c r="B20" s="23" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2">
-      <c r="A21" s="24"/>
-      <c r="B21" s="24"/>
+      <c r="A9" s="34" t="s">
+        <v>279</v>
+      </c>
+      <c r="B9" s="34" t="s">
+        <v>280</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4E6BF410-1D86-4886-AF32-D2372AA65DBD}">
-  <dimension ref="A1:B9"/>
-  <sheetFormatPr defaultRowHeight="13.5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AF701674-7A60-413B-8525-5F23C4EF17DB}">
+  <dimension ref="A1:B19"/>
+  <sheetFormatPr defaultRowHeight="13"/>
   <cols>
-    <col min="1" max="1" width="51.875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="119.375" customWidth="1"/>
+    <col min="1" max="1" width="63.08984375" customWidth="1"/>
+    <col min="2" max="2" width="73.90625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:2" ht="130">
       <c r="A1" s="34" t="s">
-        <v>278</v>
-      </c>
-      <c r="B1" s="34" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2">
+        <v>400</v>
+      </c>
+      <c r="B1" s="38" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" ht="117">
       <c r="A2" s="34" t="s">
-        <v>280</v>
+        <v>406</v>
+      </c>
+      <c r="B2" s="38" t="s">
+        <v>405</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="34" t="s">
-        <v>281</v>
+        <v>401</v>
       </c>
       <c r="B3" s="34" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" ht="67.5">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
       <c r="A4" s="34" t="s">
-        <v>283</v>
-      </c>
-      <c r="B4" s="38" t="s">
-        <v>547</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" ht="78">
       <c r="A5" s="34" t="s">
-        <v>284</v>
+        <v>408</v>
+      </c>
+      <c r="B5" s="38" t="s">
+        <v>409</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="34" t="s">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" ht="108">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
       <c r="A7" s="34" t="s">
-        <v>286</v>
-      </c>
-      <c r="B7" s="38" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" ht="102" customHeight="1">
       <c r="A8" s="34" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2">
+        <v>410</v>
+      </c>
+      <c r="B8" s="38" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" ht="102" customHeight="1">
       <c r="A9" s="34" t="s">
-        <v>288</v>
-      </c>
-      <c r="B9" s="34" t="s">
-        <v>289</v>
+        <v>413</v>
+      </c>
+      <c r="B9" s="38" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" ht="102" customHeight="1">
+      <c r="A10" s="34" t="s">
+        <v>415</v>
+      </c>
+      <c r="B10" s="38" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" ht="102" customHeight="1">
+      <c r="A11" s="34"/>
+      <c r="B11" s="38" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2">
+      <c r="A12" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
+      <c r="A13" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2">
+      <c r="A14" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2">
+      <c r="A15" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2">
+      <c r="A16" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1">
+      <c r="A17" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1">
+      <c r="A18" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1">
+      <c r="A19" t="s">
+        <v>399</v>
       </c>
     </row>
   </sheetData>
@@ -9056,150 +9346,18 @@
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AF701674-7A60-413B-8525-5F23C4EF17DB}">
-  <dimension ref="A1:B19"/>
-  <sheetFormatPr defaultRowHeight="13.5"/>
-  <cols>
-    <col min="1" max="1" width="63.125" customWidth="1"/>
-    <col min="2" max="2" width="73.875" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:2" ht="121.5">
-      <c r="A1" s="34" t="s">
-        <v>409</v>
-      </c>
-      <c r="B1" s="38" t="s">
-        <v>548</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" ht="121.5">
-      <c r="A2" s="34" t="s">
-        <v>415</v>
-      </c>
-      <c r="B2" s="38" t="s">
-        <v>414</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2">
-      <c r="A3" s="34" t="s">
-        <v>410</v>
-      </c>
-      <c r="B3" s="34" t="s">
-        <v>416</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2">
-      <c r="A4" s="34" t="s">
-        <v>411</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" ht="67.5">
-      <c r="A5" s="34" t="s">
-        <v>417</v>
-      </c>
-      <c r="B5" s="38" t="s">
-        <v>418</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2">
-      <c r="A6" s="34" t="s">
-        <v>412</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2">
-      <c r="A7" s="34" t="s">
-        <v>413</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" ht="102" customHeight="1">
-      <c r="A8" s="34" t="s">
-        <v>419</v>
-      </c>
-      <c r="B8" s="38" t="s">
-        <v>420</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" ht="102" customHeight="1">
-      <c r="A9" s="34" t="s">
-        <v>422</v>
-      </c>
-      <c r="B9" s="38" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" ht="102" customHeight="1">
-      <c r="A10" s="34" t="s">
-        <v>424</v>
-      </c>
-      <c r="B10" s="38" t="s">
-        <v>423</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" ht="102" customHeight="1">
-      <c r="A11" s="34"/>
-      <c r="B11" s="38" t="s">
-        <v>425</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2">
-      <c r="A12" t="s">
-        <v>401</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2">
-      <c r="A13" t="s">
-        <v>402</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2">
-      <c r="A14" t="s">
-        <v>403</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2">
-      <c r="A15" t="s">
-        <v>404</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2">
-      <c r="A16" t="s">
-        <v>405</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1">
-      <c r="A17" t="s">
-        <v>406</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1">
-      <c r="A18" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1">
-      <c r="A19" t="s">
-        <v>408</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="1"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7016FA33-FF68-4C3D-B093-FADADA8DE1A9}">
   <dimension ref="A1:A278"/>
-  <sheetFormatPr defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultRowHeight="13"/>
   <sheetData>
     <row r="1" spans="1:1" ht="21">
       <c r="A1" s="39" t="s">
-        <v>426</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1" ht="16.5">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" ht="16">
       <c r="A3" s="40" t="s">
-        <v>427</v>
+        <v>418</v>
       </c>
     </row>
     <row r="4" spans="1:1">
@@ -9207,42 +9365,42 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" s="42" t="s">
-        <v>428</v>
+        <v>419</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" s="42" t="s">
-        <v>429</v>
+        <v>420</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" s="42" t="s">
-        <v>430</v>
+        <v>421</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" s="42" t="s">
-        <v>431</v>
+        <v>422</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" s="42" t="s">
-        <v>432</v>
+        <v>423</v>
       </c>
     </row>
     <row r="10" spans="1:1">
       <c r="A10" s="42" t="s">
-        <v>433</v>
+        <v>424</v>
       </c>
     </row>
     <row r="14" spans="1:1" ht="21">
       <c r="A14" s="39" t="s">
-        <v>434</v>
-      </c>
-    </row>
-    <row r="16" spans="1:1" ht="16.5">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1" ht="16">
       <c r="A16" s="40" t="s">
-        <v>427</v>
+        <v>418</v>
       </c>
     </row>
     <row r="17" spans="1:1">
@@ -9250,27 +9408,27 @@
     </row>
     <row r="18" spans="1:1">
       <c r="A18" s="42" t="s">
-        <v>435</v>
+        <v>426</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" s="42" t="s">
-        <v>436</v>
+        <v>427</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" s="42" t="s">
-        <v>437</v>
+        <v>428</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" s="42" t="s">
-        <v>438</v>
+        <v>429</v>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23" s="34" t="s">
-        <v>439</v>
+        <v>430</v>
       </c>
     </row>
     <row r="24" spans="1:1">
@@ -9278,27 +9436,27 @@
     </row>
     <row r="25" spans="1:1">
       <c r="A25" s="42" t="s">
-        <v>440</v>
+        <v>431</v>
       </c>
     </row>
     <row r="26" spans="1:1">
       <c r="A26" s="42" t="s">
-        <v>441</v>
+        <v>432</v>
       </c>
     </row>
     <row r="30" spans="1:1" ht="21">
       <c r="A30" s="39" t="s">
-        <v>442</v>
-      </c>
-    </row>
-    <row r="32" spans="1:1" ht="16.5">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1" ht="16">
       <c r="A32" s="40" t="s">
-        <v>427</v>
+        <v>418</v>
       </c>
     </row>
     <row r="34" spans="1:1">
       <c r="A34" s="34" t="s">
-        <v>443</v>
+        <v>434</v>
       </c>
     </row>
     <row r="35" spans="1:1">
@@ -9306,37 +9464,37 @@
     </row>
     <row r="36" spans="1:1">
       <c r="A36" s="42" t="s">
-        <v>444</v>
+        <v>435</v>
       </c>
     </row>
     <row r="37" spans="1:1">
       <c r="A37" s="42" t="s">
-        <v>445</v>
+        <v>436</v>
       </c>
     </row>
     <row r="38" spans="1:1">
       <c r="A38" s="43" t="s">
-        <v>446</v>
+        <v>437</v>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39" s="42" t="s">
-        <v>447</v>
+        <v>438</v>
       </c>
     </row>
     <row r="40" spans="1:1">
       <c r="A40" s="43" t="s">
-        <v>448</v>
+        <v>439</v>
       </c>
     </row>
     <row r="44" spans="1:1" ht="21">
       <c r="A44" s="39" t="s">
-        <v>449</v>
-      </c>
-    </row>
-    <row r="46" spans="1:1" ht="16.5">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1" ht="16">
       <c r="A46" s="40" t="s">
-        <v>427</v>
+        <v>418</v>
       </c>
     </row>
     <row r="47" spans="1:1">
@@ -9344,32 +9502,32 @@
     </row>
     <row r="48" spans="1:1">
       <c r="A48" s="42" t="s">
-        <v>450</v>
+        <v>441</v>
       </c>
     </row>
     <row r="49" spans="1:1">
       <c r="A49" s="42" t="s">
-        <v>451</v>
+        <v>442</v>
       </c>
     </row>
     <row r="50" spans="1:1">
       <c r="A50" s="42" t="s">
-        <v>452</v>
+        <v>443</v>
       </c>
     </row>
     <row r="54" spans="1:1" ht="21">
       <c r="A54" s="39" t="s">
-        <v>453</v>
-      </c>
-    </row>
-    <row r="56" spans="1:1" ht="16.5">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="56" spans="1:1" ht="16">
       <c r="A56" s="40" t="s">
-        <v>427</v>
+        <v>418</v>
       </c>
     </row>
     <row r="58" spans="1:1">
       <c r="A58" s="34" t="s">
-        <v>454</v>
+        <v>445</v>
       </c>
     </row>
     <row r="59" spans="1:1">
@@ -9377,37 +9535,37 @@
     </row>
     <row r="60" spans="1:1">
       <c r="A60" s="42" t="s">
-        <v>455</v>
+        <v>446</v>
       </c>
     </row>
     <row r="61" spans="1:1">
       <c r="A61" s="42" t="s">
-        <v>456</v>
+        <v>447</v>
       </c>
     </row>
     <row r="62" spans="1:1">
       <c r="A62" s="42" t="s">
-        <v>457</v>
+        <v>448</v>
       </c>
     </row>
     <row r="64" spans="1:1">
       <c r="A64" s="34" t="s">
-        <v>458</v>
+        <v>449</v>
       </c>
     </row>
     <row r="66" spans="1:1">
       <c r="A66" s="34" t="s">
-        <v>459</v>
+        <v>450</v>
       </c>
     </row>
     <row r="70" spans="1:1" ht="21">
       <c r="A70" s="39" t="s">
-        <v>460</v>
-      </c>
-    </row>
-    <row r="72" spans="1:1" ht="16.5">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="72" spans="1:1" ht="16">
       <c r="A72" s="40" t="s">
-        <v>427</v>
+        <v>418</v>
       </c>
     </row>
     <row r="73" spans="1:1">
@@ -9415,27 +9573,27 @@
     </row>
     <row r="74" spans="1:1">
       <c r="A74" s="42" t="s">
-        <v>461</v>
+        <v>452</v>
       </c>
     </row>
     <row r="75" spans="1:1">
       <c r="A75" s="42" t="s">
-        <v>462</v>
+        <v>453</v>
       </c>
     </row>
     <row r="76" spans="1:1">
       <c r="A76" s="42" t="s">
-        <v>463</v>
+        <v>454</v>
       </c>
     </row>
     <row r="80" spans="1:1" ht="21">
       <c r="A80" s="39" t="s">
-        <v>464</v>
-      </c>
-    </row>
-    <row r="82" spans="1:1" ht="16.5">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="82" spans="1:1" ht="16">
       <c r="A82" s="40" t="s">
-        <v>427</v>
+        <v>418</v>
       </c>
     </row>
     <row r="83" spans="1:1">
@@ -9443,37 +9601,37 @@
     </row>
     <row r="84" spans="1:1">
       <c r="A84" s="42" t="s">
-        <v>465</v>
+        <v>456</v>
       </c>
     </row>
     <row r="85" spans="1:1">
       <c r="A85" s="42" t="s">
-        <v>466</v>
+        <v>457</v>
       </c>
     </row>
     <row r="86" spans="1:1">
       <c r="A86" s="42" t="s">
-        <v>467</v>
+        <v>458</v>
       </c>
     </row>
     <row r="87" spans="1:1">
       <c r="A87" s="42" t="s">
-        <v>468</v>
+        <v>459</v>
       </c>
     </row>
     <row r="88" spans="1:1">
       <c r="A88" s="42" t="s">
-        <v>469</v>
+        <v>460</v>
       </c>
     </row>
     <row r="92" spans="1:1" ht="21">
       <c r="A92" s="39" t="s">
-        <v>470</v>
-      </c>
-    </row>
-    <row r="94" spans="1:1" ht="16.5">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="94" spans="1:1" ht="16">
       <c r="A94" s="40" t="s">
-        <v>427</v>
+        <v>418</v>
       </c>
     </row>
     <row r="95" spans="1:1">
@@ -9481,32 +9639,32 @@
     </row>
     <row r="96" spans="1:1">
       <c r="A96" s="42" t="s">
-        <v>471</v>
+        <v>462</v>
       </c>
     </row>
     <row r="97" spans="1:1">
       <c r="A97" s="42" t="s">
-        <v>472</v>
+        <v>463</v>
       </c>
     </row>
     <row r="98" spans="1:1">
       <c r="A98" s="42" t="s">
-        <v>473</v>
+        <v>464</v>
       </c>
     </row>
     <row r="99" spans="1:1">
       <c r="A99" s="42" t="s">
-        <v>474</v>
+        <v>465</v>
       </c>
     </row>
     <row r="103" spans="1:1" ht="21">
       <c r="A103" s="39" t="s">
-        <v>475</v>
-      </c>
-    </row>
-    <row r="105" spans="1:1" ht="16.5">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="105" spans="1:1" ht="16">
       <c r="A105" s="40" t="s">
-        <v>427</v>
+        <v>418</v>
       </c>
     </row>
     <row r="106" spans="1:1">
@@ -9514,32 +9672,32 @@
     </row>
     <row r="107" spans="1:1">
       <c r="A107" s="42" t="s">
-        <v>476</v>
+        <v>467</v>
       </c>
     </row>
     <row r="108" spans="1:1">
       <c r="A108" s="42" t="s">
-        <v>477</v>
+        <v>468</v>
       </c>
     </row>
     <row r="109" spans="1:1">
       <c r="A109" s="42" t="s">
-        <v>478</v>
+        <v>469</v>
       </c>
     </row>
     <row r="110" spans="1:1">
       <c r="A110" s="42" t="s">
-        <v>479</v>
+        <v>470</v>
       </c>
     </row>
     <row r="114" spans="1:1" ht="21">
       <c r="A114" s="39" t="s">
-        <v>480</v>
-      </c>
-    </row>
-    <row r="116" spans="1:1" ht="16.5">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="116" spans="1:1" ht="16">
       <c r="A116" s="40" t="s">
-        <v>427</v>
+        <v>418</v>
       </c>
     </row>
     <row r="117" spans="1:1">
@@ -9547,22 +9705,22 @@
     </row>
     <row r="118" spans="1:1">
       <c r="A118" s="42" t="s">
-        <v>481</v>
+        <v>472</v>
       </c>
     </row>
     <row r="119" spans="1:1">
       <c r="A119" s="42" t="s">
-        <v>482</v>
+        <v>473</v>
       </c>
     </row>
     <row r="123" spans="1:1" ht="21">
       <c r="A123" s="39" t="s">
-        <v>483</v>
-      </c>
-    </row>
-    <row r="125" spans="1:1" ht="16.5">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="125" spans="1:1" ht="16">
       <c r="A125" s="40" t="s">
-        <v>427</v>
+        <v>418</v>
       </c>
     </row>
     <row r="126" spans="1:1">
@@ -9570,22 +9728,22 @@
     </row>
     <row r="127" spans="1:1">
       <c r="A127" s="42" t="s">
-        <v>484</v>
+        <v>475</v>
       </c>
     </row>
     <row r="128" spans="1:1">
       <c r="A128" s="42" t="s">
-        <v>485</v>
+        <v>476</v>
       </c>
     </row>
     <row r="132" spans="1:1" ht="21">
       <c r="A132" s="39" t="s">
-        <v>486</v>
-      </c>
-    </row>
-    <row r="134" spans="1:1" ht="16.5">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="134" spans="1:1" ht="16">
       <c r="A134" s="40" t="s">
-        <v>427</v>
+        <v>418</v>
       </c>
     </row>
     <row r="135" spans="1:1">
@@ -9593,27 +9751,27 @@
     </row>
     <row r="136" spans="1:1">
       <c r="A136" s="42" t="s">
-        <v>487</v>
+        <v>478</v>
       </c>
     </row>
     <row r="137" spans="1:1">
       <c r="A137" s="42" t="s">
-        <v>488</v>
+        <v>479</v>
       </c>
     </row>
     <row r="138" spans="1:1">
       <c r="A138" s="42" t="s">
-        <v>489</v>
+        <v>480</v>
       </c>
     </row>
     <row r="142" spans="1:1" ht="21">
       <c r="A142" s="39" t="s">
-        <v>490</v>
-      </c>
-    </row>
-    <row r="144" spans="1:1" ht="16.5">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="144" spans="1:1" ht="16">
       <c r="A144" s="40" t="s">
-        <v>427</v>
+        <v>418</v>
       </c>
     </row>
     <row r="145" spans="1:1">
@@ -9621,27 +9779,27 @@
     </row>
     <row r="146" spans="1:1">
       <c r="A146" s="42" t="s">
-        <v>491</v>
+        <v>482</v>
       </c>
     </row>
     <row r="147" spans="1:1">
       <c r="A147" s="42" t="s">
-        <v>492</v>
+        <v>483</v>
       </c>
     </row>
     <row r="148" spans="1:1">
       <c r="A148" s="42" t="s">
-        <v>493</v>
+        <v>484</v>
       </c>
     </row>
     <row r="152" spans="1:1" ht="21">
       <c r="A152" s="39" t="s">
-        <v>494</v>
-      </c>
-    </row>
-    <row r="154" spans="1:1" ht="16.5">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="154" spans="1:1" ht="16">
       <c r="A154" s="40" t="s">
-        <v>427</v>
+        <v>418</v>
       </c>
     </row>
     <row r="155" spans="1:1">
@@ -9649,27 +9807,27 @@
     </row>
     <row r="156" spans="1:1">
       <c r="A156" s="42" t="s">
-        <v>495</v>
+        <v>486</v>
       </c>
     </row>
     <row r="157" spans="1:1">
       <c r="A157" s="42" t="s">
-        <v>496</v>
+        <v>487</v>
       </c>
     </row>
     <row r="158" spans="1:1">
       <c r="A158" s="42" t="s">
-        <v>497</v>
+        <v>488</v>
       </c>
     </row>
     <row r="162" spans="1:1" ht="21">
       <c r="A162" s="39" t="s">
-        <v>498</v>
-      </c>
-    </row>
-    <row r="164" spans="1:1" ht="16.5">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="164" spans="1:1" ht="16">
       <c r="A164" s="40" t="s">
-        <v>427</v>
+        <v>418</v>
       </c>
     </row>
     <row r="165" spans="1:1">
@@ -9677,37 +9835,37 @@
     </row>
     <row r="166" spans="1:1">
       <c r="A166" s="42" t="s">
-        <v>499</v>
+        <v>490</v>
       </c>
     </row>
     <row r="167" spans="1:1">
       <c r="A167" s="42" t="s">
-        <v>500</v>
+        <v>491</v>
       </c>
     </row>
     <row r="168" spans="1:1">
       <c r="A168" s="42" t="s">
-        <v>501</v>
-      </c>
-    </row>
-    <row r="172" spans="1:1" ht="28.5">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="172" spans="1:1" ht="28">
       <c r="A172" s="44" t="s">
-        <v>502</v>
+        <v>493</v>
       </c>
     </row>
     <row r="174" spans="1:1" ht="21">
       <c r="A174" s="39" t="s">
-        <v>503</v>
-      </c>
-    </row>
-    <row r="176" spans="1:1" ht="16.5">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="176" spans="1:1" ht="16">
       <c r="A176" s="40" t="s">
-        <v>427</v>
+        <v>418</v>
       </c>
     </row>
     <row r="178" spans="1:1">
       <c r="A178" s="34" t="s">
-        <v>504</v>
+        <v>495</v>
       </c>
     </row>
     <row r="179" spans="1:1">
@@ -9715,12 +9873,12 @@
     </row>
     <row r="180" spans="1:1">
       <c r="A180" s="42" t="s">
-        <v>505</v>
+        <v>496</v>
       </c>
     </row>
     <row r="182" spans="1:1">
       <c r="A182" s="34" t="s">
-        <v>506</v>
+        <v>497</v>
       </c>
     </row>
     <row r="183" spans="1:1">
@@ -9728,32 +9886,32 @@
     </row>
     <row r="184" spans="1:1">
       <c r="A184" s="42" t="s">
-        <v>507</v>
+        <v>498</v>
       </c>
     </row>
     <row r="185" spans="1:1">
       <c r="A185" s="42" t="s">
-        <v>508</v>
+        <v>499</v>
       </c>
     </row>
     <row r="186" spans="1:1">
       <c r="A186" s="42" t="s">
-        <v>509</v>
+        <v>500</v>
       </c>
     </row>
     <row r="187" spans="1:1">
       <c r="A187" s="42" t="s">
-        <v>510</v>
+        <v>501</v>
       </c>
     </row>
     <row r="191" spans="1:1" ht="21">
       <c r="A191" s="39" t="s">
-        <v>511</v>
-      </c>
-    </row>
-    <row r="193" spans="1:1" ht="16.5">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="193" spans="1:1" ht="16">
       <c r="A193" s="40" t="s">
-        <v>427</v>
+        <v>418</v>
       </c>
     </row>
     <row r="194" spans="1:1">
@@ -9761,27 +9919,27 @@
     </row>
     <row r="195" spans="1:1">
       <c r="A195" s="42" t="s">
-        <v>512</v>
+        <v>503</v>
       </c>
     </row>
     <row r="196" spans="1:1">
       <c r="A196" s="42" t="s">
-        <v>513</v>
+        <v>504</v>
       </c>
     </row>
     <row r="197" spans="1:1">
       <c r="A197" s="42" t="s">
-        <v>514</v>
+        <v>505</v>
       </c>
     </row>
     <row r="201" spans="1:1" ht="21">
       <c r="A201" s="39" t="s">
-        <v>515</v>
-      </c>
-    </row>
-    <row r="203" spans="1:1" ht="16.5">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="203" spans="1:1" ht="16">
       <c r="A203" s="40" t="s">
-        <v>427</v>
+        <v>418</v>
       </c>
     </row>
     <row r="204" spans="1:1">
@@ -9789,27 +9947,27 @@
     </row>
     <row r="205" spans="1:1">
       <c r="A205" s="42" t="s">
-        <v>516</v>
+        <v>507</v>
       </c>
     </row>
     <row r="206" spans="1:1">
       <c r="A206" s="42" t="s">
-        <v>517</v>
+        <v>508</v>
       </c>
     </row>
     <row r="207" spans="1:1">
       <c r="A207" s="42" t="s">
-        <v>518</v>
+        <v>509</v>
       </c>
     </row>
     <row r="211" spans="1:1" ht="21">
       <c r="A211" s="39" t="s">
-        <v>519</v>
-      </c>
-    </row>
-    <row r="213" spans="1:1" ht="16.5">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="213" spans="1:1" ht="16">
       <c r="A213" s="40" t="s">
-        <v>427</v>
+        <v>418</v>
       </c>
     </row>
     <row r="214" spans="1:1">
@@ -9817,27 +9975,27 @@
     </row>
     <row r="215" spans="1:1">
       <c r="A215" s="42" t="s">
-        <v>551</v>
+        <v>542</v>
       </c>
     </row>
     <row r="216" spans="1:1">
       <c r="A216" s="42" t="s">
-        <v>520</v>
+        <v>511</v>
       </c>
     </row>
     <row r="217" spans="1:1">
       <c r="A217" s="42" t="s">
-        <v>521</v>
+        <v>512</v>
       </c>
     </row>
     <row r="221" spans="1:1" ht="21">
       <c r="A221" s="39" t="s">
-        <v>522</v>
-      </c>
-    </row>
-    <row r="223" spans="1:1" ht="16.5">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="223" spans="1:1" ht="16">
       <c r="A223" s="40" t="s">
-        <v>427</v>
+        <v>418</v>
       </c>
     </row>
     <row r="224" spans="1:1">
@@ -9845,27 +10003,27 @@
     </row>
     <row r="225" spans="1:1">
       <c r="A225" s="45" t="s">
-        <v>523</v>
+        <v>514</v>
       </c>
     </row>
     <row r="226" spans="1:1">
       <c r="A226" s="45" t="s">
-        <v>524</v>
+        <v>515</v>
       </c>
     </row>
     <row r="227" spans="1:1">
       <c r="A227" s="45" t="s">
-        <v>525</v>
+        <v>516</v>
       </c>
     </row>
     <row r="231" spans="1:1" ht="21">
       <c r="A231" s="39" t="s">
-        <v>526</v>
-      </c>
-    </row>
-    <row r="233" spans="1:1" ht="16.5">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="233" spans="1:1" ht="16">
       <c r="A233" s="40" t="s">
-        <v>427</v>
+        <v>418</v>
       </c>
     </row>
     <row r="234" spans="1:1">
@@ -9873,22 +10031,22 @@
     </row>
     <row r="235" spans="1:1">
       <c r="A235" s="42" t="s">
-        <v>527</v>
+        <v>518</v>
       </c>
     </row>
     <row r="236" spans="1:1">
       <c r="A236" s="42" t="s">
-        <v>528</v>
+        <v>519</v>
       </c>
     </row>
     <row r="240" spans="1:1" ht="21">
       <c r="A240" s="39" t="s">
-        <v>529</v>
-      </c>
-    </row>
-    <row r="242" spans="1:1" ht="16.5">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="242" spans="1:1" ht="16">
       <c r="A242" s="40" t="s">
-        <v>427</v>
+        <v>418</v>
       </c>
     </row>
     <row r="243" spans="1:1">
@@ -9896,32 +10054,32 @@
     </row>
     <row r="244" spans="1:1">
       <c r="A244" s="42" t="s">
-        <v>530</v>
+        <v>521</v>
       </c>
     </row>
     <row r="245" spans="1:1">
       <c r="A245" s="42" t="s">
-        <v>531</v>
+        <v>522</v>
       </c>
     </row>
     <row r="246" spans="1:1">
       <c r="A246" s="42" t="s">
-        <v>532</v>
+        <v>523</v>
       </c>
     </row>
     <row r="247" spans="1:1">
       <c r="A247" s="42" t="s">
-        <v>533</v>
+        <v>524</v>
       </c>
     </row>
     <row r="251" spans="1:1" ht="21">
       <c r="A251" s="39" t="s">
-        <v>534</v>
-      </c>
-    </row>
-    <row r="253" spans="1:1" ht="16.5">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="253" spans="1:1" ht="16">
       <c r="A253" s="40" t="s">
-        <v>427</v>
+        <v>418</v>
       </c>
     </row>
     <row r="254" spans="1:1">
@@ -9929,32 +10087,32 @@
     </row>
     <row r="255" spans="1:1">
       <c r="A255" s="42" t="s">
-        <v>535</v>
+        <v>526</v>
       </c>
     </row>
     <row r="256" spans="1:1">
       <c r="A256" s="42" t="s">
-        <v>536</v>
+        <v>527</v>
       </c>
     </row>
     <row r="257" spans="1:1">
       <c r="A257" s="42" t="s">
-        <v>537</v>
+        <v>528</v>
       </c>
     </row>
     <row r="258" spans="1:1">
       <c r="A258" s="42" t="s">
-        <v>538</v>
+        <v>529</v>
       </c>
     </row>
     <row r="262" spans="1:1" ht="21">
       <c r="A262" s="39" t="s">
-        <v>539</v>
-      </c>
-    </row>
-    <row r="264" spans="1:1" ht="16.5">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="264" spans="1:1" ht="16">
       <c r="A264" s="40" t="s">
-        <v>427</v>
+        <v>418</v>
       </c>
     </row>
     <row r="265" spans="1:1">
@@ -9962,27 +10120,27 @@
     </row>
     <row r="266" spans="1:1">
       <c r="A266" s="42" t="s">
-        <v>540</v>
+        <v>531</v>
       </c>
     </row>
     <row r="267" spans="1:1">
       <c r="A267" s="42" t="s">
-        <v>541</v>
+        <v>532</v>
       </c>
     </row>
     <row r="268" spans="1:1">
       <c r="A268" s="42" t="s">
-        <v>542</v>
+        <v>533</v>
       </c>
     </row>
     <row r="272" spans="1:1" ht="21">
       <c r="A272" s="39" t="s">
-        <v>543</v>
-      </c>
-    </row>
-    <row r="274" spans="1:1" ht="16.5">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="274" spans="1:1" ht="16">
       <c r="A274" s="40" t="s">
-        <v>427</v>
+        <v>418</v>
       </c>
     </row>
     <row r="275" spans="1:1">
@@ -9990,17 +10148,17 @@
     </row>
     <row r="276" spans="1:1">
       <c r="A276" s="45" t="s">
-        <v>544</v>
+        <v>535</v>
       </c>
     </row>
     <row r="277" spans="1:1">
       <c r="A277" s="45" t="s">
-        <v>545</v>
+        <v>536</v>
       </c>
     </row>
     <row r="278" spans="1:1">
       <c r="A278" s="45" t="s">
-        <v>546</v>
+        <v>537</v>
       </c>
     </row>
   </sheetData>
@@ -10011,37 +10169,69 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{18E79AA2-39D8-469F-B011-2D82F20D6FA2}">
-  <dimension ref="A2:B5"/>
-  <sheetFormatPr defaultRowHeight="13.5"/>
+  <dimension ref="A2:B9"/>
+  <sheetFormatPr defaultRowHeight="13"/>
   <cols>
     <col min="1" max="1" width="43" customWidth="1"/>
-    <col min="2" max="2" width="68.625" customWidth="1"/>
+    <col min="2" max="2" width="68.6328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:2" ht="54">
+    <row r="2" spans="1:2" ht="65">
       <c r="A2" s="34" t="s">
-        <v>557</v>
+        <v>548</v>
       </c>
       <c r="B2" s="38" t="s">
-        <v>556</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" ht="67.5">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="65">
       <c r="A3" s="34" t="s">
-        <v>558</v>
+        <v>549</v>
       </c>
       <c r="B3" s="38" t="s">
-        <v>559</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" ht="94.5">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="104">
       <c r="B4" s="38" t="s">
-        <v>560</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" ht="54">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" ht="65">
       <c r="B5" s="38" t="s">
-        <v>561</v>
+        <v>552</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" ht="208">
+      <c r="A6" s="34" t="s">
+        <v>755</v>
+      </c>
+      <c r="B6" s="38" t="s">
+        <v>754</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" ht="78">
+      <c r="A7" s="34" t="s">
+        <v>757</v>
+      </c>
+      <c r="B7" s="38" t="s">
+        <v>756</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" ht="39">
+      <c r="A8" s="34" t="s">
+        <v>758</v>
+      </c>
+      <c r="B8" s="38" t="s">
+        <v>759</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" ht="65">
+      <c r="A9" s="34" t="s">
+        <v>760</v>
+      </c>
+      <c r="B9" s="38" t="s">
+        <v>761</v>
       </c>
     </row>
   </sheetData>
@@ -10053,31 +10243,31 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2D50A871-9D78-407F-ADF0-E93D7C884AF1}">
   <dimension ref="B2:B576"/>
-  <sheetFormatPr defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultRowHeight="13"/>
   <sheetData>
-    <row r="2" spans="2:2" ht="37.5">
+    <row r="2" spans="2:2" ht="35">
       <c r="B2" s="47" t="s">
-        <v>562</v>
-      </c>
-    </row>
-    <row r="4" spans="2:2" ht="26.25">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="4" spans="2:2" ht="26">
       <c r="B4" s="48" t="s">
-        <v>563</v>
-      </c>
-    </row>
-    <row r="6" spans="2:2" ht="21">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="6" spans="2:2" ht="20.5">
       <c r="B6" s="49" t="s">
-        <v>564</v>
+        <v>555</v>
       </c>
     </row>
     <row r="8" spans="2:2" ht="16.5">
       <c r="B8" s="46" t="s">
-        <v>565</v>
-      </c>
-    </row>
-    <row r="10" spans="2:2" ht="21">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="10" spans="2:2" ht="20.5">
       <c r="B10" s="49" t="s">
-        <v>566</v>
+        <v>557</v>
       </c>
     </row>
     <row r="11" spans="2:2">
@@ -10085,37 +10275,37 @@
     </row>
     <row r="12" spans="2:2" ht="16.5">
       <c r="B12" s="50" t="s">
-        <v>567</v>
+        <v>558</v>
       </c>
     </row>
     <row r="13" spans="2:2" ht="16.5">
       <c r="B13" s="50" t="s">
-        <v>568</v>
+        <v>559</v>
       </c>
     </row>
     <row r="14" spans="2:2" ht="16.5">
       <c r="B14" s="50" t="s">
-        <v>569</v>
+        <v>560</v>
       </c>
     </row>
     <row r="15" spans="2:2" ht="16.5">
       <c r="B15" s="50" t="s">
-        <v>570</v>
-      </c>
-    </row>
-    <row r="19" spans="2:2" ht="26.25">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="19" spans="2:2" ht="26">
       <c r="B19" s="48" t="s">
-        <v>571</v>
+        <v>562</v>
       </c>
     </row>
     <row r="21" spans="2:2" ht="16.5">
       <c r="B21" s="46" t="s">
-        <v>572</v>
-      </c>
-    </row>
-    <row r="23" spans="2:2" ht="21">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="23" spans="2:2" ht="20.5">
       <c r="B23" s="49" t="s">
-        <v>566</v>
+        <v>557</v>
       </c>
     </row>
     <row r="24" spans="2:2">
@@ -10123,52 +10313,52 @@
     </row>
     <row r="25" spans="2:2" ht="16.5">
       <c r="B25" s="50" t="s">
-        <v>573</v>
+        <v>564</v>
       </c>
     </row>
     <row r="26" spans="2:2" ht="16.5">
       <c r="B26" s="50" t="s">
-        <v>574</v>
+        <v>565</v>
       </c>
     </row>
     <row r="27" spans="2:2" ht="16.5">
       <c r="B27" s="50" t="s">
-        <v>575</v>
+        <v>566</v>
       </c>
     </row>
     <row r="28" spans="2:2" ht="16.5">
       <c r="B28" s="50" t="s">
-        <v>576</v>
+        <v>567</v>
       </c>
     </row>
     <row r="29" spans="2:2" ht="16.5">
       <c r="B29" s="50" t="s">
-        <v>577</v>
+        <v>568</v>
       </c>
     </row>
     <row r="30" spans="2:2" ht="16.5">
       <c r="B30" s="50" t="s">
-        <v>578</v>
+        <v>569</v>
       </c>
     </row>
     <row r="31" spans="2:2" ht="16.5">
       <c r="B31" s="50" t="s">
-        <v>579</v>
-      </c>
-    </row>
-    <row r="35" spans="2:2" ht="26.25">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="35" spans="2:2" ht="26">
       <c r="B35" s="48" t="s">
-        <v>580</v>
+        <v>571</v>
       </c>
     </row>
     <row r="37" spans="2:2" ht="16.5">
       <c r="B37" s="46" t="s">
-        <v>581</v>
-      </c>
-    </row>
-    <row r="39" spans="2:2" ht="21">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="39" spans="2:2" ht="20.5">
       <c r="B39" s="49" t="s">
-        <v>566</v>
+        <v>557</v>
       </c>
     </row>
     <row r="40" spans="2:2">
@@ -10176,32 +10366,32 @@
     </row>
     <row r="41" spans="2:2" ht="16.5">
       <c r="B41" s="50" t="s">
-        <v>582</v>
+        <v>573</v>
       </c>
     </row>
     <row r="42" spans="2:2" ht="16.5">
       <c r="B42" s="50" t="s">
-        <v>583</v>
+        <v>574</v>
       </c>
     </row>
     <row r="43" spans="2:2" ht="16.5">
       <c r="B43" s="50" t="s">
-        <v>584</v>
-      </c>
-    </row>
-    <row r="47" spans="2:2" ht="26.25">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="47" spans="2:2" ht="26">
       <c r="B47" s="48" t="s">
-        <v>585</v>
+        <v>576</v>
       </c>
     </row>
     <row r="49" spans="2:2" ht="16.5">
       <c r="B49" s="46" t="s">
-        <v>586</v>
-      </c>
-    </row>
-    <row r="51" spans="2:2" ht="21">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="51" spans="2:2" ht="20.5">
       <c r="B51" s="49" t="s">
-        <v>566</v>
+        <v>557</v>
       </c>
     </row>
     <row r="52" spans="2:2">
@@ -10209,37 +10399,37 @@
     </row>
     <row r="53" spans="2:2" ht="16.5">
       <c r="B53" s="50" t="s">
-        <v>587</v>
+        <v>578</v>
       </c>
     </row>
     <row r="54" spans="2:2" ht="16.5">
       <c r="B54" s="50" t="s">
-        <v>588</v>
+        <v>579</v>
       </c>
     </row>
     <row r="55" spans="2:2" ht="16.5">
       <c r="B55" s="50" t="s">
-        <v>589</v>
+        <v>580</v>
       </c>
     </row>
     <row r="56" spans="2:2" ht="16.5">
       <c r="B56" s="50" t="s">
-        <v>590</v>
-      </c>
-    </row>
-    <row r="60" spans="2:2" ht="26.25">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="60" spans="2:2" ht="26">
       <c r="B60" s="48" t="s">
-        <v>591</v>
+        <v>582</v>
       </c>
     </row>
     <row r="62" spans="2:2" ht="16.5">
       <c r="B62" s="46" t="s">
-        <v>592</v>
-      </c>
-    </row>
-    <row r="64" spans="2:2" ht="21">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="64" spans="2:2" ht="20.5">
       <c r="B64" s="49" t="s">
-        <v>566</v>
+        <v>557</v>
       </c>
     </row>
     <row r="65" spans="2:2">
@@ -10247,32 +10437,32 @@
     </row>
     <row r="66" spans="2:2" ht="16.5">
       <c r="B66" s="50" t="s">
-        <v>593</v>
+        <v>584</v>
       </c>
     </row>
     <row r="67" spans="2:2" ht="16.5">
       <c r="B67" s="50" t="s">
-        <v>594</v>
+        <v>585</v>
       </c>
     </row>
     <row r="68" spans="2:2" ht="16.5">
       <c r="B68" s="50" t="s">
-        <v>595</v>
-      </c>
-    </row>
-    <row r="72" spans="2:2" ht="26.25">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="72" spans="2:2" ht="26">
       <c r="B72" s="48" t="s">
-        <v>596</v>
+        <v>587</v>
       </c>
     </row>
     <row r="74" spans="2:2" ht="16.5">
       <c r="B74" s="46" t="s">
-        <v>597</v>
-      </c>
-    </row>
-    <row r="76" spans="2:2" ht="21">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="76" spans="2:2" ht="20.5">
       <c r="B76" s="49" t="s">
-        <v>566</v>
+        <v>557</v>
       </c>
     </row>
     <row r="77" spans="2:2">
@@ -10280,32 +10470,32 @@
     </row>
     <row r="78" spans="2:2" ht="16.5">
       <c r="B78" s="50" t="s">
-        <v>598</v>
+        <v>589</v>
       </c>
     </row>
     <row r="79" spans="2:2" ht="16.5">
       <c r="B79" s="50" t="s">
-        <v>599</v>
+        <v>590</v>
       </c>
     </row>
     <row r="80" spans="2:2" ht="16.5">
       <c r="B80" s="50" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="84" spans="2:2" ht="26.25">
+        <v>591</v>
+      </c>
+    </row>
+    <row r="84" spans="2:2" ht="26">
       <c r="B84" s="48" t="s">
-        <v>601</v>
+        <v>592</v>
       </c>
     </row>
     <row r="86" spans="2:2" ht="16.5">
       <c r="B86" s="46" t="s">
-        <v>602</v>
-      </c>
-    </row>
-    <row r="88" spans="2:2" ht="21">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="88" spans="2:2" ht="20.5">
       <c r="B88" s="49" t="s">
-        <v>566</v>
+        <v>557</v>
       </c>
     </row>
     <row r="89" spans="2:2">
@@ -10313,32 +10503,32 @@
     </row>
     <row r="90" spans="2:2" ht="16.5">
       <c r="B90" s="50" t="s">
-        <v>603</v>
+        <v>594</v>
       </c>
     </row>
     <row r="91" spans="2:2" ht="16.5">
       <c r="B91" s="50" t="s">
-        <v>604</v>
+        <v>595</v>
       </c>
     </row>
     <row r="92" spans="2:2" ht="16.5">
       <c r="B92" s="50" t="s">
-        <v>605</v>
-      </c>
-    </row>
-    <row r="96" spans="2:2" ht="26.25">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="96" spans="2:2" ht="26">
       <c r="B96" s="48" t="s">
-        <v>606</v>
+        <v>597</v>
       </c>
     </row>
     <row r="98" spans="2:2" ht="16.5">
       <c r="B98" s="46" t="s">
-        <v>607</v>
-      </c>
-    </row>
-    <row r="100" spans="2:2" ht="21">
+        <v>598</v>
+      </c>
+    </row>
+    <row r="100" spans="2:2" ht="20.5">
       <c r="B100" s="49" t="s">
-        <v>566</v>
+        <v>557</v>
       </c>
     </row>
     <row r="101" spans="2:2">
@@ -10346,32 +10536,32 @@
     </row>
     <row r="102" spans="2:2" ht="16.5">
       <c r="B102" s="50" t="s">
-        <v>608</v>
+        <v>599</v>
       </c>
     </row>
     <row r="103" spans="2:2" ht="16.5">
       <c r="B103" s="50" t="s">
-        <v>609</v>
+        <v>600</v>
       </c>
     </row>
     <row r="104" spans="2:2" ht="16.5">
       <c r="B104" s="50" t="s">
-        <v>610</v>
-      </c>
-    </row>
-    <row r="108" spans="2:2" ht="26.25">
+        <v>601</v>
+      </c>
+    </row>
+    <row r="108" spans="2:2" ht="26">
       <c r="B108" s="48" t="s">
-        <v>611</v>
+        <v>602</v>
       </c>
     </row>
     <row r="110" spans="2:2" ht="16.5">
       <c r="B110" s="46" t="s">
-        <v>612</v>
-      </c>
-    </row>
-    <row r="112" spans="2:2" ht="21">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="112" spans="2:2" ht="20.5">
       <c r="B112" s="49" t="s">
-        <v>566</v>
+        <v>557</v>
       </c>
     </row>
     <row r="113" spans="2:2">
@@ -10379,27 +10569,27 @@
     </row>
     <row r="114" spans="2:2" ht="16.5">
       <c r="B114" s="50" t="s">
-        <v>613</v>
+        <v>604</v>
       </c>
     </row>
     <row r="115" spans="2:2" ht="16.5">
       <c r="B115" s="50" t="s">
-        <v>614</v>
-      </c>
-    </row>
-    <row r="119" spans="2:2" ht="26.25">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="119" spans="2:2" ht="26">
       <c r="B119" s="48" t="s">
-        <v>615</v>
+        <v>606</v>
       </c>
     </row>
     <row r="121" spans="2:2" ht="16.5">
       <c r="B121" s="46" t="s">
-        <v>616</v>
-      </c>
-    </row>
-    <row r="123" spans="2:2" ht="21">
+        <v>607</v>
+      </c>
+    </row>
+    <row r="123" spans="2:2" ht="20.5">
       <c r="B123" s="49" t="s">
-        <v>566</v>
+        <v>557</v>
       </c>
     </row>
     <row r="124" spans="2:2">
@@ -10407,32 +10597,32 @@
     </row>
     <row r="125" spans="2:2" ht="16.5">
       <c r="B125" s="50" t="s">
-        <v>617</v>
+        <v>608</v>
       </c>
     </row>
     <row r="126" spans="2:2" ht="16.5">
       <c r="B126" s="50" t="s">
-        <v>618</v>
+        <v>609</v>
       </c>
     </row>
     <row r="127" spans="2:2" ht="16.5">
       <c r="B127" s="50" t="s">
-        <v>619</v>
-      </c>
-    </row>
-    <row r="131" spans="2:2" ht="26.25">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="131" spans="2:2" ht="26">
       <c r="B131" s="48" t="s">
-        <v>620</v>
+        <v>611</v>
       </c>
     </row>
     <row r="133" spans="2:2" ht="16.5">
       <c r="B133" s="46" t="s">
-        <v>621</v>
-      </c>
-    </row>
-    <row r="135" spans="2:2" ht="21">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="135" spans="2:2" ht="20.5">
       <c r="B135" s="49" t="s">
-        <v>566</v>
+        <v>557</v>
       </c>
     </row>
     <row r="136" spans="2:2">
@@ -10440,27 +10630,27 @@
     </row>
     <row r="137" spans="2:2" ht="16.5">
       <c r="B137" s="50" t="s">
-        <v>622</v>
+        <v>613</v>
       </c>
     </row>
     <row r="138" spans="2:2" ht="16.5">
       <c r="B138" s="50" t="s">
-        <v>623</v>
-      </c>
-    </row>
-    <row r="142" spans="2:2" ht="26.25">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="142" spans="2:2" ht="26">
       <c r="B142" s="48" t="s">
-        <v>624</v>
+        <v>615</v>
       </c>
     </row>
     <row r="144" spans="2:2" ht="16.5">
       <c r="B144" s="46" t="s">
-        <v>625</v>
-      </c>
-    </row>
-    <row r="146" spans="2:2" ht="21">
+        <v>616</v>
+      </c>
+    </row>
+    <row r="146" spans="2:2" ht="20.5">
       <c r="B146" s="49" t="s">
-        <v>566</v>
+        <v>557</v>
       </c>
     </row>
     <row r="147" spans="2:2">
@@ -10468,32 +10658,32 @@
     </row>
     <row r="148" spans="2:2" ht="16.5">
       <c r="B148" s="50" t="s">
-        <v>626</v>
+        <v>617</v>
       </c>
     </row>
     <row r="149" spans="2:2" ht="16.5">
       <c r="B149" s="50" t="s">
-        <v>627</v>
+        <v>618</v>
       </c>
     </row>
     <row r="150" spans="2:2" ht="16.5">
       <c r="B150" s="50" t="s">
-        <v>628</v>
-      </c>
-    </row>
-    <row r="154" spans="2:2" ht="26.25">
+        <v>619</v>
+      </c>
+    </row>
+    <row r="154" spans="2:2" ht="26">
       <c r="B154" s="48" t="s">
-        <v>629</v>
+        <v>620</v>
       </c>
     </row>
     <row r="156" spans="2:2" ht="16.5">
       <c r="B156" s="46" t="s">
-        <v>630</v>
-      </c>
-    </row>
-    <row r="158" spans="2:2" ht="21">
+        <v>621</v>
+      </c>
+    </row>
+    <row r="158" spans="2:2" ht="20.5">
       <c r="B158" s="49" t="s">
-        <v>566</v>
+        <v>557</v>
       </c>
     </row>
     <row r="159" spans="2:2">
@@ -10501,130 +10691,130 @@
     </row>
     <row r="160" spans="2:2" ht="16.5">
       <c r="B160" s="50" t="s">
-        <v>631</v>
+        <v>622</v>
       </c>
     </row>
     <row r="161" spans="2:2" ht="16.5">
       <c r="B161" s="50" t="s">
-        <v>632</v>
+        <v>623</v>
       </c>
     </row>
     <row r="162" spans="2:2" ht="16.5">
       <c r="B162" s="50" t="s">
-        <v>633</v>
-      </c>
-    </row>
-    <row r="166" spans="2:2" ht="37.5">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="166" spans="2:2" ht="35">
       <c r="B166" s="47" t="s">
-        <v>634</v>
-      </c>
-    </row>
-    <row r="168" spans="2:2" ht="21">
+        <v>625</v>
+      </c>
+    </row>
+    <row r="168" spans="2:2" ht="20.5">
       <c r="B168" s="49">
         <v>1</v>
       </c>
     </row>
     <row r="170" spans="2:2" ht="16.5">
       <c r="B170" s="46" t="s">
-        <v>635</v>
-      </c>
-    </row>
-    <row r="172" spans="2:2" ht="21">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="172" spans="2:2" ht="20.5">
       <c r="B172" s="49">
         <v>2</v>
       </c>
     </row>
     <row r="174" spans="2:2" ht="16.5">
       <c r="B174" s="46" t="s">
-        <v>636</v>
-      </c>
-    </row>
-    <row r="176" spans="2:2" ht="21">
+        <v>627</v>
+      </c>
+    </row>
+    <row r="176" spans="2:2" ht="20.5">
       <c r="B176" s="49">
         <v>3</v>
       </c>
     </row>
     <row r="178" spans="2:2" ht="16.5">
       <c r="B178" s="46" t="s">
-        <v>637</v>
-      </c>
-    </row>
-    <row r="180" spans="2:2" ht="21">
+        <v>628</v>
+      </c>
+    </row>
+    <row r="180" spans="2:2" ht="20.5">
       <c r="B180" s="49">
         <v>4</v>
       </c>
     </row>
     <row r="182" spans="2:2" ht="16.5">
       <c r="B182" s="46" t="s">
-        <v>638</v>
-      </c>
-    </row>
-    <row r="184" spans="2:2" ht="21">
+        <v>629</v>
+      </c>
+    </row>
+    <row r="184" spans="2:2" ht="20.5">
       <c r="B184" s="49">
         <v>5</v>
       </c>
     </row>
     <row r="186" spans="2:2" ht="16.5">
       <c r="B186" s="46" t="s">
-        <v>639</v>
-      </c>
-    </row>
-    <row r="188" spans="2:2" ht="21">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="188" spans="2:2" ht="20.5">
       <c r="B188" s="49">
         <v>6</v>
       </c>
     </row>
     <row r="190" spans="2:2" ht="16.5">
       <c r="B190" s="46" t="s">
-        <v>640</v>
-      </c>
-    </row>
-    <row r="192" spans="2:2" ht="21">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="192" spans="2:2" ht="20.5">
       <c r="B192" s="49">
         <v>7</v>
       </c>
     </row>
     <row r="194" spans="2:2" ht="16.5">
       <c r="B194" s="46" t="s">
-        <v>641</v>
-      </c>
-    </row>
-    <row r="196" spans="2:2" ht="21">
+        <v>632</v>
+      </c>
+    </row>
+    <row r="196" spans="2:2" ht="20.5">
       <c r="B196" s="49">
         <v>8</v>
       </c>
     </row>
     <row r="198" spans="2:2" ht="16.5">
       <c r="B198" s="46" t="s">
-        <v>642</v>
+        <v>633</v>
       </c>
     </row>
     <row r="200" spans="2:2" ht="16.5">
       <c r="B200" s="46"/>
     </row>
-    <row r="202" spans="2:2" ht="37.5">
+    <row r="202" spans="2:2" ht="35">
       <c r="B202" s="47" t="s">
-        <v>643</v>
-      </c>
-    </row>
-    <row r="204" spans="2:2" ht="26.25">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="204" spans="2:2" ht="26">
       <c r="B204" s="48" t="s">
-        <v>563</v>
-      </c>
-    </row>
-    <row r="206" spans="2:2" ht="21">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="206" spans="2:2" ht="20.5">
       <c r="B206" s="49" t="s">
-        <v>564</v>
+        <v>555</v>
       </c>
     </row>
     <row r="208" spans="2:2" ht="16.5">
       <c r="B208" s="46" t="s">
-        <v>644</v>
-      </c>
-    </row>
-    <row r="210" spans="2:2" ht="21">
+        <v>635</v>
+      </c>
+    </row>
+    <row r="210" spans="2:2" ht="20.5">
       <c r="B210" s="49" t="s">
-        <v>566</v>
+        <v>557</v>
       </c>
     </row>
     <row r="211" spans="2:2">
@@ -10632,37 +10822,37 @@
     </row>
     <row r="212" spans="2:2" ht="16.5">
       <c r="B212" s="50" t="s">
-        <v>645</v>
+        <v>636</v>
       </c>
     </row>
     <row r="213" spans="2:2" ht="16.5">
       <c r="B213" s="50" t="s">
-        <v>646</v>
+        <v>637</v>
       </c>
     </row>
     <row r="214" spans="2:2" ht="16.5">
       <c r="B214" s="50" t="s">
-        <v>647</v>
+        <v>638</v>
       </c>
     </row>
     <row r="215" spans="2:2" ht="16.5">
       <c r="B215" s="50" t="s">
-        <v>648</v>
-      </c>
-    </row>
-    <row r="219" spans="2:2" ht="26.25">
+        <v>639</v>
+      </c>
+    </row>
+    <row r="219" spans="2:2" ht="26">
       <c r="B219" s="48" t="s">
-        <v>571</v>
+        <v>562</v>
       </c>
     </row>
     <row r="221" spans="2:2" ht="16.5">
       <c r="B221" s="46" t="s">
-        <v>649</v>
-      </c>
-    </row>
-    <row r="223" spans="2:2" ht="21">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="223" spans="2:2" ht="20.5">
       <c r="B223" s="49" t="s">
-        <v>566</v>
+        <v>557</v>
       </c>
     </row>
     <row r="224" spans="2:2">
@@ -10670,37 +10860,37 @@
     </row>
     <row r="225" spans="2:2" ht="16.5">
       <c r="B225" s="50" t="s">
-        <v>650</v>
+        <v>641</v>
       </c>
     </row>
     <row r="226" spans="2:2" ht="16.5">
       <c r="B226" s="50" t="s">
-        <v>651</v>
+        <v>642</v>
       </c>
     </row>
     <row r="227" spans="2:2" ht="16.5">
       <c r="B227" s="50" t="s">
-        <v>652</v>
+        <v>643</v>
       </c>
     </row>
     <row r="228" spans="2:2" ht="16.5">
       <c r="B228" s="50" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="232" spans="2:2" ht="26.25">
+        <v>644</v>
+      </c>
+    </row>
+    <row r="232" spans="2:2" ht="26">
       <c r="B232" s="48" t="s">
-        <v>580</v>
+        <v>571</v>
       </c>
     </row>
     <row r="234" spans="2:2" ht="16.5">
       <c r="B234" s="46" t="s">
-        <v>654</v>
-      </c>
-    </row>
-    <row r="236" spans="2:2" ht="21">
+        <v>645</v>
+      </c>
+    </row>
+    <row r="236" spans="2:2" ht="20.5">
       <c r="B236" s="49" t="s">
-        <v>566</v>
+        <v>557</v>
       </c>
     </row>
     <row r="237" spans="2:2">
@@ -10708,32 +10898,32 @@
     </row>
     <row r="238" spans="2:2" ht="16.5">
       <c r="B238" s="50" t="s">
-        <v>655</v>
+        <v>646</v>
       </c>
     </row>
     <row r="239" spans="2:2" ht="16.5">
       <c r="B239" s="50" t="s">
-        <v>656</v>
+        <v>647</v>
       </c>
     </row>
     <row r="240" spans="2:2" ht="16.5">
       <c r="B240" s="50" t="s">
-        <v>657</v>
-      </c>
-    </row>
-    <row r="244" spans="2:2" ht="26.25">
+        <v>648</v>
+      </c>
+    </row>
+    <row r="244" spans="2:2" ht="26">
       <c r="B244" s="48" t="s">
-        <v>585</v>
+        <v>576</v>
       </c>
     </row>
     <row r="246" spans="2:2" ht="16.5">
       <c r="B246" s="46" t="s">
-        <v>658</v>
-      </c>
-    </row>
-    <row r="248" spans="2:2" ht="21">
+        <v>649</v>
+      </c>
+    </row>
+    <row r="248" spans="2:2" ht="20.5">
       <c r="B248" s="49" t="s">
-        <v>566</v>
+        <v>557</v>
       </c>
     </row>
     <row r="249" spans="2:2">
@@ -10741,32 +10931,32 @@
     </row>
     <row r="250" spans="2:2" ht="16.5">
       <c r="B250" s="50" t="s">
-        <v>659</v>
+        <v>650</v>
       </c>
     </row>
     <row r="251" spans="2:2" ht="16.5">
       <c r="B251" s="50" t="s">
-        <v>660</v>
+        <v>651</v>
       </c>
     </row>
     <row r="252" spans="2:2" ht="16.5">
       <c r="B252" s="50" t="s">
-        <v>661</v>
-      </c>
-    </row>
-    <row r="256" spans="2:2" ht="26.25">
+        <v>652</v>
+      </c>
+    </row>
+    <row r="256" spans="2:2" ht="26">
       <c r="B256" s="48" t="s">
-        <v>591</v>
+        <v>582</v>
       </c>
     </row>
     <row r="258" spans="2:2" ht="16.5">
       <c r="B258" s="46" t="s">
-        <v>662</v>
-      </c>
-    </row>
-    <row r="260" spans="2:2" ht="21">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="260" spans="2:2" ht="20.5">
       <c r="B260" s="49" t="s">
-        <v>566</v>
+        <v>557</v>
       </c>
     </row>
     <row r="261" spans="2:2">
@@ -10774,32 +10964,32 @@
     </row>
     <row r="262" spans="2:2" ht="16.5">
       <c r="B262" s="50" t="s">
-        <v>663</v>
+        <v>654</v>
       </c>
     </row>
     <row r="263" spans="2:2" ht="16.5">
       <c r="B263" s="50" t="s">
-        <v>664</v>
+        <v>655</v>
       </c>
     </row>
     <row r="264" spans="2:2" ht="16.5">
       <c r="B264" s="50" t="s">
-        <v>665</v>
-      </c>
-    </row>
-    <row r="268" spans="2:2" ht="26.25">
+        <v>656</v>
+      </c>
+    </row>
+    <row r="268" spans="2:2" ht="26">
       <c r="B268" s="48" t="s">
-        <v>596</v>
+        <v>587</v>
       </c>
     </row>
     <row r="270" spans="2:2" ht="16.5">
       <c r="B270" s="46" t="s">
-        <v>666</v>
-      </c>
-    </row>
-    <row r="272" spans="2:2" ht="21">
+        <v>657</v>
+      </c>
+    </row>
+    <row r="272" spans="2:2" ht="20.5">
       <c r="B272" s="49" t="s">
-        <v>566</v>
+        <v>557</v>
       </c>
     </row>
     <row r="273" spans="2:2">
@@ -10807,37 +10997,37 @@
     </row>
     <row r="274" spans="2:2" ht="16.5">
       <c r="B274" s="50" t="s">
-        <v>667</v>
+        <v>658</v>
       </c>
     </row>
     <row r="275" spans="2:2" ht="16.5">
       <c r="B275" s="50" t="s">
-        <v>668</v>
+        <v>659</v>
       </c>
     </row>
     <row r="276" spans="2:2" ht="16.5">
       <c r="B276" s="50" t="s">
-        <v>669</v>
+        <v>660</v>
       </c>
     </row>
     <row r="277" spans="2:2" ht="16.5">
       <c r="B277" s="50" t="s">
-        <v>670</v>
-      </c>
-    </row>
-    <row r="281" spans="2:2" ht="26.25">
+        <v>661</v>
+      </c>
+    </row>
+    <row r="281" spans="2:2" ht="26">
       <c r="B281" s="48" t="s">
-        <v>601</v>
+        <v>592</v>
       </c>
     </row>
     <row r="283" spans="2:2" ht="16.5">
       <c r="B283" s="46" t="s">
-        <v>671</v>
-      </c>
-    </row>
-    <row r="285" spans="2:2" ht="21">
+        <v>662</v>
+      </c>
+    </row>
+    <row r="285" spans="2:2" ht="20.5">
       <c r="B285" s="49" t="s">
-        <v>566</v>
+        <v>557</v>
       </c>
     </row>
     <row r="286" spans="2:2">
@@ -10845,32 +11035,32 @@
     </row>
     <row r="287" spans="2:2" ht="16.5">
       <c r="B287" s="50" t="s">
-        <v>672</v>
+        <v>663</v>
       </c>
     </row>
     <row r="288" spans="2:2" ht="16.5">
       <c r="B288" s="50" t="s">
-        <v>673</v>
+        <v>664</v>
       </c>
     </row>
     <row r="289" spans="2:2" ht="16.5">
       <c r="B289" s="50" t="s">
-        <v>674</v>
-      </c>
-    </row>
-    <row r="293" spans="2:2" ht="26.25">
+        <v>665</v>
+      </c>
+    </row>
+    <row r="293" spans="2:2" ht="26">
       <c r="B293" s="48" t="s">
-        <v>606</v>
+        <v>597</v>
       </c>
     </row>
     <row r="295" spans="2:2" ht="16.5">
       <c r="B295" s="46" t="s">
-        <v>675</v>
-      </c>
-    </row>
-    <row r="297" spans="2:2" ht="21">
+        <v>666</v>
+      </c>
+    </row>
+    <row r="297" spans="2:2" ht="20.5">
       <c r="B297" s="49" t="s">
-        <v>566</v>
+        <v>557</v>
       </c>
     </row>
     <row r="298" spans="2:2">
@@ -10878,32 +11068,32 @@
     </row>
     <row r="299" spans="2:2" ht="16.5">
       <c r="B299" s="50" t="s">
-        <v>676</v>
+        <v>667</v>
       </c>
     </row>
     <row r="300" spans="2:2" ht="16.5">
       <c r="B300" s="50" t="s">
-        <v>677</v>
+        <v>668</v>
       </c>
     </row>
     <row r="301" spans="2:2" ht="16.5">
       <c r="B301" s="50" t="s">
-        <v>678</v>
-      </c>
-    </row>
-    <row r="305" spans="2:2" ht="26.25">
+        <v>669</v>
+      </c>
+    </row>
+    <row r="305" spans="2:2" ht="26">
       <c r="B305" s="48" t="s">
-        <v>611</v>
+        <v>602</v>
       </c>
     </row>
     <row r="307" spans="2:2" ht="16.5">
       <c r="B307" s="46" t="s">
-        <v>679</v>
-      </c>
-    </row>
-    <row r="309" spans="2:2" ht="21">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="309" spans="2:2" ht="20.5">
       <c r="B309" s="49" t="s">
-        <v>566</v>
+        <v>557</v>
       </c>
     </row>
     <row r="310" spans="2:2">
@@ -10911,37 +11101,37 @@
     </row>
     <row r="311" spans="2:2" ht="16.5">
       <c r="B311" s="50" t="s">
-        <v>680</v>
+        <v>671</v>
       </c>
     </row>
     <row r="312" spans="2:2" ht="16.5">
       <c r="B312" s="50" t="s">
-        <v>681</v>
+        <v>672</v>
       </c>
     </row>
     <row r="313" spans="2:2" ht="16.5">
       <c r="B313" s="50" t="s">
-        <v>682</v>
+        <v>673</v>
       </c>
     </row>
     <row r="314" spans="2:2" ht="16.5">
       <c r="B314" s="50" t="s">
-        <v>683</v>
-      </c>
-    </row>
-    <row r="318" spans="2:2" ht="26.25">
+        <v>674</v>
+      </c>
+    </row>
+    <row r="318" spans="2:2" ht="26">
       <c r="B318" s="48" t="s">
-        <v>615</v>
+        <v>606</v>
       </c>
     </row>
     <row r="320" spans="2:2" ht="16.5">
       <c r="B320" s="46" t="s">
-        <v>684</v>
-      </c>
-    </row>
-    <row r="322" spans="2:2" ht="21">
+        <v>675</v>
+      </c>
+    </row>
+    <row r="322" spans="2:2" ht="20.5">
       <c r="B322" s="49" t="s">
-        <v>566</v>
+        <v>557</v>
       </c>
     </row>
     <row r="323" spans="2:2">
@@ -10949,130 +11139,130 @@
     </row>
     <row r="324" spans="2:2" ht="16.5">
       <c r="B324" s="50" t="s">
-        <v>685</v>
+        <v>676</v>
       </c>
     </row>
     <row r="325" spans="2:2" ht="16.5">
       <c r="B325" s="50" t="s">
-        <v>686</v>
+        <v>677</v>
       </c>
     </row>
     <row r="326" spans="2:2" ht="16.5">
       <c r="B326" s="50" t="s">
-        <v>687</v>
-      </c>
-    </row>
-    <row r="330" spans="2:2" ht="37.5">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="330" spans="2:2" ht="35">
       <c r="B330" s="47" t="s">
-        <v>688</v>
-      </c>
-    </row>
-    <row r="332" spans="2:2" ht="21">
+        <v>679</v>
+      </c>
+    </row>
+    <row r="332" spans="2:2" ht="20.5">
       <c r="B332" s="49">
         <v>1</v>
       </c>
     </row>
     <row r="334" spans="2:2" ht="16.5">
       <c r="B334" s="46" t="s">
-        <v>689</v>
-      </c>
-    </row>
-    <row r="336" spans="2:2" ht="21">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="336" spans="2:2" ht="20.5">
       <c r="B336" s="49">
         <v>2</v>
       </c>
     </row>
     <row r="338" spans="2:2" ht="16.5">
       <c r="B338" s="46" t="s">
-        <v>690</v>
-      </c>
-    </row>
-    <row r="340" spans="2:2" ht="21">
+        <v>681</v>
+      </c>
+    </row>
+    <row r="340" spans="2:2" ht="20.5">
       <c r="B340" s="49">
         <v>3</v>
       </c>
     </row>
     <row r="342" spans="2:2" ht="16.5">
       <c r="B342" s="46" t="s">
-        <v>691</v>
-      </c>
-    </row>
-    <row r="344" spans="2:2" ht="21">
+        <v>682</v>
+      </c>
+    </row>
+    <row r="344" spans="2:2" ht="20.5">
       <c r="B344" s="49">
         <v>4</v>
       </c>
     </row>
     <row r="346" spans="2:2" ht="16.5">
       <c r="B346" s="46" t="s">
-        <v>692</v>
-      </c>
-    </row>
-    <row r="348" spans="2:2" ht="21">
+        <v>683</v>
+      </c>
+    </row>
+    <row r="348" spans="2:2" ht="20.5">
       <c r="B348" s="49">
         <v>5</v>
       </c>
     </row>
     <row r="350" spans="2:2" ht="16.5">
       <c r="B350" s="46" t="s">
-        <v>693</v>
-      </c>
-    </row>
-    <row r="352" spans="2:2" ht="21">
+        <v>684</v>
+      </c>
+    </row>
+    <row r="352" spans="2:2" ht="20.5">
       <c r="B352" s="49">
         <v>6</v>
       </c>
     </row>
     <row r="354" spans="2:2" ht="16.5">
       <c r="B354" s="46" t="s">
-        <v>694</v>
-      </c>
-    </row>
-    <row r="356" spans="2:2" ht="21">
+        <v>685</v>
+      </c>
+    </row>
+    <row r="356" spans="2:2" ht="20.5">
       <c r="B356" s="49">
         <v>7</v>
       </c>
     </row>
     <row r="358" spans="2:2" ht="16.5">
       <c r="B358" s="46" t="s">
-        <v>695</v>
-      </c>
-    </row>
-    <row r="360" spans="2:2" ht="21">
+        <v>686</v>
+      </c>
+    </row>
+    <row r="360" spans="2:2" ht="20.5">
       <c r="B360" s="49">
         <v>8</v>
       </c>
     </row>
     <row r="362" spans="2:2" ht="16.5">
       <c r="B362" s="46" t="s">
-        <v>696</v>
+        <v>687</v>
       </c>
     </row>
     <row r="364" spans="2:2" ht="16.5">
       <c r="B364" s="46"/>
     </row>
-    <row r="366" spans="2:2" ht="37.5">
+    <row r="366" spans="2:2" ht="35">
       <c r="B366" s="47" t="s">
-        <v>697</v>
-      </c>
-    </row>
-    <row r="368" spans="2:2" ht="26.25">
+        <v>688</v>
+      </c>
+    </row>
+    <row r="368" spans="2:2" ht="26">
       <c r="B368" s="48" t="s">
-        <v>563</v>
-      </c>
-    </row>
-    <row r="370" spans="2:2" ht="21">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="370" spans="2:2" ht="20.5">
       <c r="B370" s="49" t="s">
-        <v>564</v>
+        <v>555</v>
       </c>
     </row>
     <row r="372" spans="2:2" ht="16.5">
       <c r="B372" s="46" t="s">
-        <v>644</v>
-      </c>
-    </row>
-    <row r="374" spans="2:2" ht="21">
+        <v>635</v>
+      </c>
+    </row>
+    <row r="374" spans="2:2" ht="20.5">
       <c r="B374" s="49" t="s">
-        <v>566</v>
+        <v>557</v>
       </c>
     </row>
     <row r="375" spans="2:2">
@@ -11080,47 +11270,47 @@
     </row>
     <row r="376" spans="2:2" ht="16.5">
       <c r="B376" s="50" t="s">
-        <v>567</v>
+        <v>558</v>
       </c>
     </row>
     <row r="377" spans="2:2" ht="16.5">
       <c r="B377" s="50" t="s">
-        <v>698</v>
+        <v>689</v>
       </c>
     </row>
     <row r="378" spans="2:2" ht="16.5">
       <c r="B378" s="50" t="s">
-        <v>699</v>
+        <v>690</v>
       </c>
     </row>
     <row r="379" spans="2:2" ht="16.5">
       <c r="B379" s="50" t="s">
-        <v>700</v>
+        <v>691</v>
       </c>
     </row>
     <row r="380" spans="2:2" ht="16.5">
       <c r="B380" s="50" t="s">
-        <v>701</v>
+        <v>692</v>
       </c>
     </row>
     <row r="381" spans="2:2" ht="16.5">
       <c r="B381" s="50" t="s">
-        <v>702</v>
-      </c>
-    </row>
-    <row r="385" spans="2:2" ht="26.25">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="385" spans="2:2" ht="26">
       <c r="B385" s="48" t="s">
-        <v>571</v>
+        <v>562</v>
       </c>
     </row>
     <row r="387" spans="2:2" ht="16.5">
       <c r="B387" s="46" t="s">
-        <v>703</v>
-      </c>
-    </row>
-    <row r="389" spans="2:2" ht="21">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="389" spans="2:2" ht="20.5">
       <c r="B389" s="49" t="s">
-        <v>566</v>
+        <v>557</v>
       </c>
     </row>
     <row r="390" spans="2:2">
@@ -11128,47 +11318,47 @@
     </row>
     <row r="391" spans="2:2" ht="16.5">
       <c r="B391" s="50" t="s">
-        <v>704</v>
+        <v>695</v>
       </c>
     </row>
     <row r="392" spans="2:2" ht="16.5">
       <c r="B392" s="50" t="s">
-        <v>705</v>
+        <v>696</v>
       </c>
     </row>
     <row r="393" spans="2:2" ht="16.5">
       <c r="B393" s="50" t="s">
-        <v>706</v>
+        <v>697</v>
       </c>
     </row>
     <row r="394" spans="2:2" ht="16.5">
       <c r="B394" s="50" t="s">
-        <v>707</v>
+        <v>698</v>
       </c>
     </row>
     <row r="395" spans="2:2" ht="16.5">
       <c r="B395" s="50" t="s">
-        <v>708</v>
+        <v>699</v>
       </c>
     </row>
     <row r="396" spans="2:2" ht="16.5">
       <c r="B396" s="50" t="s">
-        <v>709</v>
-      </c>
-    </row>
-    <row r="400" spans="2:2" ht="26.25">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="400" spans="2:2" ht="26">
       <c r="B400" s="48" t="s">
-        <v>580</v>
+        <v>571</v>
       </c>
     </row>
     <row r="402" spans="2:2" ht="16.5">
       <c r="B402" s="46" t="s">
-        <v>654</v>
-      </c>
-    </row>
-    <row r="404" spans="2:2" ht="21">
+        <v>645</v>
+      </c>
+    </row>
+    <row r="404" spans="2:2" ht="20.5">
       <c r="B404" s="49" t="s">
-        <v>566</v>
+        <v>557</v>
       </c>
     </row>
     <row r="405" spans="2:2">
@@ -11176,32 +11366,32 @@
     </row>
     <row r="406" spans="2:2" ht="16.5">
       <c r="B406" s="50" t="s">
-        <v>710</v>
+        <v>701</v>
       </c>
     </row>
     <row r="407" spans="2:2" ht="16.5">
       <c r="B407" s="50" t="s">
-        <v>711</v>
+        <v>702</v>
       </c>
     </row>
     <row r="408" spans="2:2" ht="16.5">
       <c r="B408" s="50" t="s">
-        <v>712</v>
-      </c>
-    </row>
-    <row r="412" spans="2:2" ht="26.25">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="412" spans="2:2" ht="26">
       <c r="B412" s="48" t="s">
-        <v>585</v>
+        <v>576</v>
       </c>
     </row>
     <row r="414" spans="2:2" ht="16.5">
       <c r="B414" s="46" t="s">
-        <v>713</v>
-      </c>
-    </row>
-    <row r="416" spans="2:2" ht="21">
+        <v>704</v>
+      </c>
+    </row>
+    <row r="416" spans="2:2" ht="20.5">
       <c r="B416" s="49" t="s">
-        <v>566</v>
+        <v>557</v>
       </c>
     </row>
     <row r="417" spans="2:2">
@@ -11209,32 +11399,32 @@
     </row>
     <row r="418" spans="2:2" ht="16.5">
       <c r="B418" s="50" t="s">
-        <v>714</v>
+        <v>705</v>
       </c>
     </row>
     <row r="419" spans="2:2" ht="16.5">
       <c r="B419" s="50" t="s">
-        <v>715</v>
+        <v>706</v>
       </c>
     </row>
     <row r="420" spans="2:2" ht="16.5">
       <c r="B420" s="50" t="s">
-        <v>716</v>
-      </c>
-    </row>
-    <row r="424" spans="2:2" ht="26.25">
+        <v>707</v>
+      </c>
+    </row>
+    <row r="424" spans="2:2" ht="26">
       <c r="B424" s="48" t="s">
-        <v>591</v>
+        <v>582</v>
       </c>
     </row>
     <row r="426" spans="2:2" ht="16.5">
       <c r="B426" s="46" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="428" spans="2:2" ht="21">
+        <v>708</v>
+      </c>
+    </row>
+    <row r="428" spans="2:2" ht="20.5">
       <c r="B428" s="49" t="s">
-        <v>566</v>
+        <v>557</v>
       </c>
     </row>
     <row r="429" spans="2:2">
@@ -11242,32 +11432,32 @@
     </row>
     <row r="430" spans="2:2" ht="16.5">
       <c r="B430" s="50" t="s">
-        <v>718</v>
+        <v>709</v>
       </c>
     </row>
     <row r="431" spans="2:2" ht="16.5">
       <c r="B431" s="50" t="s">
-        <v>719</v>
+        <v>710</v>
       </c>
     </row>
     <row r="432" spans="2:2" ht="16.5">
       <c r="B432" s="50" t="s">
-        <v>720</v>
-      </c>
-    </row>
-    <row r="436" spans="2:2" ht="26.25">
+        <v>711</v>
+      </c>
+    </row>
+    <row r="436" spans="2:2" ht="26">
       <c r="B436" s="48" t="s">
-        <v>596</v>
+        <v>587</v>
       </c>
     </row>
     <row r="438" spans="2:2" ht="16.5">
       <c r="B438" s="46" t="s">
-        <v>721</v>
-      </c>
-    </row>
-    <row r="440" spans="2:2" ht="21">
+        <v>712</v>
+      </c>
+    </row>
+    <row r="440" spans="2:2" ht="20.5">
       <c r="B440" s="49" t="s">
-        <v>566</v>
+        <v>557</v>
       </c>
     </row>
     <row r="441" spans="2:2">
@@ -11275,32 +11465,32 @@
     </row>
     <row r="442" spans="2:2" ht="16.5">
       <c r="B442" s="50" t="s">
-        <v>722</v>
+        <v>713</v>
       </c>
     </row>
     <row r="443" spans="2:2" ht="16.5">
       <c r="B443" s="50" t="s">
-        <v>723</v>
+        <v>714</v>
       </c>
     </row>
     <row r="444" spans="2:2" ht="16.5">
       <c r="B444" s="50" t="s">
-        <v>724</v>
-      </c>
-    </row>
-    <row r="448" spans="2:2" ht="26.25">
+        <v>715</v>
+      </c>
+    </row>
+    <row r="448" spans="2:2" ht="26">
       <c r="B448" s="48" t="s">
-        <v>601</v>
+        <v>592</v>
       </c>
     </row>
     <row r="450" spans="2:2" ht="16.5">
       <c r="B450" s="46" t="s">
-        <v>725</v>
-      </c>
-    </row>
-    <row r="452" spans="2:2" ht="21">
+        <v>716</v>
+      </c>
+    </row>
+    <row r="452" spans="2:2" ht="20.5">
       <c r="B452" s="49" t="s">
-        <v>566</v>
+        <v>557</v>
       </c>
     </row>
     <row r="453" spans="2:2">
@@ -11308,27 +11498,27 @@
     </row>
     <row r="454" spans="2:2" ht="16.5">
       <c r="B454" s="50" t="s">
-        <v>726</v>
+        <v>717</v>
       </c>
     </row>
     <row r="455" spans="2:2" ht="16.5">
       <c r="B455" s="50" t="s">
-        <v>727</v>
-      </c>
-    </row>
-    <row r="459" spans="2:2" ht="26.25">
+        <v>718</v>
+      </c>
+    </row>
+    <row r="459" spans="2:2" ht="26">
       <c r="B459" s="48" t="s">
-        <v>606</v>
+        <v>597</v>
       </c>
     </row>
     <row r="461" spans="2:2" ht="16.5">
       <c r="B461" s="46" t="s">
-        <v>728</v>
-      </c>
-    </row>
-    <row r="463" spans="2:2" ht="21">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="463" spans="2:2" ht="20.5">
       <c r="B463" s="49" t="s">
-        <v>566</v>
+        <v>557</v>
       </c>
     </row>
     <row r="464" spans="2:2">
@@ -11336,37 +11526,37 @@
     </row>
     <row r="465" spans="2:2" ht="16.5">
       <c r="B465" s="50" t="s">
-        <v>729</v>
+        <v>720</v>
       </c>
     </row>
     <row r="466" spans="2:2" ht="16.5">
       <c r="B466" s="50" t="s">
-        <v>730</v>
+        <v>721</v>
       </c>
     </row>
     <row r="467" spans="2:2" ht="16.5">
       <c r="B467" s="50" t="s">
-        <v>731</v>
-      </c>
-    </row>
-    <row r="471" spans="2:2" ht="26.25">
+        <v>722</v>
+      </c>
+    </row>
+    <row r="471" spans="2:2" ht="26">
       <c r="B471" s="48" t="s">
-        <v>611</v>
+        <v>602</v>
       </c>
     </row>
     <row r="473" spans="2:2" ht="16.5">
       <c r="B473" s="46" t="s">
-        <v>732</v>
-      </c>
-    </row>
-    <row r="475" spans="2:2" ht="21">
+        <v>723</v>
+      </c>
+    </row>
+    <row r="475" spans="2:2" ht="20.5">
       <c r="B475" s="49" t="s">
-        <v>566</v>
+        <v>557</v>
       </c>
     </row>
     <row r="477" spans="2:2" ht="16.5">
       <c r="B477" s="51" t="s">
-        <v>733</v>
+        <v>724</v>
       </c>
     </row>
     <row r="478" spans="2:2">
@@ -11374,22 +11564,22 @@
     </row>
     <row r="479" spans="2:2" ht="16.5">
       <c r="B479" s="50" t="s">
-        <v>734</v>
+        <v>725</v>
       </c>
     </row>
     <row r="480" spans="2:2" ht="16.5">
       <c r="B480" s="50" t="s">
-        <v>735</v>
+        <v>726</v>
       </c>
     </row>
     <row r="481" spans="2:2" ht="16.5">
       <c r="B481" s="50" t="s">
-        <v>736</v>
+        <v>727</v>
       </c>
     </row>
     <row r="483" spans="2:2" ht="16.5">
       <c r="B483" s="51" t="s">
-        <v>737</v>
+        <v>728</v>
       </c>
     </row>
     <row r="484" spans="2:2">
@@ -11397,27 +11587,27 @@
     </row>
     <row r="485" spans="2:2" ht="16.5">
       <c r="B485" s="50" t="s">
-        <v>738</v>
+        <v>729</v>
       </c>
     </row>
     <row r="486" spans="2:2" ht="16.5">
       <c r="B486" s="50" t="s">
-        <v>739</v>
-      </c>
-    </row>
-    <row r="490" spans="2:2" ht="26.25">
+        <v>730</v>
+      </c>
+    </row>
+    <row r="490" spans="2:2" ht="26">
       <c r="B490" s="48" t="s">
-        <v>615</v>
+        <v>606</v>
       </c>
     </row>
     <row r="492" spans="2:2" ht="16.5">
       <c r="B492" s="46" t="s">
-        <v>740</v>
-      </c>
-    </row>
-    <row r="494" spans="2:2" ht="21">
+        <v>731</v>
+      </c>
+    </row>
+    <row r="494" spans="2:2" ht="20.5">
       <c r="B494" s="49" t="s">
-        <v>566</v>
+        <v>557</v>
       </c>
     </row>
     <row r="495" spans="2:2">
@@ -11425,22 +11615,22 @@
     </row>
     <row r="496" spans="2:2" ht="16.5">
       <c r="B496" s="50" t="s">
-        <v>741</v>
-      </c>
-    </row>
-    <row r="500" spans="2:2" ht="26.25">
+        <v>732</v>
+      </c>
+    </row>
+    <row r="500" spans="2:2" ht="26">
       <c r="B500" s="48" t="s">
-        <v>620</v>
+        <v>611</v>
       </c>
     </row>
     <row r="502" spans="2:2" ht="16.5">
       <c r="B502" s="46" t="s">
-        <v>742</v>
-      </c>
-    </row>
-    <row r="504" spans="2:2" ht="21">
+        <v>733</v>
+      </c>
+    </row>
+    <row r="504" spans="2:2" ht="20.5">
       <c r="B504" s="49" t="s">
-        <v>566</v>
+        <v>557</v>
       </c>
     </row>
     <row r="505" spans="2:2">
@@ -11448,27 +11638,27 @@
     </row>
     <row r="506" spans="2:2" ht="16.5">
       <c r="B506" s="50" t="s">
-        <v>743</v>
+        <v>734</v>
       </c>
     </row>
     <row r="507" spans="2:2" ht="16.5">
       <c r="B507" s="50" t="s">
-        <v>744</v>
-      </c>
-    </row>
-    <row r="511" spans="2:2" ht="26.25">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="511" spans="2:2" ht="26">
       <c r="B511" s="48" t="s">
-        <v>624</v>
+        <v>615</v>
       </c>
     </row>
     <row r="513" spans="2:2" ht="16.5">
       <c r="B513" s="46" t="s">
-        <v>745</v>
-      </c>
-    </row>
-    <row r="515" spans="2:2" ht="21">
+        <v>736</v>
+      </c>
+    </row>
+    <row r="515" spans="2:2" ht="20.5">
       <c r="B515" s="49" t="s">
-        <v>566</v>
+        <v>557</v>
       </c>
     </row>
     <row r="516" spans="2:2">
@@ -11476,32 +11666,32 @@
     </row>
     <row r="517" spans="2:2" ht="16.5">
       <c r="B517" s="50" t="s">
-        <v>746</v>
+        <v>737</v>
       </c>
     </row>
     <row r="518" spans="2:2" ht="16.5">
       <c r="B518" s="50" t="s">
-        <v>747</v>
+        <v>738</v>
       </c>
     </row>
     <row r="519" spans="2:2" ht="16.5">
       <c r="B519" s="50" t="s">
-        <v>748</v>
-      </c>
-    </row>
-    <row r="523" spans="2:2" ht="26.25">
+        <v>739</v>
+      </c>
+    </row>
+    <row r="523" spans="2:2" ht="26">
       <c r="B523" s="48" t="s">
-        <v>629</v>
+        <v>620</v>
       </c>
     </row>
     <row r="525" spans="2:2" ht="16.5">
       <c r="B525" s="46" t="s">
-        <v>749</v>
-      </c>
-    </row>
-    <row r="527" spans="2:2" ht="21">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="527" spans="2:2" ht="20.5">
       <c r="B527" s="49" t="s">
-        <v>566</v>
+        <v>557</v>
       </c>
     </row>
     <row r="528" spans="2:2">
@@ -11509,117 +11699,117 @@
     </row>
     <row r="529" spans="2:2" ht="16.5">
       <c r="B529" s="50" t="s">
-        <v>750</v>
+        <v>741</v>
       </c>
     </row>
     <row r="530" spans="2:2" ht="16.5">
       <c r="B530" s="50" t="s">
-        <v>751</v>
-      </c>
-    </row>
-    <row r="534" spans="2:2" ht="37.5">
+        <v>742</v>
+      </c>
+    </row>
+    <row r="534" spans="2:2" ht="35">
       <c r="B534" s="47" t="s">
-        <v>752</v>
-      </c>
-    </row>
-    <row r="536" spans="2:2" ht="21">
+        <v>743</v>
+      </c>
+    </row>
+    <row r="536" spans="2:2" ht="20.5">
       <c r="B536" s="49">
         <v>1</v>
       </c>
     </row>
     <row r="538" spans="2:2" ht="16.5">
       <c r="B538" s="46" t="s">
-        <v>753</v>
-      </c>
-    </row>
-    <row r="540" spans="2:2" ht="21">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="540" spans="2:2" ht="20.5">
       <c r="B540" s="49">
         <v>2</v>
       </c>
     </row>
     <row r="542" spans="2:2" ht="16.5">
       <c r="B542" s="46" t="s">
-        <v>754</v>
-      </c>
-    </row>
-    <row r="544" spans="2:2" ht="21">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="544" spans="2:2" ht="20.5">
       <c r="B544" s="49">
         <v>3</v>
       </c>
     </row>
     <row r="546" spans="2:2" ht="16.5">
       <c r="B546" s="46" t="s">
-        <v>755</v>
-      </c>
-    </row>
-    <row r="548" spans="2:2" ht="21">
+        <v>746</v>
+      </c>
+    </row>
+    <row r="548" spans="2:2" ht="20.5">
       <c r="B548" s="49">
         <v>4</v>
       </c>
     </row>
     <row r="550" spans="2:2" ht="16.5">
       <c r="B550" s="46" t="s">
-        <v>756</v>
-      </c>
-    </row>
-    <row r="552" spans="2:2" ht="21">
+        <v>747</v>
+      </c>
+    </row>
+    <row r="552" spans="2:2" ht="20.5">
       <c r="B552" s="49">
         <v>5</v>
       </c>
     </row>
     <row r="554" spans="2:2" ht="16.5">
       <c r="B554" s="46" t="s">
-        <v>757</v>
-      </c>
-    </row>
-    <row r="556" spans="2:2" ht="21">
+        <v>748</v>
+      </c>
+    </row>
+    <row r="556" spans="2:2" ht="20.5">
       <c r="B556" s="49">
         <v>6</v>
       </c>
     </row>
     <row r="558" spans="2:2" ht="16.5">
       <c r="B558" s="46" t="s">
-        <v>758</v>
-      </c>
-    </row>
-    <row r="560" spans="2:2" ht="21">
+        <v>749</v>
+      </c>
+    </row>
+    <row r="560" spans="2:2" ht="20.5">
       <c r="B560" s="49">
         <v>7</v>
       </c>
     </row>
     <row r="562" spans="2:2" ht="16.5">
       <c r="B562" s="46" t="s">
-        <v>759</v>
-      </c>
-    </row>
-    <row r="564" spans="2:2" ht="21">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="564" spans="2:2" ht="20.5">
       <c r="B564" s="49">
         <v>8</v>
       </c>
     </row>
     <row r="566" spans="2:2" ht="16.5">
       <c r="B566" s="46" t="s">
-        <v>760</v>
-      </c>
-    </row>
-    <row r="568" spans="2:2" ht="21">
+        <v>751</v>
+      </c>
+    </row>
+    <row r="568" spans="2:2" ht="20.5">
       <c r="B568" s="49">
         <v>9</v>
       </c>
     </row>
     <row r="570" spans="2:2" ht="16.5">
       <c r="B570" s="46" t="s">
-        <v>761</v>
-      </c>
-    </row>
-    <row r="572" spans="2:2" ht="21">
+        <v>752</v>
+      </c>
+    </row>
+    <row r="572" spans="2:2" ht="20.5">
       <c r="B572" s="49">
         <v>10</v>
       </c>
     </row>
     <row r="574" spans="2:2" ht="16.5">
       <c r="B574" s="46" t="s">
-        <v>762</v>
+        <v>753</v>
       </c>
     </row>
     <row r="575" spans="2:2" ht="16.5">
@@ -11637,16 +11827,16 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EFC6BB78-2366-4CBC-BDE4-AE3B7D4D0F5C}">
   <dimension ref="B2:B3"/>
-  <sheetFormatPr defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultRowHeight="13"/>
   <sheetData>
     <row r="2" spans="2:2" ht="16.5">
       <c r="B2" s="46" t="s">
-        <v>554</v>
+        <v>545</v>
       </c>
     </row>
     <row r="3" spans="2:2" ht="16.5">
       <c r="B3" s="46" t="s">
-        <v>555</v>
+        <v>546</v>
       </c>
     </row>
   </sheetData>
@@ -11658,646 +11848,646 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{40E537D0-355C-44F6-821F-B309AC3764BF}">
   <dimension ref="A1:A139"/>
-  <sheetFormatPr defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultRowHeight="13"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" t="s">
-        <v>294</v>
+        <v>285</v>
       </c>
     </row>
     <row r="2" spans="1:1">
       <c r="A2" t="s">
-        <v>295</v>
+        <v>286</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" t="s">
-        <v>296</v>
+        <v>287</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" t="s">
-        <v>297</v>
+        <v>288</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>298</v>
+        <v>289</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>299</v>
+        <v>290</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" t="s">
-        <v>300</v>
+        <v>291</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" t="s">
-        <v>301</v>
+        <v>292</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" t="s">
-        <v>302</v>
+        <v>293</v>
       </c>
     </row>
     <row r="10" spans="1:1">
       <c r="A10" t="s">
-        <v>303</v>
+        <v>294</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" t="s">
-        <v>304</v>
+        <v>295</v>
       </c>
     </row>
     <row r="12" spans="1:1">
       <c r="A12" t="s">
-        <v>305</v>
+        <v>296</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" t="s">
-        <v>306</v>
+        <v>297</v>
       </c>
     </row>
     <row r="14" spans="1:1">
       <c r="A14" t="s">
-        <v>307</v>
+        <v>298</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" t="s">
-        <v>308</v>
+        <v>299</v>
       </c>
     </row>
     <row r="16" spans="1:1">
       <c r="A16" t="s">
-        <v>309</v>
+        <v>300</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" t="s">
-        <v>310</v>
+        <v>301</v>
       </c>
     </row>
     <row r="18" spans="1:1">
       <c r="A18" t="s">
-        <v>311</v>
+        <v>302</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" t="s">
-        <v>312</v>
+        <v>303</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" t="s">
-        <v>313</v>
+        <v>304</v>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23" t="s">
-        <v>294</v>
+        <v>285</v>
       </c>
     </row>
     <row r="24" spans="1:1">
       <c r="A24" t="s">
-        <v>295</v>
+        <v>286</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" t="s">
-        <v>296</v>
+        <v>287</v>
       </c>
     </row>
     <row r="26" spans="1:1">
       <c r="A26" t="s">
-        <v>297</v>
+        <v>288</v>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27" t="s">
-        <v>314</v>
+        <v>305</v>
       </c>
     </row>
     <row r="28" spans="1:1">
       <c r="A28" t="s">
-        <v>315</v>
+        <v>306</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" t="s">
-        <v>316</v>
+        <v>307</v>
       </c>
     </row>
     <row r="30" spans="1:1">
       <c r="A30" t="s">
-        <v>317</v>
+        <v>308</v>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" t="s">
-        <v>318</v>
+        <v>309</v>
       </c>
     </row>
     <row r="32" spans="1:1">
       <c r="A32" t="s">
-        <v>319</v>
+        <v>310</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" t="s">
-        <v>320</v>
+        <v>311</v>
       </c>
     </row>
     <row r="34" spans="1:1">
       <c r="A34" t="s">
-        <v>321</v>
+        <v>312</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" t="s">
-        <v>322</v>
+        <v>313</v>
       </c>
     </row>
     <row r="36" spans="1:1">
       <c r="A36" t="s">
-        <v>323</v>
+        <v>314</v>
       </c>
     </row>
     <row r="37" spans="1:1">
       <c r="A37" t="s">
-        <v>324</v>
+        <v>315</v>
       </c>
     </row>
     <row r="38" spans="1:1">
       <c r="A38" t="s">
-        <v>325</v>
+        <v>316</v>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39" t="s">
-        <v>326</v>
+        <v>317</v>
       </c>
     </row>
     <row r="40" spans="1:1">
       <c r="A40" t="s">
-        <v>327</v>
+        <v>318</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" t="s">
-        <v>328</v>
+        <v>319</v>
       </c>
     </row>
     <row r="42" spans="1:1">
       <c r="A42" t="s">
-        <v>311</v>
+        <v>302</v>
       </c>
     </row>
     <row r="43" spans="1:1">
       <c r="A43" t="s">
-        <v>329</v>
+        <v>320</v>
       </c>
     </row>
     <row r="46" spans="1:1">
       <c r="A46" t="s">
-        <v>294</v>
+        <v>285</v>
       </c>
     </row>
     <row r="47" spans="1:1">
       <c r="A47" t="s">
-        <v>330</v>
+        <v>321</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" t="s">
-        <v>331</v>
+        <v>322</v>
       </c>
     </row>
     <row r="49" spans="1:1">
       <c r="A49" t="s">
-        <v>332</v>
+        <v>323</v>
       </c>
     </row>
     <row r="50" spans="1:1">
       <c r="A50" t="s">
-        <v>333</v>
+        <v>324</v>
       </c>
     </row>
     <row r="51" spans="1:1">
       <c r="A51" t="s">
-        <v>334</v>
+        <v>325</v>
       </c>
     </row>
     <row r="52" spans="1:1">
       <c r="A52" t="s">
-        <v>335</v>
+        <v>326</v>
       </c>
     </row>
     <row r="53" spans="1:1">
       <c r="A53" t="s">
-        <v>336</v>
+        <v>327</v>
       </c>
     </row>
     <row r="54" spans="1:1">
       <c r="A54" t="s">
-        <v>337</v>
+        <v>328</v>
       </c>
     </row>
     <row r="55" spans="1:1">
       <c r="A55" t="s">
-        <v>338</v>
+        <v>329</v>
       </c>
     </row>
     <row r="56" spans="1:1">
       <c r="A56" t="s">
-        <v>339</v>
+        <v>330</v>
       </c>
     </row>
     <row r="57" spans="1:1">
       <c r="A57" t="s">
-        <v>340</v>
+        <v>331</v>
       </c>
     </row>
     <row r="58" spans="1:1">
       <c r="A58" t="s">
-        <v>341</v>
+        <v>332</v>
       </c>
     </row>
     <row r="59" spans="1:1">
       <c r="A59" t="s">
-        <v>342</v>
+        <v>333</v>
       </c>
     </row>
     <row r="60" spans="1:1">
       <c r="A60" t="s">
-        <v>343</v>
+        <v>334</v>
       </c>
     </row>
     <row r="61" spans="1:1">
       <c r="A61" t="s">
-        <v>344</v>
+        <v>335</v>
       </c>
     </row>
     <row r="62" spans="1:1">
       <c r="A62" t="s">
-        <v>345</v>
+        <v>336</v>
       </c>
     </row>
     <row r="63" spans="1:1">
       <c r="A63" t="s">
-        <v>346</v>
+        <v>337</v>
       </c>
     </row>
     <row r="64" spans="1:1">
       <c r="A64" t="s">
-        <v>347</v>
+        <v>338</v>
       </c>
     </row>
     <row r="65" spans="1:1">
       <c r="A65" t="s">
-        <v>330</v>
+        <v>321</v>
       </c>
     </row>
     <row r="66" spans="1:1">
       <c r="A66" t="s">
-        <v>348</v>
+        <v>339</v>
       </c>
     </row>
     <row r="69" spans="1:1">
       <c r="A69" t="s">
-        <v>294</v>
+        <v>285</v>
       </c>
     </row>
     <row r="70" spans="1:1">
       <c r="A70" t="s">
-        <v>330</v>
+        <v>321</v>
       </c>
     </row>
     <row r="71" spans="1:1">
       <c r="A71" t="s">
-        <v>331</v>
+        <v>322</v>
       </c>
     </row>
     <row r="72" spans="1:1">
       <c r="A72" t="s">
-        <v>332</v>
+        <v>323</v>
       </c>
     </row>
     <row r="73" spans="1:1">
       <c r="A73" t="s">
-        <v>349</v>
+        <v>340</v>
       </c>
     </row>
     <row r="74" spans="1:1">
       <c r="A74" t="s">
-        <v>350</v>
+        <v>341</v>
       </c>
     </row>
     <row r="75" spans="1:1">
       <c r="A75" t="s">
-        <v>351</v>
+        <v>342</v>
       </c>
     </row>
     <row r="76" spans="1:1">
       <c r="A76" t="s">
-        <v>352</v>
+        <v>343</v>
       </c>
     </row>
     <row r="77" spans="1:1">
       <c r="A77" t="s">
-        <v>353</v>
+        <v>344</v>
       </c>
     </row>
     <row r="78" spans="1:1">
       <c r="A78" t="s">
-        <v>354</v>
+        <v>345</v>
       </c>
     </row>
     <row r="79" spans="1:1">
       <c r="A79" t="s">
-        <v>355</v>
+        <v>346</v>
       </c>
     </row>
     <row r="80" spans="1:1">
       <c r="A80" t="s">
-        <v>356</v>
+        <v>347</v>
       </c>
     </row>
     <row r="81" spans="1:1">
       <c r="A81" t="s">
-        <v>357</v>
+        <v>348</v>
       </c>
     </row>
     <row r="82" spans="1:1">
       <c r="A82" t="s">
-        <v>358</v>
+        <v>349</v>
       </c>
     </row>
     <row r="83" spans="1:1">
       <c r="A83" t="s">
-        <v>330</v>
+        <v>321</v>
       </c>
     </row>
     <row r="84" spans="1:1">
       <c r="A84" t="s">
-        <v>359</v>
+        <v>350</v>
       </c>
     </row>
     <row r="85" spans="1:1">
       <c r="A85" t="s">
-        <v>360</v>
+        <v>351</v>
       </c>
     </row>
     <row r="86" spans="1:1">
       <c r="A86" t="s">
-        <v>311</v>
+        <v>302</v>
       </c>
     </row>
     <row r="87" spans="1:1">
       <c r="A87" t="s">
-        <v>361</v>
+        <v>352</v>
       </c>
     </row>
     <row r="88" spans="1:1">
       <c r="A88" t="s">
-        <v>362</v>
+        <v>353</v>
       </c>
     </row>
     <row r="92" spans="1:1">
       <c r="A92" t="s">
-        <v>294</v>
+        <v>285</v>
       </c>
     </row>
     <row r="93" spans="1:1">
       <c r="A93" t="s">
-        <v>330</v>
+        <v>321</v>
       </c>
     </row>
     <row r="94" spans="1:1">
       <c r="A94" t="s">
-        <v>295</v>
+        <v>286</v>
       </c>
     </row>
     <row r="95" spans="1:1">
       <c r="A95" t="s">
-        <v>363</v>
+        <v>354</v>
       </c>
     </row>
     <row r="96" spans="1:1">
       <c r="A96" t="s">
-        <v>364</v>
+        <v>355</v>
       </c>
     </row>
     <row r="97" spans="1:1">
       <c r="A97" t="s">
-        <v>365</v>
+        <v>356</v>
       </c>
     </row>
     <row r="98" spans="1:1">
       <c r="A98" t="s">
-        <v>366</v>
+        <v>357</v>
       </c>
     </row>
     <row r="99" spans="1:1">
       <c r="A99" t="s">
-        <v>350</v>
+        <v>341</v>
       </c>
     </row>
     <row r="100" spans="1:1">
       <c r="A100" t="s">
-        <v>367</v>
+        <v>358</v>
       </c>
     </row>
     <row r="101" spans="1:1">
       <c r="A101" t="s">
-        <v>368</v>
+        <v>359</v>
       </c>
     </row>
     <row r="102" spans="1:1">
       <c r="A102" t="s">
-        <v>369</v>
+        <v>360</v>
       </c>
     </row>
     <row r="103" spans="1:1">
       <c r="A103" t="s">
-        <v>370</v>
+        <v>361</v>
       </c>
     </row>
     <row r="104" spans="1:1">
       <c r="A104" t="s">
-        <v>371</v>
+        <v>362</v>
       </c>
     </row>
     <row r="105" spans="1:1">
       <c r="A105" t="s">
-        <v>372</v>
+        <v>363</v>
       </c>
     </row>
     <row r="106" spans="1:1">
       <c r="A106" t="s">
-        <v>373</v>
+        <v>364</v>
       </c>
     </row>
     <row r="107" spans="1:1">
       <c r="A107" t="s">
-        <v>374</v>
+        <v>365</v>
       </c>
     </row>
     <row r="108" spans="1:1">
       <c r="A108" t="s">
-        <v>375</v>
+        <v>366</v>
       </c>
     </row>
     <row r="109" spans="1:1">
       <c r="A109" t="s">
-        <v>330</v>
+        <v>321</v>
       </c>
     </row>
     <row r="110" spans="1:1">
       <c r="A110" t="s">
-        <v>376</v>
+        <v>367</v>
       </c>
     </row>
     <row r="111" spans="1:1">
       <c r="A111" t="s">
-        <v>377</v>
+        <v>368</v>
       </c>
     </row>
     <row r="112" spans="1:1">
       <c r="A112" t="s">
-        <v>311</v>
+        <v>302</v>
       </c>
     </row>
     <row r="113" spans="1:1">
       <c r="A113" t="s">
-        <v>378</v>
+        <v>369</v>
       </c>
     </row>
     <row r="114" spans="1:1">
       <c r="A114" t="s">
-        <v>379</v>
+        <v>370</v>
       </c>
     </row>
     <row r="117" spans="1:1">
       <c r="A117" t="s">
-        <v>294</v>
+        <v>285</v>
       </c>
     </row>
     <row r="118" spans="1:1">
       <c r="A118" t="s">
-        <v>380</v>
+        <v>371</v>
       </c>
     </row>
     <row r="119" spans="1:1">
       <c r="A119" t="s">
-        <v>381</v>
+        <v>372</v>
       </c>
     </row>
     <row r="120" spans="1:1">
       <c r="A120" t="s">
-        <v>382</v>
+        <v>373</v>
       </c>
     </row>
     <row r="121" spans="1:1">
       <c r="A121" t="s">
-        <v>383</v>
+        <v>374</v>
       </c>
     </row>
     <row r="122" spans="1:1">
       <c r="A122" t="s">
-        <v>384</v>
+        <v>375</v>
       </c>
     </row>
     <row r="123" spans="1:1">
       <c r="A123" t="s">
-        <v>385</v>
+        <v>376</v>
       </c>
     </row>
     <row r="124" spans="1:1">
       <c r="A124" t="s">
-        <v>386</v>
+        <v>377</v>
       </c>
     </row>
     <row r="125" spans="1:1">
       <c r="A125" t="s">
-        <v>387</v>
+        <v>378</v>
       </c>
     </row>
     <row r="126" spans="1:1">
       <c r="A126" t="s">
-        <v>388</v>
+        <v>379</v>
       </c>
     </row>
     <row r="127" spans="1:1">
       <c r="A127" t="s">
-        <v>389</v>
+        <v>380</v>
       </c>
     </row>
     <row r="128" spans="1:1">
       <c r="A128" t="s">
-        <v>390</v>
+        <v>381</v>
       </c>
     </row>
     <row r="129" spans="1:1">
       <c r="A129" t="s">
-        <v>391</v>
+        <v>382</v>
       </c>
     </row>
     <row r="130" spans="1:1">
       <c r="A130" t="s">
-        <v>392</v>
+        <v>383</v>
       </c>
     </row>
     <row r="131" spans="1:1">
       <c r="A131" t="s">
-        <v>393</v>
+        <v>384</v>
       </c>
     </row>
     <row r="132" spans="1:1">
       <c r="A132" t="s">
-        <v>394</v>
+        <v>385</v>
       </c>
     </row>
     <row r="133" spans="1:1">
       <c r="A133" t="s">
-        <v>395</v>
+        <v>386</v>
       </c>
     </row>
     <row r="134" spans="1:1">
       <c r="A134" t="s">
-        <v>396</v>
+        <v>387</v>
       </c>
     </row>
     <row r="135" spans="1:1">
       <c r="A135" t="s">
-        <v>311</v>
+        <v>302</v>
       </c>
     </row>
     <row r="136" spans="1:1">
       <c r="A136" t="s">
-        <v>397</v>
+        <v>388</v>
       </c>
     </row>
     <row r="137" spans="1:1">
       <c r="A137" t="s">
-        <v>398</v>
+        <v>389</v>
       </c>
     </row>
     <row r="138" spans="1:1">
       <c r="A138" t="s">
-        <v>399</v>
+        <v>390</v>
       </c>
     </row>
     <row r="139" spans="1:1">
       <c r="A139" t="s">
-        <v>400</v>
+        <v>391</v>
       </c>
     </row>
   </sheetData>
@@ -12307,44 +12497,147 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C945A8A3-E413-4358-BBE4-EF5A44242598}">
-  <dimension ref="A1:A12"/>
-  <sheetFormatPr defaultRowHeight="13.5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:B21"/>
+  <sheetFormatPr defaultRowHeight="13"/>
+  <cols>
+    <col min="1" max="1" width="150.36328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="103.36328125" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:1">
-      <c r="A1" s="34" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1">
-      <c r="A2" s="34" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="34" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1">
-      <c r="A4" s="34" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1">
-      <c r="A6" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1">
-      <c r="A9" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="12" spans="1:1">
-      <c r="A12" t="s">
-        <v>275</v>
-      </c>
+    <row r="1" spans="1:2">
+      <c r="A1" s="24"/>
+      <c r="B1" s="24"/>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" s="24" t="s">
+        <v>150</v>
+      </c>
+      <c r="B2" s="24"/>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" s="24" t="s">
+        <v>151</v>
+      </c>
+      <c r="B3" s="24"/>
+    </row>
+    <row r="4" spans="1:2" ht="52">
+      <c r="A4" s="24" t="s">
+        <v>152</v>
+      </c>
+      <c r="B4" s="23" t="s">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" s="24" t="s">
+        <v>153</v>
+      </c>
+      <c r="B5" s="24"/>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" s="24" t="s">
+        <v>154</v>
+      </c>
+      <c r="B6" s="24"/>
+    </row>
+    <row r="7" spans="1:2" ht="52">
+      <c r="A7" s="24" t="s">
+        <v>155</v>
+      </c>
+      <c r="B7" s="23" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" ht="39">
+      <c r="A8" s="24" t="s">
+        <v>156</v>
+      </c>
+      <c r="B8" s="23" t="s">
+        <v>766</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" s="24" t="s">
+        <v>157</v>
+      </c>
+      <c r="B9" s="24"/>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10" s="24" t="s">
+        <v>158</v>
+      </c>
+      <c r="B10" s="24"/>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" s="24" t="s">
+        <v>159</v>
+      </c>
+      <c r="B11" s="24"/>
+    </row>
+    <row r="12" spans="1:2">
+      <c r="A12" s="24" t="s">
+        <v>160</v>
+      </c>
+      <c r="B12" s="24"/>
+    </row>
+    <row r="13" spans="1:2" ht="52">
+      <c r="A13" s="24" t="s">
+        <v>161</v>
+      </c>
+      <c r="B13" s="23" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2">
+      <c r="A14" s="24" t="s">
+        <v>162</v>
+      </c>
+      <c r="B14" s="24"/>
+    </row>
+    <row r="15" spans="1:2">
+      <c r="A15" s="24" t="s">
+        <v>163</v>
+      </c>
+      <c r="B15" s="24"/>
+    </row>
+    <row r="16" spans="1:2">
+      <c r="A16" s="24" t="s">
+        <v>164</v>
+      </c>
+      <c r="B16" s="24"/>
+    </row>
+    <row r="17" spans="1:2">
+      <c r="A17" s="24" t="s">
+        <v>165</v>
+      </c>
+      <c r="B17" s="24"/>
+    </row>
+    <row r="18" spans="1:2">
+      <c r="A18" s="24" t="s">
+        <v>166</v>
+      </c>
+      <c r="B18" s="24"/>
+    </row>
+    <row r="19" spans="1:2">
+      <c r="A19" s="24" t="s">
+        <v>167</v>
+      </c>
+      <c r="B19" s="24"/>
+    </row>
+    <row r="20" spans="1:2" ht="91">
+      <c r="A20" s="24" t="s">
+        <v>168</v>
+      </c>
+      <c r="B20" s="23" t="s">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2">
+      <c r="A21" s="24" t="s">
+        <v>169</v>
+      </c>
+      <c r="B21" s="24"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
@@ -12353,141 +12646,101 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:B21"/>
-  <sheetFormatPr defaultRowHeight="13.5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <dimension ref="A1:B11"/>
+  <sheetFormatPr defaultRowHeight="13"/>
   <cols>
-    <col min="1" max="1" width="150.375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="103.375" customWidth="1"/>
+    <col min="1" max="1" width="69.6328125" customWidth="1"/>
+    <col min="2" max="2" width="66.36328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2">
-      <c r="A1" s="24"/>
-      <c r="B1" s="24"/>
-    </row>
-    <row r="2" spans="1:2">
-      <c r="A2" s="24" t="s">
-        <v>150</v>
-      </c>
-      <c r="B2" s="24"/>
-    </row>
-    <row r="3" spans="1:2">
-      <c r="A3" s="24" t="s">
-        <v>151</v>
-      </c>
-      <c r="B3" s="24"/>
-    </row>
-    <row r="4" spans="1:2">
-      <c r="A4" s="24" t="s">
-        <v>152</v>
-      </c>
-      <c r="B4" s="24"/>
-    </row>
-    <row r="5" spans="1:2">
-      <c r="A5" s="24" t="s">
-        <v>153</v>
-      </c>
-      <c r="B5" s="24"/>
-    </row>
-    <row r="6" spans="1:2">
-      <c r="A6" s="24" t="s">
-        <v>154</v>
-      </c>
-      <c r="B6" s="24"/>
-    </row>
-    <row r="7" spans="1:2" ht="54">
-      <c r="A7" s="24" t="s">
-        <v>155</v>
-      </c>
-      <c r="B7" s="23" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2">
-      <c r="A8" s="24" t="s">
-        <v>156</v>
-      </c>
-      <c r="B8" s="24"/>
-    </row>
-    <row r="9" spans="1:2">
-      <c r="A9" s="24" t="s">
-        <v>157</v>
-      </c>
-      <c r="B9" s="24"/>
-    </row>
-    <row r="10" spans="1:2">
-      <c r="A10" s="24" t="s">
-        <v>158</v>
-      </c>
-      <c r="B10" s="24"/>
-    </row>
-    <row r="11" spans="1:2">
-      <c r="A11" s="24" t="s">
-        <v>159</v>
-      </c>
-      <c r="B11" s="24"/>
-    </row>
-    <row r="12" spans="1:2">
-      <c r="A12" s="24" t="s">
-        <v>160</v>
-      </c>
-      <c r="B12" s="24"/>
-    </row>
-    <row r="13" spans="1:2">
-      <c r="A13" s="24" t="s">
-        <v>161</v>
-      </c>
-      <c r="B13" s="24"/>
-    </row>
-    <row r="14" spans="1:2">
-      <c r="A14" s="24" t="s">
-        <v>162</v>
-      </c>
-      <c r="B14" s="24"/>
-    </row>
-    <row r="15" spans="1:2">
-      <c r="A15" s="24" t="s">
-        <v>163</v>
-      </c>
-      <c r="B15" s="24"/>
-    </row>
-    <row r="16" spans="1:2">
-      <c r="A16" s="24" t="s">
-        <v>164</v>
-      </c>
-      <c r="B16" s="24"/>
-    </row>
-    <row r="17" spans="1:2">
-      <c r="A17" s="24" t="s">
-        <v>165</v>
-      </c>
-      <c r="B17" s="24"/>
-    </row>
-    <row r="18" spans="1:2">
-      <c r="A18" s="24" t="s">
-        <v>166</v>
-      </c>
-      <c r="B18" s="24"/>
-    </row>
-    <row r="19" spans="1:2">
-      <c r="A19" s="24" t="s">
-        <v>167</v>
-      </c>
-      <c r="B19" s="24"/>
-    </row>
-    <row r="20" spans="1:2" ht="94.5">
-      <c r="A20" s="24" t="s">
-        <v>168</v>
-      </c>
-      <c r="B20" s="23" t="s">
-        <v>550</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2">
-      <c r="A21" s="24" t="s">
-        <v>169</v>
-      </c>
-      <c r="B21" s="24"/>
+    <row r="1" spans="1:2" ht="58">
+      <c r="A1" s="31" t="s">
+        <v>223</v>
+      </c>
+      <c r="B1" s="32" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" ht="55" customHeight="1">
+      <c r="A2" s="31" t="s">
+        <v>224</v>
+      </c>
+      <c r="B2" s="32" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="55" customHeight="1">
+      <c r="A3" s="31" t="s">
+        <v>225</v>
+      </c>
+      <c r="B3" s="32" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="87">
+      <c r="A4" s="31" t="s">
+        <v>226</v>
+      </c>
+      <c r="B4" s="32" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" ht="55" customHeight="1">
+      <c r="A5" s="31" t="s">
+        <v>227</v>
+      </c>
+      <c r="B5" s="32" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" ht="55" customHeight="1">
+      <c r="A6" s="31" t="s">
+        <v>228</v>
+      </c>
+      <c r="B6" s="32" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" ht="58">
+      <c r="A7" s="31" t="s">
+        <v>229</v>
+      </c>
+      <c r="B7" s="32" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" ht="58">
+      <c r="A8" s="31" t="s">
+        <v>230</v>
+      </c>
+      <c r="B8" s="32" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" ht="55" customHeight="1">
+      <c r="A9" s="31" t="s">
+        <v>231</v>
+      </c>
+      <c r="B9" s="32" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" ht="55" customHeight="1">
+      <c r="A10" s="31" t="s">
+        <v>232</v>
+      </c>
+      <c r="B10" s="32" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" ht="55" customHeight="1">
+      <c r="A11" s="31" t="s">
+        <v>233</v>
+      </c>
+      <c r="B11" s="32" t="s">
+        <v>242</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
@@ -12496,101 +12749,113 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:B11"/>
-  <sheetFormatPr defaultRowHeight="13.5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{05FA0C31-4B39-4CC9-AFFE-ADB97979182D}">
+  <dimension ref="A1:B21"/>
+  <sheetFormatPr defaultRowHeight="13"/>
   <cols>
-    <col min="1" max="1" width="69.625" customWidth="1"/>
-    <col min="2" max="2" width="66.375" customWidth="1"/>
+    <col min="1" max="1" width="150.36328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="103.36328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="60">
-      <c r="A1" s="31" t="s">
-        <v>225</v>
-      </c>
-      <c r="B1" s="32" t="s">
+    <row r="1" spans="1:2">
+      <c r="A1" s="24"/>
+      <c r="B1" s="24"/>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" s="24" t="s">
+        <v>150</v>
+      </c>
+      <c r="B2" s="24"/>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" s="33" t="s">
+        <v>249</v>
+      </c>
+      <c r="B3" s="24"/>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" s="33" t="s">
         <v>245</v>
       </c>
-    </row>
-    <row r="2" spans="1:2" ht="54.95" customHeight="1">
-      <c r="A2" s="31" t="s">
-        <v>226</v>
-      </c>
-      <c r="B2" s="32" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" ht="54.95" customHeight="1">
-      <c r="A3" s="31" t="s">
-        <v>227</v>
-      </c>
-      <c r="B3" s="32" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" ht="90">
-      <c r="A4" s="31" t="s">
-        <v>228</v>
-      </c>
-      <c r="B4" s="32" t="s">
+      <c r="B4" s="24"/>
+    </row>
+    <row r="5" spans="1:2" ht="65">
+      <c r="A5" s="33" t="s">
         <v>246</v>
       </c>
-    </row>
-    <row r="5" spans="1:2" ht="54.95" customHeight="1">
-      <c r="A5" s="31" t="s">
-        <v>229</v>
-      </c>
-      <c r="B5" s="32" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" ht="54.95" customHeight="1">
-      <c r="A6" s="31" t="s">
-        <v>230</v>
-      </c>
-      <c r="B6" s="32" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" ht="60">
-      <c r="A7" s="31" t="s">
-        <v>231</v>
-      </c>
-      <c r="B7" s="32" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" ht="60">
-      <c r="A8" s="31" t="s">
-        <v>232</v>
-      </c>
-      <c r="B8" s="32" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" ht="54.95" customHeight="1">
-      <c r="A9" s="31" t="s">
-        <v>233</v>
-      </c>
-      <c r="B9" s="32" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" ht="54.95" customHeight="1">
-      <c r="A10" s="31" t="s">
-        <v>234</v>
-      </c>
-      <c r="B10" s="32" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" ht="54.95" customHeight="1">
-      <c r="A11" s="31" t="s">
-        <v>235</v>
-      </c>
-      <c r="B11" s="32" t="s">
-        <v>244</v>
-      </c>
+      <c r="B5" s="23" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" s="33" t="s">
+        <v>247</v>
+      </c>
+      <c r="B6" s="24"/>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" s="33" t="s">
+        <v>248</v>
+      </c>
+      <c r="B7" s="23"/>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" s="24"/>
+      <c r="B8" s="24"/>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" s="24"/>
+      <c r="B9" s="24"/>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10" s="24"/>
+      <c r="B10" s="24"/>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" s="24"/>
+      <c r="B11" s="24"/>
+    </row>
+    <row r="12" spans="1:2">
+      <c r="A12" s="24"/>
+      <c r="B12" s="24"/>
+    </row>
+    <row r="13" spans="1:2">
+      <c r="A13" s="24"/>
+      <c r="B13" s="24"/>
+    </row>
+    <row r="14" spans="1:2">
+      <c r="A14" s="24"/>
+      <c r="B14" s="24"/>
+    </row>
+    <row r="15" spans="1:2">
+      <c r="A15" s="24"/>
+      <c r="B15" s="24"/>
+    </row>
+    <row r="16" spans="1:2">
+      <c r="A16" s="24"/>
+      <c r="B16" s="24"/>
+    </row>
+    <row r="17" spans="1:2">
+      <c r="A17" s="24"/>
+      <c r="B17" s="24"/>
+    </row>
+    <row r="18" spans="1:2">
+      <c r="A18" s="24"/>
+      <c r="B18" s="24"/>
+    </row>
+    <row r="19" spans="1:2">
+      <c r="A19" s="24"/>
+      <c r="B19" s="24"/>
+    </row>
+    <row r="20" spans="1:2" ht="65">
+      <c r="A20" s="24"/>
+      <c r="B20" s="23" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2">
+      <c r="A21" s="24"/>
+      <c r="B21" s="24"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
@@ -12599,12 +12864,12 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{05FA0C31-4B39-4CC9-AFFE-ADB97979182D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E3B1E147-F943-43CF-88AE-86DE70DEEA3B}">
   <dimension ref="A1:B21"/>
-  <sheetFormatPr defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultRowHeight="13"/>
   <cols>
-    <col min="1" max="1" width="150.375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="103.375" customWidth="1"/>
+    <col min="1" max="1" width="150.36328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="103.36328125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
@@ -12619,66 +12884,86 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="33" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="B3" s="24"/>
     </row>
-    <row r="4" spans="1:2">
+    <row r="4" spans="1:2" ht="39">
       <c r="A4" s="33" t="s">
-        <v>247</v>
-      </c>
-      <c r="B4" s="24"/>
-    </row>
-    <row r="5" spans="1:2" ht="67.5">
+        <v>252</v>
+      </c>
+      <c r="B4" s="23" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
       <c r="A5" s="33" t="s">
-        <v>248</v>
-      </c>
-      <c r="B5" s="23" t="s">
         <v>253</v>
       </c>
+      <c r="B5" s="23"/>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="33" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="B6" s="24"/>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="33" t="s">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="B7" s="23"/>
     </row>
     <row r="8" spans="1:2">
-      <c r="A8" s="24"/>
-      <c r="B8" s="24"/>
+      <c r="A8" s="35" t="s">
+        <v>256</v>
+      </c>
+      <c r="B8" s="33" t="s">
+        <v>265</v>
+      </c>
     </row>
     <row r="9" spans="1:2">
-      <c r="A9" s="24"/>
+      <c r="A9" s="33" t="s">
+        <v>257</v>
+      </c>
       <c r="B9" s="24"/>
     </row>
-    <row r="10" spans="1:2">
-      <c r="A10" s="24"/>
-      <c r="B10" s="24"/>
+    <row r="10" spans="1:2" ht="39">
+      <c r="A10" s="33" t="s">
+        <v>258</v>
+      </c>
+      <c r="B10" s="23" t="s">
+        <v>266</v>
+      </c>
     </row>
     <row r="11" spans="1:2">
-      <c r="A11" s="24"/>
+      <c r="A11" s="33" t="s">
+        <v>259</v>
+      </c>
       <c r="B11" s="24"/>
     </row>
     <row r="12" spans="1:2">
-      <c r="A12" s="24"/>
+      <c r="A12" s="35" t="s">
+        <v>260</v>
+      </c>
       <c r="B12" s="24"/>
     </row>
     <row r="13" spans="1:2">
-      <c r="A13" s="24"/>
+      <c r="A13" s="33" t="s">
+        <v>261</v>
+      </c>
       <c r="B13" s="24"/>
     </row>
     <row r="14" spans="1:2">
-      <c r="A14" s="24"/>
+      <c r="A14" s="33" t="s">
+        <v>262</v>
+      </c>
       <c r="B14" s="24"/>
     </row>
     <row r="15" spans="1:2">
-      <c r="A15" s="24"/>
+      <c r="A15" s="33" t="s">
+        <v>263</v>
+      </c>
       <c r="B15" s="24"/>
     </row>
     <row r="16" spans="1:2">
@@ -12697,7 +12982,7 @@
       <c r="A19" s="24"/>
       <c r="B19" s="24"/>
     </row>
-    <row r="20" spans="1:2" ht="67.5">
+    <row r="20" spans="1:2" ht="65">
       <c r="A20" s="24"/>
       <c r="B20" s="23" t="s">
         <v>176</v>
@@ -12710,5 +12995,6 @@
   </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>